--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-05 16:27</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-06 09:12</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-05 16:27</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-06 09:12</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-06 09:12</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-06 16:45</t>
         </is>
       </c>
     </row>
@@ -16948,7 +16948,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-06 09:12</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-06 16:45</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-12 09:22</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-12 16:43</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16462,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-12 09:22</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-12 16:43</t>
         </is>
       </c>
     </row>
@@ -17642,7 +17642,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -17652,12 +17652,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>高雄市橋頭區興糖國民小學</t>
+          <t>臺南市善化區善化國民小學</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>xtn1150831</t>
+          <t>SHES20260825</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -17667,11 +17667,11 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>115年幼兒園遊戲場改善工程</t>
+          <t>115年度善化國小附設幼兒園充實及改善教學環境設施設備工程</t>
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>707098</v>
+        <v>851027</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>115/09/16</t>
+          <t>115/09/15</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -17705,26 +17705,26 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>新竹縣竹東鎮公所</t>
+          <t>高雄市橋頭區興糖國民小學</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>115-41</t>
+          <t>xtn1150831</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>竹東鎮仁愛公有停車場入口意象工程</t>
+          <t>115年幼兒園遊戲場改善工程</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>629437</v>
+        <v>707098</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/16</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -17758,26 +17758,26 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>南投縣中寮鄉公所</t>
+          <t>新竹縣竹東鎮公所</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>115-0011</t>
+          <t>115-41</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>G480-14006八仙村仙鹿巷21號前路面工程(1)等2件(114121~1151231)</t>
+          <t>竹東鎮仁愛公有停車場入口意象工程</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>539350</v>
+        <v>629437</v>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
@@ -17786,7 +17786,7 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>115/09/23</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
@@ -17801,7 +17801,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -17811,40 +17811,40 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>南投縣中寮鄉公所</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>11150707</t>
+          <t>115-0011</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>臺南市政府消防局第七救災救護大隊及德興分隊辦公廳舍新建工程</t>
+          <t>G480-14006八仙村仙鹿巷21號前路面工程(1)等2件(114121~1151231)</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>113907327</v>
+        <v>539350</v>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
-          <t>115/09/11</t>
+          <t>115/09/14</t>
         </is>
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/23</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -17854,7 +17854,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -17864,12 +17864,12 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>北投區農會</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>115B003</t>
+          <t>11150707</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -17879,11 +17879,11 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>臺北市直轄市定古蹟「北投穀倉」修復工程</t>
+          <t>臺南市政府消防局第七救災救護大隊及德興分隊辦公廳舍新建工程</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>112768346</v>
+        <v>113907327</v>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -17907,7 +17907,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -17917,26 +17917,26 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>北投區農會</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>1155021602</t>
+          <t>115B003</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>台20線188k+500邊坡災害修復工程</t>
+          <t>臺北市直轄市定古蹟「北投穀倉」修復工程</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>83738194</v>
+        <v>112768346</v>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>115/09/17</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -17960,7 +17960,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -17970,26 +17970,26 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>內政部國家公園署陽明山國家公園管理處</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>115050204-1</t>
+          <t>1155021602</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>歷史建築竹子湖蓬萊米原種田事務所暨種籾倉庫、竹子山莊修復再利用工程</t>
+          <t>台20線188k+500邊坡災害修復工程</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>82316227</v>
+        <v>83738194</v>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
@@ -17998,7 +17998,7 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>115/09/15</t>
+          <t>115/09/17</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
@@ -18013,7 +18013,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -18023,12 +18023,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司台北西區營業處</t>
+          <t>內政部國家公園署陽明山國家公園管理處</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>1171570011</t>
+          <t>115050204-1</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -18038,11 +18038,11 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>台北西區營業處115年配電維護工程(甲工區)</t>
+          <t>歷史建築竹子湖蓬萊米原種田事務所暨種籾倉庫、竹子山莊修復再利用工程</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>67872000</v>
+        <v>82316227</v>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
@@ -18051,7 +18051,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>115/09/23</t>
+          <t>115/09/15</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -18066,7 +18066,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -18076,12 +18076,12 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>宜蘭縣員山鄉公所</t>
+          <t>台灣電力股份有限公司台北西區營業處</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>1171570011</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -18091,11 +18091,11 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>26-115年員山鄉道路基礎設施改善及效能提升專案工程</t>
+          <t>台北西區營業處115年配電維護工程(甲工區)</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>60412465</v>
+        <v>67872000</v>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
@@ -18104,7 +18104,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/23</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -18119,7 +18119,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -18129,12 +18129,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>宜蘭縣員山鄉公所</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>115EM631167619008200</t>
+          <t>11526</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -18144,11 +18144,11 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>臺南基地1-7號棚廠整修工程</t>
+          <t>26-115年員山鄉道路基礎設施改善及效能提升專案工程</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>48790000</v>
+        <v>60412465</v>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
@@ -18157,7 +18157,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -18172,7 +18172,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -18182,12 +18182,12 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局東區養護工程分局</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>1154B098</t>
+          <t>115EM631167619008200</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -18197,11 +18197,11 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>獨立山工務段四季監工站116年度預約經常性災害搶修工程</t>
+          <t>臺南基地1-7號棚廠整修工程</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>47199829</v>
+        <v>48790000</v>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -18235,12 +18235,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>交通部公路局東區養護工程分局</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>115EM631167621009200</t>
+          <t>1154B098</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -18250,11 +18250,11 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>基地廢料庫、油分棚廠及航材庫儲設施整修工程</t>
+          <t>獨立山工務段四季監工站116年度預約經常性災害搶修工程</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>46615778</v>
+        <v>47199829</v>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>中央/海軍</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -18288,26 +18288,26 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>國防部海軍司令部</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>116PK516053556010200</t>
+          <t>115EM631167621009200</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>第 06 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>輕兵器庫整建工程</t>
+          <t>基地廢料庫、油分棚廠及航材庫儲設施整修工程</t>
         </is>
       </c>
       <c r="H36" s="11" t="n">
-        <v>46300000</v>
+        <v>46615778</v>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>115/09/16</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -18331,7 +18331,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>中央/海軍</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -18341,26 +18341,26 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>國防部海軍司令部</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>115EF00302260000180</t>
+          <t>116PK516053556010200</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 06 次</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>北竿午沙廢棄加油站土壤污染整治工程</t>
+          <t>輕兵器庫整建工程</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>45878811</v>
+        <v>46300000</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -18394,26 +18394,26 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>115-BN-001</t>
+          <t>115EF00302260000180</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>竹崎車庫新建工程</t>
+          <t>北竿午沙廢棄加油站土壤污染整治工程</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>43294832</v>
+        <v>45878811</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>115/09/17</t>
+          <t>115/09/16</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
@@ -18437,7 +18437,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -18447,26 +18447,26 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府工務局新建工程處</t>
+          <t>農業部林業及自然保育署阿里山林業鐵路及文化資產管理處</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>114141A</t>
+          <t>115-BN-001</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>第 05 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>漢聲廣播電臺高雄轉播站鐵塔遷移工程</t>
+          <t>竹崎車庫新建工程</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>33300504</v>
+        <v>43294832</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>115/09/15</t>
+          <t>115/09/17</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -18490,7 +18490,7 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
@@ -18500,26 +18500,26 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局北區養護工程分局</t>
+          <t>高雄市政府工務局新建工程處</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>1161A1D00</t>
+          <t>114141A</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 05 次</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>116年新竹段鳳鼻尾隧道委託管理及機電維護、轄內預約經常性路燈維護工程</t>
+          <t>漢聲廣播電臺高雄轉播站鐵塔遷移工程</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>28573832</v>
+        <v>33300504</v>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
@@ -18528,7 +18528,7 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>115/09/16</t>
+          <t>115/09/15</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
@@ -18543,7 +18543,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -18553,26 +18553,26 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>交通部公路局北區養護工程分局</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>YL115J224</t>
+          <t>1161A1D00</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>115年度下溪農地重劃區安慶圳排水(4+495~4+975)(第一階段)緊急農水路改善工程</t>
+          <t>116年新竹段鳳鼻尾隧道委託管理及機電維護、轄內預約經常性路燈維護工程</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>25022000</v>
+        <v>28573832</v>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
@@ -18581,7 +18581,7 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/16</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -18596,22 +18596,22 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>KCLP16001</t>
+          <t>YL115J224</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -18621,11 +18621,11 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>高雄榮總台南分院116年度醫療設備集中採購共10項</t>
+          <t>115年度下溪農地重劃區安慶圳排水(4+495~4+975)(第一階段)緊急農水路改善工程</t>
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>24725000</v>
+        <v>25022000</v>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>115/10/15</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
@@ -18649,22 +18649,22 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺北分署</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>115-LL-22-1-002</t>
+          <t>KCLP16001</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -18674,11 +18674,11 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>新北市石碇區LL001大崙山大規模崩塌特定水土保持區野溪整治及改善工程</t>
+          <t>高雄榮總台南分院116年度醫療設備集中採購共10項</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>23542000</v>
+        <v>24725000</v>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
@@ -18687,7 +18687,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/10/15</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -18702,22 +18702,22 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>農業部農村發展及水土保持署臺北分署</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>1155024336</t>
+          <t>115-LL-22-1-002</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -18727,11 +18727,11 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>116年度台88線快速公路伸縮縫與橋面排水設施清疏及路面維護工作</t>
+          <t>新北市石碇區LL001大崙山大規模崩塌特定水土保持區野溪整治及改善工程</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>19439879</v>
+        <v>23542000</v>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
@@ -18755,36 +18755,36 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>新北市林口區公所</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>115-020</t>
+          <t>1155024336</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>新北市林口區大崙公園環境改善工程</t>
+          <t>116年度台88線快速公路伸縮縫與橋面排水設施清疏及路面維護工作</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>18856164</v>
+        <v>19439879</v>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
@@ -18793,7 +18793,7 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>115/09/18</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -18818,26 +18818,26 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>臺北市立聯合醫院</t>
+          <t>新北市林口區公所</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>1151JA32002</t>
+          <t>115-020</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>115年度婦女兒童全齡照護及早療服務品質提升整修工程</t>
+          <t>新北市林口區大崙公園環境改善工程</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>15760446</v>
+        <v>18856164</v>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/18</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
@@ -18861,7 +18861,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -18871,26 +18871,26 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>台灣糖業股份有限公司畜殖事業部</t>
+          <t>臺北市立聯合醫院</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>06E1150601</t>
+          <t>1151JA32002</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>畜殖事業部廠區丹娜絲颱風災害復建工程</t>
+          <t>115年度婦女兒童全齡照護及早療服務品質提升整修工程</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>15405600</v>
+        <v>15760446</v>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>115/09/24</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -18924,26 +18924,26 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>台灣糖業股份有限公司畜殖事業部</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>1155025538</t>
+          <t>06E1150601</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>115年度高雄段轄區省道行人照明增設工程</t>
+          <t>畜殖事業部廠區丹娜絲颱風災害復建工程</t>
         </is>
       </c>
       <c r="H48" s="11" t="n">
-        <v>15146000</v>
+        <v>15405600</v>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
@@ -18952,7 +18952,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/24</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
@@ -18977,26 +18977,26 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>國立高雄科技大學</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>1131112002</t>
+          <t>1155025538</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>第 13 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>建工校區雙科館7樓及屋頂外牆整修工程</t>
+          <t>115年度高雄段轄區省道行人照明增設工程</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>12120800</v>
+        <v>15146000</v>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
@@ -19005,7 +19005,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>115/09/17</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -19020,36 +19020,36 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>國立高雄科技大學</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>1155024679</t>
+          <t>1131112002</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 13 次</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>116年度台88線快速道路高架PVC排水管汰換改善及疏濬工作</t>
+          <t>建工校區雙科館7樓及屋頂外牆整修工程</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>11960274</v>
+        <v>12120800</v>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/17</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr">
@@ -19073,36 +19073,36 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>中央/中油</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>LDA1531032</t>
+          <t>1155024679</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>竹服竹科工業東十路區域6吋中壓A氣源管線遷移工程</t>
+          <t>116年度台88線快速道路高架PVC排水管汰換改善及疏濬工作</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>9993941</v>
+        <v>11960274</v>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
@@ -19111,7 +19111,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>115/09/17</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>中央/中油</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -19136,26 +19136,26 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>台灣中油股份有限公司</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>1155026191</t>
+          <t>LDA1531032</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>高雄工務段旗山監工站轄區116年度省道預約經常性瀝青路面零星修補工程</t>
+          <t>竹服竹科工業東十路區域6吋中壓A氣源管線遷移工程</t>
         </is>
       </c>
       <c r="H52" s="11" t="n">
-        <v>9455569</v>
+        <v>9993941</v>
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/17</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
@@ -19179,7 +19179,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -19189,12 +19189,12 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>11150901</t>
+          <t>1155026191</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -19204,11 +19204,11 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>116年臺南市轄區路燈維修改善工程(永華行政工區)(開口契約)</t>
+          <t>高雄工務段旗山監工站轄區116年度省道預約經常性瀝青路面零星修補工程</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>8908174</v>
+        <v>9455569</v>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
@@ -19217,7 +19217,7 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -19232,22 +19232,22 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>1155024131</t>
+          <t>11150901</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -19257,11 +19257,11 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>鳳屏工務段轄區116年度省道（未含台88線）路面及路肩清掃維護工作</t>
+          <t>116年臺南市轄區路燈維修改善工程(永華行政工區)(開口契約)</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>8188899</v>
+        <v>8908174</v>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
@@ -19285,7 +19285,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -19295,12 +19295,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>高雄市立凱旋醫院</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>KSPH1153053</t>
+          <t>1155024131</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -19310,11 +19310,11 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>高雄市數位心理守門人計畫關懷AI助手系統</t>
+          <t>鳳屏工務段轄區116年度省道（未含台88線）路面及路肩清掃維護工作</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>7927500</v>
+        <v>8188899</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
@@ -19323,12 +19323,12 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -19338,22 +19338,22 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>高雄市立凱旋醫院</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>143-F1150910-1</t>
+          <t>KSPH1153053</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -19363,11 +19363,11 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>115年度屏東縣污水下水道系統用戶接管開口契約工程</t>
+          <t>高雄市數位心理守門人計畫關懷AI助手系統</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>7300000</v>
+        <v>7927500</v>
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
       </c>
       <c r="K56" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -19391,7 +19391,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -19401,12 +19401,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>新竹縣竹北市興隆國民小學</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>hlps1150827</t>
+          <t>143-F1150910-1</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -19416,11 +19416,11 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>新竹縣竹北市興隆國小115年足球場地與周邊設施整修工程採購</t>
+          <t>115年度屏東縣污水下水道系統用戶接管開口契約工程</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>7200362</v>
+        <v>7300000</v>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -19454,12 +19454,12 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>高雄市立翠屏國民中小學</t>
+          <t>新竹縣竹北市興隆國民小學</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>1150929</t>
+          <t>hlps1150827</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -19469,11 +19469,11 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>高雄市立翠屏國民中小學國小部C棟老舊廁所整修工程</t>
+          <t>新竹縣竹北市興隆國小115年足球場地與周邊設施整修工程採購</t>
         </is>
       </c>
       <c r="H58" s="11" t="n">
-        <v>7164069</v>
+        <v>7200362</v>
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>115/09/24</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
@@ -19507,26 +19507,26 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>新竹瓦斯股份有限公司</t>
+          <t>高雄市立翠屏國民中小學</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>GE115-06-04</t>
+          <t>1150929</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>湖口鄉鳳山村榮光路輸配氣管線新設工程</t>
+          <t>高雄市立翠屏國民中小學國小部C棟老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>6466784</v>
+        <v>7164069</v>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
@@ -19535,7 +19535,7 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>115/09/16</t>
+          <t>115/09/24</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -19550,36 +19550,36 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>新竹瓦斯股份有限公司</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>C1150910-2</t>
+          <t>GE115-06-04</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>屏東縣行人安全環境調查暨管理系統建置計畫-人本環境營造專業服務</t>
+          <t>湖口鄉鳳山村榮光路輸配氣管線新設工程</t>
         </is>
       </c>
       <c r="H60" s="11" t="n">
-        <v>6000000</v>
+        <v>6466784</v>
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
@@ -19588,12 +19588,12 @@
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>115/09/23</t>
+          <t>115/09/16</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -19603,22 +19603,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署花蓮分署</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>11507MT005</t>
+          <t>C1150910-2</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -19628,7 +19628,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>115-116年「馬太鞍堰塞湖周邊林道維護及緊急搶修工程」</t>
+          <t>屏東縣行人安全環境調查暨管理系統建置計畫-人本環境營造專業服務</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
@@ -19641,12 +19641,12 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/23</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -19656,7 +19656,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -19666,12 +19666,12 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>雲林縣政府</t>
+          <t>農業部林業及自然保育署花蓮分署</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>1151C10045</t>
+          <t>11507MT005</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -19681,11 +19681,11 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>115年度新生農地重劃區部子段31等地號農路改善工程</t>
+          <t>115-116年「馬太鞍堰塞湖周邊林道維護及緊急搶修工程」</t>
         </is>
       </c>
       <c r="H62" s="11" t="n">
-        <v>5631000</v>
+        <v>6000000</v>
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
@@ -19694,7 +19694,7 @@
       </c>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
@@ -19709,22 +19709,22 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>財政部國有財產署南區分署</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1151300484</t>
+          <t>1151C10045</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -19734,11 +19734,11 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>115-116年度委外辦理屏東縣國產業務訴訟案件作業</t>
+          <t>115年度新生農地重劃區部子段31等地號農路改善工程</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>5230000</v>
+        <v>5631000</v>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
@@ -19747,12 +19747,12 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -19762,36 +19762,36 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>財政部國有財產署南區分署</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>Danas-H-01-06-7-36</t>
+          <t>1151300484</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>Danas-H-01-06-7-南化區中坑里中坑段225地號及北平里過嶺農路(南化276右56)農路災害復建工程</t>
+          <t>115-116年度委外辦理屏東縣國產業務訴訟案件作業</t>
         </is>
       </c>
       <c r="H64" s="11" t="n">
-        <v>5109353</v>
+        <v>5230000</v>
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
@@ -19800,12 +19800,12 @@
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>115/09/15</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -19815,7 +19815,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -19825,26 +19825,26 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1155025857</t>
+          <t>Danas-H-01-06-7-36</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>鳳屏工務段轄區116年度省道預約經常性公路零星修復及災害搶修工程</t>
+          <t>Danas-H-01-06-7-南化區中坑里中坑段225地號及北平里過嶺農路(南化276右56)農路災害復建工程</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>4999805</v>
+        <v>5109353</v>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/15</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -19868,36 +19868,36 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>W7-115-0701-80-1</t>
+          <t>1155025857</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>115年度高雄所南區管線設備維修(開口契約)</t>
+          <t>鳳屏工務段轄區116年度省道預約經常性公路零星修復及災害搶修工程</t>
         </is>
       </c>
       <c r="H66" s="11" t="n">
-        <v>4838971</v>
+        <v>4999805</v>
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
@@ -19906,7 +19906,7 @@
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>115/09/17</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
@@ -19921,36 +19921,36 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>彰化縣彰化市公所</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>A115-062</t>
+          <t>W7-115-0701-80-1</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>彰化市福山段1023地號坡地改善工程</t>
+          <t>115年度高雄所南區管線設備維修(開口契約)</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>4348000</v>
+        <v>4838971</v>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/17</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -19974,36 +19974,36 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>彰化縣彰化市公所</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>C1150910-1</t>
+          <t>A115-062</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>115年東港鹽埔漁港金財滿3號漁船清除工作</t>
+          <t>彰化市福山段1023地號坡地改善工程</t>
         </is>
       </c>
       <c r="H68" s="11" t="n">
-        <v>4320800</v>
+        <v>4348000</v>
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>115/09/23</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr">
@@ -20027,36 +20027,36 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺北分署</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>115-WS-04-1-001</t>
+          <t>C1150910-1</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>玉峰宇老部落及天主堂坑溝整治工程</t>
+          <t>115年東港鹽埔漁港金財滿3號漁船清除工作</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>4166000</v>
+        <v>4320800</v>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
@@ -20065,7 +20065,7 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/23</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -20090,26 +20090,26 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府工務局道路養護工程處</t>
+          <t>農業部農村發展及水土保持署臺北分署</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>11503CA017</t>
+          <t>115-WS-04-1-001</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>115年度高雄市區道路附屬設施修繕及緊急搶修工程第5標(開口契約)</t>
+          <t>玉峰宇老部落及天主堂坑溝整治工程</t>
         </is>
       </c>
       <c r="H70" s="11" t="n">
-        <v>4000000</v>
+        <v>4166000</v>
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
@@ -20118,7 +20118,7 @@
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>115/09/16</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
@@ -20133,7 +20133,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -20143,26 +20143,26 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>屏東縣泰武鄉泰武國民小學</t>
+          <t>高雄市政府工務局道路養護工程處</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>1150901</t>
+          <t>11503CA017</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>屏東縣泰武國民小學幼兒園115年度充實及改善教學環境設施設備計畫工程採購案</t>
+          <t>115年度高雄市區道路附屬設施修繕及緊急搶修工程第5標(開口契約)</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>3985524</v>
+        <v>4000000</v>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
@@ -20171,7 +20171,7 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/16</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -20186,7 +20186,7 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -20196,26 +20196,26 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>高雄市田寮區公所</t>
+          <t>屏東縣泰武鄉泰武國民小學</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>1151026</t>
+          <t>1150901</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>田寮區大同里平安路46號前及七星里水蛙潭段323-73等地號農路改善工程</t>
+          <t>屏東縣泰武國民小學幼兒園115年度充實及改善教學環境設施設備計畫工程採購案</t>
         </is>
       </c>
       <c r="H72" s="11" t="n">
-        <v>3888000</v>
+        <v>3985524</v>
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
@@ -20224,7 +20224,7 @@
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>115/09/17</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
@@ -20249,12 +20249,12 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司高雄港務分公司</t>
+          <t>高雄市田寮區公所</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>A3E260811</t>
+          <t>1151026</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -20264,11 +20264,11 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>高雄港第四貨櫃中心備援電源申請11.4kV作業工程</t>
+          <t>田寮區大同里平安路46號前及七星里水蛙潭段323-73等地號農路改善工程</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>3819820</v>
+        <v>3888000</v>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>115/09/16</t>
+          <t>115/09/17</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -20292,7 +20292,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -20302,12 +20302,12 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>臺東縣池上鄉公所</t>
+          <t>臺灣港務股份有限公司高雄港務分公司</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>115A004-2</t>
+          <t>A3E260811</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -20317,11 +20317,11 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Danas-A-06-01-07-福文部落12及19鄰排水改善工程</t>
+          <t>高雄港第四貨櫃中心備援電源申請11.4kV作業工程</t>
         </is>
       </c>
       <c r="H74" s="11" t="n">
-        <v>3759286</v>
+        <v>3819820</v>
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
@@ -20355,26 +20355,26 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>臺東縣金峰鄉公所</t>
+          <t>臺東縣池上鄉公所</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>114-C12-3</t>
+          <t>115A004-2</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>113年10月康芮颱風-H3-其他農路工程-金峰鄉新興村目日本農路ABC工區災害復建工程</t>
+          <t>Danas-A-06-01-07-福文部落12及19鄰排水改善工程</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>3581367</v>
+        <v>3759286</v>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
@@ -20383,7 +20383,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/16</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
@@ -20408,12 +20408,12 @@
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣造橋鄉公所</t>
+          <t>臺東縣金峰鄉公所</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>1150908001</t>
+          <t>114-C12-3</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -20423,11 +20423,11 @@
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>115年度造橋鄉水利及水保設施改善工程第六期(朝陽村、談文村)</t>
+          <t>113年10月康芮颱風-H3-其他農路工程-金峰鄉新興村目日本農路ABC工區災害復建工程</t>
         </is>
       </c>
       <c r="H76" s="11" t="n">
-        <v>3441000</v>
+        <v>3581367</v>
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
@@ -20436,7 +20436,7 @@
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
@@ -20461,26 +20461,26 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>國營臺灣鐵路股份有限公司</t>
+          <t>苗栗縣造橋鄉公所</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>L0515C3017M</t>
+          <t>1150908001</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>代辦苗栗縣政府「苗14線拓寬工程(造橋交流道聯絡道)-老莊路平交道拓寬工程(周邊相關線路號誌部分)」</t>
+          <t>115年度造橋鄉水利及水保設施改善工程第六期(朝陽村、談文村)</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>3398027</v>
+        <v>3441000</v>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -20504,7 +20504,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -20514,26 +20514,26 @@
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>雲林縣莿桐鄉公所</t>
+          <t>國營臺灣鐵路股份有限公司</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>115A056</t>
+          <t>L0515C3017M</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>莿桐鄉饒平社區活動中心整修工程</t>
+          <t>代辦苗栗縣政府「苗14線拓寬工程(造橋交流道聯絡道)-老莊路平交道拓寬工程(周邊相關線路號誌部分)」</t>
         </is>
       </c>
       <c r="H78" s="11" t="n">
-        <v>3378000</v>
+        <v>3398027</v>
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
@@ -20542,7 +20542,7 @@
       </c>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t>115/09/23</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
@@ -20557,7 +20557,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -20567,12 +20567,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>國營臺灣鐵路股份有限公司</t>
+          <t>雲林縣莿桐鄉公所</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>L0515S1028W</t>
+          <t>115A056</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -20582,11 +20582,11 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>新市站報廢倉庫及房屋拆除工程</t>
+          <t>莿桐鄉饒平社區活動中心整修工程</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>3024074</v>
+        <v>3378000</v>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
@@ -20595,7 +20595,7 @@
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/23</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
@@ -20610,7 +20610,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -20620,12 +20620,12 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公所</t>
+          <t>國營臺灣鐵路股份有限公司</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>115055</t>
+          <t>L0515S1028W</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -20635,11 +20635,11 @@
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>長安里光復路378-15號旁產業道路拓寬工程</t>
+          <t>新市站報廢倉庫及房屋拆除工程</t>
         </is>
       </c>
       <c r="H80" s="11" t="n">
-        <v>3000000</v>
+        <v>3024074</v>
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
@@ -20663,7 +20663,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -20673,26 +20673,26 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>屏東縣屏東市公所</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>Danas-H-01-06-7-34</t>
+          <t>115055</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Danas-H-01-06-7-楠西區照興里格坑、龜丹里嚴仔頂及仿仔湖農路災害復建工程</t>
+          <t>長安里光復路378-15號旁產業道路拓寬工程</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>2601850</v>
+        <v>3000000</v>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>115/09/15</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -20726,12 +20726,12 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>臺北市立龍山國民中學</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>115C03</t>
+          <t>Danas-H-01-06-7-34</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -20741,11 +20741,11 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>115年校園無障礙環境改善工程</t>
+          <t>Danas-H-01-06-7-楠西區照興里格坑、龜丹里嚴仔頂及仿仔湖農路災害復建工程</t>
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>2437822</v>
+        <v>2601850</v>
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
@@ -20769,7 +20769,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -20779,26 +20779,26 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>彰化縣二水鄉公所</t>
+          <t>臺北市立龍山國民中學</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>115-11264</t>
+          <t>115C03</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>二水鄉過圳路旁等道路排水改善工程</t>
+          <t>115年校園無障礙環境改善工程</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>2426000</v>
+        <v>2437822</v>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
@@ -20807,7 +20807,7 @@
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>115/09/24</t>
+          <t>115/09/15</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -20822,7 +20822,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -20832,26 +20832,26 @@
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>新竹瓦斯股份有限公司</t>
+          <t>彰化縣二水鄉公所</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>GC115-02-09</t>
+          <t>115-11264</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>竹北市環北路五段(鼎文匯)大樓表外管工程</t>
+          <t>二水鄉過圳路旁等道路排水改善工程</t>
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>2249330</v>
+        <v>2426000</v>
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
@@ -20860,7 +20860,7 @@
       </c>
       <c r="J84" s="12" t="inlineStr">
         <is>
-          <t>115/09/16</t>
+          <t>115/09/24</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
@@ -20875,7 +20875,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -20885,12 +20885,12 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>雲林縣崙背鄉崙背國民小學</t>
+          <t>新竹瓦斯股份有限公司</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>lpes1150804</t>
+          <t>GC115-02-09</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -20900,11 +20900,11 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>115年度雲林縣崙背國民小學球場整修工程</t>
+          <t>竹北市環北路五段(鼎文匯)大樓表外管工程</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>2144917</v>
+        <v>2249330</v>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
@@ -20913,7 +20913,7 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>115/09/18</t>
+          <t>115/09/16</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -20928,7 +20928,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -20938,26 +20938,26 @@
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>國防部軍備局生產製造中心</t>
+          <t>雲林縣崙背鄉崙背國民小學</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>115AO202015714009200</t>
+          <t>lpes1150804</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>光華營區餐廳屋頂防水工程</t>
+          <t>115年度雲林縣崙背國民小學球場整修工程</t>
         </is>
       </c>
       <c r="H86" s="11" t="n">
-        <v>2144320</v>
+        <v>2144917</v>
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/18</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr">
@@ -20991,26 +20991,26 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>國防部軍備局生產製造中心</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>115128c</t>
+          <t>115AO202015714009200</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>頭份市湳湖段368地號坑溝災修復建工程</t>
+          <t>光華營區餐廳屋頂防水工程</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>2117000</v>
+        <v>2144320</v>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>115/09/16</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -21034,22 +21034,22 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司高雄郵局</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>115-044</t>
+          <t>115128c</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -21059,11 +21059,11 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>高雄-枋寮線承攬郵件運輸</t>
+          <t>頭份市湳湖段368地號坑溝災修復建工程</t>
         </is>
       </c>
       <c r="H88" s="11" t="n">
-        <v>2057900</v>
+        <v>2117000</v>
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
@@ -21087,36 +21087,36 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>中華郵政股份有限公司高雄郵局</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>1150501005A</t>
+          <t>115-044</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>115年度南投縣轄內污水下水道系統管線修復工程(開口契約)</t>
+          <t>高雄-枋寮線承攬郵件運輸</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>1975250</v>
+        <v>2057900</v>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -21150,26 +21150,26 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮新興國民小學</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>SSES11511</t>
+          <t>1150501005A</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>彰化縣新興國小115年度書福悅讀校園閱讀推展實施計畫改善學校及圖書館(室)空間環境計畫工程案</t>
+          <t>115年度南投縣轄內污水下水道系統管線修復工程(開口契約)</t>
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>1920626</v>
+        <v>1975250</v>
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
       </c>
       <c r="J90" s="12" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/16</t>
         </is>
       </c>
       <c r="K90" s="9" t="inlineStr">
@@ -21193,7 +21193,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -21203,26 +21203,26 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣頭城鎮公所</t>
+          <t>彰化縣鹿港鎮新興國民小學</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>TC115010</t>
+          <t>SSES11511</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>柴油客車展示區建置工程</t>
+          <t>彰化縣新興國小115年度書福悅讀校園閱讀推展實施計畫改善學校及圖書館(室)空間環境計畫工程案</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>1866885</v>
+        <v>1920626</v>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
@@ -21231,7 +21231,7 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>115/09/16</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-12 16:43</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-13 09:17</t>
         </is>
       </c>
     </row>
@@ -16462,7 +16462,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-12 16:43</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-13 09:17</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-19 09:23</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-19 16:53</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-19 09:23</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-19 16:53</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-19 16:53</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-20 09:23</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-19 16:53</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-20 09:23</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-20 09:23</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-20 17:22</t>
         </is>
       </c>
     </row>
@@ -16354,7 +16354,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-20 09:23</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-20 17:22</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'🏛️ 設計監造標'!$A$2:$K$302</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🏗️ 工程施工標'!$A$2:$K$365</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🏗️ 工程施工標'!$A$2:$K$364</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-24 17:25</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-25 09:43</t>
         </is>
       </c>
     </row>
@@ -16821,7 +16821,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K365"/>
+  <dimension ref="A1:K364"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16840,7 +16840,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-24 17:25</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-25 09:43</t>
         </is>
       </c>
     </row>
@@ -34662,22 +34662,22 @@
       </c>
       <c r="B338" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C338" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D338" s="9" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E338" s="8" t="inlineStr">
         <is>
-          <t>1140508D003A</t>
+          <t>1155026249</t>
         </is>
       </c>
       <c r="F338" s="8" t="inlineStr">
@@ -34687,11 +34687,11 @@
       </c>
       <c r="G338" s="10" t="inlineStr">
         <is>
-          <t>Danas-H-01-07-4-中寮鄉福盛村二尖農路災修復建工程等4件</t>
+          <t>南分局轄管優先關注及C+邊坡委外定期檢測作業</t>
         </is>
       </c>
       <c r="H338" s="11" t="n">
-        <v>29633079</v>
+        <v>15818303</v>
       </c>
       <c r="I338" s="12" t="inlineStr">
         <is>
@@ -34700,12 +34700,12 @@
       </c>
       <c r="J338" s="12" t="inlineStr">
         <is>
-          <t>115/09/24</t>
+          <t>115/10/13</t>
         </is>
       </c>
       <c r="K338" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -34715,7 +34715,7 @@
       </c>
       <c r="B339" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C339" s="3" t="inlineStr">
@@ -34730,7 +34730,7 @@
       </c>
       <c r="E339" s="3" t="inlineStr">
         <is>
-          <t>1155026249</t>
+          <t>1555024554</t>
         </is>
       </c>
       <c r="F339" s="3" t="inlineStr">
@@ -34740,11 +34740,11 @@
       </c>
       <c r="G339" s="5" t="inlineStr">
         <is>
-          <t>南分局轄管優先關注及C+邊坡委外定期檢測作業</t>
+          <t>潮州工務段東港監工站116年度台1線潮州~水底寮及台17線東港~水底寮綠美化維護工作</t>
         </is>
       </c>
       <c r="H339" s="6" t="n">
-        <v>15818303</v>
+        <v>14155203</v>
       </c>
       <c r="I339" s="7" t="inlineStr">
         <is>
@@ -34753,12 +34753,12 @@
       </c>
       <c r="J339" s="7" t="inlineStr">
         <is>
-          <t>115/10/13</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K339" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -34783,7 +34783,7 @@
       </c>
       <c r="E340" s="8" t="inlineStr">
         <is>
-          <t>1555024554</t>
+          <t>1155024515</t>
         </is>
       </c>
       <c r="F340" s="8" t="inlineStr">
@@ -34793,11 +34793,11 @@
       </c>
       <c r="G340" s="10" t="inlineStr">
         <is>
-          <t>潮州工務段東港監工站116年度台1線潮州~水底寮及台17線東港~水底寮綠美化維護工作</t>
+          <t>潮州工務段東港監工站116年度台1線麟洛~潮州綠美化維護工作</t>
         </is>
       </c>
       <c r="H340" s="11" t="n">
-        <v>14155203</v>
+        <v>11970984</v>
       </c>
       <c r="I340" s="12" t="inlineStr">
         <is>
@@ -34826,17 +34826,17 @@
       </c>
       <c r="C341" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D341" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E341" s="3" t="inlineStr">
         <is>
-          <t>1155024515</t>
+          <t>115-073-0910P3</t>
         </is>
       </c>
       <c r="F341" s="3" t="inlineStr">
@@ -34846,11 +34846,11 @@
       </c>
       <c r="G341" s="5" t="inlineStr">
         <is>
-          <t>潮州工務段東港監工站116年度台1線麟洛~潮州綠美化維護工作</t>
+          <t>(115)縣道185甲線5K+730-15K+630擇要道路改善工程</t>
         </is>
       </c>
       <c r="H341" s="6" t="n">
-        <v>11970984</v>
+        <v>11870000</v>
       </c>
       <c r="I341" s="7" t="inlineStr">
         <is>
@@ -34859,7 +34859,7 @@
       </c>
       <c r="J341" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K341" s="4" t="inlineStr">
@@ -34874,22 +34874,22 @@
       </c>
       <c r="B342" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C342" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D342" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E342" s="8" t="inlineStr">
         <is>
-          <t>115-073-0910P3</t>
+          <t>DC11507010012</t>
         </is>
       </c>
       <c r="F342" s="8" t="inlineStr">
@@ -34899,11 +34899,11 @@
       </c>
       <c r="G342" s="10" t="inlineStr">
         <is>
-          <t>(115)縣道185甲線5K+730-15K+630擇要道路改善工程</t>
+          <t>115年高雄所及鳳山所供水監測設備維護開口契約</t>
         </is>
       </c>
       <c r="H342" s="11" t="n">
-        <v>11870000</v>
+        <v>9923286</v>
       </c>
       <c r="I342" s="12" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
       </c>
       <c r="J342" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K342" s="9" t="inlineStr">
@@ -34927,22 +34927,22 @@
       </c>
       <c r="B343" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C343" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D343" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E343" s="3" t="inlineStr">
         <is>
-          <t>DC11507010012</t>
+          <t>115-073-0910P2</t>
         </is>
       </c>
       <c r="F343" s="3" t="inlineStr">
@@ -34952,11 +34952,11 @@
       </c>
       <c r="G343" s="5" t="inlineStr">
         <is>
-          <t>115年高雄所及鳳山所供水監測設備維護開口契約</t>
+          <t>(115)屏24線1K+020-5K+580擇要道路改善工程</t>
         </is>
       </c>
       <c r="H343" s="6" t="n">
-        <v>9923286</v>
+        <v>8653000</v>
       </c>
       <c r="I343" s="7" t="inlineStr">
         <is>
@@ -34965,7 +34965,7 @@
       </c>
       <c r="J343" s="7" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K343" s="4" t="inlineStr">
@@ -34995,7 +34995,7 @@
       </c>
       <c r="E344" s="8" t="inlineStr">
         <is>
-          <t>115-073-0910P2</t>
+          <t>115-073-0910P1</t>
         </is>
       </c>
       <c r="F344" s="8" t="inlineStr">
@@ -35005,11 +35005,11 @@
       </c>
       <c r="G344" s="10" t="inlineStr">
         <is>
-          <t>(115)屏24線1K+020-5K+580擇要道路改善工程</t>
+          <t>(115)縣道189線0K+570-6K+880擇要道路改善工程</t>
         </is>
       </c>
       <c r="H344" s="11" t="n">
-        <v>8653000</v>
+        <v>6299000</v>
       </c>
       <c r="I344" s="12" t="inlineStr">
         <is>
@@ -35033,7 +35033,7 @@
       </c>
       <c r="B345" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C345" s="3" t="inlineStr">
@@ -35043,12 +35043,12 @@
       </c>
       <c r="D345" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E345" s="3" t="inlineStr">
         <is>
-          <t>115-073-0910P1</t>
+          <t>1155026074</t>
         </is>
       </c>
       <c r="F345" s="3" t="inlineStr">
@@ -35058,11 +35058,11 @@
       </c>
       <c r="G345" s="5" t="inlineStr">
         <is>
-          <t>(115)縣道189線0K+570-6K+880擇要道路改善工程</t>
+          <t>楓港段116年度提升人行及自行車路線標線改善工程</t>
         </is>
       </c>
       <c r="H345" s="6" t="n">
-        <v>6299000</v>
+        <v>5539462</v>
       </c>
       <c r="I345" s="7" t="inlineStr">
         <is>
@@ -35071,7 +35071,7 @@
       </c>
       <c r="J345" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K345" s="4" t="inlineStr">
@@ -35086,7 +35086,7 @@
       </c>
       <c r="B346" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C346" s="8" t="inlineStr">
@@ -35096,12 +35096,12 @@
       </c>
       <c r="D346" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E346" s="8" t="inlineStr">
         <is>
-          <t>1155026074</t>
+          <t>115-073-0910P4</t>
         </is>
       </c>
       <c r="F346" s="8" t="inlineStr">
@@ -35111,11 +35111,11 @@
       </c>
       <c r="G346" s="10" t="inlineStr">
         <is>
-          <t>楓港段116年度提升人行及自行車路線標線改善工程</t>
+          <t>(114年11月鳳凰颱風)縣200甲線港口橋P1橋墩保護工程</t>
         </is>
       </c>
       <c r="H346" s="11" t="n">
-        <v>5539462</v>
+        <v>4640000</v>
       </c>
       <c r="I346" s="12" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
       </c>
       <c r="J346" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K346" s="9" t="inlineStr">
@@ -35144,17 +35144,17 @@
       </c>
       <c r="C347" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D347" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>屏東縣屏東市民和國民小學</t>
         </is>
       </c>
       <c r="E347" s="3" t="inlineStr">
         <is>
-          <t>115-073-0910P4</t>
+          <t>mhps1150911-1</t>
         </is>
       </c>
       <c r="F347" s="3" t="inlineStr">
@@ -35164,11 +35164,11 @@
       </c>
       <c r="G347" s="5" t="inlineStr">
         <is>
-          <t>(114年11月鳳凰颱風)縣200甲線港口橋P1橋墩保護工程</t>
+          <t>屏東縣屏東市民和國民小學115學年度1-5年級戶外教育活動採購</t>
         </is>
       </c>
       <c r="H347" s="6" t="n">
-        <v>4640000</v>
+        <v>267930</v>
       </c>
       <c r="I347" s="7" t="inlineStr">
         <is>
@@ -35177,12 +35177,12 @@
       </c>
       <c r="J347" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K347" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -35192,22 +35192,22 @@
       </c>
       <c r="B348" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C348" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D348" s="9" t="inlineStr">
         <is>
-          <t>屏東縣屏東市民和國民小學</t>
+          <t>北投區農會</t>
         </is>
       </c>
       <c r="E348" s="8" t="inlineStr">
         <is>
-          <t>mhps1150911-1</t>
+          <t>115B003</t>
         </is>
       </c>
       <c r="F348" s="8" t="inlineStr">
@@ -35217,15 +35217,15 @@
       </c>
       <c r="G348" s="10" t="inlineStr">
         <is>
-          <t>屏東縣屏東市民和國民小學115學年度1-5年級戶外教育活動採購</t>
+          <t>臺北市直轄市定古蹟「北投穀倉」修復工程</t>
         </is>
       </c>
       <c r="H348" s="11" t="n">
-        <v>267930</v>
+        <v>112768346</v>
       </c>
       <c r="I348" s="12" t="inlineStr">
         <is>
-          <t>115/09/14</t>
+          <t>115/09/11</t>
         </is>
       </c>
       <c r="J348" s="12" t="inlineStr">
@@ -35235,7 +35235,7 @@
       </c>
       <c r="K348" s="9" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -35245,7 +35245,7 @@
       </c>
       <c r="B349" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C349" s="3" t="inlineStr">
@@ -35255,12 +35255,12 @@
       </c>
       <c r="D349" s="4" t="inlineStr">
         <is>
-          <t>北投區農會</t>
+          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
         </is>
       </c>
       <c r="E349" s="3" t="inlineStr">
         <is>
-          <t>115B003</t>
+          <t>6541551031</t>
         </is>
       </c>
       <c r="F349" s="3" t="inlineStr">
@@ -35270,20 +35270,20 @@
       </c>
       <c r="G349" s="5" t="inlineStr">
         <is>
-          <t>臺北市直轄市定古蹟「北投穀倉」修復工程</t>
+          <t>汐止E/S改建工程(第一期)</t>
         </is>
       </c>
       <c r="H349" s="6" t="n">
-        <v>112768346</v>
+        <v>1256000000</v>
       </c>
       <c r="I349" s="7" t="inlineStr">
         <is>
-          <t>115/09/11</t>
+          <t>115/09/10</t>
         </is>
       </c>
       <c r="J349" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/15</t>
         </is>
       </c>
       <c r="K349" s="4" t="inlineStr">
@@ -35298,22 +35298,22 @@
       </c>
       <c r="B350" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C350" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D350" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
+          <t>台灣自來水股份有限公司第六區管理處</t>
         </is>
       </c>
       <c r="E350" s="8" t="inlineStr">
         <is>
-          <t>6541551031</t>
+          <t>WA-115-0601-12</t>
         </is>
       </c>
       <c r="F350" s="8" t="inlineStr">
@@ -35323,11 +35323,11 @@
       </c>
       <c r="G350" s="10" t="inlineStr">
         <is>
-          <t>汐止E/S改建工程(第一期)</t>
+          <t>115年台南所西安南及中西區用戶用水設備新(改)裝工作勞務採購</t>
         </is>
       </c>
       <c r="H350" s="11" t="n">
-        <v>1256000000</v>
+        <v>9346749</v>
       </c>
       <c r="I350" s="12" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
       </c>
       <c r="J350" s="12" t="inlineStr">
         <is>
-          <t>115/10/15</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K350" s="9" t="inlineStr">
@@ -35351,36 +35351,36 @@
       </c>
       <c r="B351" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C351" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D351" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第六區管理處</t>
+          <t>臺灣銀行股份有限公司</t>
         </is>
       </c>
       <c r="E351" s="3" t="inlineStr">
         <is>
-          <t>WA-115-0601-12</t>
+          <t>115-017-E-2-1</t>
         </is>
       </c>
       <c r="F351" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G351" s="5" t="inlineStr">
         <is>
-          <t>115年台南所西安南及中西區用戶用水設備新(改)裝工作勞務採購</t>
+          <t>屏東分行高壓用電變更為低壓用電工程案</t>
         </is>
       </c>
       <c r="H351" s="6" t="n">
-        <v>9346749</v>
+        <v>1499141</v>
       </c>
       <c r="I351" s="7" t="inlineStr">
         <is>
@@ -35389,12 +35389,12 @@
       </c>
       <c r="J351" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/02</t>
         </is>
       </c>
       <c r="K351" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -35404,36 +35404,36 @@
       </c>
       <c r="B352" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C352" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D352" s="9" t="inlineStr">
         <is>
-          <t>臺灣銀行股份有限公司</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E352" s="8" t="inlineStr">
         <is>
-          <t>115-017-E-2-1</t>
+          <t>KCLP16003</t>
         </is>
       </c>
       <c r="F352" s="8" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G352" s="10" t="inlineStr">
         <is>
-          <t>屏東分行高壓用電變更為低壓用電工程案</t>
+          <t>高雄榮總臺南分院116年度醫療設備集中採購計14項</t>
         </is>
       </c>
       <c r="H352" s="11" t="n">
-        <v>1499141</v>
+        <v>0</v>
       </c>
       <c r="I352" s="12" t="inlineStr">
         <is>
@@ -35442,7 +35442,7 @@
       </c>
       <c r="J352" s="12" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/10/15</t>
         </is>
       </c>
       <c r="K352" s="9" t="inlineStr">
@@ -35457,22 +35457,22 @@
       </c>
       <c r="B353" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C353" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D353" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>經濟部水利署南區水資源分署</t>
         </is>
       </c>
       <c r="E353" s="3" t="inlineStr">
         <is>
-          <t>KCLP16003</t>
+          <t>115-KPRW-L09</t>
         </is>
       </c>
       <c r="F353" s="3" t="inlineStr">
@@ -35482,25 +35482,25 @@
       </c>
       <c r="G353" s="5" t="inlineStr">
         <is>
-          <t>高雄榮總臺南分院116年度醫療設備集中採購計14項</t>
+          <t>高屏堰115及116年度採售分離週邊計畫(左岸出料)</t>
         </is>
       </c>
       <c r="H353" s="6" t="n">
-        <v>0</v>
+        <v>75000000</v>
       </c>
       <c r="I353" s="7" t="inlineStr">
         <is>
-          <t>115/09/10</t>
+          <t>115/09/09</t>
         </is>
       </c>
       <c r="J353" s="7" t="inlineStr">
         <is>
-          <t>115/10/15</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K353" s="4" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -35515,17 +35515,17 @@
       </c>
       <c r="C354" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D354" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署南區水資源分署</t>
+          <t>台灣電力股份有限公司核能火力發電工程處南部施工處</t>
         </is>
       </c>
       <c r="E354" s="8" t="inlineStr">
         <is>
-          <t>115-KPRW-L09</t>
+          <t>6751053310</t>
         </is>
       </c>
       <c r="F354" s="8" t="inlineStr">
@@ -35535,20 +35535,20 @@
       </c>
       <c r="G354" s="10" t="inlineStr">
         <is>
-          <t>高屏堰115及116年度採售分離週邊計畫(左岸出料)</t>
+          <t>興達電廠燃氣機組更新改建計畫廠區永久道路排水工程</t>
         </is>
       </c>
       <c r="H354" s="11" t="n">
-        <v>75000000</v>
+        <v>1950000000</v>
       </c>
       <c r="I354" s="12" t="inlineStr">
         <is>
-          <t>115/09/09</t>
+          <t>115/09/08</t>
         </is>
       </c>
       <c r="J354" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/20</t>
         </is>
       </c>
       <c r="K354" s="9" t="inlineStr">
@@ -35563,7 +35563,7 @@
       </c>
       <c r="B355" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C355" s="3" t="inlineStr">
@@ -35573,12 +35573,12 @@
       </c>
       <c r="D355" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司核能火力發電工程處南部施工處</t>
+          <t>臺中市新建工程處</t>
         </is>
       </c>
       <c r="E355" s="3" t="inlineStr">
         <is>
-          <t>6751053310</t>
+          <t>115A-056</t>
         </is>
       </c>
       <c r="F355" s="3" t="inlineStr">
@@ -35588,11 +35588,11 @@
       </c>
       <c r="G355" s="5" t="inlineStr">
         <is>
-          <t>興達電廠燃氣機組更新改建計畫廠區永久道路排水工程</t>
+          <t>大雅區烏橋及農路橋改建工程(含烏橋上下游、農路橋上游左右岸護岸)</t>
         </is>
       </c>
       <c r="H355" s="6" t="n">
-        <v>1950000000</v>
+        <v>239702131</v>
       </c>
       <c r="I355" s="7" t="inlineStr">
         <is>
@@ -35601,7 +35601,7 @@
       </c>
       <c r="J355" s="7" t="inlineStr">
         <is>
-          <t>115/10/20</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K355" s="4" t="inlineStr">
@@ -35616,7 +35616,7 @@
       </c>
       <c r="B356" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C356" s="8" t="inlineStr">
@@ -35626,26 +35626,26 @@
       </c>
       <c r="D356" s="9" t="inlineStr">
         <is>
-          <t>臺中市新建工程處</t>
+          <t>桃園市政府消防局</t>
         </is>
       </c>
       <c r="E356" s="8" t="inlineStr">
         <is>
-          <t>115A-056</t>
+          <t>S115-02-2</t>
         </is>
       </c>
       <c r="F356" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G356" s="10" t="inlineStr">
         <is>
-          <t>大雅區烏橋及農路橋改建工程(含烏橋上下游、農路橋上游左右岸護岸)</t>
+          <t>桃園市政府消防局石門分隊暨經濟部水利署北區水資源分署車庫新建工程</t>
         </is>
       </c>
       <c r="H356" s="11" t="n">
-        <v>239702131</v>
+        <v>199667903</v>
       </c>
       <c r="I356" s="12" t="inlineStr">
         <is>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="J356" s="12" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K356" s="9" t="inlineStr">
@@ -35669,36 +35669,36 @@
       </c>
       <c r="B357" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C357" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D357" s="4" t="inlineStr">
         <is>
-          <t>桃園市政府消防局</t>
+          <t>台灣自來水股份有限公司屏東區管理處</t>
         </is>
       </c>
       <c r="E357" s="3" t="inlineStr">
         <is>
-          <t>S115-02-2</t>
+          <t>WA-15-1313-18</t>
         </is>
       </c>
       <c r="F357" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G357" s="5" t="inlineStr">
         <is>
-          <t>桃園市政府消防局石門分隊暨經濟部水利署北區水資源分署車庫新建工程</t>
+          <t>115年度屏東所用戶新裝單價工作(七)(開口合約)</t>
         </is>
       </c>
       <c r="H357" s="6" t="n">
-        <v>199667903</v>
+        <v>9966600</v>
       </c>
       <c r="I357" s="7" t="inlineStr">
         <is>
@@ -35707,7 +35707,7 @@
       </c>
       <c r="J357" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K357" s="4" t="inlineStr">
@@ -35722,7 +35722,7 @@
       </c>
       <c r="B358" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C358" s="8" t="inlineStr">
@@ -35732,40 +35732,40 @@
       </c>
       <c r="D358" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司屏東區管理處</t>
+          <t>內政部移民署</t>
         </is>
       </c>
       <c r="E358" s="8" t="inlineStr">
         <is>
-          <t>WA-15-1313-18</t>
+          <t>3-1150747</t>
         </is>
       </c>
       <c r="F358" s="8" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G358" s="10" t="inlineStr">
         <is>
-          <t>115年度屏東所用戶新裝單價工作(七)(開口合約)</t>
+          <t>116年高雄收容所伙食採購案</t>
         </is>
       </c>
       <c r="H358" s="11" t="n">
-        <v>9966600</v>
+        <v>20664000</v>
       </c>
       <c r="I358" s="12" t="inlineStr">
         <is>
-          <t>115/09/08</t>
+          <t>115/09/04</t>
         </is>
       </c>
       <c r="J358" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K358" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -35775,22 +35775,22 @@
       </c>
       <c r="B359" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C359" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D359" s="4" t="inlineStr">
         <is>
-          <t>內政部移民署</t>
+          <t>桃園市中壢區公所</t>
         </is>
       </c>
       <c r="E359" s="3" t="inlineStr">
         <is>
-          <t>3-1150747</t>
+          <t>115-08-075</t>
         </is>
       </c>
       <c r="F359" s="3" t="inlineStr">
@@ -35800,25 +35800,25 @@
       </c>
       <c r="G359" s="5" t="inlineStr">
         <is>
-          <t>116年高雄收容所伙食採購案</t>
+          <t>中壢區龍慈路635巷水利溝整建及道路拓寬工程</t>
         </is>
       </c>
       <c r="H359" s="6" t="n">
-        <v>20664000</v>
+        <v>373998519</v>
       </c>
       <c r="I359" s="7" t="inlineStr">
         <is>
-          <t>115/09/04</t>
+          <t>115/09/03</t>
         </is>
       </c>
       <c r="J359" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K359" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -35828,22 +35828,22 @@
       </c>
       <c r="B360" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C360" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D360" s="9" t="inlineStr">
         <is>
-          <t>桃園市中壢區公所</t>
+          <t>高雄市政府環境保護局</t>
         </is>
       </c>
       <c r="E360" s="8" t="inlineStr">
         <is>
-          <t>115-08-075</t>
+          <t>115A1001</t>
         </is>
       </c>
       <c r="F360" s="8" t="inlineStr">
@@ -35853,15 +35853,15 @@
       </c>
       <c r="G360" s="10" t="inlineStr">
         <is>
-          <t>中壢區龍慈路635巷水利溝整建及道路拓寬工程</t>
+          <t>116-117年度高雄市產業園區3D全時陳情稽查計畫</t>
         </is>
       </c>
       <c r="H360" s="11" t="n">
-        <v>373998519</v>
+        <v>46093000</v>
       </c>
       <c r="I360" s="12" t="inlineStr">
         <is>
-          <t>115/09/03</t>
+          <t>115/09/02</t>
         </is>
       </c>
       <c r="J360" s="12" t="inlineStr">
@@ -35871,7 +35871,7 @@
       </c>
       <c r="K360" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -35881,22 +35881,22 @@
       </c>
       <c r="B361" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C361" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D361" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府環境保護局</t>
+          <t>交通部高速公路局</t>
         </is>
       </c>
       <c r="E361" s="3" t="inlineStr">
         <is>
-          <t>115A1001</t>
+          <t>115A051P004</t>
         </is>
       </c>
       <c r="F361" s="3" t="inlineStr">
@@ -35906,25 +35906,25 @@
       </c>
       <c r="G361" s="5" t="inlineStr">
         <is>
-          <t>116-117年度高雄市產業園區3D全時陳情稽查計畫</t>
+          <t>國道1號五堵交流道至汐止交流道路段拓寬工程（第C109R標）</t>
         </is>
       </c>
       <c r="H361" s="6" t="n">
-        <v>46093000</v>
+        <v>3110190422</v>
       </c>
       <c r="I361" s="7" t="inlineStr">
         <is>
-          <t>115/09/02</t>
+          <t>115/09/01</t>
         </is>
       </c>
       <c r="J361" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K361" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -35934,22 +35934,22 @@
       </c>
       <c r="B362" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C362" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D362" s="9" t="inlineStr">
         <is>
-          <t>交通部高速公路局</t>
+          <t>台灣電力股份有限公司台中發電廠</t>
         </is>
       </c>
       <c r="E362" s="8" t="inlineStr">
         <is>
-          <t>115A051P004</t>
+          <t>3711500256</t>
         </is>
       </c>
       <c r="F362" s="8" t="inlineStr">
@@ -35959,20 +35959,20 @@
       </c>
       <c r="G362" s="10" t="inlineStr">
         <is>
-          <t>國道1號五堵交流道至汐止交流道路段拓寬工程（第C109R標）</t>
+          <t>連續式卸煤機CSU-3安全性檢查、鋼構修復及雜項維護等工作</t>
         </is>
       </c>
       <c r="H362" s="11" t="n">
-        <v>3110190422</v>
+        <v>24990000</v>
       </c>
       <c r="I362" s="12" t="inlineStr">
         <is>
-          <t>115/09/01</t>
+          <t>115/08/25</t>
         </is>
       </c>
       <c r="J362" s="12" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K362" s="9" t="inlineStr">
@@ -35987,22 +35987,22 @@
       </c>
       <c r="B363" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C363" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D363" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司台中發電廠</t>
+          <t>高雄市政府</t>
         </is>
       </c>
       <c r="E363" s="3" t="inlineStr">
         <is>
-          <t>3711500256</t>
+          <t>115G0821A</t>
         </is>
       </c>
       <c r="F363" s="3" t="inlineStr">
@@ -36012,20 +36012,20 @@
       </c>
       <c r="G363" s="5" t="inlineStr">
         <is>
-          <t>連續式卸煤機CSU-3安全性檢查、鋼構修復及雜項維護等工作</t>
+          <t>高雄環狀輕軌增購列車統包工程</t>
         </is>
       </c>
       <c r="H363" s="6" t="n">
-        <v>24990000</v>
+        <v>6467000000</v>
       </c>
       <c r="I363" s="7" t="inlineStr">
         <is>
-          <t>115/08/25</t>
+          <t>115/08/21</t>
         </is>
       </c>
       <c r="J363" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K363" s="4" t="inlineStr">
@@ -36055,30 +36055,30 @@
       </c>
       <c r="E364" s="8" t="inlineStr">
         <is>
-          <t>115G0821A</t>
+          <t>115F0423A</t>
         </is>
       </c>
       <c r="F364" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G364" s="10" t="inlineStr">
         <is>
-          <t>高雄環狀輕軌增購列車統包工程</t>
+          <t>高雄都會區大眾捷運系統都會線(黃線)YC04標土建及設施機電工程</t>
         </is>
       </c>
       <c r="H364" s="11" t="n">
-        <v>6467000000</v>
+        <v>17469196681</v>
       </c>
       <c r="I364" s="12" t="inlineStr">
         <is>
-          <t>115/08/21</t>
+          <t>115/08/20</t>
         </is>
       </c>
       <c r="J364" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K364" s="9" t="inlineStr">
@@ -36087,61 +36087,8 @@
         </is>
       </c>
     </row>
-    <row r="365" ht="26" customHeight="1">
-      <c r="A365" s="3" t="n">
-        <v>363</v>
-      </c>
-      <c r="B365" s="3" t="inlineStr">
-        <is>
-          <t>高雄市</t>
-        </is>
-      </c>
-      <c r="C365" s="3" t="inlineStr">
-        <is>
-          <t>工程類</t>
-        </is>
-      </c>
-      <c r="D365" s="4" t="inlineStr">
-        <is>
-          <t>高雄市政府</t>
-        </is>
-      </c>
-      <c r="E365" s="3" t="inlineStr">
-        <is>
-          <t>115F0423A</t>
-        </is>
-      </c>
-      <c r="F365" s="3" t="inlineStr">
-        <is>
-          <t>第 03 次</t>
-        </is>
-      </c>
-      <c r="G365" s="5" t="inlineStr">
-        <is>
-          <t>高雄都會區大眾捷運系統都會線(黃線)YC04標土建及設施機電工程</t>
-        </is>
-      </c>
-      <c r="H365" s="6" t="n">
-        <v>17469196681</v>
-      </c>
-      <c r="I365" s="7" t="inlineStr">
-        <is>
-          <t>115/08/20</t>
-        </is>
-      </c>
-      <c r="J365" s="7" t="inlineStr">
-        <is>
-          <t>115/10/08</t>
-        </is>
-      </c>
-      <c r="K365" s="4" t="inlineStr">
-        <is>
-          <t>公開招標</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:K365"/>
+  <autoFilter ref="A2:K364"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -36508,7 +36455,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G362" r:id="rId360"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G363" r:id="rId361"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G364" r:id="rId362"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G365" r:id="rId363"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-25 09:43</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-25 17:42</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-25 09:43</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-25 17:42</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-25 17:42</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-26 09:48</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-25 17:42</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-26 09:48</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -16917,40 +16917,40 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>宜蘭縣政府文化局</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>111508022</t>
+          <t>L115094901c</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Danas-F-06-02-08-白河區頭前溪甘宅橋改建工程及Danas-F-06-02-08-白河區南86線頭前溪橋改建工程</t>
+          <t>縣定古蹟「羅東鎮聖母醫院耶穌聖心堂」緊急修復工程</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
-        <v>267712133</v>
+        <v>848025</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -16960,36 +16960,36 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>財團法人國家衛生研究院</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>115A0D0272</t>
+          <t>111508022</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>「BP2/NIDB工程」- E棟高防護實驗室儀器設備採購案</t>
+          <t>Danas-F-06-02-08-白河區頭前溪甘宅橋改建工程及Danas-F-06-02-08-白河區南86線頭前溪橋改建工程</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>165894325</v>
+        <v>267712133</v>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
@@ -16998,7 +16998,7 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -17013,22 +17013,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>高雄市兵役處</t>
+          <t>財團法人國家衛生研究院</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1150922</t>
+          <t>115A0D0272</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -17038,11 +17038,11 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>高雄市115年軍人忠靈祠鳥松園區櫃位整修工程</t>
+          <t>「BP2/NIDB工程」- E棟高防護實驗室儀器設備採購案</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18049966</v>
+        <v>165894325</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -17066,7 +17066,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -17076,12 +17076,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>新竹縣北埔鄉公所</t>
+          <t>高雄市兵役處</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>115A004</t>
+          <t>1150922</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -17091,11 +17091,11 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>北埔鄉大湖村、南埔村、大林村、水磜村等11處道路災害復建工程</t>
+          <t>高雄市115年軍人忠靈祠鳥松園區櫃位整修工程</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>17217692</v>
+        <v>18049966</v>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -17129,12 +17129,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市建國國民小學</t>
+          <t>新竹縣北埔鄉公所</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>HS115006</t>
+          <t>115A004</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -17144,11 +17144,11 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>苗栗縣建國國小115年度校舍油漆粉刷工程</t>
+          <t>北埔鄉大湖村、南埔村、大林村、水磜村等11處道路災害復建工程</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>12609155</v>
+        <v>17217692</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -17182,26 +17182,26 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>國立高雄科技大學</t>
+          <t>苗栗縣頭份市建國國民小學</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>1131112002</t>
+          <t>HS115006</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>第 14 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>建工校區雙科館7樓及屋頂外牆整修工程</t>
+          <t>苗栗縣建國國小115年度校舍油漆粉刷工程</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>12120800</v>
+        <v>12609155</v>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -17235,26 +17235,26 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣南澳鄉公所</t>
+          <t>國立高雄科技大學</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>B115-17</t>
+          <t>1131112002</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 14 次</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>澳花上部落排水改善工程</t>
+          <t>建工校區雙科館7樓及屋頂外牆整修工程</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>8091597</v>
+        <v>12120800</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -17278,22 +17278,22 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>宜蘭縣南澳鄉公所</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>1155027844</t>
+          <t>B115-17</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -17303,11 +17303,11 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>臺東工務段利家監工站轄區116年度預約經常性路面清掃維護工作</t>
+          <t>澳花上部落排水改善工程</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>7857136</v>
+        <v>8091597</v>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -17331,22 +17331,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮鹿港國民小學</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>LG115E</t>
+          <t>1155027844</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -17356,11 +17356,11 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>鹿港國小既設水電系統遷移工程</t>
+          <t>臺東工務段利家監工站轄區116年度預約經常性路面清掃維護工作</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>7423795</v>
+        <v>7857136</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -17384,7 +17384,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -17394,12 +17394,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>新竹縣新豐鄉公所</t>
+          <t>彰化縣鹿港鎮鹿港國民小學</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>HE115705</t>
+          <t>LG115E</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -17409,11 +17409,11 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>新豐鄉綠景莊園網球場整修工程</t>
+          <t>鹿港國小既設水電系統遷移工程</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>6305735</v>
+        <v>7423795</v>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -17447,26 +17447,26 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺東分署</t>
+          <t>新竹縣新豐鄉公所</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>115-FR-19-5-013</t>
+          <t>HE115705</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>農東成208支線及忠孝里周遭農路改善工程</t>
+          <t>新豐鄉綠景莊園網球場整修工程</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>6268603</v>
+        <v>6305735</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -17500,26 +17500,26 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>宜蘭縣海洋及漁業發展所</t>
+          <t>農業部農村發展及水土保持署臺東分署</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>1150828</t>
+          <t>115-FR-19-5-013</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>115年度宜蘭縣養殖漁業生產區環境清理及公共設施維護修繕工程(開口契約)</t>
+          <t>農東成208支線及忠孝里周遭農路改善工程</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
-        <v>5142000</v>
+        <v>6268603</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -17553,12 +17553,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>財團法人工業技術研究院</t>
+          <t>宜蘭縣海洋及漁業發展所</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>A712000687</t>
+          <t>1150828</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -17568,11 +17568,11 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>「無人化創新科技實驗室-快速試製廠房建置」基地整地喬木移植工程</t>
+          <t>115年度宜蘭縣養殖漁業生產區環境清理及公共設施維護修繕工程(開口契約)</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>3000000</v>
+        <v>5142000</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -17606,12 +17606,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>南投縣南投市光華國民小學</t>
+          <t>財團法人工業技術研究院</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>115009SE</t>
+          <t>A712000687</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -17621,11 +17621,11 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>光華國小向陽樓無障礙電梯整建工程</t>
+          <t>「無人化創新科技實驗室-快速試製廠房建置」基地整地喬木移植工程</t>
         </is>
       </c>
       <c r="H16" s="11" t="n">
-        <v>2853055</v>
+        <v>3000000</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
@@ -17659,26 +17659,26 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣立新港國民中小學</t>
+          <t>南投縣南投市光華國民小學</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1150904</t>
+          <t>115009SE</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>學校圖書館空間整修工程</t>
+          <t>光華國小向陽樓無障礙電梯整建工程</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2655702</v>
+        <v>2853055</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -17702,7 +17702,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -17712,12 +17712,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>臺中市霧峰區霧峰國民小學</t>
+          <t>苗栗縣立新港國民中小學</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>115YUGU</t>
+          <t>1150904</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -17727,11 +17727,11 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>臺中市霧峰區霧峰國小新設第2座兒童遊戲場工程採購案</t>
+          <t>學校圖書館空間整修工程</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
-        <v>1793611</v>
+        <v>2655702</v>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -17765,12 +17765,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>桃園市立大園幼兒園</t>
+          <t>臺中市霧峰區霧峰國民小學</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>DY11509</t>
+          <t>115YUGU</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -17780,11 +17780,11 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>桃園市立大園幼兒園三和分班電力改善工程</t>
+          <t>臺中市霧峰區霧峰國小新設第2座兒童遊戲場工程採購案</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1290998</v>
+        <v>1793611</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -17793,12 +17793,12 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -17808,36 +17808,36 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>桃園市立大園幼兒園</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>1155026686</t>
+          <t>DY11509</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>116年度鳳屏工務段文書檔案管理工作</t>
+          <t>桃園市立大園幼兒園三和分班電力改善工程</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
-        <v>1156284</v>
+        <v>1290998</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
@@ -17861,22 +17861,22 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>臺南市新市區大社國民小學</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>dashe115008</t>
+          <t>1155026686</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -17886,11 +17886,11 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>臺南市大社國小115年附設幼兒園盥洗室改善工程</t>
+          <t>116年度鳳屏工務段文書檔案管理工作</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1071857</v>
+        <v>1156284</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -17914,7 +17914,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -17924,12 +17924,12 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>臺中市立豐原商業高級中等學校</t>
+          <t>臺南市新市區大社國民小學</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>115022</t>
+          <t>dashe115008</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -17939,11 +17939,11 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>豐原高商宿舍及浴廁環境改善工程</t>
+          <t>臺南市大社國小115年附設幼兒園盥洗室改善工程</t>
         </is>
       </c>
       <c r="H22" s="11" t="n">
-        <v>1059933</v>
+        <v>1071857</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -17967,7 +17967,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -17977,12 +17977,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>高雄市大樹區大樹國民小學</t>
+          <t>臺中市立豐原商業高級中等學校</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>dsp1150901</t>
+          <t>115022</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -17992,11 +17992,11 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>偏遠地區學校及非山非市學校設施設備計畫工程案。</t>
+          <t>豐原高商宿舍及浴廁環境改善工程</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>916922</v>
+        <v>1059933</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -18030,12 +18030,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>國立虎尾科技大學</t>
+          <t>高雄市大樹區大樹國民小學</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>1150920</t>
+          <t>dsp1150901</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -18045,11 +18045,11 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>綠能材料低碳製程教學場域優化工程</t>
+          <t>偏遠地區學校及非山非市學校設施設備計畫工程案。</t>
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>842400</v>
+        <v>916922</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
@@ -18083,12 +18083,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>基隆市公共汽車管理處</t>
+          <t>國立虎尾科技大學</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>115A104</t>
+          <t>1150920</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -18098,11 +18098,11 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>和平島智慧型候車亭增建工程</t>
+          <t>綠能材料低碳製程教學場域優化工程</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>654302</v>
+        <v>842400</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -18126,7 +18126,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -18136,26 +18136,26 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>新北市瑞芳區九份國民小學</t>
+          <t>基隆市公共汽車管理處</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>jfes2026-09-09</t>
+          <t>115A104</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>115年度改善偏遠地區國民中小學教師宿舍工程</t>
+          <t>和平島智慧型候車亭增建工程</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>651370</v>
+        <v>654302</v>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
@@ -18194,21 +18194,21 @@
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>jfes2026-09-13</t>
+          <t>jfes2026-09-09</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>幼兒園教室地坪工程</t>
+          <t>115年度改善偏遠地區國民中小學教師宿舍工程</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>439920</v>
+        <v>651370</v>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/02</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -18232,22 +18232,22 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公所</t>
+          <t>新北市瑞芳區九份國民小學</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>115212</t>
+          <t>jfes2026-09-13</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -18257,11 +18257,11 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>115年度屏東市公園監視系統設置</t>
+          <t>幼兒園教室地坪工程</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>207700</v>
+        <v>439920</v>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -18285,22 +18285,22 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>屏東縣屏東市公所</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>1150806C0146</t>
+          <t>115212</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -18310,25 +18310,25 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>臺北市大安區金華特四基地行政大樓新建工程</t>
+          <t>115年度屏東市公園監視系統設置</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>1108616262</v>
+        <v>207700</v>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
-          <t>115/09/24</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -18338,7 +18338,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -18348,26 +18348,26 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉公所</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>1150902</t>
+          <t>1150806C0146</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>古坑鄉多功能社會福利大樓興建工程</t>
+          <t>臺北市大安區金華特四基地行政大樓新建工程</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>95076841</v>
+        <v>1108616262</v>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
@@ -18391,7 +18391,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -18401,12 +18401,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第六區管理處</t>
+          <t>雲林縣古坑鄉公所</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>RC-115-0601-0038</t>
+          <t>1150902</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -18416,11 +18416,11 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>歸仁區中山路一段汰換管線工程(二)</t>
+          <t>古坑鄉多功能社會福利大樓興建工程</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>47356103</v>
+        <v>95076841</v>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -18454,26 +18454,26 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>台灣自來水股份有限公司第六區管理處</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>115-117</t>
+          <t>RC-115-0601-0038</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>116年度苗栗段轄區省道路面零星及擇要修復工程(開口契約)</t>
+          <t>歸仁區中山路一段汰換管線工程(二)</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>46968385</v>
+        <v>47356103</v>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -18507,26 +18507,26 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>國立勤益科技大學</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>CY1154-010</t>
+          <t>115-117</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>將軍道及校內停車場整建工程</t>
+          <t>116年度苗栗段轄區省道路面零星及擇要修復工程(開口契約)</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>43020000</v>
+        <v>46968385</v>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -18550,36 +18550,36 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>交通部高速公路局南區養護工程分局</t>
+          <t>國立勤益科技大學</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>115D120P023</t>
+          <t>CY1154-010</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>南分局服務區閉路電視(CCTV)增設汰換採購(115)</t>
+          <t>將軍道及校內停車場整建工程</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>35506296</v>
+        <v>43020000</v>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/02</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
@@ -18603,22 +18603,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>交通部高速公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>115-213</t>
+          <t>115D120P023</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -18628,11 +18628,11 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>116年度臺中工務段轄線省道路面擇要修復工程（開口契約）</t>
+          <t>南分局服務區閉路電視(CCTV)增設汰換採購(115)</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>32880793</v>
+        <v>35506296</v>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
@@ -18641,7 +18641,7 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -18656,7 +18656,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -18666,12 +18666,12 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>新竹縣北埔鄉公所</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>115A003</t>
+          <t>115-213</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -18681,11 +18681,11 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>北埔鄉外坪村及大林村等8處村里聯絡道路災害復建工程</t>
+          <t>116年度臺中工務段轄線省道路面擇要修復工程（開口契約）</t>
         </is>
       </c>
       <c r="H36" s="11" t="n">
-        <v>27802651</v>
+        <v>32880793</v>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -18719,26 +18719,26 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>臺東縣海端鄉公所</t>
+          <t>新竹縣北埔鄉公所</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>HE1150831</t>
+          <t>115A003</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>紅石部落基礎設施改善工程</t>
+          <t>北埔鄉外坪村及大林村等8處村里聯絡道路災害復建工程</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>24204000</v>
+        <v>27802651</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
@@ -18747,7 +18747,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -18772,26 +18772,26 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>南投縣竹山鎮公所</t>
+          <t>臺東縣海端鄉公所</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>115054</t>
+          <t>HE1150831</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>竹山鎮中崎社區活動中心暨老人會館新建工程</t>
+          <t>紅石部落基礎設施改善工程</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>24028700</v>
+        <v>24204000</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
@@ -18825,12 +18825,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>連江縣自來水廠</t>
+          <t>南投縣竹山鎮公所</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>WL1150901</t>
+          <t>115054</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -18840,11 +18840,11 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>珠螺水庫浚渫及南竿各水庫周邊設施改善工程</t>
+          <t>竹山鎮中崎社區活動中心暨老人會館新建工程</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>22796000</v>
+        <v>24028700</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
@@ -18853,7 +18853,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -18878,12 +18878,12 @@
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局北區養護工程分局</t>
+          <t>連江縣自來水廠</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>1161A1E05</t>
+          <t>WL1150901</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -18893,11 +18893,11 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>復興段116年台7線22K~60K預約經常性公路零星修復工程</t>
+          <t>珠螺水庫浚渫及南竿各水庫周邊設施改善工程</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>18302949</v>
+        <v>22796000</v>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
@@ -18906,7 +18906,7 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
@@ -18931,12 +18931,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司花東供電區營運處</t>
+          <t>交通部公路局北區養護工程分局</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>4951570010</t>
+          <t>1161A1E05</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -18946,11 +18946,11 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>161kV台東~鹿野線#11鐵塔基礎改建工程</t>
+          <t>復興段116年台7線22K~60K預約經常性公路零星修復工程</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>17560000</v>
+        <v>18302949</v>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -18974,7 +18974,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>中央/中油</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -18984,12 +18984,12 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司</t>
+          <t>台灣電力股份有限公司花東供電區營運處</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>LDA1531007</t>
+          <t>4951570010</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -18999,11 +18999,11 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>竹服寶山鄉愛山林建設公司(6-1區)159戶裝置新設工程</t>
+          <t>161kV台東~鹿野線#11鐵塔基礎改建工程</t>
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>17297523</v>
+        <v>17560000</v>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>115/10/13</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
@@ -19027,7 +19027,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>中央/中油</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -19037,26 +19037,26 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府水利局</t>
+          <t>台灣中油股份有限公司</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>C1150743</t>
+          <t>LDA1531007</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>前金區河東路與光復三街周邊新設抽水機組應急工程</t>
+          <t>竹服寶山鄉愛山林建設公司(6-1區)159戶裝置新設工程</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>17218000</v>
+        <v>17297523</v>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/13</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -19090,26 +19090,26 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署臺東分署</t>
+          <t>高雄市政府水利局</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>11506A2002-001</t>
+          <t>C1150743</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>知本國家森林遊樂區榕蔭步道修復工程</t>
+          <t>前金區河東路與光復三街周邊新設抽水機組應急工程</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>16341000</v>
+        <v>17218000</v>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
@@ -19143,12 +19143,12 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局北區養護工程分局</t>
+          <t>農業部林業及自然保育署臺東分署</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1161A1E04</t>
+          <t>11506A2002-001</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -19158,11 +19158,11 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>復興段116年台7線0k~22k、台7乙線8k~14k預約經常性公路零星修復工程</t>
+          <t>知本國家森林遊樂區榕蔭步道修復工程</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>16140043</v>
+        <v>16341000</v>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
@@ -19186,7 +19186,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -19196,26 +19196,26 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府衛生局</t>
+          <t>交通部公路局北區養護工程分局</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>1161A1E04</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>屏東縣來義鄉南和村衛生室重建工程</t>
+          <t>復興段116年台7線0k~22k、台7乙線8k~14k預約經常性公路零星修復工程</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>13771003</v>
+        <v>16140043</v>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
@@ -19224,7 +19224,7 @@
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
@@ -19239,36 +19239,36 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>屏東縣政府衛生局</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>1153063242</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>楓港工務段116年度台1線436K+470~461K+081綠美化及路容維護工作</t>
+          <t>屏東縣來義鄉南和村衛生室重建工程</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>11829463</v>
+        <v>13771003</v>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -19297,17 +19297,17 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>交通部高速公路局南區養護工程分局</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>115D120P025</t>
+          <t>1153063242</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -19317,11 +19317,11 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>南區交通控制中心虛擬化環境之儲存系統優化提升(115)</t>
+          <t>楓港工務段116年度台1線436K+470~461K+081綠美化及路容維護工作</t>
         </is>
       </c>
       <c r="H48" s="11" t="n">
-        <v>10901647</v>
+        <v>11829463</v>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
@@ -19345,22 +19345,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>交通部高速公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>115RA-13-001</t>
+          <t>115D120P025</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -19370,11 +19370,11 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>後壁區菁寮老街環境營造改善工程</t>
+          <t>南區交通控制中心虛擬化環境之儲存系統優化提升(115)</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>9908021</v>
+        <v>10901647</v>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -19398,7 +19398,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -19408,12 +19408,12 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局北區養護工程分局</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>1161A1C14</t>
+          <t>115RA-13-001</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -19423,11 +19423,11 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>中壢段116年台1、台1甲、台4線預約及北分局轄區備援災害搶修及修復工程</t>
+          <t>後壁區菁寮老街環境營造改善工程</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>9367408</v>
+        <v>9908021</v>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
@@ -19436,7 +19436,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr">
@@ -19451,7 +19451,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -19461,12 +19461,12 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>交通部公路局北區養護工程分局</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>115-214</t>
+          <t>1161A1C14</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -19476,11 +19476,11 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>116年度臺中段轄區省道照明改善及災害搶修工程(開口契約)</t>
+          <t>中壢段116年台1、台1甲、台4線預約及北分局轄區備援災害搶修及修復工程</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>9334683</v>
+        <v>9367408</v>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
@@ -19504,7 +19504,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -19514,12 +19514,12 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>1155027563</t>
+          <t>115-214</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -19529,11 +19529,11 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>潮州工務段屏東監工站轄區116年度省道預約經常性瀝青路面零星修補工程</t>
+          <t>116年度臺中段轄區省道照明改善及災害搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H52" s="11" t="n">
-        <v>9091512</v>
+        <v>9334683</v>
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
@@ -19542,7 +19542,7 @@
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
@@ -19557,7 +19557,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -19572,7 +19572,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>1153067533</t>
+          <t>1155027563</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -19582,11 +19582,11 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>楓港工務段楓港監工站116年度省道預約經常性公路零星修復工程</t>
+          <t>潮州工務段屏東監工站轄區116年度省道預約經常性瀝青路面零星修補工程</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>9089078</v>
+        <v>9091512</v>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -19620,26 +19620,26 @@
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>桃園市楊梅區公所</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>YM-115021</t>
+          <t>1153067533</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>楊梅區楊新北路321巷鐵路涵洞降挖改善工程</t>
+          <t>楓港工務段楓港監工站116年度省道預約經常性公路零星修復工程</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>8996194</v>
+        <v>9089078</v>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>115/10/13</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
@@ -19663,36 +19663,36 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>桃園市楊梅區公所</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>1153063244</t>
+          <t>YM-115021</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>楓港工務段116年度台9線及台9戊線綠美化及路容維護工作</t>
+          <t>楊梅區楊新北路321巷鐵路涵洞降挖改善工程</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>7860273</v>
+        <v>8996194</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/13</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -19716,12 +19716,12 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
@@ -19731,7 +19731,7 @@
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>1153064556</t>
+          <t>1153063244</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -19741,11 +19741,11 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>楓港工務段恆春監工站116年度省道預約經常性瀝青路面零星修補工程</t>
+          <t>楓港工務段116年度台9線及台9戊線綠美化及路容維護工作</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>7104788</v>
+        <v>7860273</v>
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
@@ -19769,22 +19769,22 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>CN115-2-20</t>
+          <t>1153064556</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -19794,11 +19794,11 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>116年諮議委員及水利小組長國內考察開口契約</t>
+          <t>楓港工務段恆春監工站116年度省道預約經常性瀝青路面零星修補工程</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>7015000</v>
+        <v>7104788</v>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
@@ -19807,12 +19807,12 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>115/10/13</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -19822,22 +19822,22 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>1153064558</t>
+          <t>CN115-2-20</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -19847,11 +19847,11 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>楓港工務段116年度楓港監工站台9線、台9戊線及台26線間預約經常性瀝青路面零星修補工程</t>
+          <t>116年諮議委員及水利小組長國內考察開口契約</t>
         </is>
       </c>
       <c r="H58" s="11" t="n">
-        <v>6881025</v>
+        <v>7015000</v>
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
@@ -19860,12 +19860,12 @@
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/13</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -19875,7 +19875,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -19885,26 +19885,26 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>農業部林業及自然保育署花蓮分署</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>11507MT005</t>
+          <t>1153064558</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>115-116年「馬太鞍堰塞湖周邊林道維護及緊急搶修工程」</t>
+          <t>楓港工務段116年度楓港監工站台9線、台9戊線及台26線間預約經常性瀝青路面零星修補工程</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>6000000</v>
+        <v>6881025</v>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
@@ -19913,7 +19913,7 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -19928,7 +19928,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -19938,26 +19938,26 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>國立臺北藝術大學</t>
+          <t>農業部林業及自然保育署花蓮分署</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>C115017</t>
+          <t>11507MT005</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>115年度教學大樓能效改善及淨零示範工程</t>
+          <t>115-116年「馬太鞍堰塞湖周邊林道維護及緊急搶修工程」</t>
         </is>
       </c>
       <c r="H60" s="11" t="n">
-        <v>5802364</v>
+        <v>6000000</v>
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
@@ -19986,17 +19986,17 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>臺北大眾捷運股份有限公司</t>
+          <t>國立臺北藝術大學</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>B15A05295</t>
+          <t>C115017</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -20006,11 +20006,11 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>文湖線370型電聯車車廂地板修復工作</t>
+          <t>115年度教學大樓能效改善及淨零示範工程</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>5466400</v>
+        <v>5802364</v>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -20034,22 +20034,22 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>臺北大眾捷運股份有限公司</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>115RA-04-014-1</t>
+          <t>B15A05295</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -20059,11 +20059,11 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>南勝社區勝荔園區地坪及磱碡坑段⼆⼩段 935-433護岸改善⼯程</t>
+          <t>文湖線370型電聯車車廂地板修復工作</t>
         </is>
       </c>
       <c r="H62" s="11" t="n">
-        <v>5307804</v>
+        <v>5466400</v>
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
@@ -20072,7 +20072,7 @@
       </c>
       <c r="J62" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K62" s="9" t="inlineStr">
@@ -20087,7 +20087,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -20097,26 +20097,26 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1155025857</t>
+          <t>115RA-04-014-1</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>鳳屏工務段轄區116年度省道預約經常性公路零星修復及災害搶修工程</t>
+          <t>南勝社區勝荔園區地坪及磱碡坑段⼆⼩段 935-433護岸改善⼯程</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>4999805</v>
+        <v>5307804</v>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
@@ -20140,22 +20140,22 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司高雄港務分公司</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>115-E-04</t>
+          <t>1155025857</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -20165,11 +20165,11 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>116年度高雄港區高低壓設備巡檢維護工作</t>
+          <t>鳳屏工務段轄區116年度省道預約經常性公路零星修復及災害搶修工程</t>
         </is>
       </c>
       <c r="H64" s="11" t="n">
-        <v>4982494</v>
+        <v>4999805</v>
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
@@ -20178,7 +20178,7 @@
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
@@ -20193,36 +20193,36 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>金門縣金湖鎮公所</t>
+          <t>臺灣港務股份有限公司高雄港務分公司</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1150923</t>
+          <t>115-E-04</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>金湖鎮安民聯外道路拓寬改善工程</t>
+          <t>116年度高雄港區高低壓設備巡檢維護工作</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>4945165</v>
+        <v>4982494</v>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -20256,12 +20256,12 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>金門縣金湖鎮公所</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>1153064557</t>
+          <t>1150923</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -20271,11 +20271,11 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>楓港工務段116年度台1線436k+470~461k+081間預約經常性瀝青路面零星修補工程</t>
+          <t>金湖鎮安民聯外道路拓寬改善工程</t>
         </is>
       </c>
       <c r="H66" s="11" t="n">
-        <v>4679676</v>
+        <v>4945165</v>
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
@@ -20284,7 +20284,7 @@
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
@@ -20299,7 +20299,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -20309,26 +20309,26 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>南投縣南投市南投國民小學</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>115-03-42-011-A</t>
+          <t>1153064557</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>南投國小114-116年度公立國民中小學老舊廁所整修工程-工程採購案3</t>
+          <t>楓港工務段116年度台1線436k+470~461k+081間預約經常性瀝青路面零星修補工程</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>4481793</v>
+        <v>4679676</v>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
@@ -20337,7 +20337,7 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -20352,7 +20352,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -20362,26 +20362,26 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>南投縣南投市南投國民小學</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>115EI63719006104220</t>
+          <t>115-03-42-011-A</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>大崗山營區052營舍整修工程</t>
+          <t>南投國小114-116年度公立國民中小學老舊廁所整修工程-工程採購案3</t>
         </is>
       </c>
       <c r="H68" s="11" t="n">
-        <v>4410113</v>
+        <v>4481793</v>
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr">
@@ -20405,7 +20405,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -20415,26 +20415,26 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>115-073-0831A1</t>
+          <t>115EI63719006104220</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>(115)屏41線6K+522-8K+733擇要道路改善工程</t>
+          <t>大崗山營區052營舍整修工程</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>4299000</v>
+        <v>4410113</v>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
@@ -20443,7 +20443,7 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -20458,7 +20458,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -20468,26 +20468,26 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>臺東縣政府</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>115300310464</t>
+          <t>115-073-0831A1</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>光明國小--115年度附設幼兒園充實及改善教學環境工程</t>
+          <t>(115)屏41線6K+522-8K+733擇要道路改善工程</t>
         </is>
       </c>
       <c r="H70" s="11" t="n">
-        <v>4295585</v>
+        <v>4299000</v>
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
@@ -20521,26 +20521,26 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>南投縣立南投國民中學</t>
+          <t>臺東縣政府</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>115-03-12-003-09</t>
+          <t>115300310464</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>114年度老舊廁所整修工程</t>
+          <t>光明國小--115年度附設幼兒園充實及改善教學環境工程</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>4238963</v>
+        <v>4295585</v>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
@@ -20549,7 +20549,7 @@
       </c>
       <c r="J71" s="7" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K71" s="4" t="inlineStr">
@@ -20564,7 +20564,7 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -20574,26 +20574,26 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>國立花蓮女子高級中學</t>
+          <t>南投縣立南投國民中學</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>11510</t>
+          <t>115-03-12-003-09</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>115年度游泳池整建維修工程</t>
+          <t>114年度老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H72" s="11" t="n">
-        <v>3941489</v>
+        <v>4238963</v>
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
@@ -20602,7 +20602,7 @@
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
@@ -20617,7 +20617,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -20627,26 +20627,26 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>國立花蓮女子高級中學</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>115RA-04-013</t>
+          <t>11510</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>東山區高原里神農宮前社區道路改善工程</t>
+          <t>115年度游泳池整建維修工程</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>3935653</v>
+        <v>3941489</v>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -20680,26 +20680,26 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府水利局</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>B1150850</t>
+          <t>115RA-04-013</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>燕巢區瓊林排水（瓊西段388地號旁）護岸損壞修復工程（115年4月豪雨）</t>
+          <t>東山區高原里神農宮前社區道路改善工程</t>
         </is>
       </c>
       <c r="H74" s="11" t="n">
-        <v>3582000</v>
+        <v>3935653</v>
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
@@ -20723,7 +20723,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
@@ -20733,26 +20733,26 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>新北市立圖書館</t>
+          <t>高雄市政府水利局</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>NTCLA115-015</t>
+          <t>B1150850</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>三重五常分館屋頂防水暨滲漏水處修繕工程</t>
+          <t>燕巢區瓊林排水（瓊西段388地號旁）護岸損壞修復工程（115年4月豪雨）</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>3473323</v>
+        <v>3582000</v>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
@@ -20776,7 +20776,7 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
@@ -20786,26 +20786,26 @@
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>新北市立圖書館</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>115028G</t>
+          <t>NTCLA115-015</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>第 06 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>南庄鄉蓬萊社區週邊設施空間機能改善工程</t>
+          <t>三重五常分館屋頂防水暨滲漏水處修繕工程</t>
         </is>
       </c>
       <c r="H76" s="11" t="n">
-        <v>3452448</v>
+        <v>3473323</v>
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
@@ -20814,7 +20814,7 @@
       </c>
       <c r="J76" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K76" s="9" t="inlineStr">
@@ -20839,26 +20839,26 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣造橋鄉公所</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>1150908001</t>
+          <t>115028G</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 06 次</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>115年度造橋鄉水利及水保設施改善工程第六期(朝陽村、談文村)</t>
+          <t>南庄鄉蓬萊社區週邊設施空間機能改善工程</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>3441000</v>
+        <v>3452448</v>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
@@ -20882,7 +20882,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -20892,26 +20892,26 @@
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮東國民小學</t>
+          <t>苗栗縣造橋鄉公所</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>ctps1150801</t>
+          <t>1150908001</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>屏東縣潮東國小附設幼兒園115年度充實及改善教學環境設施設備工程採購案</t>
+          <t>115年度造橋鄉水利及水保設施改善工程第六期(朝陽村、談文村)</t>
         </is>
       </c>
       <c r="H78" s="11" t="n">
-        <v>3224173</v>
+        <v>3441000</v>
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
       </c>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
@@ -20935,7 +20935,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -20945,12 +20945,12 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>雲林縣口湖鄉下崙國民小學</t>
+          <t>屏東縣潮州鎮潮東國民小學</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>A1150923</t>
+          <t>ctps1150801</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -20960,11 +20960,11 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>下崙國小115年度改善偏遠地區國民中小學教師宿舍計畫工程</t>
+          <t>屏東縣潮東國小附設幼兒園115年度充實及改善教學環境設施設備工程採購案</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>3076849</v>
+        <v>3224173</v>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
@@ -20973,7 +20973,7 @@
       </c>
       <c r="J79" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K79" s="4" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
@@ -20998,26 +20998,26 @@
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>國立宜蘭高級中學</t>
+          <t>雲林縣口湖鄉下崙國民小學</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>YLSH-11521</t>
+          <t>A1150923</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>人文館綜合教室整修及活化工程</t>
+          <t>下崙國小115年度改善偏遠地區國民中小學教師宿舍計畫工程</t>
         </is>
       </c>
       <c r="H80" s="11" t="n">
-        <v>3022522</v>
+        <v>3076849</v>
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
       </c>
       <c r="J80" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K80" s="9" t="inlineStr">
@@ -21041,7 +21041,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -21051,12 +21051,12 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公所</t>
+          <t>國立宜蘭高級中學</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>115055</t>
+          <t>YLSH-11521</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -21066,11 +21066,11 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>長安里光復路378-15號旁產業道路拓寬工程</t>
+          <t>人文館綜合教室整修及活化工程</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>3000000</v>
+        <v>3022522</v>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
@@ -21079,7 +21079,7 @@
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -21094,7 +21094,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -21104,12 +21104,12 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>高雄市仁武區八卦國民小學</t>
+          <t>屏東縣屏東市公所</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>115055</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -21119,11 +21119,11 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>高雄市仁武區八卦國民小學附設幼兒園室內外空間改善工程</t>
+          <t>長安里光復路378-15號旁產業道路拓寬工程</t>
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>2962754</v>
+        <v>3000000</v>
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
       </c>
       <c r="J82" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -21157,12 +21157,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>新竹縣寶山鄉雙溪國民小學</t>
+          <t>高雄市仁武區八卦國民小學</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>1150904</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -21172,11 +21172,11 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>新竹縣寶山鄉雙溪國民小學115年度老舊廁所整修工程</t>
+          <t>高雄市仁武區八卦國民小學附設幼兒園室內外空間改善工程</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>2822589</v>
+        <v>2962754</v>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
@@ -21185,7 +21185,7 @@
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -21200,7 +21200,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -21210,12 +21210,12 @@
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>屏東縣萬巒鄉佳佐國民小學</t>
+          <t>新竹縣寶山鄉雙溪國民小學</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>JZ11508</t>
+          <t>1150904</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -21225,11 +21225,11 @@
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>屏東縣萬巒鄉佳佐國民小學114 年度老舊廁所整修工程</t>
+          <t>新竹縣寶山鄉雙溪國民小學115年度老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>2764895</v>
+        <v>2822589</v>
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
       </c>
       <c r="J84" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/02</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
@@ -21253,7 +21253,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -21263,26 +21263,26 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>嘉義縣水上鄉公所</t>
+          <t>屏東縣萬巒鄉佳佐國民小學</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>115A18</t>
+          <t>JZ11508</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>水上鄉南和村及塗溝村道路改善工程</t>
+          <t>屏東縣萬巒鄉佳佐國民小學114 年度老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>2720000</v>
+        <v>2764895</v>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
@@ -21291,7 +21291,7 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -21306,22 +21306,22 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府警察局岡山分局</t>
+          <t>嘉義縣水上鄉公所</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>ks115007</t>
+          <t>115A18</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -21331,11 +21331,11 @@
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>高雄市政府警察局岡山分局資訊機房設備搬遷及建置作業採購案</t>
+          <t>水上鄉南和村及塗溝村道路改善工程</t>
         </is>
       </c>
       <c r="H86" s="11" t="n">
-        <v>2700335</v>
+        <v>2720000</v>
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
@@ -21359,22 +21359,22 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>新北市立江翠國民中學</t>
+          <t>高雄市政府警察局岡山分局</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>J115-0922</t>
+          <t>ks115007</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -21384,11 +21384,11 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>綜合大樓1樓家政教室教學環境設施改善工程第1期</t>
+          <t>高雄市政府警察局岡山分局資訊機房設備搬遷及建置作業採購案</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>2682357</v>
+        <v>2700335</v>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -21412,7 +21412,7 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
@@ -21422,12 +21422,12 @@
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>國立暨南國際大學附屬高級中學</t>
+          <t>新北市立江翠國民中學</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>1150923</t>
+          <t>J115-0922</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -21437,11 +21437,11 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>「115年度汙水及排水系統建置暨改善工程計畫」工程採購</t>
+          <t>綜合大樓1樓家政教室教學環境設施改善工程第1期</t>
         </is>
       </c>
       <c r="H88" s="11" t="n">
-        <v>2582754</v>
+        <v>2682357</v>
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
       </c>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr">
@@ -21465,7 +21465,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -21475,12 +21475,12 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>臺南市山上區公所</t>
+          <t>國立暨南國際大學附屬高級中學</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>NO115033</t>
+          <t>1150923</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -21490,11 +21490,11 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>山上區懷恩堂納骨塔外牆油漆防水及屋簷補強修繕工程</t>
+          <t>「115年度汙水及排水系統建置暨改善工程計畫」工程採購</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>2440515</v>
+        <v>2582754</v>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -21518,7 +21518,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -21528,12 +21528,12 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>新北市雙溪區牡丹國民小學</t>
+          <t>臺南市山上區公所</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>115005-MDPS</t>
+          <t>NO115033</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -21543,11 +21543,11 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>牡丹國小115年度改善偏遠地區國民小學教師宿舍整修工程</t>
+          <t>山上區懷恩堂納骨塔外牆油漆防水及屋簷補強修繕工程</t>
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>2357301</v>
+        <v>2440515</v>
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
@@ -21556,7 +21556,7 @@
       </c>
       <c r="J90" s="12" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K90" s="9" t="inlineStr">
@@ -21571,22 +21571,22 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府消防局</t>
+          <t>新北市雙溪區牡丹國民小學</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>115A10</t>
+          <t>115005-MDPS</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -21596,11 +21596,11 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>115年度本局暨所屬分隊網路監視系統汰換建置採購案</t>
+          <t>牡丹國小115年度改善偏遠地區國民小學教師宿舍整修工程</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>2320000</v>
+        <v>2357301</v>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/02</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -21624,7 +21624,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -21634,26 +21634,26 @@
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司</t>
+          <t>屏東縣政府消防局</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>A0P260911</t>
+          <t>115A10</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>高雄港蓬萊區景觀流動廁所採購案</t>
+          <t>115年度本局暨所屬分隊網路監視系統汰換建置採購案</t>
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>2180500</v>
+        <v>2320000</v>
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
@@ -21662,7 +21662,7 @@
       </c>
       <c r="J92" s="12" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K92" s="9" t="inlineStr">
@@ -21677,36 +21677,36 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>屏東縣立車城國民中學</t>
+          <t>臺灣港務股份有限公司</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>1150922</t>
+          <t>A0P260911</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>屏東縣立車城國民中學-老舊廁所整修工程</t>
+          <t>高雄港蓬萊區景觀流動廁所採購案</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>2172012</v>
+        <v>2180500</v>
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
@@ -21715,7 +21715,7 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/02</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
@@ -21730,7 +21730,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -21740,26 +21740,26 @@
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>基隆市中正區中正國民小學</t>
+          <t>屏東縣立車城國民中學</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>ccps115C014</t>
+          <t>1150922</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>仁愛樓2、3樓廁所整修工程</t>
+          <t>屏東縣立車城國民中學-老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H94" s="11" t="n">
-        <v>2157331</v>
+        <v>2172012</v>
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
@@ -21768,7 +21768,7 @@
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr">
@@ -21783,22 +21783,22 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>海洋委員會海巡署艦隊分署</t>
+          <t>基隆市中正區中正國民小學</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>B115734</t>
+          <t>ccps115C014</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -21808,11 +21808,11 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>第五(高雄)海巡隊PP-3581艇115年度歲修案</t>
+          <t>仁愛樓2、3樓廁所整修工程</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>2100000</v>
+        <v>2157331</v>
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
@@ -21836,22 +21836,22 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>澎湖縣白沙鄉講美國民小學</t>
+          <t>海洋委員會海巡署艦隊分署</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>115-0901</t>
+          <t>B115734</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -21861,11 +21861,11 @@
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>講美國小114-116年公立國民中小學老舊廁所整修工程採購案</t>
+          <t>第五(高雄)海巡隊PP-3581艇115年度歲修案</t>
         </is>
       </c>
       <c r="H96" s="11" t="n">
-        <v>2032914</v>
+        <v>2100000</v>
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
@@ -21874,7 +21874,7 @@
       </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr">
@@ -21889,7 +21889,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -21899,26 +21899,26 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>新北市立江翠國民中學</t>
+          <t>澎湖縣白沙鄉講美國民小學</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>J115-0923</t>
+          <t>115-0901</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>校門口設施改善、交通器材室及周邊設施工程</t>
+          <t>講美國小114-116年公立國民中小學老舊廁所整修工程採購案</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>2016453</v>
+        <v>2032914</v>
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
@@ -21927,7 +21927,7 @@
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -21952,26 +21952,26 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>屏東縣萬巒鄉五溝國民小學</t>
+          <t>新北市立江翠國民中學</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>1150820</t>
+          <t>J115-0923</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>屏東縣萬巒鄉五溝國小114年度老舊廁所整修工程</t>
+          <t>校門口設施改善、交通器材室及周邊設施工程</t>
         </is>
       </c>
       <c r="H98" s="11" t="n">
-        <v>1940400</v>
+        <v>2016453</v>
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
@@ -21980,7 +21980,7 @@
       </c>
       <c r="J98" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
@@ -21995,7 +21995,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -22005,26 +22005,26 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>雲林縣衛生局</t>
+          <t>屏東縣萬巒鄉五溝國民小學</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>11537</t>
+          <t>1150820</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>口湖鄉衛生所屋頂防水及室內修繕工程</t>
+          <t>屏東縣萬巒鄉五溝國小114年度老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>1920831</v>
+        <v>1940400</v>
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
@@ -22033,7 +22033,7 @@
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -22048,7 +22048,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -22058,26 +22058,26 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>屏東縣車城鄉公所</t>
+          <t>雲林縣衛生局</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>1150923</t>
+          <t>11537</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>屏東縣車城鄉保力活動中心暨客家文物館設備改善工程</t>
+          <t>口湖鄉衛生所屋頂防水及室內修繕工程</t>
         </is>
       </c>
       <c r="H100" s="11" t="n">
-        <v>1854117</v>
+        <v>1920831</v>
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">
@@ -22101,7 +22101,7 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
@@ -22111,26 +22111,26 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>臺南市楠西區公所</t>
+          <t>屏東縣車城鄉公所</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>11503016</t>
+          <t>1150923</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>楠西區密枝里新社區邊坡防落石工程</t>
+          <t>屏東縣車城鄉保力活動中心暨客家文物館設備改善工程</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
-        <v>1797451</v>
+        <v>1854117</v>
       </c>
       <c r="I101" s="7" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
       </c>
       <c r="J101" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K101" s="4" t="inlineStr">
@@ -22164,26 +22164,26 @@
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>臺南市佳里區子龍國民小學</t>
+          <t>臺南市楠西區公所</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>ZL115003</t>
+          <t>11503016</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>臺南市子龍國小北棟教室外牆防水工程</t>
+          <t>楠西區密枝里新社區邊坡防落石工程</t>
         </is>
       </c>
       <c r="H102" s="11" t="n">
-        <v>1796378</v>
+        <v>1797451</v>
       </c>
       <c r="I102" s="12" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
       </c>
       <c r="J102" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K102" s="9" t="inlineStr">
@@ -22207,22 +22207,22 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府工務局</t>
+          <t>臺南市佳里區子龍國民小學</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>1151672</t>
+          <t>ZL115003</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -22232,11 +22232,11 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>115年度「個人電腦租賃購置採購案」</t>
+          <t>臺南市子龍國小北棟教室外牆防水工程</t>
         </is>
       </c>
       <c r="H103" s="6" t="n">
-        <v>1631400</v>
+        <v>1796378</v>
       </c>
       <c r="I103" s="7" t="inlineStr">
         <is>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="J103" s="7" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K103" s="4" t="inlineStr">
@@ -22260,36 +22260,36 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>高雄市政府工務局</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>AB1150005505</t>
+          <t>1151672</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>巴爾巴蘭廣場遮陽設施修繕工程</t>
+          <t>115年度「個人電腦租賃購置採購案」</t>
         </is>
       </c>
       <c r="H104" s="11" t="n">
-        <v>1545000</v>
+        <v>1631400</v>
       </c>
       <c r="I104" s="12" t="inlineStr">
         <is>
@@ -22298,7 +22298,7 @@
       </c>
       <c r="J104" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K104" s="9" t="inlineStr">
@@ -22313,7 +22313,7 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
@@ -22323,12 +22323,12 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>國立永靖高級工業職業學校</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>115-17</t>
+          <t>AB1150005505</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -22338,11 +22338,11 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>宜蘭地震災害復建工程採購案</t>
+          <t>巴爾巴蘭廣場遮陽設施修繕工程</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
-        <v>1531022</v>
+        <v>1545000</v>
       </c>
       <c r="I105" s="7" t="inlineStr">
         <is>
@@ -22351,7 +22351,7 @@
       </c>
       <c r="J105" s="7" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K105" s="4" t="inlineStr">
@@ -22366,7 +22366,7 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
@@ -22376,26 +22376,26 @@
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>新北市板橋區後埔國民小學</t>
+          <t>國立永靖高級工業職業學校</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>HP-115A23</t>
+          <t>115-17</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>新北市板橋區後埔國民小學115年度生態園地坪整修工程</t>
+          <t>宜蘭地震災害復建工程採購案</t>
         </is>
       </c>
       <c r="H106" s="11" t="n">
-        <v>1499692</v>
+        <v>1531022</v>
       </c>
       <c r="I106" s="12" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
       </c>
       <c r="K106" s="9" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -22419,22 +22419,22 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>交通部民用航空局高雄國際航空站</t>
+          <t>新北市板橋區後埔國民小學</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>K1151001PWM</t>
+          <t>HP-115A23</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -22444,11 +22444,11 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>高雄國際航空站汰換污水處理廠污泥脫水機</t>
+          <t>新北市板橋區後埔國民小學115年度生態園地坪整修工程</t>
         </is>
       </c>
       <c r="H107" s="6" t="n">
-        <v>1494000</v>
+        <v>1499692</v>
       </c>
       <c r="I107" s="7" t="inlineStr">
         <is>
@@ -22457,7 +22457,7 @@
       </c>
       <c r="J107" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K107" s="4" t="inlineStr">
@@ -22482,12 +22482,12 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>高雄市茂林區公所</t>
+          <t>交通部民用航空局高雄國際航空站</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>115090</t>
+          <t>K1151001PWM</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
@@ -22497,11 +22497,11 @@
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>高雄市茂林區公所115年度「茂林原鄉農林資材轉化與創新經濟推升計畫」機具設備採購案</t>
+          <t>高雄國際航空站汰換污水處理廠污泥脫水機</t>
         </is>
       </c>
       <c r="H108" s="11" t="n">
-        <v>1490000</v>
+        <v>1494000</v>
       </c>
       <c r="I108" s="12" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
       </c>
       <c r="J108" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K108" s="9" t="inlineStr">
@@ -22525,36 +22525,36 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉公所</t>
+          <t>高雄市茂林區公所</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>1151207</t>
+          <t>115090</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>新竹縣尖石鄉梅花村3鄰空間改善工程</t>
+          <t>高雄市茂林區公所115年度「茂林原鄉農林資材轉化與創新經濟推升計畫」機具設備採購案</t>
         </is>
       </c>
       <c r="H109" s="6" t="n">
-        <v>1474194</v>
+        <v>1490000</v>
       </c>
       <c r="I109" s="7" t="inlineStr">
         <is>
@@ -22563,12 +22563,12 @@
       </c>
       <c r="J109" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K109" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -22578,7 +22578,7 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
@@ -22588,26 +22588,26 @@
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>新北市三重區集美國民小學</t>
+          <t>新竹縣尖石鄉公所</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>115-007</t>
+          <t>1151207</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>地下室教學活動空間通風及空調設備改善工程</t>
+          <t>新竹縣尖石鄉梅花村3鄰空間改善工程</t>
         </is>
       </c>
       <c r="H110" s="11" t="n">
-        <v>1430000</v>
+        <v>1474194</v>
       </c>
       <c r="I110" s="12" t="inlineStr">
         <is>
@@ -22616,12 +22616,12 @@
       </c>
       <c r="J110" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K110" s="9" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -22631,7 +22631,7 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
@@ -22641,12 +22641,12 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>臺北市立景美女子高級中學</t>
+          <t>新北市三重區集美國民小學</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>11530</t>
+          <t>115-007</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -22656,11 +22656,11 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>115年度新世代學習空間工程</t>
+          <t>地下室教學活動空間通風及空調設備改善工程</t>
         </is>
       </c>
       <c r="H111" s="6" t="n">
-        <v>1407773</v>
+        <v>1430000</v>
       </c>
       <c r="I111" s="7" t="inlineStr">
         <is>
@@ -22684,7 +22684,7 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
@@ -22694,12 +22694,12 @@
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公所</t>
+          <t>臺北市立景美女子高級中學</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>115062</t>
+          <t>11530</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -22709,11 +22709,11 @@
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>屏東市勝興段752地號排水改善工程</t>
+          <t>115年度新世代學習空間工程</t>
         </is>
       </c>
       <c r="H112" s="11" t="n">
-        <v>1273500</v>
+        <v>1407773</v>
       </c>
       <c r="I112" s="12" t="inlineStr">
         <is>
@@ -22722,7 +22722,7 @@
       </c>
       <c r="J112" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K112" s="9" t="inlineStr">
@@ -22737,7 +22737,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -22747,12 +22747,12 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>臺南市白河區公所</t>
+          <t>屏東縣屏東市公所</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>115064-1</t>
+          <t>115062</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -22762,11 +22762,11 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>白河區溫泉段543地號邊坡改善工程</t>
+          <t>屏東市勝興段752地號排水改善工程</t>
         </is>
       </c>
       <c r="H113" s="6" t="n">
-        <v>1271252</v>
+        <v>1273500</v>
       </c>
       <c r="I113" s="7" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
       </c>
       <c r="J113" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K113" s="4" t="inlineStr">
@@ -22790,7 +22790,7 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -22800,26 +22800,26 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>國立竹南高級中學</t>
+          <t>臺南市白河區公所</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>cnsh115b08</t>
+          <t>115064-1</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>115年化工實習館3樓教室整修工程</t>
+          <t>白河區溫泉段543地號邊坡改善工程</t>
         </is>
       </c>
       <c r="H114" s="11" t="n">
-        <v>1257000</v>
+        <v>1271252</v>
       </c>
       <c r="I114" s="12" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
       </c>
       <c r="J114" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K114" s="9" t="inlineStr">
@@ -22843,7 +22843,7 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
@@ -22853,26 +22853,26 @@
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>新北市三重區碧華國民小學</t>
+          <t>國立竹南高級中學</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>BHES1150924</t>
+          <t>cnsh115b08</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>活動中心2樓地坪整修工程</t>
+          <t>115年化工實習館3樓教室整修工程</t>
         </is>
       </c>
       <c r="H115" s="6" t="n">
-        <v>1216170</v>
+        <v>1257000</v>
       </c>
       <c r="I115" s="7" t="inlineStr">
         <is>
@@ -22896,36 +22896,36 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>新北市三重區碧華國民小學</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>W7A-115-0701-05-2</t>
+          <t>BHES1150924</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>115年度屆(逾)齡水量計委外換裝作業南區(高雄所口徑50~300mm)</t>
+          <t>活動中心2樓地坪整修工程</t>
         </is>
       </c>
       <c r="H116" s="11" t="n">
-        <v>1190576</v>
+        <v>1216170</v>
       </c>
       <c r="I116" s="12" t="inlineStr">
         <is>
@@ -22934,12 +22934,12 @@
       </c>
       <c r="J116" s="12" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="K116" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -22949,36 +22949,36 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>嘉義縣竹崎鄉龍山國民小學</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>lsps11502</t>
+          <t>W7A-115-0701-05-2</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
         <is>
-          <t>第 05 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>嘉義縣龍山國小行政教學樓老舊廁所整修工程</t>
+          <t>115年度屆(逾)齡水量計委外換裝作業南區(高雄所口徑50~300mm)</t>
         </is>
       </c>
       <c r="H117" s="6" t="n">
-        <v>1165131</v>
+        <v>1190576</v>
       </c>
       <c r="I117" s="7" t="inlineStr">
         <is>
@@ -22987,12 +22987,12 @@
       </c>
       <c r="J117" s="7" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K117" s="4" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -23002,7 +23002,7 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
@@ -23012,26 +23012,26 @@
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>經濟部產業園區管理局臺南分局</t>
+          <t>嘉義縣竹崎鄉龍山國民小學</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>30911522</t>
+          <t>lsps11502</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 05 次</t>
         </is>
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>115年台南產業園區道路及附屬設施維護工程</t>
+          <t>嘉義縣龍山國小行政教學樓老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H118" s="11" t="n">
-        <v>1149516</v>
+        <v>1165131</v>
       </c>
       <c r="I118" s="12" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
       </c>
       <c r="J118" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K118" s="9" t="inlineStr">
@@ -23055,36 +23055,36 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>經濟部產業園區管理局臺南分局</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>W7-115-0701-111</t>
+          <t>30911522</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>115年高雄服務所委外發送停水宣傳單</t>
+          <t>115年台南產業園區道路及附屬設施維護工程</t>
         </is>
       </c>
       <c r="H119" s="6" t="n">
-        <v>1120980</v>
+        <v>1149516</v>
       </c>
       <c r="I119" s="7" t="inlineStr">
         <is>
@@ -23093,12 +23093,12 @@
       </c>
       <c r="J119" s="7" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K119" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -23113,17 +23113,17 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>高雄市桃源區建山國民小學</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>js11504</t>
+          <t>W7-115-0701-111</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
@@ -23133,11 +23133,11 @@
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>建山國小側門地坪改善暨教學樓後方排水溝與地面改善等2件工程</t>
+          <t>115年高雄服務所委外發送停水宣傳單</t>
         </is>
       </c>
       <c r="H120" s="11" t="n">
-        <v>988264</v>
+        <v>1120980</v>
       </c>
       <c r="I120" s="12" t="inlineStr">
         <is>
@@ -23146,12 +23146,12 @@
       </c>
       <c r="J120" s="12" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K120" s="9" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -23171,12 +23171,12 @@
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>臺灣高雄地方法院</t>
+          <t>高雄市桃源區建山國民小學</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>115ksd0910</t>
+          <t>js11504</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -23186,11 +23186,11 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>臺灣高雄地方法院115年度高雄簡易庭柏油路面整修工程採購案</t>
+          <t>建山國小側門地坪改善暨教學樓後方排水溝與地面改善等2件工程</t>
         </is>
       </c>
       <c r="H121" s="6" t="n">
-        <v>965880</v>
+        <v>988264</v>
       </c>
       <c r="I121" s="7" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
       </c>
       <c r="J121" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K121" s="4" t="inlineStr">
@@ -23219,17 +23219,17 @@
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>高雄市前鎮區公所</t>
+          <t>臺灣高雄地方法院</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>115046</t>
+          <t>115ksd0910</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
@@ -23239,11 +23239,11 @@
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>高雄市前鎮區115年各里聯誼暨自然生態觀摩及登革熱宣導活動</t>
+          <t>臺灣高雄地方法院115年度高雄簡易庭柏油路面整修工程採購案</t>
         </is>
       </c>
       <c r="H122" s="11" t="n">
-        <v>960000</v>
+        <v>965880</v>
       </c>
       <c r="I122" s="12" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
       </c>
       <c r="J122" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K122" s="9" t="inlineStr">
@@ -23267,7 +23267,7 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
@@ -23277,12 +23277,12 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>高雄市前鎮區公所</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>EM16024P017</t>
+          <t>115046</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -23292,11 +23292,11 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>台南基地除夕餐會</t>
+          <t>高雄市前鎮區115年各里聯誼暨自然生態觀摩及登革熱宣導活動</t>
         </is>
       </c>
       <c r="H123" s="6" t="n">
-        <v>900000</v>
+        <v>960000</v>
       </c>
       <c r="I123" s="7" t="inlineStr">
         <is>
@@ -23305,7 +23305,7 @@
       </c>
       <c r="J123" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K123" s="4" t="inlineStr">
@@ -23325,17 +23325,17 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>臺南市新營區新民國民小學</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>115004</t>
+          <t>EM16024P017</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
@@ -23345,11 +23345,11 @@
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>新民國小停車棚改善工程</t>
+          <t>台南基地除夕餐會</t>
         </is>
       </c>
       <c r="H124" s="11" t="n">
-        <v>895216</v>
+        <v>900000</v>
       </c>
       <c r="I124" s="12" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
       </c>
       <c r="J124" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K124" s="9" t="inlineStr">
@@ -23373,7 +23373,7 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
@@ -23383,12 +23383,12 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>屏東縣萬丹鄉公所</t>
+          <t>臺南市新營區新民國民小學</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>1150805</t>
+          <t>115004</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -23398,11 +23398,11 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>115-萬丹鄉萬生村泉生路擋土牆修復工程</t>
+          <t>新民國小停車棚改善工程</t>
         </is>
       </c>
       <c r="H125" s="6" t="n">
-        <v>889144</v>
+        <v>895216</v>
       </c>
       <c r="I125" s="7" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
       </c>
       <c r="J125" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K125" s="4" t="inlineStr">
@@ -23426,7 +23426,7 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
@@ -23436,12 +23436,12 @@
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>宜蘭縣政府文化局</t>
+          <t>屏東縣萬丹鄉公所</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>L115094901c</t>
+          <t>1150805</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
@@ -23451,11 +23451,11 @@
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>縣定古蹟「羅東鎮聖母醫院耶穌聖心堂」緊急修復工程</t>
+          <t>115-萬丹鄉萬生村泉生路擋土牆修復工程</t>
         </is>
       </c>
       <c r="H126" s="11" t="n">
-        <v>848025</v>
+        <v>889144</v>
       </c>
       <c r="I126" s="12" t="inlineStr">
         <is>
@@ -23464,7 +23464,7 @@
       </c>
       <c r="J126" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K126" s="9" t="inlineStr">

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-26 09:48</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-26 17:27</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-26 09:48</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-26 17:27</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-26 17:27</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-27 09:38</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-26 17:27</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-27 09:38</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-27 09:38</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-27 18:06</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-27 09:38</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-27 18:06</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-27 18:06</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-28 09:51</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-27 18:06</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-28 09:51</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-28 09:51</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-09-28 19:06</t>
         </is>
       </c>
     </row>
@@ -16840,7 +16840,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-28 09:51</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-09-28 19:06</t>
         </is>
       </c>
     </row>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣政府文化局</t>
+          <t>國立二林高級工商職業學校</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>L115094901c</t>
+          <t>ELVS1150701</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -16932,11 +16932,11 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>縣定古蹟「羅東鎮聖母醫院耶穌聖心堂」緊急修復工程</t>
+          <t>活動中心屋頂防水工程</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
-        <v>848025</v>
+        <v>3538564</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -16945,12 +16945,12 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/02</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -16960,7 +16960,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -16970,40 +16970,40 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>宜蘭縣政府文化局</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>111508022</t>
+          <t>L115094901c</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>Danas-F-06-02-08-白河區頭前溪甘宅橋改建工程及Danas-F-06-02-08-白河區南86線頭前溪橋改建工程</t>
+          <t>縣定古蹟「羅東鎮聖母醫院耶穌聖心堂」緊急修復工程</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>267712133</v>
+        <v>848025</v>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
-          <t>115/09/29</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -17013,36 +17013,36 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>財團法人國家衛生研究院</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>115A0D0272</t>
+          <t>111508022</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>「BP2/NIDB工程」- E棟高防護實驗室儀器設備採購案</t>
+          <t>Danas-F-06-02-08-白河區頭前溪甘宅橋改建工程及Danas-F-06-02-08-白河區南86線頭前溪橋改建工程</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>165894325</v>
+        <v>267712133</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -17051,7 +17051,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -17066,22 +17066,22 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>高雄市兵役處</t>
+          <t>財團法人國家衛生研究院</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>1150922</t>
+          <t>115A0D0272</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -17091,11 +17091,11 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>高雄市115年軍人忠靈祠鳥松園區櫃位整修工程</t>
+          <t>「BP2/NIDB工程」- E棟高防護實驗室儀器設備採購案</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>18049966</v>
+        <v>165894325</v>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -17119,7 +17119,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -17129,12 +17129,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>新竹縣北埔鄉公所</t>
+          <t>高雄市兵役處</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>115A004</t>
+          <t>1150922</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -17144,11 +17144,11 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>北埔鄉大湖村、南埔村、大林村、水磜村等11處道路災害復建工程</t>
+          <t>高雄市115年軍人忠靈祠鳥松園區櫃位整修工程</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>17217692</v>
+        <v>18049966</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -17157,7 +17157,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -17172,7 +17172,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -17182,12 +17182,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市建國國民小學</t>
+          <t>新竹縣北埔鄉公所</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>HS115006</t>
+          <t>115A004</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -17197,11 +17197,11 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>苗栗縣建國國小115年度校舍油漆粉刷工程</t>
+          <t>北埔鄉大湖村、南埔村、大林村、水磜村等11處道路災害復建工程</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>12609155</v>
+        <v>17217692</v>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -17225,7 +17225,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -17235,26 +17235,26 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>國立高雄科技大學</t>
+          <t>苗栗縣頭份市建國國民小學</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1131112002</t>
+          <t>HS115006</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>第 14 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>建工校區雙科館7樓及屋頂外牆整修工程</t>
+          <t>苗栗縣建國國小115年度校舍油漆粉刷工程</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>12120800</v>
+        <v>12609155</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -17278,7 +17278,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -17288,26 +17288,26 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>宜蘭縣南澳鄉公所</t>
+          <t>國立高雄科技大學</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>B115-17</t>
+          <t>1131112002</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 14 次</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>澳花上部落排水改善工程</t>
+          <t>建工校區雙科館7樓及屋頂外牆整修工程</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>8091597</v>
+        <v>12120800</v>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
@@ -17316,7 +17316,7 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -17331,22 +17331,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>宜蘭縣南澳鄉公所</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1155027844</t>
+          <t>B115-17</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -17356,11 +17356,11 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>臺東工務段利家監工站轄區116年度預約經常性路面清掃維護工作</t>
+          <t>澳花上部落排水改善工程</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>7857136</v>
+        <v>8091597</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -17369,7 +17369,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -17384,22 +17384,22 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>彰化縣鹿港鎮鹿港國民小學</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>LG115E</t>
+          <t>1155027844</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -17409,11 +17409,11 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>鹿港國小既設水電系統遷移工程</t>
+          <t>臺東工務段利家監工站轄區116年度預約經常性路面清掃維護工作</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>7423795</v>
+        <v>7857136</v>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
@@ -17422,7 +17422,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -17437,7 +17437,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -17447,12 +17447,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>新竹縣新豐鄉公所</t>
+          <t>彰化縣鹿港鎮鹿港國民小學</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>HE115705</t>
+          <t>LG115E</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -17462,11 +17462,11 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>新豐鄉綠景莊園網球場整修工程</t>
+          <t>鹿港國小既設水電系統遷移工程</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>6305735</v>
+        <v>7423795</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -17475,7 +17475,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -17490,7 +17490,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -17500,26 +17500,26 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺東分署</t>
+          <t>新竹縣新豐鄉公所</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>115-FR-19-5-013</t>
+          <t>HE115705</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>農東成208支線及忠孝里周遭農路改善工程</t>
+          <t>新豐鄉綠景莊園網球場整修工程</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
-        <v>6268603</v>
+        <v>6305735</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -17543,7 +17543,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -17553,26 +17553,26 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣海洋及漁業發展所</t>
+          <t>農業部農村發展及水土保持署臺東分署</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>1150828</t>
+          <t>115-FR-19-5-013</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>115年度宜蘭縣養殖漁業生產區環境清理及公共設施維護修繕工程(開口契約)</t>
+          <t>農東成208支線及忠孝里周遭農路改善工程</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>5142000</v>
+        <v>6268603</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -17581,7 +17581,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -17596,7 +17596,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -17606,12 +17606,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>財團法人工業技術研究院</t>
+          <t>宜蘭縣海洋及漁業發展所</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>A712000687</t>
+          <t>1150828</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -17621,11 +17621,11 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>「無人化創新科技實驗室-快速試製廠房建置」基地整地喬木移植工程</t>
+          <t>115年度宜蘭縣養殖漁業生產區環境清理及公共設施維護修繕工程(開口契約)</t>
         </is>
       </c>
       <c r="H16" s="11" t="n">
-        <v>3000000</v>
+        <v>5142000</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
@@ -17659,12 +17659,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>南投縣南投市光華國民小學</t>
+          <t>財團法人工業技術研究院</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>115009SE</t>
+          <t>A712000687</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -17674,11 +17674,11 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>光華國小向陽樓無障礙電梯整建工程</t>
+          <t>「無人化創新科技實驗室-快速試製廠房建置」基地整地喬木移植工程</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>2853055</v>
+        <v>3000000</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -17712,26 +17712,26 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣立新港國民中小學</t>
+          <t>南投縣南投市光華國民小學</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>1150904</t>
+          <t>115009SE</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>學校圖書館空間整修工程</t>
+          <t>光華國小向陽樓無障礙電梯整建工程</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
-        <v>2655702</v>
+        <v>2853055</v>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -17765,12 +17765,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>臺中市霧峰區霧峰國民小學</t>
+          <t>苗栗縣立新港國民中小學</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>115YUGU</t>
+          <t>1150904</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -17780,11 +17780,11 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>臺中市霧峰區霧峰國小新設第2座兒童遊戲場工程採購案</t>
+          <t>學校圖書館空間整修工程</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>1793611</v>
+        <v>2655702</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -17808,7 +17808,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -17818,12 +17818,12 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>桃園市立大園幼兒園</t>
+          <t>臺中市霧峰區霧峰國民小學</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>DY11509</t>
+          <t>115YUGU</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -17833,11 +17833,11 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>桃園市立大園幼兒園三和分班電力改善工程</t>
+          <t>臺中市霧峰區霧峰國小新設第2座兒童遊戲場工程採購案</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
-        <v>1290998</v>
+        <v>1793611</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
@@ -17846,12 +17846,12 @@
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -17861,36 +17861,36 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>桃園市立大園幼兒園</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>1155026686</t>
+          <t>DY11509</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>116年度鳳屏工務段文書檔案管理工作</t>
+          <t>桃園市立大園幼兒園三和分班電力改善工程</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>1156284</v>
+        <v>1290998</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -17899,7 +17899,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -17914,22 +17914,22 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>臺南市新市區大社國民小學</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>dashe115008</t>
+          <t>1155026686</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -17939,11 +17939,11 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>臺南市大社國小115年附設幼兒園盥洗室改善工程</t>
+          <t>116年度鳳屏工務段文書檔案管理工作</t>
         </is>
       </c>
       <c r="H22" s="11" t="n">
-        <v>1071857</v>
+        <v>1156284</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -17967,7 +17967,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -17977,12 +17977,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>臺中市立豐原商業高級中等學校</t>
+          <t>臺南市新市區大社國民小學</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>115022</t>
+          <t>dashe115008</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -17992,11 +17992,11 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>豐原高商宿舍及浴廁環境改善工程</t>
+          <t>臺南市大社國小115年附設幼兒園盥洗室改善工程</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>1059933</v>
+        <v>1071857</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -18020,7 +18020,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -18030,12 +18030,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>高雄市大樹區大樹國民小學</t>
+          <t>臺中市立豐原商業高級中等學校</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>dsp1150901</t>
+          <t>115022</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -18045,11 +18045,11 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>偏遠地區學校及非山非市學校設施設備計畫工程案。</t>
+          <t>豐原高商宿舍及浴廁環境改善工程</t>
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>916922</v>
+        <v>1059933</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
@@ -18073,7 +18073,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -18083,12 +18083,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>國立虎尾科技大學</t>
+          <t>高雄市大樹區大樹國民小學</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>1150920</t>
+          <t>dsp1150901</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -18098,11 +18098,11 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>綠能材料低碳製程教學場域優化工程</t>
+          <t>偏遠地區學校及非山非市學校設施設備計畫工程案。</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>842400</v>
+        <v>916922</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -18136,12 +18136,12 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>基隆市公共汽車管理處</t>
+          <t>國立虎尾科技大學</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>115A104</t>
+          <t>1150920</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -18151,11 +18151,11 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>和平島智慧型候車亭增建工程</t>
+          <t>綠能材料低碳製程教學場域優化工程</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>654302</v>
+        <v>842400</v>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
@@ -18164,7 +18164,7 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
@@ -18179,7 +18179,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -18189,26 +18189,26 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>新北市瑞芳區九份國民小學</t>
+          <t>基隆市公共汽車管理處</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>jfes2026-09-09</t>
+          <t>115A104</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>115年度改善偏遠地區國民中小學教師宿舍工程</t>
+          <t>和平島智慧型候車亭增建工程</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>651370</v>
+        <v>654302</v>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
@@ -18217,7 +18217,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -18247,21 +18247,21 @@
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>jfes2026-09-13</t>
+          <t>jfes2026-09-09</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>幼兒園教室地坪工程</t>
+          <t>115年度改善偏遠地區國民中小學教師宿舍工程</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>439920</v>
+        <v>651370</v>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
@@ -18270,7 +18270,7 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/02</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -18285,22 +18285,22 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公所</t>
+          <t>新北市瑞芳區九份國民小學</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>115212</t>
+          <t>jfes2026-09-13</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -18310,11 +18310,11 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>115年度屏東市公園監視系統設置</t>
+          <t>幼兒園教室地坪工程</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>207700</v>
+        <v>439920</v>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
@@ -18323,7 +18323,7 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
@@ -18338,22 +18338,22 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>屏東縣屏東市公所</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>1150806C0146</t>
+          <t>115212</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -18363,25 +18363,25 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>臺北市大安區金華特四基地行政大樓新建工程</t>
+          <t>115年度屏東市公園監視系統設置</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>1108616262</v>
+        <v>207700</v>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
-          <t>115/09/24</t>
+          <t>115/09/29</t>
         </is>
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -18391,7 +18391,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -18401,26 +18401,26 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉公所</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>1150902</t>
+          <t>1150806C0146</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>古坑鄉多功能社會福利大樓興建工程</t>
+          <t>臺北市大安區金華特四基地行政大樓新建工程</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>95076841</v>
+        <v>1108616262</v>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
@@ -18429,7 +18429,7 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
@@ -18444,7 +18444,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -18454,12 +18454,12 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第六區管理處</t>
+          <t>雲林縣古坑鄉公所</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>RC-115-0601-0038</t>
+          <t>1150902</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -18469,11 +18469,11 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>歸仁區中山路一段汰換管線工程(二)</t>
+          <t>古坑鄉多功能社會福利大樓興建工程</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>47356103</v>
+        <v>95076841</v>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -18507,26 +18507,26 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>台灣自來水股份有限公司第六區管理處</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>115-117</t>
+          <t>RC-115-0601-0038</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>116年度苗栗段轄區省道路面零星及擇要修復工程(開口契約)</t>
+          <t>歸仁區中山路一段汰換管線工程(二)</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>46968385</v>
+        <v>47356103</v>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
@@ -18535,7 +18535,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -18560,26 +18560,26 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>國立勤益科技大學</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>CY1154-010</t>
+          <t>115-117</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>將軍道及校內停車場整建工程</t>
+          <t>116年度苗栗段轄區省道路面零星及擇要修復工程(開口契約)</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>43020000</v>
+        <v>46968385</v>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-02 18:37</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-03 10:12</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>高雄市立圓富國民中學</t>
+          <t>國立臺北科技大學附屬桃園農工高級中等學校</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>115-004</t>
+          <t>tyai115043</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -688,11 +688,11 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>高雄市圓富國中運動場及周邊設施整建工程委託設計監造技術服務</t>
+          <t>汙水下水道工程第一期委託監造技術服務案</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>740000</v>
+        <v>801000</v>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
@@ -701,7 +701,7 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/14</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>高雄市桃源區樟山國民小學</t>
+          <t>高雄市立圓富國民中學</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>ZAS11507</t>
+          <t>115-004</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -741,11 +741,11 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>復興分班運動場跑道整建工程委託規畫設計監造技術服務採購案</t>
+          <t>高雄市圓富國中運動場及周邊設施整建工程委託設計監造技術服務</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>456922</v>
+        <v>740000</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -754,7 +754,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -769,22 +769,22 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>臺中市政府捷運工程局</t>
+          <t>高雄市桃源區樟山國民小學</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>11508250050</t>
+          <t>ZAS11507</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -794,25 +794,25 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>臺中捷運藍線建設計畫BC21標土建及設施機電工程</t>
+          <t>復興分班運動場跑道整建工程委託規畫設計監造技術服務採購案</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>13908824895</v>
+        <v>456922</v>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -822,22 +822,22 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會新竹科學園區管理局</t>
+          <t>臺中市政府捷運工程局</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>F1150801</t>
+          <t>11508250050</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -847,11 +847,11 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>新竹科學園區新四期C棟標準廠房新建工程規劃設計及監造工作標案</t>
+          <t>臺中捷運藍線建設計畫BC21標土建及設施機電工程</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>234095737</v>
+        <v>13908824895</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -860,12 +860,12 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>115/10/19</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>國家科學及技術委員會新竹科學園區管理局</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>115-508</t>
+          <t>F1150801</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -900,11 +900,11 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>115~119年度谷關工務段轄區省道地錨檢測、監測、安全評估及委託設計服務工作</t>
+          <t>新竹科學園區新四期C棟標準廠房新建工程規劃設計及監造工作標案</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>108563129</v>
+        <v>234095737</v>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
@@ -913,7 +913,7 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/10/19</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
@@ -938,26 +938,26 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>交通部鐵道局中部工程分局</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>115-B-Z-001</t>
+          <t>115-508</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>第 05 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>代辦臺鐵公司「石榴班溪橋及八掌溪橋改建工程」委託規劃、設計及監造技術服務</t>
+          <t>115~119年度谷關工務段轄區省道地錨檢測、監測、安全評估及委託設計服務工作</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>97680908</v>
+        <v>108563129</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
@@ -991,26 +991,26 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>交通部鐵道局中部工程分局</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>115-608</t>
+          <t>115-B-Z-001</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 05 次</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>115~118年度中分局埔里段轄區地錨邊坡定期檢測、補充調查及補強設計服務工作</t>
+          <t>代辦臺鐵公司「石榴班溪橋及八掌溪橋改建工程」委託規劃、設計及監造技術服務</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>73650913</v>
+        <v>97680908</v>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -1044,26 +1044,26 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1151209SC022</t>
+          <t>115-608</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>「臺北市立大安國中校舍新建工程（第二期）」委託規劃設計及監造技術服務</t>
+          <t>115~118年度中分局埔里段轄區地錨邊坡定期檢測、補充調查及補強設計服務工作</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>52974000</v>
+        <v>73650913</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>A061-1150831-2</t>
+          <t>1151209SC022</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1112,11 +1112,11 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>屏東縣屏東市糖業園區市地重劃工程委託設計監造技術服務案</t>
+          <t>「臺北市立大安國中校舍新建工程（第二期）」委託規劃設計及監造技術服務</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>25200000</v>
+        <v>52974000</v>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
@@ -1125,7 +1125,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>115FA03907657000100</t>
+          <t>A061-1150831-2</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -1165,11 +1165,11 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>「TA專案」專案管理委託技術服務</t>
+          <t>屏東縣屏東市糖業園區市地重劃工程委託設計監造技術服務案</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>22209975</v>
+        <v>25200000</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>115/10/30</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>國立傳統藝術中心</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>1152221</t>
+          <t>115FA03907657000100</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -1218,11 +1218,11 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>116年高雄園區營運規劃委託專業服務採購案</t>
+          <t>「TA專案」專案管理委託技術服務</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
-        <v>20000000</v>
+        <v>22209975</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
@@ -1231,7 +1231,7 @@
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/30</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -1246,7 +1246,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -1256,26 +1256,26 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>國立傳統藝術中心</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>B057-1150720-1B</t>
+          <t>1152221</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>潮州親子館委託經營管理服務方案</t>
+          <t>116年高雄園區營運規劃委託專業服務採購案</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>19937000</v>
+        <v>20000000</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>衛生福利部</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>M1506440</t>
+          <t>B057-1150720-1B</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -1324,11 +1324,11 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>115年度「蘭嶼健康檢查全人照護專案管理計畫」</t>
+          <t>潮州親子館委託經營管理服務方案</t>
         </is>
       </c>
       <c r="H16" s="11" t="n">
-        <v>14500000</v>
+        <v>19937000</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
@@ -1352,7 +1352,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -1362,26 +1362,26 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣頭城鎮公所</t>
+          <t>衛生福利部</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>TA1150915</t>
+          <t>M1506440</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>115年頭城鎮社福教育館新建工程委託規劃設計監造技術服務案</t>
+          <t>115年度「蘭嶼健康檢查全人照護專案管理計畫」</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>12567380</v>
+        <v>14500000</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>115/10/19</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -1415,26 +1415,26 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>臺南市肉品市場股份有限公司</t>
+          <t>宜蘭縣頭城鎮公所</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>1150901</t>
+          <t>TA1150915</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>設置新式毛豬屠宰場-設計監造暨委託規劃公共工程審議計畫</t>
+          <t>115年頭城鎮社福教育館新建工程委託規劃設計監造技術服務案</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
-        <v>11475000</v>
+        <v>12567380</v>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
@@ -1443,12 +1443,12 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/19</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -1468,26 +1468,26 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府水利局</t>
+          <t>臺南市肉品市場股份有限公司</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>B1150830</t>
+          <t>1150901</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>後勁溪仁武橋疏洪道治理工程委託設計技術服務</t>
+          <t>設置新式毛豬屠宰場-設計監造暨委託規劃公共工程審議計畫</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>11349000</v>
+        <v>11475000</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -1496,12 +1496,12 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>115/10/13</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -1511,36 +1511,36 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>臺南市立博物館</t>
+          <t>高雄市政府水利局</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>115TCM11E</t>
+          <t>B1150830</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>噍吧哖文化園區A北棟、A南棟、B+D棟、E棟場館耐震補強工程</t>
+          <t>後勁溪仁武橋疏洪道治理工程委託設計技術服務</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
-        <v>11290473</v>
+        <v>11349000</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
@@ -1549,12 +1549,12 @@
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/10/13</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -1564,36 +1564,36 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中央/海軍</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>國防部海軍司令部</t>
+          <t>臺南市立博物館</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>115PI51600000010700</t>
+          <t>115TCM11E</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>115-117年度海軍單位工程委託設計技術服務開口契約</t>
+          <t>噍吧哖文化園區A北棟、A南棟、B+D棟、E棟場館耐震補強工程</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>9860000</v>
+        <v>11290473</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>115/10/13</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/海軍</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -1627,12 +1627,12 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>國防部海軍司令部</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>TT115E05</t>
+          <t>115PI51600000010700</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -1642,11 +1642,11 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>115-117年度農田水利署臺東管理處生態檢核作業委託服務(開口契約)</t>
+          <t>115-117年度海軍單位工程委託設計技術服務開口契約</t>
         </is>
       </c>
       <c r="H22" s="11" t="n">
-        <v>9700000</v>
+        <v>9860000</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>115/10/14</t>
+          <t>115/10/13</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -1670,7 +1670,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>141-F1150909-2</t>
+          <t>TT115E05</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -1695,11 +1695,11 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>牛埔溪排水治理工程 (萬華橋上游~牛埔橋)(含橋梁改建)委託設計及後續擴充監造技術服務</t>
+          <t>115-117年度農田水利署臺東管理處生態檢核作業委託服務(開口契約)</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>8920000</v>
+        <v>9700000</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -1723,36 +1723,36 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>雲林縣古坑鄉公所</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>115091501</t>
+          <t>141-F1150909-2</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>古坑鄉崎坪坵示範公墓納骨塔耐震補強工程</t>
+          <t>牛埔溪排水治理工程 (萬華橋上游~牛埔橋)(含橋梁改建)委託設計及後續擴充監造技術服務</t>
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>8300000</v>
+        <v>8920000</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/10/14</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -1776,36 +1776,36 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司基隆港務分公司</t>
+          <t>雲林縣古坑鄉公所</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>A1W260081</t>
+          <t>115091501</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>基隆港東岸基隆港務警察總隊辦公廳舍拆除工程監造暨新抽水站設計監造委託技術服務</t>
+          <t>古坑鄉崎坪坵示範公墓納骨塔耐震補強工程</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>7195200</v>
+        <v>8300000</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -1814,12 +1814,12 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>115/10/14</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -1829,7 +1829,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>臺灣港務股份有限公司基隆港務分公司</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>C1150923-1</t>
+          <t>A1W260081</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -1854,11 +1854,11 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮、東港鎮行人及高齡友善示範區規劃案</t>
+          <t>基隆港東岸基隆港務警察總隊辦公廳舍拆除工程監造暨新抽水站設計監造委託技術服務</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>7124000</v>
+        <v>7195200</v>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/14</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -1892,12 +1892,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>115-314</t>
+          <t>C1150923-1</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -1907,11 +1907,11 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>台1線第三溪州橋改建工程委託監造(含簽證)技術服務工作</t>
+          <t>屏東縣潮州鎮、東港鎮行人及高齡友善示範區規劃案</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>6780816</v>
+        <v>7124000</v>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>A073-1151001-1</t>
+          <t>115-314</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -1960,11 +1960,11 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>116年度屏東縣公共設施管線圖資品質提升暨系統整合應用建置計畫-委託建置案</t>
+          <t>台1線第三溪州橋改建工程委託監造(含簽證)技術服務工作</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>6600000</v>
+        <v>6780816</v>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -1988,7 +1988,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -1998,12 +1998,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府環境保護局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>11531003</t>
+          <t>A073-1151001-1</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -2013,11 +2013,11 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>臺南市廚餘再利用處理設施促參案前期規劃暨專案管理服務計畫</t>
+          <t>116年度屏東縣公共設施管線圖資品質提升暨系統整合應用建置計畫-委託建置案</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>6000000</v>
+        <v>6600000</v>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -2041,7 +2041,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>交通部觀光署茂林國家風景區管理處</t>
+          <t>臺南市政府環境保護局</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>115010509</t>
+          <t>11531003</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>高雄市圓山段4-1地號土地民間參與營運移轉前置作業委託服務案</t>
+          <t>臺南市廚餘再利用處理設施促參案前期規劃暨專案管理服務計畫</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>115/10/15</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
@@ -2094,36 +2094,36 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>南投縣竹山鎮公所</t>
+          <t>交通部觀光署茂林國家風景區管理處</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>115056</t>
+          <t>115010509</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>竹山鎮延正社區活動中心耐震補強</t>
+          <t>高雄市圓山段4-1地號土地民間參與營運移轉前置作業委託服務案</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>4970000</v>
+        <v>6000000</v>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/15</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -2147,36 +2147,36 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>衛生福利部臺北醫院</t>
+          <t>南投縣竹山鎮公所</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>TPH-2874-11532</t>
+          <t>115056</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>2026台灣醫療科技展-展佈設計</t>
+          <t>竹山鎮延正社區活動中心耐震補強</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>4000000</v>
+        <v>4970000</v>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
@@ -2185,12 +2185,12 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>115/10/13</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -2210,12 +2210,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>衛生福利部臺北醫院</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>115211</t>
+          <t>TPH-2874-11532</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -2225,7 +2225,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>苗栗縣政府115年度消防人力動員演習及教育訓練專案管理勞務委託服務案</t>
+          <t>2026台灣醫療科技展-展佈設計</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/13</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
@@ -2253,22 +2253,22 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>新北市立鶯歌高級工商職業學校</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>yk1151024</t>
+          <t>115211</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -2278,11 +2278,11 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>陶工科雙美未計畫空間設計裝修統包工程採購案</t>
+          <t>苗栗縣政府115年度消防人力動員演習及教育訓練專案管理勞務委託服務案</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>3272157</v>
+        <v>4000000</v>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -2306,22 +2306,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>臺南市鹽水區公所</t>
+          <t>新北市立鶯歌高級工商職業學校</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>1151001</t>
+          <t>yk1151024</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -2331,11 +2331,11 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>116年度鹽水區水利工程委託測設監造案開口契約</t>
+          <t>陶工科雙美未計畫空間設計裝修統包工程採購案</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>3100000</v>
+        <v>3272157</v>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>115/10/14</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -2359,7 +2359,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>財團法人桃園市原住民族發展基金會</t>
+          <t>臺南市鹽水區公所</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>1150929-1</t>
+          <t>1151001</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -2384,11 +2384,11 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>「2026MASA&amp;#39;OPO藝術節－音樂現場展演硬體設計與執行」委託服務採購案</t>
+          <t>116年度鹽水區水利工程委託測設監造案開口契約</t>
         </is>
       </c>
       <c r="H36" s="11" t="n">
-        <v>2500000</v>
+        <v>3100000</v>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
@@ -2397,7 +2397,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/14</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -2422,12 +2422,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>嘉義縣消防局</t>
+          <t>財團法人桃園市原住民族發展基金會</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>115059</t>
+          <t>1150929-1</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>115年度消防人力動員教育訓練及演練專案管理勞務委託服務</t>
+          <t>「2026MASA&amp;#39;OPO藝術節－音樂現場展演硬體設計與執行」委託服務採購案</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
@@ -2450,7 +2450,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>115/10/13</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -2475,26 +2475,26 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>交通部民用航空局金門航空站</t>
+          <t>嘉義縣消防局</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>KMA-L116-A01</t>
+          <t>115059</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>金門機場空側設施維護設計監造及巡查評估等委託技術服務(116-117)</t>
+          <t>115年度消防人力動員教育訓練及演練專案管理勞務委託服務</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>2491020</v>
+        <v>2500000</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
@@ -2518,36 +2518,36 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>新北市立鶯歌高級工商職業學校</t>
+          <t>交通部民用航空局金門航空站</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>yk1150716-1</t>
+          <t>KMA-L116-A01</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>新北市AI應用與數位設計中心空間設計裝修統包工程採購案</t>
+          <t>金門機場空側設施維護設計監造及巡查評估等委託技術服務(116-117)</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>2056710</v>
+        <v>2491020</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
@@ -2556,12 +2556,12 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/13</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -2571,22 +2571,22 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>國立臺灣博物館</t>
+          <t>新北市立鶯歌高級工商職業學校</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>NTM115011a</t>
+          <t>yk1150716-1</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -2596,11 +2596,11 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>臺博天光─穹頂廊道整修計畫─可行性方案評估暨先期規劃及基本設計案</t>
+          <t>新北市AI應用與數位設計中心空間設計裝修統包工程採購案</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>1900000</v>
+        <v>2056710</v>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
@@ -2609,12 +2609,12 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>115/10/15</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>國立臺灣博物館</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>C1151001-2</t>
+          <t>NTM115011a</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -2649,11 +2649,11 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>屏東縣112年度土壤液化調查與風險評估計畫專案顧問</t>
+          <t>臺博天光─穹頂廊道整修計畫─可行性方案評估暨先期規劃及基本設計案</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>1840000</v>
+        <v>1900000</v>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/15</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
@@ -2677,7 +2677,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -2687,12 +2687,12 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府農業局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>KCT004</t>
+          <t>C1151001-2</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -2702,11 +2702,11 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>(Danas-H-01-07-8-1)高雄市桃源區高中里春風農路災後復建工程計畫-工程委託設計監造</t>
+          <t>屏東縣112年度土壤液化調查與風險評估計畫專案顧問</t>
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>1800000</v>
+        <v>1840000</v>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>115/10/13</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
@@ -2730,36 +2730,36 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>屏東縣竹田鄉公所</t>
+          <t>高雄市政府農業局</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>115Q001-1</t>
+          <t>KCT004</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>糶糴村集會所耐震能力補強工程</t>
+          <t>(Danas-H-01-07-8-1)高雄市桃源區高中里春風農路災後復建工程計畫-工程委託設計監造</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>1716170</v>
+        <v>1800000</v>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
@@ -2768,12 +2768,12 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/13</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -2783,36 +2783,36 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>新北市板橋區公所</t>
+          <t>屏東縣竹田鄉公所</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>E116001</t>
+          <t>115Q001-1</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>116年新北市板橋區公園兒童遊戲場暨體健設施改善維護工程委託設計監造技術服務</t>
+          <t>糶糴村集會所耐震能力補強工程</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>1600000</v>
+        <v>1716170</v>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K44" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2846,26 +2846,26 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司基隆港務分公司</t>
+          <t>新北市板橋區公所</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>A1S260761</t>
+          <t>E116001</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>基隆港橋式貨櫃起重機整修委託監督技術服務</t>
+          <t>116年新北市板橋區公園兒童遊戲場暨體健設施改善維護工程委託設計監造技術服務</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>1400000</v>
+        <v>1600000</v>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
@@ -2874,12 +2874,12 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>115/10/15</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -2889,7 +2889,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>中央/中油</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -2899,26 +2899,26 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司</t>
+          <t>臺灣港務股份有限公司基隆港務分公司</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>MAC1500008</t>
+          <t>A1S260761</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>國光診所與僱員單身宿舍區用電申請與變電站規劃委託設計監造技術服務</t>
+          <t>基隆港橋式貨櫃起重機整修委託監督技術服務</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>1342499</v>
+        <v>1400000</v>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>115/10/19</t>
+          <t>115/10/15</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
@@ -2942,7 +2942,7 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>中央/中油</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
@@ -2952,12 +2952,12 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>臺北市信義區吳興國民小學</t>
+          <t>台灣中油股份有限公司</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>115021</t>
+          <t>MAC1500008</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -2967,11 +2967,11 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>教學大樓新建工程安置計畫—機水電消防設施搬遷改善第二期工程委託設計監造技術服務</t>
+          <t>國光診所與僱員單身宿舍區用電申請與變電站規劃委託設計監造技術服務</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>1326553</v>
+        <v>1342499</v>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/10/19</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -2995,36 +2995,36 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>國營臺灣鐵路股份有限公司</t>
+          <t>臺北市信義區吳興國民小學</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>L0515C1025J</t>
+          <t>115021</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>銅鑼隧道電力設備周邊結構修復工程</t>
+          <t>教學大樓新建工程安置計畫—機水電消防設施搬遷改善第二期工程委託設計監造技術服務</t>
         </is>
       </c>
       <c r="H48" s="11" t="n">
-        <v>1305369</v>
+        <v>1326553</v>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -3048,36 +3048,36 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>國營臺灣鐵路股份有限公司</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>E1151001-1</t>
+          <t>L0515C1025J</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>屏東縣潮青暨客青基地工程動土典禮勞務委託</t>
+          <t>銅鑼隧道電力設備周邊結構修復工程</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>1200000</v>
+        <v>1305369</v>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
@@ -3086,12 +3086,12 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>115/10/07</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -3111,12 +3111,12 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣立美崙國民中學</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>115-05</t>
+          <t>E1151001-1</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -3126,11 +3126,11 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>美崙國中污水接管工程委託設計監造</t>
+          <t>屏東縣潮青暨客青基地工程動土典禮勞務委託</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>1150000</v>
+        <v>1200000</v>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>115/10/14</t>
+          <t>115/10/07</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -3164,12 +3164,12 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>內政部國家公園署海洋國家公園管理處</t>
+          <t>花蓮縣立美崙國民中學</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>115201</t>
+          <t>115-05</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -3179,11 +3179,11 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>海管處新建遊客中心室內裝修工程委託規劃設計與監造技術服務案</t>
+          <t>美崙國中污水接管工程委託設計監造</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>1067360</v>
+        <v>1150000</v>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>115/10/12</t>
+          <t>115/10/14</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -3217,12 +3217,12 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>臺中市西屯區大鵬國民小學</t>
+          <t>內政部國家公園署海洋國家公園管理處</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>dpes1151013</t>
+          <t>115201</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -3232,11 +3232,11 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>臺中市清溪計畫-水質改善執行子計畫大鵬國小污水納管校內接管工程委託設計監造技術服務</t>
+          <t>海管處新建遊客中心室內裝修工程委託規劃設計與監造技術服務案</t>
         </is>
       </c>
       <c r="H52" s="11" t="n">
-        <v>1043337</v>
+        <v>1067360</v>
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>彰化縣福興鄉公所</t>
+          <t>臺中市西屯區大鵬國民小學</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>115054</t>
+          <t>dpes1151013</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -3285,11 +3285,11 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>福興鄉老人文康中心修繕、福興鄉立幼兒園廁所整修等二案委託設計監造技術服務</t>
+          <t>臺中市清溪計畫-水質改善執行子計畫大鵬國小污水納管校內接管工程委託設計監造技術服務</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>1043219</v>
+        <v>1043337</v>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
@@ -3298,7 +3298,7 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/10/12</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -3313,7 +3313,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -3323,12 +3323,12 @@
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>新北市土城區公所</t>
+          <t>彰化縣福興鄉公所</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>11509A049</t>
+          <t>115054</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -3338,11 +3338,11 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>116年度土城區公園廣場、農路等設施修繕工程委託設計監造技術服務</t>
+          <t>福興鄉老人文康中心修繕、福興鄉立幼兒園廁所整修等二案委託設計監造技術服務</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>1002750</v>
+        <v>1043219</v>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>115/10/14</t>
+          <t>115/10/08</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>內政部國家公園署墾丁國家公園管理處</t>
+          <t>新北市土城區公所</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>594-115-01-882</t>
+          <t>11509A049</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -3391,11 +3391,11 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>116年墾丁國家公園系列文創商品委託設計規劃案</t>
+          <t>116年度土城區公園廣場、農路等設施修繕工程委託設計監造技術服務</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>900000</v>
+        <v>1002750</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/14</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>新竹市立建功高級中學</t>
+          <t>內政部國家公園署墾丁國家公園管理處</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>115-19</t>
+          <t>594-115-01-882</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -3444,11 +3444,11 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>115年度修整建足球運動場計畫委託設計規劃監造服務</t>
+          <t>116年墾丁國家公園系列文創商品委託設計規劃案</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>820000</v>
+        <v>900000</v>
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3482,12 +3482,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>國立臺北科技大學附屬桃園農工高級中等學校</t>
+          <t>新竹市立建功高級中學</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>tyai115043</t>
+          <t>115-19</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -3497,11 +3497,11 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>汙水下水道工程第一期委託監造技術服務案</t>
+          <t>115年度修整建足球運動場計畫委託設計規劃監造服務</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>800001</v>
+        <v>820000</v>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>115/10/08</t>
+          <t>115/10/06</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -16516,7 +16516,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-02 18:37</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-03 10:12</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-03 17:58</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-04 10:48</t>
         </is>
       </c>
     </row>
@@ -16516,7 +16516,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-03 17:58</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-04 10:48</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-04 10:48</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-04 18:41</t>
         </is>
       </c>
     </row>
@@ -16516,7 +16516,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-04 10:48</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-04 18:41</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-08 19:30</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-09 11:01</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17110,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-08 19:30</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-09 11:01</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-09 11:01</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-09 19:26</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17110,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-09 11:01</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-09 19:26</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-10 10:33</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-10 18:43</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17110,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-10 10:33</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-10 18:43</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-10 18:43</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-11 10:02</t>
         </is>
       </c>
     </row>
@@ -17110,7 +17110,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-10 18:43</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-11 10:02</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -12,7 +12,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'🏛️ 設計監造標'!$A$2:$K$299</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🏗️ 工程施工標'!$A$2:$K$429</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'🏗️ 工程施工標'!$A$2:$K$428</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-16 17:09</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-17 09:24</t>
         </is>
       </c>
     </row>
@@ -16659,7 +16659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K429"/>
+  <dimension ref="A1:K428"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -16678,7 +16678,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-16 17:09</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-17 09:24</t>
         </is>
       </c>
     </row>
@@ -16745,7 +16745,7 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -16755,12 +16755,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司</t>
+          <t>桃園市立楊明國民中學</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>6021455203</t>
+          <t>11503A</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -16770,20 +16770,20 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>大林電廠燃氣機組更新改建計畫新161kV開關場統包工程</t>
+          <t>育賢樓西北側老舊廁所整修工程採購</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
-        <v>7560000000</v>
+        <v>4602973</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
-          <t>115/10/19</t>
+          <t>115/10/20</t>
         </is>
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>115/11/04</t>
+          <t>115/10/21</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -16798,7 +16798,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -16808,12 +16808,12 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>台灣糖業股份有限公司中彰區處</t>
+          <t>台灣電力股份有限公司</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>115-M131-6920-01</t>
+          <t>6021455203</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -16823,11 +16823,11 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>臺中泉源段形象商圈新建統包工程</t>
+          <t>大林電廠燃氣機組更新改建計畫新161kV開關場統包工程</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>262824293</v>
+        <v>7560000000</v>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
@@ -16836,7 +16836,7 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>115/11/23</t>
+          <t>115/11/04</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -16851,7 +16851,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -16861,12 +16861,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>國立國父紀念館</t>
+          <t>台灣糖業股份有限公司中彰區處</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>1151012</t>
+          <t>115-M131-6920-01</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -16876,11 +16876,11 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>國立國父紀念館景觀改造工程 (含館四周舖面及相關設施等)</t>
+          <t>臺中泉源段形象商圈新建統包工程</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>85653000</v>
+        <v>262824293</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>115/11/09</t>
+          <t>115/11/23</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
@@ -16904,7 +16904,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -16914,26 +16914,26 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>國立國父紀念館</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>EA1150022587</t>
+          <t>1151012</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>花蓮縣身心障礙福利服務中心室內裝修工程</t>
+          <t>國立國父紀念館景觀改造工程 (含館四周舖面及相關設施等)</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
-        <v>59756692</v>
+        <v>85653000</v>
       </c>
       <c r="I6" s="12" t="inlineStr">
         <is>
@@ -16942,7 +16942,7 @@
       </c>
       <c r="J6" s="12" t="inlineStr">
         <is>
-          <t>115/10/21</t>
+          <t>115/11/09</t>
         </is>
       </c>
       <c r="K6" s="9" t="inlineStr">
@@ -16957,7 +16957,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -16967,26 +16967,26 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司屏東區管理處</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>PA-115-1318-0001</t>
+          <t>EA1150022587</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>屏東縣三地門德文村延管工程(一)、115年度高樹所用戶新裝單價工作(三)(德文村)(併案發包)</t>
+          <t>花蓮縣身心障礙福利服務中心室內裝修工程</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>49273835</v>
+        <v>59756692</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -16995,7 +16995,7 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/21</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
@@ -17010,22 +17010,22 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府環境保護局</t>
+          <t>台灣自來水股份有限公司屏東區管理處</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>H16012</t>
+          <t>PA-115-1318-0001</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -17035,11 +17035,11 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>116-117年高雄市固定污染源空氣污染防制費徵審暨總量管制計畫</t>
+          <t>屏東縣三地門德文村延管工程(一)、115年度高樹所用戶新裝單價工作(三)(德文村)(併案發包)</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>43665000</v>
+        <v>49273835</v>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
@@ -17048,12 +17048,12 @@
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>115/11/16</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -17063,22 +17063,22 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>中央造幣廠</t>
+          <t>高雄市政府環境保護局</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>GA-15010</t>
+          <t>H16012</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -17088,11 +17088,11 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>中央造幣廠宿舍拆除工程</t>
+          <t>116-117年高雄市固定污染源空氣污染防制費徵審暨總量管制計畫</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>33633306</v>
+        <v>43665000</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
@@ -17101,12 +17101,12 @@
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/16</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -17126,12 +17126,12 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>農業部獸醫研究所</t>
+          <t>中央造幣廠</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>115024-AR</t>
+          <t>GA-15010</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -17141,11 +17141,11 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>SPF動物舍A、B、C棟空調系統節能改善工程</t>
+          <t>中央造幣廠宿舍拆除工程</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>20731711</v>
+        <v>33633306</v>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -17169,7 +17169,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -17179,12 +17179,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>高雄市大樹區公所</t>
+          <t>農業部獸醫研究所</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1151004</t>
+          <t>115024-AR</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -17194,11 +17194,11 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>高雄市大樹區舊鐵道下邊坡滑落災害復建工程</t>
+          <t>SPF動物舍A、B、C棟空調系統節能改善工程</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>9253000</v>
+        <v>20731711</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -17207,7 +17207,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -17222,7 +17222,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -17232,12 +17232,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>桃園市桃園區永順國民小學</t>
+          <t>高雄市大樹區公所</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Y115-024</t>
+          <t>1151004</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -17247,11 +17247,11 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>永順國小114-116年公立國民中小學老舊廁所整修工程</t>
+          <t>高雄市大樹區舊鐵道下邊坡滑落災害復建工程</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>5244957</v>
+        <v>9253000</v>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -17275,7 +17275,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -17285,12 +17285,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>澎湖縣政府</t>
+          <t>桃園市桃園區永順國民小學</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>CW-11150044</t>
+          <t>Y115-024</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -17300,11 +17300,11 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>115年龍門漁港漁具倉庫南側突堤修建工程</t>
+          <t>永順國小114-116年公立國民中小學老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>3592781</v>
+        <v>5244957</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -17313,7 +17313,7 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
@@ -17328,7 +17328,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -17338,12 +17338,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣萬榮鄉公所</t>
+          <t>澎湖縣政府</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>11509-N02</t>
+          <t>CW-11150044</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -17353,11 +17353,11 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>115年度北區基層建設工程(A區)</t>
+          <t>115年龍門漁港漁具倉庫南側突堤修建工程</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
-        <v>2519575</v>
+        <v>3592781</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -17391,12 +17391,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>臺中市立龍津高級中等學校</t>
+          <t>花蓮縣萬榮鄉公所</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>115-021</t>
+          <t>11509-N02</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -17406,11 +17406,11 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>龍津高中閱覽室空間活化工程</t>
+          <t>115年度北區基層建設工程(A區)</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>1795244</v>
+        <v>2519575</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
       </c>
       <c r="J15" s="7" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -17434,7 +17434,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -17444,26 +17444,26 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>臺中市立龍津高級中等學校</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>115054</t>
+          <t>115-021</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>南世運動場聖火臺及牆面彩繪工程</t>
+          <t>龍津高中閱覽室空間活化工程</t>
         </is>
       </c>
       <c r="H16" s="11" t="n">
-        <v>1236656</v>
+        <v>1795244</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
@@ -17472,12 +17472,12 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>115/10/20</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -17487,7 +17487,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -17497,26 +17497,26 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>臺中市大雅區汝鎏國民小學</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>115054</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>汝鎏國小幼兒園設備改善工程</t>
+          <t>南世運動場聖火臺及牆面彩繪工程</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>1166677</v>
+        <v>1236656</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -17525,7 +17525,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>115/10/21</t>
+          <t>115/10/20</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -17540,7 +17540,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -17550,12 +17550,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>法務部法醫研究所</t>
+          <t>臺中市大雅區汝鎏國民小學</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>211150826</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -17565,11 +17565,11 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>本所南區辦公室整修案之後續水電分表工程</t>
+          <t>汝鎏國小幼兒園設備改善工程</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
-        <v>1000000</v>
+        <v>1166677</v>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
@@ -17578,7 +17578,7 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/21</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -17593,7 +17593,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -17603,12 +17603,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>臺中市立潭子幼兒園</t>
+          <t>法務部法醫研究所</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>toujiaoutdoormat</t>
+          <t>211150826</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -17618,11 +17618,11 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>臺中市立潭子幼兒園115年度地墊改善工程</t>
+          <t>本所南區辦公室整修案之後續水電分表工程</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>701100</v>
+        <v>1000000</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -17631,12 +17631,12 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>115/10/23</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>公開取得電子報價單</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -17646,7 +17646,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -17656,40 +17656,40 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>交通部高速公路局</t>
+          <t>臺中市立潭子幼兒園</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>115A051P004</t>
+          <t>toujiaoutdoormat</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>國道1號五堵交流道至汐止交流道路段拓寬工程（第C109R標）</t>
+          <t>臺中市立潭子幼兒園115年度地墊改善工程</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
-        <v>3110190422</v>
+        <v>701100</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
-          <t>115/10/16</t>
+          <t>115/10/19</t>
         </is>
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>115/10/22</t>
+          <t>115/10/23</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得電子報價單</t>
         </is>
       </c>
     </row>
@@ -17699,7 +17699,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -17709,26 +17709,26 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>新竹縣政府</t>
+          <t>交通部高速公路局</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>CS115-016</t>
+          <t>115A051P004</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>竹43線6K+000-9K+705拓寬工程</t>
+          <t>國道1號五堵交流道至汐止交流道路段拓寬工程（第C109R標）</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>971836387</v>
+        <v>3110190422</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>115/11/06</t>
+          <t>115/10/22</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -17762,26 +17762,26 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>新竹縣政府</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>115A121</t>
+          <t>CS115-016</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>新竹市大鵬新城地下室滲漏水整修工程</t>
+          <t>竹43線6K+000-9K+705拓寬工程</t>
         </is>
       </c>
       <c r="H22" s="11" t="n">
-        <v>436966745</v>
+        <v>971836387</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>115/10/21</t>
+          <t>115/11/06</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -17815,26 +17815,26 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府水利局</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>wat115098</t>
+          <t>115A121</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>Danas-F-06-02-08-臺南市永康區大灣排水分區公5滯洪池治理工程</t>
+          <t>新竹市大鵬新城地下室滲漏水整修工程</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>129600000</v>
+        <v>436966745</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/10/21</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -17858,7 +17858,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -17868,12 +17868,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司核能火力發電工程處北部施工處</t>
+          <t>臺南市政府水利局</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>6381552602</t>
+          <t>wat115098</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -17883,11 +17883,11 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>大潭電廠8及9號機勵磁變壓器房及海水電解室電氣設備房增設氣體滅火系統工程</t>
+          <t>Danas-F-06-02-08-臺南市永康區大灣排水分區公5滯洪池治理工程</t>
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>97790000</v>
+        <v>129600000</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>115/11/09</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
@@ -17921,26 +17921,26 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>頭城鎮農會</t>
+          <t>台灣電力股份有限公司核能火力發電工程處北部施工處</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>TFA115-01</t>
+          <t>6381552602</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>頭城鎮農會頭圍農驛園區第一期計畫統包工程</t>
+          <t>大潭電廠8及9號機勵磁變壓器房及海水電解室電氣設備房增設氣體滅火系統工程</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>95952966</v>
+        <v>97790000</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -17949,7 +17949,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/11/09</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -17964,22 +17964,22 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>交通部高速公路局南區養護工程分局</t>
+          <t>頭城鎮農會</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>115D020P006</t>
+          <t>TFA115-01</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -17989,11 +17989,11 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>116~118年度南區交通控制中心部分業務委外工作</t>
+          <t>頭城鎮農會頭圍農驛園區第一期計畫統包工程</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>74831186</v>
+        <v>95952966</v>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
@@ -18002,12 +18002,12 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>115/10/20</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -18017,36 +18017,36 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司嘉南供電區營運處</t>
+          <t>交通部高速公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>4851570027</t>
+          <t>115D020P006</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>115~116年度零星管路積點工程</t>
+          <t>116~118年度南區交通控制中心部分業務委外工作</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>49500000</v>
+        <v>74831186</v>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
@@ -18055,12 +18055,12 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/20</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -18070,7 +18070,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -18080,26 +18080,26 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司台中供電區營運處</t>
+          <t>台灣電力股份有限公司嘉南供電區營運處</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>4801572028</t>
+          <t>4851570027</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>115年度彰化段輸電架空線路設備積點工程</t>
+          <t>115~116年度零星管路積點工程</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>49000000</v>
+        <v>49500000</v>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>115/10/20</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -18123,36 +18123,36 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府環境保護局</t>
+          <t>台灣電力股份有限公司台中供電區營運處</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>H16009</t>
+          <t>4801572028</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>116-117年高雄市空氣品質維護綜合管理計畫</t>
+          <t>115年度彰化段輸電架空線路設備積點工程</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>44262000</v>
+        <v>49000000</v>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
@@ -18161,12 +18161,12 @@
       </c>
       <c r="J29" s="7" t="inlineStr">
         <is>
-          <t>115/11/16</t>
+          <t>115/10/20</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -18176,22 +18176,22 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>臺南市政府交通局</t>
+          <t>高雄市政府環境保護局</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>1150221</t>
+          <t>H16009</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -18201,11 +18201,11 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>116年臺南市新設、改善、搶修及維修交通設施工程(東南工區)(開口契約)</t>
+          <t>116-117年高雄市空氣品質維護綜合管理計畫</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>35916048</v>
+        <v>44262000</v>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
@@ -18214,12 +18214,12 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/16</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -18229,7 +18229,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
@@ -18239,12 +18239,12 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>新竹瓦斯股份有限公司</t>
+          <t>臺南市政府交通局</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>GL116-31-04</t>
+          <t>1150221</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -18254,11 +18254,11 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>116年度用戶瓦斯裝置及24小時零星搶修工程(新豐、湖口地區)(開口契約)</t>
+          <t>116年臺南市新設、改善、搶修及維修交通設施工程(東南工區)(開口契約)</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>35616395</v>
+        <v>35916048</v>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -18292,12 +18292,12 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>新竹瓦斯股份有限公司</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>115-620</t>
+          <t>GL116-31-04</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -18307,11 +18307,11 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>116年度埔里段轄區省道瀝青鋪面擇要路段修復工程(開口契約)</t>
+          <t>116年度用戶瓦斯裝置及24小時零星搶修工程(新豐、湖口地區)(開口契約)</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>32166791</v>
+        <v>35616395</v>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
@@ -18320,7 +18320,7 @@
       </c>
       <c r="J32" s="12" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K32" s="9" t="inlineStr">
@@ -18335,7 +18335,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -18345,12 +18345,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>交通部高速公路局南區養護工程分局</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>115D010P020</t>
+          <t>115-620</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -18360,11 +18360,11 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>新營段轄區護欄柵欄及界樁維護工程(116)</t>
+          <t>116年度埔里段轄區省道瀝青鋪面擇要路段修復工程(開口契約)</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>23050138</v>
+        <v>32166791</v>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
@@ -18388,7 +18388,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -18398,12 +18398,12 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>普濟寺（原名鐵真院）</t>
+          <t>交通部高速公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>PUJI11500002</t>
+          <t>115D010P020</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -18413,11 +18413,11 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>直轄市定古蹟「北投普濟寺」修復工程</t>
+          <t>新營段轄區護欄柵欄及界樁維護工程(116)</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>20151763</v>
+        <v>23050138</v>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -18451,12 +18451,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司屏東區管理處</t>
+          <t>普濟寺（原名鐵真院）</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>RC-115-1350-0009</t>
+          <t>PUJI11500002</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -18466,11 +18466,11 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>屏東縣枋寮鄉中華路等汰換管線工程</t>
+          <t>直轄市定古蹟「北投普濟寺」修復工程</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>18133500</v>
+        <v>20151763</v>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -18504,26 +18504,26 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局北區養護工程分局</t>
+          <t>台灣自來水股份有限公司屏東區管理處</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>1161A1D09</t>
+          <t>RC-115-1350-0009</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>新竹段116年台1線、台13線及台31線預約經常性公路零星修復工程</t>
+          <t>屏東縣枋寮鄉中華路等汰換管線工程</t>
         </is>
       </c>
       <c r="H36" s="11" t="n">
-        <v>17466028</v>
+        <v>18133500</v>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>115/10/22</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -18557,26 +18557,26 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府水利局</t>
+          <t>交通部公路局北區養護工程分局</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>C1150920</t>
+          <t>1161A1D09</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>高雄市三民區幸福川防潮閘門更新工程</t>
+          <t>新竹段116年台1線、台13線及台31線預約經常性公路零星修復工程</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>15548000</v>
+        <v>17466028</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/10/22</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -18600,7 +18600,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -18610,12 +18610,12 @@
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>高雄市政府水利局</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>141-F1151015-1</t>
+          <t>C1150920</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -18625,11 +18625,11 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>(115年6月豪雨)新埤鄉獅頭排水右岸災害復建工程</t>
+          <t>高雄市三民區幸福川防潮閘門更新工程</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>13442000</v>
+        <v>15548000</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
       </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K38" s="9" t="inlineStr">
@@ -18663,26 +18663,26 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司屏東區管理處</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>PA11513130001</t>
+          <t>141-F1151015-1</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>第 11 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>屏東縣瑪家鄉涼山村等供水延管工程-土建機電</t>
+          <t>(115年6月豪雨)新埤鄉獅頭排水右岸災害復建工程</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>13206421</v>
+        <v>13442000</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>115/10/22</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -18706,36 +18706,36 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府環境保護局</t>
+          <t>台灣自來水股份有限公司屏東區管理處</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>H16010</t>
+          <t>PA11513130001</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 11 次</t>
         </is>
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>116年高雄市餐飲油煙、室內空氣品質管制暨紙錢集中燒推動整合計畫</t>
+          <t>屏東縣瑪家鄉涼山村等供水延管工程-土建機電</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>12426000</v>
+        <v>13206421</v>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
@@ -18744,12 +18744,12 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>115/11/16</t>
+          <t>115/10/22</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -18764,17 +18764,17 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>法務部矯正署高雄女子監獄</t>
+          <t>高雄市政府環境保護局</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>115-20</t>
+          <t>H16010</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -18784,11 +18784,11 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>116年上半年度高雄一區矯正機關收容人副食品聯合採購案-南北雜貨類</t>
+          <t>116年高雄市餐飲油煙、室內空氣品質管制暨紙錢集中燒推動整合計畫</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>12131551</v>
+        <v>12426000</v>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
@@ -18797,12 +18797,12 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/16</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -18812,22 +18812,22 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>國立臺灣大學醫學院附設醫院癌醫中心分院</t>
+          <t>法務部矯正署高雄女子監獄</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>FA115001</t>
+          <t>115-20</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -18837,11 +18837,11 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>永真樓地下4樓藥劑部藥庫空間裝修工程</t>
+          <t>116年上半年度高雄一區矯正機關收容人副食品聯合採購案-南北雜貨類</t>
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>11370801</v>
+        <v>12131551</v>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
@@ -18875,26 +18875,26 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣通霄鎮公所</t>
+          <t>國立臺灣大學醫學院附設醫院癌醫中心分院</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>A1150813A</t>
+          <t>FA115001</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>通霄海水浴場新設人行道與停車場工程</t>
+          <t>永真樓地下4樓藥劑部藥庫空間裝修工程</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>10600000</v>
+        <v>11370801</v>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -18918,7 +18918,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -18928,26 +18928,26 @@
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>苗栗縣通霄鎮公所</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>1153077162</t>
+          <t>A1150813A</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>116年度楓港工務段轄內排水及其它公路設施改善工程</t>
+          <t>通霄海水浴場新設人行道與停車場工程</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>9981739</v>
+        <v>10600000</v>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
@@ -18971,22 +18971,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>YKP16009</t>
+          <t>1153077162</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -18996,11 +18996,11 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>「數位乳房X光攝影系統1組」(採購案號YKP16009) (台南分院)</t>
+          <t>116年度楓港工務段轄內排水及其它公路設施改善工程</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>8000000</v>
+        <v>9981739</v>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -19024,36 +19024,36 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>1155027844</t>
+          <t>YKP16009</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>臺東工務段利家監工站轄區116年度預約經常性路面清掃維護工作</t>
+          <t>「數位乳房X光攝影系統1組」(採購案號YKP16009) (台南分院)</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>7857136</v>
+        <v>8000000</v>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>115/10/21</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
@@ -19077,36 +19077,36 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>國立臺灣大學</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>MB115072301</t>
+          <t>1155027844</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>教職員宿舍潮州街3巷2-4號等3棟斜屋頂工程</t>
+          <t>臺東工務段利家監工站轄區116年度預約經常性路面清掃維護工作</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>7565147</v>
+        <v>7857136</v>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>115/10/22</t>
+          <t>115/10/21</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -19130,7 +19130,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -19140,26 +19140,26 @@
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>高雄市楠梓戶政事務所</t>
+          <t>國立臺灣大學</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>MB115072301</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>高雄市楠梓戶政事務所115年辦公廳舍室內裝修及設備工程採購案</t>
+          <t>教職員宿舍潮州街3巷2-4號等3棟斜屋頂工程</t>
         </is>
       </c>
       <c r="H48" s="11" t="n">
-        <v>6800000</v>
+        <v>7565147</v>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
@@ -19168,7 +19168,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/22</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
@@ -19193,26 +19193,26 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>國營臺灣鐵路股份有限公司</t>
+          <t>高雄市楠梓戶政事務所</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>L0515S1029W</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>基礎設施建設重置第1期計畫_高雄電務段轄內線槽重置工程(第一期)</t>
+          <t>高雄市楠梓戶政事務所115年辦公廳舍室內裝修及設備工程採購案</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>6754545</v>
+        <v>6800000</v>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
@@ -19221,7 +19221,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -19236,7 +19236,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -19246,26 +19246,26 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>衛生福利部中央健康保險署</t>
+          <t>國營臺灣鐵路股份有限公司</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>1150818CD</t>
+          <t>L0515S1029W</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>新竹聯絡辦公室裝修工程採購案</t>
+          <t>基礎設施建設重置第1期計畫_高雄電務段轄內線槽重置工程(第一期)</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>6730000</v>
+        <v>6754545</v>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr">
@@ -19289,22 +19289,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府環境保護局</t>
+          <t>衛生福利部中央健康保險署</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>H16006</t>
+          <t>1150818CD</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -19314,11 +19314,11 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>116年度高雄市氣候變遷減緩及調適計畫－以推動永續發展為主軸</t>
+          <t>新竹聯絡辦公室裝修工程採購案</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>6700000</v>
+        <v>6730000</v>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
@@ -19327,12 +19327,12 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -19342,36 +19342,36 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣通霄鎮公所</t>
+          <t>高雄市政府環境保護局</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>115AG015</t>
+          <t>H16006</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>115年福龍等8里路面及排水改善工程</t>
+          <t>116年度高雄市氣候變遷減緩及調適計畫－以推動永續發展為主軸</t>
         </is>
       </c>
       <c r="H52" s="11" t="n">
-        <v>6699738</v>
+        <v>6700000</v>
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
@@ -19380,12 +19380,12 @@
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -19405,26 +19405,26 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>南投縣政府</t>
+          <t>苗栗縣通霄鎮公所</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>1150504041A</t>
+          <t>115AG015</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>115年4月豪雨-名間鄉坑內坑排水幹線3K+300處右側堤防災修復建工程</t>
+          <t>115年福龍等8里路面及排水改善工程</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>6390000</v>
+        <v>6699738</v>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
@@ -19448,22 +19448,22 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>南投縣政府</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>1155029867</t>
+          <t>1150504041A</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -19473,11 +19473,11 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>甲仙工務段轄區116年度省道預約排水設施疏濬工作</t>
+          <t>115年4月豪雨-名間鄉坑內坑排水幹線3K+300處右側堤防災修復建工程</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>6018350</v>
+        <v>6390000</v>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
@@ -19501,36 +19501,36 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>115RA-04-005</t>
+          <t>1155029867</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>新化區大坑里大坑社區產業體驗環境改善工程</t>
+          <t>甲仙工務段轄區116年度省道預約排水設施疏濬工作</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>5207300</v>
+        <v>6018350</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
@@ -19539,7 +19539,7 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>115/10/22</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -19554,7 +19554,7 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
@@ -19564,26 +19564,26 @@
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>雲林縣麥寮鄉公所</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>115-78</t>
+          <t>115RA-04-005</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>115年雲林縣麥寮鄉社教園區環境綠美化工程</t>
+          <t>新化區大坑里大坑社區產業體驗環境改善工程</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>4867000</v>
+        <v>5207300</v>
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
@@ -19592,7 +19592,7 @@
       </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/22</t>
         </is>
       </c>
       <c r="K56" s="9" t="inlineStr">
@@ -19607,7 +19607,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -19617,26 +19617,26 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>財團法人喜憨兒社會福利基金會</t>
+          <t>雲林縣麥寮鄉公所</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>11501</t>
+          <t>115-78</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>喜憨兒基金會天鵝堡五樓禮堂及各樓層廁所地坪翻修工程採購契約</t>
+          <t>115年雲林縣麥寮鄉社教園區環境綠美化工程</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>4824000</v>
+        <v>4867000</v>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
@@ -19645,7 +19645,7 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>115/10/22</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -19660,7 +19660,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -19670,26 +19670,26 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>財團法人喜憨兒社會福利基金會</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>115-ADE-49-4-011</t>
+          <t>11501</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>馬蹄腳野溪整治工程</t>
+          <t>喜憨兒基金會天鵝堡五樓禮堂及各樓層廁所地坪翻修工程採購契約</t>
         </is>
       </c>
       <c r="H58" s="11" t="n">
-        <v>4720874</v>
+        <v>4824000</v>
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
@@ -19698,7 +19698,7 @@
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/10/22</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
@@ -19713,7 +19713,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -19723,26 +19723,26 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>115EN632164335009100</t>
+          <t>115-ADE-49-4-011</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>西滑道管路整修工程</t>
+          <t>馬蹄腳野溪整治工程</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>4488028</v>
+        <v>4720874</v>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -19766,7 +19766,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -19776,26 +19776,26 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>臺東縣政府</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>115190210394</t>
+          <t>115EN632164335009100</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>Danas-F-06-02-12-114年8月楊柳颱風金崙溪下多良一號護岸災後復建工程</t>
+          <t>西滑道管路整修工程</t>
         </is>
       </c>
       <c r="H60" s="11" t="n">
-        <v>4395600</v>
+        <v>4488028</v>
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
@@ -19804,7 +19804,7 @@
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>115/10/21</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
@@ -38114,12 +38114,12 @@
       </c>
       <c r="D406" s="9" t="inlineStr">
         <is>
-          <t>高雄市立凱旋醫院</t>
+          <t>高雄市政府工務局道路養護工程處</t>
         </is>
       </c>
       <c r="E406" s="8" t="inlineStr">
         <is>
-          <t>KSPH115107</t>
+          <t>11505CA014</t>
         </is>
       </c>
       <c r="F406" s="8" t="inlineStr">
@@ -38129,11 +38129,11 @@
       </c>
       <c r="G406" s="10" t="inlineStr">
         <is>
-          <t>115年度大寮精神護理之家公廁馬桶改建工程</t>
+          <t>115年度高雄市橋頭、燕巢、梓官等地區瀝青路面與道路附屬設施（不含燕巢區）緊急搶修及經常性養護工程（開口契約）（第2標）</t>
         </is>
       </c>
       <c r="H406" s="11" t="n">
-        <v>2245700</v>
+        <v>2000000</v>
       </c>
       <c r="I406" s="12" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
       </c>
       <c r="J406" s="12" t="inlineStr">
         <is>
-          <t>115/10/16</t>
+          <t>115/10/19</t>
         </is>
       </c>
       <c r="K406" s="9" t="inlineStr">
@@ -38157,7 +38157,7 @@
       </c>
       <c r="B407" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C407" s="3" t="inlineStr">
@@ -38167,12 +38167,12 @@
       </c>
       <c r="D407" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府工務局道路養護工程處</t>
+          <t>屏東縣三地門鄉青葉國民小學</t>
         </is>
       </c>
       <c r="E407" s="3" t="inlineStr">
         <is>
-          <t>11505CA014</t>
+          <t>1151019</t>
         </is>
       </c>
       <c r="F407" s="3" t="inlineStr">
@@ -38182,11 +38182,11 @@
       </c>
       <c r="G407" s="5" t="inlineStr">
         <is>
-          <t>115年度高雄市橋頭、燕巢、梓官等地區瀝青路面與道路附屬設施（不含燕巢區）緊急搶修及經常性養護工程（開口契約）（第2標）</t>
+          <t>115年度屏東縣青葉國小改善無障礙校園環境工程</t>
         </is>
       </c>
       <c r="H407" s="6" t="n">
-        <v>2000000</v>
+        <v>1772568</v>
       </c>
       <c r="I407" s="7" t="inlineStr">
         <is>
@@ -38210,7 +38210,7 @@
       </c>
       <c r="B408" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C408" s="8" t="inlineStr">
@@ -38220,12 +38220,12 @@
       </c>
       <c r="D408" s="9" t="inlineStr">
         <is>
-          <t>屏東縣三地門鄉青葉國民小學</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E408" s="8" t="inlineStr">
         <is>
-          <t>1151019</t>
+          <t>Danas-H-01-06-9-44</t>
         </is>
       </c>
       <c r="F408" s="8" t="inlineStr">
@@ -38235,11 +38235,11 @@
       </c>
       <c r="G408" s="10" t="inlineStr">
         <is>
-          <t>115年度屏東縣青葉國小改善無障礙校園環境工程</t>
+          <t>Danas-H-01-06-9-力里往老七佳農路災害復建工程</t>
         </is>
       </c>
       <c r="H408" s="11" t="n">
-        <v>1772568</v>
+        <v>1533601</v>
       </c>
       <c r="I408" s="12" t="inlineStr">
         <is>
@@ -38263,7 +38263,7 @@
       </c>
       <c r="B409" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C409" s="3" t="inlineStr">
@@ -38273,35 +38273,35 @@
       </c>
       <c r="D409" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>台灣電力股份有限公司綜合施工處</t>
         </is>
       </c>
       <c r="E409" s="3" t="inlineStr">
         <is>
-          <t>Danas-H-01-06-9-44</t>
+          <t>6021370001</t>
         </is>
       </c>
       <c r="F409" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G409" s="5" t="inlineStr">
         <is>
-          <t>Danas-H-01-06-9-力里往老七佳農路災害復建工程</t>
+          <t>市定古蹟金瓜石太子賓館修復工程</t>
         </is>
       </c>
       <c r="H409" s="6" t="n">
-        <v>1533601</v>
+        <v>179208764</v>
       </c>
       <c r="I409" s="7" t="inlineStr">
         <is>
-          <t>115/10/06</t>
+          <t>115/10/05</t>
         </is>
       </c>
       <c r="J409" s="7" t="inlineStr">
         <is>
-          <t>115/10/19</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K409" s="4" t="inlineStr">
@@ -38316,7 +38316,7 @@
       </c>
       <c r="B410" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C410" s="8" t="inlineStr">
@@ -38326,26 +38326,26 @@
       </c>
       <c r="D410" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司綜合施工處</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E410" s="8" t="inlineStr">
         <is>
-          <t>6021370001</t>
+          <t>11151002</t>
         </is>
       </c>
       <c r="F410" s="8" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G410" s="10" t="inlineStr">
         <is>
-          <t>市定古蹟金瓜石太子賓館修復工程</t>
+          <t>116年路燈新設及管線換新工程(開口契約)</t>
         </is>
       </c>
       <c r="H410" s="11" t="n">
-        <v>179208764</v>
+        <v>8870744</v>
       </c>
       <c r="I410" s="12" t="inlineStr">
         <is>
@@ -38354,7 +38354,7 @@
       </c>
       <c r="J410" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K410" s="9" t="inlineStr">
@@ -38369,7 +38369,7 @@
       </c>
       <c r="B411" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C411" s="3" t="inlineStr">
@@ -38379,12 +38379,12 @@
       </c>
       <c r="D411" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>高雄市政府水利局</t>
         </is>
       </c>
       <c r="E411" s="3" t="inlineStr">
         <is>
-          <t>11151002</t>
+          <t>C1150931</t>
         </is>
       </c>
       <c r="F411" s="3" t="inlineStr">
@@ -38394,11 +38394,11 @@
       </c>
       <c r="G411" s="5" t="inlineStr">
         <is>
-          <t>116年路燈新設及管線換新工程(開口契約)</t>
+          <t>仁武區烏林排水匯流口護岸損壞修復工程(115年4月豪雨)</t>
         </is>
       </c>
       <c r="H411" s="6" t="n">
-        <v>8870744</v>
+        <v>6975000</v>
       </c>
       <c r="I411" s="7" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
       </c>
       <c r="J411" s="7" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/20</t>
         </is>
       </c>
       <c r="K411" s="4" t="inlineStr">
@@ -38422,7 +38422,7 @@
       </c>
       <c r="B412" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C412" s="8" t="inlineStr">
@@ -38432,12 +38432,12 @@
       </c>
       <c r="D412" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府水利局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E412" s="8" t="inlineStr">
         <is>
-          <t>C1150931</t>
+          <t>073-F1151002-4</t>
         </is>
       </c>
       <c r="F412" s="8" t="inlineStr">
@@ -38447,11 +38447,11 @@
       </c>
       <c r="G412" s="10" t="inlineStr">
         <is>
-          <t>仁武區烏林排水匯流口護岸損壞修復工程(115年4月豪雨)</t>
+          <t>(115)縣道185線56K+900-60K+246擇要道路改善工程</t>
         </is>
       </c>
       <c r="H412" s="11" t="n">
-        <v>6975000</v>
+        <v>5270000</v>
       </c>
       <c r="I412" s="12" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
       </c>
       <c r="J412" s="12" t="inlineStr">
         <is>
-          <t>115/10/20</t>
+          <t>115/10/19</t>
         </is>
       </c>
       <c r="K412" s="9" t="inlineStr">
@@ -38490,7 +38490,7 @@
       </c>
       <c r="E413" s="3" t="inlineStr">
         <is>
-          <t>073-F1151002-4</t>
+          <t>073-F1151002-1</t>
         </is>
       </c>
       <c r="F413" s="3" t="inlineStr">
@@ -38500,11 +38500,11 @@
       </c>
       <c r="G413" s="5" t="inlineStr">
         <is>
-          <t>(115)縣道185線56K+900-60K+246擇要道路改善工程</t>
+          <t>(115)屏60線1K+670-3K+028道路改善工程</t>
         </is>
       </c>
       <c r="H413" s="6" t="n">
-        <v>5270000</v>
+        <v>5061000</v>
       </c>
       <c r="I413" s="7" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
       </c>
       <c r="E414" s="8" t="inlineStr">
         <is>
-          <t>073-F1151002-1</t>
+          <t>BP-1150930-01</t>
         </is>
       </c>
       <c r="F414" s="8" t="inlineStr">
@@ -38553,11 +38553,11 @@
       </c>
       <c r="G414" s="10" t="inlineStr">
         <is>
-          <t>(115)屏60線1K+670-3K+028道路改善工程</t>
+          <t>本局所屬廳舍及廁所修繕工程</t>
         </is>
       </c>
       <c r="H414" s="11" t="n">
-        <v>5061000</v>
+        <v>4255613</v>
       </c>
       <c r="I414" s="12" t="inlineStr">
         <is>
@@ -38596,7 +38596,7 @@
       </c>
       <c r="E415" s="3" t="inlineStr">
         <is>
-          <t>BP-1150930-01</t>
+          <t>073-F1151002-5</t>
         </is>
       </c>
       <c r="F415" s="3" t="inlineStr">
@@ -38606,11 +38606,11 @@
       </c>
       <c r="G415" s="5" t="inlineStr">
         <is>
-          <t>本局所屬廳舍及廁所修繕工程</t>
+          <t>(115年6月豪雨)屏172線8K+890-8K+945災後復建工程</t>
         </is>
       </c>
       <c r="H415" s="6" t="n">
-        <v>4255613</v>
+        <v>3962000</v>
       </c>
       <c r="I415" s="7" t="inlineStr">
         <is>
@@ -38649,7 +38649,7 @@
       </c>
       <c r="E416" s="8" t="inlineStr">
         <is>
-          <t>073-F1151002-5</t>
+          <t>073-F1151002-3</t>
         </is>
       </c>
       <c r="F416" s="8" t="inlineStr">
@@ -38659,11 +38659,11 @@
       </c>
       <c r="G416" s="10" t="inlineStr">
         <is>
-          <t>(115年6月豪雨)屏172線8K+890-8K+945災後復建工程</t>
+          <t>(115)屏57線1K+500-2K+555道路改善工程</t>
         </is>
       </c>
       <c r="H416" s="11" t="n">
-        <v>3962000</v>
+        <v>3229000</v>
       </c>
       <c r="I416" s="12" t="inlineStr">
         <is>
@@ -38687,7 +38687,7 @@
       </c>
       <c r="B417" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C417" s="3" t="inlineStr">
@@ -38697,12 +38697,12 @@
       </c>
       <c r="D417" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E417" s="3" t="inlineStr">
         <is>
-          <t>073-F1151002-3</t>
+          <t>11151001</t>
         </is>
       </c>
       <c r="F417" s="3" t="inlineStr">
@@ -38712,11 +38712,11 @@
       </c>
       <c r="G417" s="5" t="inlineStr">
         <is>
-          <t>(115)屏57線1K+500-2K+555道路改善工程</t>
+          <t>116年度臺南市公園綠地花架及遮陽亭新設工程（開口契約）</t>
         </is>
       </c>
       <c r="H417" s="6" t="n">
-        <v>3229000</v>
+        <v>3000000</v>
       </c>
       <c r="I417" s="7" t="inlineStr">
         <is>
@@ -38725,7 +38725,7 @@
       </c>
       <c r="J417" s="7" t="inlineStr">
         <is>
-          <t>115/10/19</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K417" s="4" t="inlineStr">
@@ -38755,7 +38755,7 @@
       </c>
       <c r="E418" s="8" t="inlineStr">
         <is>
-          <t>11151001</t>
+          <t>111510012</t>
         </is>
       </c>
       <c r="F418" s="8" t="inlineStr">
@@ -38765,11 +38765,11 @@
       </c>
       <c r="G418" s="10" t="inlineStr">
         <is>
-          <t>116年度臺南市公園綠地花架及遮陽亭新設工程（開口契約）</t>
+          <t>東區EB-13-6m道路工程(中段)(裕農路771巷)</t>
         </is>
       </c>
       <c r="H418" s="11" t="n">
-        <v>3000000</v>
+        <v>2462800</v>
       </c>
       <c r="I418" s="12" t="inlineStr">
         <is>
@@ -38778,7 +38778,7 @@
       </c>
       <c r="J418" s="12" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/20</t>
         </is>
       </c>
       <c r="K418" s="9" t="inlineStr">
@@ -38793,7 +38793,7 @@
       </c>
       <c r="B419" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C419" s="3" t="inlineStr">
@@ -38803,12 +38803,12 @@
       </c>
       <c r="D419" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E419" s="3" t="inlineStr">
         <is>
-          <t>111510012</t>
+          <t>073-F1151002-2</t>
         </is>
       </c>
       <c r="F419" s="3" t="inlineStr">
@@ -38818,11 +38818,11 @@
       </c>
       <c r="G419" s="5" t="inlineStr">
         <is>
-          <t>東區EB-13-6m道路工程(中段)(裕農路771巷)</t>
+          <t>(115)縣道187乙線9K+940-10K+202道路護欄擇要改善工程</t>
         </is>
       </c>
       <c r="H419" s="6" t="n">
-        <v>2462800</v>
+        <v>534000</v>
       </c>
       <c r="I419" s="7" t="inlineStr">
         <is>
@@ -38831,7 +38831,7 @@
       </c>
       <c r="J419" s="7" t="inlineStr">
         <is>
-          <t>115/10/20</t>
+          <t>115/10/19</t>
         </is>
       </c>
       <c r="K419" s="4" t="inlineStr">
@@ -38846,7 +38846,7 @@
       </c>
       <c r="B420" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C420" s="8" t="inlineStr">
@@ -38856,35 +38856,35 @@
       </c>
       <c r="D420" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>臺北市政府工務局</t>
         </is>
       </c>
       <c r="E420" s="8" t="inlineStr">
         <is>
-          <t>073-F1151002-2</t>
+          <t>1150111C0009</t>
         </is>
       </c>
       <c r="F420" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G420" s="10" t="inlineStr">
         <is>
-          <t>(115)縣道187乙線9K+940-10K+202道路護欄擇要改善工程</t>
+          <t>中正路配水池整體改建工程</t>
         </is>
       </c>
       <c r="H420" s="11" t="n">
-        <v>534000</v>
+        <v>114165000</v>
       </c>
       <c r="I420" s="12" t="inlineStr">
         <is>
-          <t>115/10/05</t>
+          <t>115/10/02</t>
         </is>
       </c>
       <c r="J420" s="12" t="inlineStr">
         <is>
-          <t>115/10/19</t>
+          <t>115/10/23</t>
         </is>
       </c>
       <c r="K420" s="9" t="inlineStr">
@@ -38899,50 +38899,50 @@
       </c>
       <c r="B421" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C421" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D421" s="4" t="inlineStr">
         <is>
-          <t>臺北市政府工務局</t>
+          <t>屏東縣政府消防局</t>
         </is>
       </c>
       <c r="E421" s="3" t="inlineStr">
         <is>
-          <t>1150111C0009</t>
+          <t>115C11-1</t>
         </is>
       </c>
       <c r="F421" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G421" s="5" t="inlineStr">
         <is>
-          <t>中正路配水池整體改建工程</t>
+          <t>屏東縣115年度公所暨防災協作中心TTX及HSEEP講習、核心課程暨基礎課程與種子教官培訓考核計畫</t>
         </is>
       </c>
       <c r="H421" s="6" t="n">
-        <v>114165000</v>
+        <v>9900000</v>
       </c>
       <c r="I421" s="7" t="inlineStr">
         <is>
-          <t>115/10/02</t>
+          <t>115/10/01</t>
         </is>
       </c>
       <c r="J421" s="7" t="inlineStr">
         <is>
-          <t>115/10/23</t>
+          <t>115/10/19</t>
         </is>
       </c>
       <c r="K421" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -38952,22 +38952,22 @@
       </c>
       <c r="B422" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C422" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D422" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府消防局</t>
+          <t>交通部公路局雲嘉南區養護工程分局</t>
         </is>
       </c>
       <c r="E422" s="8" t="inlineStr">
         <is>
-          <t>115C11-1</t>
+          <t>115060058</t>
         </is>
       </c>
       <c r="F422" s="8" t="inlineStr">
@@ -38977,25 +38977,25 @@
       </c>
       <c r="G422" s="10" t="inlineStr">
         <is>
-          <t>屏東縣115年度公所暨防災協作中心TTX及HSEEP講習、核心課程暨基礎課程與種子教官培訓考核計畫</t>
+          <t>台1線244k+690大湖口溪橋改建工程</t>
         </is>
       </c>
       <c r="H422" s="11" t="n">
-        <v>9900000</v>
+        <v>348862402</v>
       </c>
       <c r="I422" s="12" t="inlineStr">
         <is>
-          <t>115/10/01</t>
+          <t>115/09/30</t>
         </is>
       </c>
       <c r="J422" s="12" t="inlineStr">
         <is>
-          <t>115/10/19</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K422" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -39005,22 +39005,22 @@
       </c>
       <c r="B423" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C423" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D423" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局雲嘉南區養護工程分局</t>
+          <t>臺北榮民總醫院</t>
         </is>
       </c>
       <c r="E423" s="3" t="inlineStr">
         <is>
-          <t>115060058</t>
+          <t>1150670Y</t>
         </is>
       </c>
       <c r="F423" s="3" t="inlineStr">
@@ -39030,11 +39030,11 @@
       </c>
       <c r="G423" s="5" t="inlineStr">
         <is>
-          <t>台1線244k+690大湖口溪橋改建工程</t>
+          <t>生物可吸收肌腱修復片及固定系統組等2項2年單價開口契約</t>
         </is>
       </c>
       <c r="H423" s="6" t="n">
-        <v>348862402</v>
+        <v>36000000</v>
       </c>
       <c r="I423" s="7" t="inlineStr">
         <is>
@@ -39043,7 +39043,7 @@
       </c>
       <c r="J423" s="7" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K423" s="4" t="inlineStr">
@@ -39058,7 +39058,7 @@
       </c>
       <c r="B424" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C424" s="8" t="inlineStr">
@@ -39068,12 +39068,12 @@
       </c>
       <c r="D424" s="9" t="inlineStr">
         <is>
-          <t>臺北榮民總醫院</t>
+          <t>交通部高速公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E424" s="8" t="inlineStr">
         <is>
-          <t>1150670Y</t>
+          <t>115D120P025</t>
         </is>
       </c>
       <c r="F424" s="8" t="inlineStr">
@@ -39083,20 +39083,20 @@
       </c>
       <c r="G424" s="10" t="inlineStr">
         <is>
-          <t>生物可吸收肌腱修復片及固定系統組等2項2年單價開口契約</t>
+          <t>南區交通控制中心虛擬化環境之儲存系統優化提升(115)</t>
         </is>
       </c>
       <c r="H424" s="11" t="n">
-        <v>36000000</v>
+        <v>10901647</v>
       </c>
       <c r="I424" s="12" t="inlineStr">
         <is>
-          <t>115/09/30</t>
+          <t>115/09/24</t>
         </is>
       </c>
       <c r="J424" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K424" s="9" t="inlineStr">
@@ -39111,22 +39111,22 @@
       </c>
       <c r="B425" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C425" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D425" s="4" t="inlineStr">
         <is>
-          <t>交通部高速公路局南區養護工程分局</t>
+          <t>高雄市政府工務局</t>
         </is>
       </c>
       <c r="E425" s="3" t="inlineStr">
         <is>
-          <t>115D120P025</t>
+          <t>115418C</t>
         </is>
       </c>
       <c r="F425" s="3" t="inlineStr">
@@ -39136,20 +39136,20 @@
       </c>
       <c r="G425" s="5" t="inlineStr">
         <is>
-          <t>南區交通控制中心虛擬化環境之儲存系統優化提升(115)</t>
+          <t>高雄市立路竹高級中學校舍拆除及新建工程(第一期工程)</t>
         </is>
       </c>
       <c r="H425" s="6" t="n">
-        <v>10901647</v>
+        <v>232314129</v>
       </c>
       <c r="I425" s="7" t="inlineStr">
         <is>
-          <t>115/09/24</t>
+          <t>115/09/22</t>
         </is>
       </c>
       <c r="J425" s="7" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/19</t>
         </is>
       </c>
       <c r="K425" s="4" t="inlineStr">
@@ -39164,7 +39164,7 @@
       </c>
       <c r="B426" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C426" s="8" t="inlineStr">
@@ -39174,26 +39174,26 @@
       </c>
       <c r="D426" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府工務局</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E426" s="8" t="inlineStr">
         <is>
-          <t>115418C</t>
+          <t>111507012</t>
         </is>
       </c>
       <c r="F426" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 04 次</t>
         </is>
       </c>
       <c r="G426" s="10" t="inlineStr">
         <is>
-          <t>高雄市立路竹高級中學校舍拆除及新建工程(第一期工程)</t>
+          <t>115年臺南市配合道路開闢路燈增設工程暨路燈搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H426" s="11" t="n">
-        <v>232314129</v>
+        <v>18655286</v>
       </c>
       <c r="I426" s="12" t="inlineStr">
         <is>
@@ -39202,7 +39202,7 @@
       </c>
       <c r="J426" s="12" t="inlineStr">
         <is>
-          <t>115/10/19</t>
+          <t>115/10/20</t>
         </is>
       </c>
       <c r="K426" s="9" t="inlineStr">
@@ -39217,7 +39217,7 @@
       </c>
       <c r="B427" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C427" s="3" t="inlineStr">
@@ -39227,35 +39227,35 @@
       </c>
       <c r="D427" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>屏東縣潮州鎮公所</t>
         </is>
       </c>
       <c r="E427" s="3" t="inlineStr">
         <is>
-          <t>111507012</t>
+          <t>115-08-12</t>
         </is>
       </c>
       <c r="F427" s="3" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G427" s="5" t="inlineStr">
         <is>
-          <t>115年臺南市配合道路開闢路燈增設工程暨路燈搶修工程(開口契約)</t>
+          <t>屏東縣潮州鎮潮州國中校園周邊道路改善工程</t>
         </is>
       </c>
       <c r="H427" s="6" t="n">
-        <v>18655286</v>
+        <v>48515000</v>
       </c>
       <c r="I427" s="7" t="inlineStr">
         <is>
-          <t>115/09/22</t>
+          <t>115/09/21</t>
         </is>
       </c>
       <c r="J427" s="7" t="inlineStr">
         <is>
-          <t>115/10/20</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K427" s="4" t="inlineStr">
@@ -39270,7 +39270,7 @@
       </c>
       <c r="B428" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C428" s="8" t="inlineStr">
@@ -39280,12 +39280,12 @@
       </c>
       <c r="D428" s="9" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮公所</t>
+          <t>台灣電力股份有限公司核能火力發電工程處南部施工處</t>
         </is>
       </c>
       <c r="E428" s="8" t="inlineStr">
         <is>
-          <t>115-08-12</t>
+          <t>6751053310</t>
         </is>
       </c>
       <c r="F428" s="8" t="inlineStr">
@@ -39295,20 +39295,20 @@
       </c>
       <c r="G428" s="10" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮州國中校園周邊道路改善工程</t>
+          <t>興達電廠燃氣機組更新改建計畫廠區永久道路排水工程</t>
         </is>
       </c>
       <c r="H428" s="11" t="n">
-        <v>48515000</v>
+        <v>1950000000</v>
       </c>
       <c r="I428" s="12" t="inlineStr">
         <is>
-          <t>115/09/21</t>
+          <t>115/09/08</t>
         </is>
       </c>
       <c r="J428" s="12" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/10/20</t>
         </is>
       </c>
       <c r="K428" s="9" t="inlineStr">
@@ -39317,61 +39317,8 @@
         </is>
       </c>
     </row>
-    <row r="429" ht="26" customHeight="1">
-      <c r="A429" s="3" t="n">
-        <v>427</v>
-      </c>
-      <c r="B429" s="3" t="inlineStr">
-        <is>
-          <t>全國 / 其他</t>
-        </is>
-      </c>
-      <c r="C429" s="3" t="inlineStr">
-        <is>
-          <t>工程類</t>
-        </is>
-      </c>
-      <c r="D429" s="4" t="inlineStr">
-        <is>
-          <t>台灣電力股份有限公司核能火力發電工程處南部施工處</t>
-        </is>
-      </c>
-      <c r="E429" s="3" t="inlineStr">
-        <is>
-          <t>6751053310</t>
-        </is>
-      </c>
-      <c r="F429" s="3" t="inlineStr">
-        <is>
-          <t>第 01 次</t>
-        </is>
-      </c>
-      <c r="G429" s="5" t="inlineStr">
-        <is>
-          <t>興達電廠燃氣機組更新改建計畫廠區永久道路排水工程</t>
-        </is>
-      </c>
-      <c r="H429" s="6" t="n">
-        <v>1950000000</v>
-      </c>
-      <c r="I429" s="7" t="inlineStr">
-        <is>
-          <t>115/09/08</t>
-        </is>
-      </c>
-      <c r="J429" s="7" t="inlineStr">
-        <is>
-          <t>115/10/20</t>
-        </is>
-      </c>
-      <c r="K429" s="4" t="inlineStr">
-        <is>
-          <t>公開招標</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A2:K429"/>
+  <autoFilter ref="A2:K428"/>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -39802,7 +39749,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G426" r:id="rId424"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G427" r:id="rId425"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G428" r:id="rId426"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G429" r:id="rId427"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-17 09:24</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-17 16:42</t>
         </is>
       </c>
     </row>
@@ -16678,7 +16678,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-17 09:24</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-17 16:42</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-17 16:42</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-18 09:22</t>
         </is>
       </c>
     </row>
@@ -16678,7 +16678,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-17 16:42</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-18 09:22</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-18 09:22</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-18 16:57</t>
         </is>
       </c>
     </row>
@@ -16678,7 +16678,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-18 09:22</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-18 16:57</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-23 09:44</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-23 17:27</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-23 09:44</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-23 17:27</t>
         </is>
       </c>
     </row>
@@ -18091,7 +18091,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -18101,26 +18101,26 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>新北市汐止區公所</t>
+          <t>桃園市觀音區富林國民小學</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>SZ115-050</t>
+          <t>FLES1150901</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>115年度汐止區低地排水設備改善更新工程</t>
+          <t>富林城堡老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
-        <v>852490</v>
+        <v>2666853</v>
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
@@ -18129,12 +18129,12 @@
       </c>
       <c r="J7" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>公開取得報價單或企劃書</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -18144,7 +18144,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -18154,40 +18154,40 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處南區施工處</t>
+          <t>新北市汐止區公所</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>6561551012</t>
+          <t>SZ115-050</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>第 05 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>興達~南科線路土建統包工程(第一A工區)</t>
+          <t>115年度汐止區低地排水設備改善更新工程</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
-        <v>8470000000</v>
+        <v>852490</v>
       </c>
       <c r="I8" s="12" t="inlineStr">
         <is>
-          <t>115/10/23</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="J8" s="12" t="inlineStr">
         <is>
-          <t>115/11/24</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K8" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -18197,7 +18197,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -18207,12 +18207,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>交通部鐵道局東部工程分局</t>
+          <t>屏東縣來義鄉公所</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>RBEREO-1208</t>
+          <t>115LY1020</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -18222,25 +18222,25 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>「花東地區鐵路雙軌電氣化計畫」PB01B標干城至壽豐電車線工程</t>
+          <t>115-新來義社區出入口及既有裝置藝術增設地標投射燈工程</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
-        <v>370013111</v>
+        <v>578000</v>
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>115/10/23</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="J9" s="7" t="inlineStr">
         <is>
-          <t>115/12/01</t>
+          <t>115/10/30</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開取得報價單或企劃書</t>
         </is>
       </c>
     </row>
@@ -18250,7 +18250,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -18260,26 +18260,26 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局雲嘉南區養護工程分局</t>
+          <t>台灣電力股份有限公司輸變電工程處南區施工處</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>115100105</t>
+          <t>6561551012</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 05 次</t>
         </is>
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>台1線、台39線、台19甲線路面改善工程(第2標)</t>
+          <t>興達~南科線路土建統包工程(第一A工區)</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
-        <v>88431343</v>
+        <v>8470000000</v>
       </c>
       <c r="I10" s="12" t="inlineStr">
         <is>
@@ -18288,7 +18288,7 @@
       </c>
       <c r="J10" s="12" t="inlineStr">
         <is>
-          <t>115/11/12</t>
+          <t>115/11/24</t>
         </is>
       </c>
       <c r="K10" s="9" t="inlineStr">
@@ -18303,7 +18303,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -18313,12 +18313,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>彰化縣政府</t>
+          <t>交通部鐵道局東部工程分局</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>115-051-105-133</t>
+          <t>RBEREO-1208</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -18328,11 +18328,11 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>彰化縣北斗鎮螺陽國民小學學生活動中心新建工程</t>
+          <t>「花東地區鐵路雙軌電氣化計畫」PB01B標干城至壽豐電車線工程</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
-        <v>77524909</v>
+        <v>370013111</v>
       </c>
       <c r="I11" s="7" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
       </c>
       <c r="J11" s="7" t="inlineStr">
         <is>
-          <t>115/11/10</t>
+          <t>115/12/01</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -18366,12 +18366,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>新北市政府採購處</t>
+          <t>交通部公路局雲嘉南區養護工程分局</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>1151105-4</t>
+          <t>115100105</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -18381,11 +18381,11 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>萬里區員潭溪出河口拓寬及分洪、河道拓寬等三案改善工程</t>
+          <t>台1線、台39線、台19甲線路面改善工程(第2標)</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
-        <v>76819076</v>
+        <v>88431343</v>
       </c>
       <c r="I12" s="12" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
       </c>
       <c r="J12" s="12" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/11/12</t>
         </is>
       </c>
       <c r="K12" s="9" t="inlineStr">
@@ -18409,36 +18409,36 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>交通部高速公路局南區養護工程分局</t>
+          <t>彰化縣政府</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>115D020P006</t>
+          <t>115-051-105-133</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>116~118年度南區交通控制中心部分業務委外工作</t>
+          <t>彰化縣北斗鎮螺陽國民小學學生活動中心新建工程</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
-        <v>74831186</v>
+        <v>77524909</v>
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
@@ -18447,12 +18447,12 @@
       </c>
       <c r="J13" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/10</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -18462,7 +18462,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -18472,12 +18472,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第四區管理處</t>
+          <t>新北市政府採購處</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>11518</t>
+          <t>1151105-4</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -18487,11 +18487,11 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>沙鹿營運所管線單價採購工程(115年度開口契約)(二)</t>
+          <t>萬里區員潭溪出河口拓寬及分洪、河道拓寬等三案改善工程</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
-        <v>65000053</v>
+        <v>76819076</v>
       </c>
       <c r="I14" s="12" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
       </c>
       <c r="J14" s="12" t="inlineStr">
         <is>
-          <t>115/11/12</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K14" s="9" t="inlineStr">
@@ -18515,36 +18515,36 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府都市發展局</t>
+          <t>交通部高速公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>115B304</t>
+          <t>115D020P006</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>臺南市佳里區水綠心川廊計畫工程</t>
+          <t>116~118年度南區交通控制中心部分業務委外工作</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
-        <v>61700000</v>
+        <v>74831186</v>
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -18568,7 +18568,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>中央/中油</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -18578,26 +18578,26 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司</t>
+          <t>臺南市政府都市發展局</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>LDA1531001</t>
+          <t>115B304</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>竹南轄區管線埋設零星發包工程(115)</t>
+          <t>臺南市佳里區水綠心川廊計畫工程</t>
         </is>
       </c>
       <c r="H16" s="11" t="n">
-        <v>49160051</v>
+        <v>61700000</v>
       </c>
       <c r="I16" s="12" t="inlineStr">
         <is>
@@ -18606,7 +18606,7 @@
       </c>
       <c r="J16" s="12" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K16" s="9" t="inlineStr">
@@ -18621,7 +18621,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>中央/中油</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -18631,26 +18631,26 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>台灣中油股份有限公司</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>115A127</t>
+          <t>LDA1531001</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>新竹豐功文化推廣中心新建工程</t>
+          <t>竹南轄區管線埋設零星發包工程(115)</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
-        <v>39709164</v>
+        <v>49160051</v>
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
       </c>
       <c r="J17" s="7" t="inlineStr">
         <is>
-          <t>115/11/04</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
@@ -18674,7 +18674,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -18684,26 +18684,26 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府工務局道路養護工程處</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>11503CA019</t>
+          <t>115A127</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>中華四路(青年二路至興中二路)人行環境改善工程</t>
+          <t>新竹豐功文化推廣中心新建工程</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
-        <v>36073257</v>
+        <v>39709164</v>
       </c>
       <c r="I18" s="12" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
       </c>
       <c r="J18" s="12" t="inlineStr">
         <is>
-          <t>115/11/06</t>
+          <t>115/11/04</t>
         </is>
       </c>
       <c r="K18" s="9" t="inlineStr">
@@ -18727,7 +18727,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -18737,26 +18737,26 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>國家科學及技術委員會南部科學園區管理局</t>
+          <t>高雄市政府工務局道路養護工程處</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>115630D05968</t>
+          <t>11503CA019</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>臺南園區永康再生水高階處理等設施擴建統包工程</t>
+          <t>中華四路(青年二路至興中二路)人行環境改善工程</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
-        <v>36000356</v>
+        <v>36073257</v>
       </c>
       <c r="I19" s="7" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
       </c>
       <c r="J19" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/06</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
@@ -18780,7 +18780,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -18790,26 +18790,26 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局雲嘉南區養護工程分局</t>
+          <t>國家科學及技術委員會南部科學園區管理局</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>115100109</t>
+          <t>115630D05968</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>水上工務段台17線景觀改善工程</t>
+          <t>臺南園區永康再生水高階處理等設施擴建統包工程</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
-        <v>29936676</v>
+        <v>36000356</v>
       </c>
       <c r="I20" s="12" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
       </c>
       <c r="J20" s="12" t="inlineStr">
         <is>
-          <t>115/11/04</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K20" s="9" t="inlineStr">
@@ -18833,7 +18833,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -18843,12 +18843,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>雲林縣東勢鄉公所</t>
+          <t>交通部公路局雲嘉南區養護工程分局</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>5139-1151022</t>
+          <t>115100109</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -18858,11 +18858,11 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>東勢鄉主題運動公園建置工程（併案）</t>
+          <t>水上工務段台17線景觀改善工程</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
-        <v>29621000</v>
+        <v>29936676</v>
       </c>
       <c r="I21" s="7" t="inlineStr">
         <is>
@@ -18871,7 +18871,7 @@
       </c>
       <c r="J21" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/04</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
@@ -18886,7 +18886,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -18896,26 +18896,26 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>雲林縣東勢鄉公所</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>115-LL-25-4-002</t>
+          <t>5139-1151022</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>三地門鄉D089達來村集會所旁及達發達旺巷邊坡整治工程</t>
+          <t>東勢鄉主題運動公園建置工程（併案）</t>
         </is>
       </c>
       <c r="H22" s="11" t="n">
-        <v>29139559</v>
+        <v>29621000</v>
       </c>
       <c r="I22" s="12" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
       </c>
       <c r="J22" s="12" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K22" s="9" t="inlineStr">
@@ -18939,7 +18939,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -18949,26 +18949,26 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府工務局公園處</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>11601CA003</t>
+          <t>115-LL-25-4-002</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>亞灣濱海特色公廁工程</t>
+          <t>三地門鄉D089達來村集會所旁及達發達旺巷邊坡整治工程</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
-        <v>27450000</v>
+        <v>29139559</v>
       </c>
       <c r="I23" s="7" t="inlineStr">
         <is>
@@ -18977,7 +18977,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
@@ -18992,7 +18992,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -19002,12 +19002,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>臺北榮民總醫院玉里分院</t>
+          <t>高雄市政府工務局公園處</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>TT11510022</t>
+          <t>11601CA003</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -19017,11 +19017,11 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>115年更生院區醫療大樓建築能效改善及淨零示範工程</t>
+          <t>亞灣濱海特色公廁工程</t>
         </is>
       </c>
       <c r="H24" s="11" t="n">
-        <v>24905114</v>
+        <v>27450000</v>
       </c>
       <c r="I24" s="12" t="inlineStr">
         <is>
@@ -19030,7 +19030,7 @@
       </c>
       <c r="J24" s="12" t="inlineStr">
         <is>
-          <t>115/11/09</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K24" s="9" t="inlineStr">
@@ -19045,7 +19045,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -19055,26 +19055,26 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局北區養護工程分局</t>
+          <t>臺北榮民總醫院玉里分院</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>1161A1A08</t>
+          <t>TT11510022</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>景美段116年台9線預約及北分局轄區備援災害搶修工程</t>
+          <t>115年更生院區醫療大樓建築能效改善及淨零示範工程</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
-        <v>23710281</v>
+        <v>24905114</v>
       </c>
       <c r="I25" s="7" t="inlineStr">
         <is>
@@ -19083,7 +19083,7 @@
       </c>
       <c r="J25" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/09</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
@@ -19098,7 +19098,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -19108,26 +19108,26 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>交通部高速公路局南區養護工程分局</t>
+          <t>交通部公路局北區養護工程分局</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>115D010P023</t>
+          <t>1161A1A08</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>屏東段轄區護欄柵欄及界樁維護工程(116)</t>
+          <t>景美段116年台9線預約及北分局轄區備援災害搶修工程</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
-        <v>22136380</v>
+        <v>23710281</v>
       </c>
       <c r="I26" s="12" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
       </c>
       <c r="J26" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K26" s="9" t="inlineStr">
@@ -19151,7 +19151,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -19161,12 +19161,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第五河川分署</t>
+          <t>交通部高速公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>116-I-01010-002-126</t>
+          <t>115D010P023</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -19176,11 +19176,11 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>116年度急水溪水系緊急搶險(修)工程 (開口契約)</t>
+          <t>屏東段轄區護欄柵欄及界樁維護工程(116)</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
-        <v>20137000</v>
+        <v>22136380</v>
       </c>
       <c r="I27" s="7" t="inlineStr">
         <is>
@@ -19189,7 +19189,7 @@
       </c>
       <c r="J27" s="7" t="inlineStr">
         <is>
-          <t>115/11/04</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
@@ -19214,26 +19214,26 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局北區養護工程分局</t>
+          <t>經濟部水利署第五河川分署</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>1161A1A09</t>
+          <t>116-I-01010-002-126</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>景美段116年台2線0K-52K、台2甲線、台2乙線預約及北分局轄區備援災害搶修工程</t>
+          <t>116年度急水溪水系緊急搶險(修)工程 (開口契約)</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
-        <v>18537930</v>
+        <v>20137000</v>
       </c>
       <c r="I28" s="12" t="inlineStr">
         <is>
@@ -19242,7 +19242,7 @@
       </c>
       <c r="J28" s="12" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/04</t>
         </is>
       </c>
       <c r="K28" s="9" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>1161A1A10</t>
+          <t>1161A1A09</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -19282,11 +19282,11 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>景美段116年台2線0K-52K、台2甲線、台2乙線預約災害修復工程</t>
+          <t>景美段116年台2線0K-52K、台2甲線、台2乙線預約及北分局轄區備援災害搶修工程</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
-        <v>18340776</v>
+        <v>18537930</v>
       </c>
       <c r="I29" s="7" t="inlineStr">
         <is>
@@ -19310,36 +19310,36 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府環境保護局</t>
+          <t>交通部公路局北區養護工程分局</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>H16021</t>
+          <t>1161A1A10</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>116年高雄市環境教育宣導計畫</t>
+          <t>景美段116年台2線0K-52K、台2甲線、台2乙線預約災害修復工程</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
-        <v>17742000</v>
+        <v>18340776</v>
       </c>
       <c r="I30" s="12" t="inlineStr">
         <is>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="J30" s="12" t="inlineStr">
         <is>
-          <t>115/11/23</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -19363,22 +19363,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>雲林縣水林鄉公所</t>
+          <t>高雄市政府環境保護局</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>115046</t>
+          <t>H16021</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -19388,11 +19388,11 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>水林鄉115年度轄内公路設施經常性零星修復及搶修搶險工程 (第二期)(開口契約)</t>
+          <t>116年高雄市環境教育宣導計畫</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
-        <v>16874500</v>
+        <v>17742000</v>
       </c>
       <c r="I31" s="7" t="inlineStr">
         <is>
@@ -19401,12 +19401,12 @@
       </c>
       <c r="J31" s="7" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/11/23</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -19416,7 +19416,7 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
@@ -19426,12 +19426,12 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府水利局</t>
+          <t>雲林縣水林鄉公所</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>C1151003</t>
+          <t>115046</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -19441,11 +19441,11 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>桃源部落屋後邊坡擋土設施災後復建工程(水利設施)</t>
+          <t>水林鄉115年度轄内公路設施經常性零星修復及搶修搶險工程 (第二期)(開口契約)</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
-        <v>15931050</v>
+        <v>16874500</v>
       </c>
       <c r="I32" s="12" t="inlineStr">
         <is>
@@ -19474,31 +19474,31 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>內政部移民署</t>
+          <t>高雄市政府水利局</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>3-1150968</t>
+          <t>C1151003</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>116年高雄庇護所安置保護委外服務案</t>
+          <t>桃源部落屋後邊坡擋土設施災後復建工程(水利設施)</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
-        <v>14579081</v>
+        <v>15931050</v>
       </c>
       <c r="I33" s="7" t="inlineStr">
         <is>
@@ -19507,12 +19507,12 @@
       </c>
       <c r="J33" s="7" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -19522,36 +19522,36 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>臺南市動物防疫保護處</t>
+          <t>內政部移民署</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>O-1151001</t>
+          <t>3-1150968</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>臺南市設置遊蕩犬暫置區及臨時性設施工程(開口契約)</t>
+          <t>116年高雄庇護所安置保護委外服務案</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
-        <v>12815000</v>
+        <v>14579081</v>
       </c>
       <c r="I34" s="12" t="inlineStr">
         <is>
@@ -19560,12 +19560,12 @@
       </c>
       <c r="J34" s="12" t="inlineStr">
         <is>
-          <t>115/11/06</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K34" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -19575,7 +19575,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -19585,12 +19585,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>臺南市動物防疫保護處</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>060801-115407</t>
+          <t>O-1151001</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -19600,11 +19600,11 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>116年度桃園市政府養護工程處轄管公園遊具及體健設施修繕工程(開口契約)</t>
+          <t>臺南市設置遊蕩犬暫置區及臨時性設施工程(開口契約)</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
-        <v>12000000</v>
+        <v>12815000</v>
       </c>
       <c r="I35" s="7" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
       </c>
       <c r="J35" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/06</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
@@ -19628,22 +19628,22 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司高屏發電廠</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>2711500008</t>
+          <t>060801-115407</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -19653,11 +19653,11 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>高屏發電廠六龜新進水口排砂門水工機械修復工作</t>
+          <t>116年度桃園市政府養護工程處轄管公園遊具及體健設施修繕工程(開口契約)</t>
         </is>
       </c>
       <c r="H36" s="11" t="n">
-        <v>9975000</v>
+        <v>12000000</v>
       </c>
       <c r="I36" s="12" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
       </c>
       <c r="J36" s="12" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K36" s="9" t="inlineStr">
@@ -19681,7 +19681,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -19691,26 +19691,26 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>台灣電力股份有限公司高屏發電廠</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>DC11507010012</t>
+          <t>2711500008</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>115年高雄所及鳳山所供水監測設備維護開口契約</t>
+          <t>高屏發電廠六龜新進水口排砂門水工機械修復工作</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
-        <v>9923286</v>
+        <v>9975000</v>
       </c>
       <c r="I37" s="7" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
       </c>
       <c r="J37" s="7" t="inlineStr">
         <is>
-          <t>115/11/06</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
@@ -19739,31 +19739,31 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>明陽中學</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>MYG115009</t>
+          <t>DC11507010012</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>116年上半年度高雄二區矯正機關收容人副食品聯合採購- 肉品類</t>
+          <t>115年高雄所及鳳山所供水監測設備維護開口契約</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
-        <v>9621540</v>
+        <v>9923286</v>
       </c>
       <c r="I38" s="12" t="inlineStr">
         <is>
@@ -19787,22 +19787,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>新北市林口區公所</t>
+          <t>明陽中學</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>115-030</t>
+          <t>MYG115009</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -19812,11 +19812,11 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>115-116年行道樹綠美學及樹木傾倒復舊工程(開口契約)</t>
+          <t>116年上半年度高雄二區矯正機關收容人副食品聯合採購- 肉品類</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
-        <v>9258848</v>
+        <v>9621540</v>
       </c>
       <c r="I39" s="7" t="inlineStr">
         <is>
@@ -19825,7 +19825,7 @@
       </c>
       <c r="J39" s="7" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/11/06</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
@@ -19840,22 +19840,22 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府環境保護局</t>
+          <t>新北市林口區公所</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>H16022</t>
+          <t>115-030</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -19865,11 +19865,11 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>116年度高雄市有害空氣污染物質暨毒性及關注化學物質源頭查核管理計畫</t>
+          <t>115-116年行道樹綠美學及樹木傾倒復舊工程(開口契約)</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
-        <v>9227000</v>
+        <v>9258848</v>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
@@ -19878,12 +19878,12 @@
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>115/11/23</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>經公開評選或公開徵求之限制性招標</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -19893,22 +19893,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司屏東區管理處</t>
+          <t>高雄市政府環境保護局</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>WR11513500015</t>
+          <t>H16022</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -19918,11 +19918,11 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>恆春營運所管有房舍整修資產活化工程</t>
+          <t>116年度高雄市有害空氣污染物質暨毒性及關注化學物質源頭查核管理計畫</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
-        <v>9111933</v>
+        <v>9227000</v>
       </c>
       <c r="I41" s="7" t="inlineStr">
         <is>
@@ -19931,12 +19931,12 @@
       </c>
       <c r="J41" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/23</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>經公開評選或公開徵求之限制性招標</t>
         </is>
       </c>
     </row>
@@ -19946,7 +19946,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -19956,26 +19956,26 @@
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局南區養護工程分局</t>
+          <t>台灣自來水股份有限公司屏東區管理處</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>1153067533</t>
+          <t>WR11513500015</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>楓港工務段楓港監工站116年度省道預約經常性公路零星修復工程</t>
+          <t>恆春營運所管有房舍整修資產活化工程</t>
         </is>
       </c>
       <c r="H42" s="11" t="n">
-        <v>9089078</v>
+        <v>9111933</v>
       </c>
       <c r="I42" s="12" t="inlineStr">
         <is>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K42" s="9" t="inlineStr">
@@ -19999,12 +19999,12 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>勞務類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1155026910</t>
+          <t>1153067533</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -20024,11 +20024,11 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>高雄工務段岡山監工站轄區116年度台1線、台19甲線、台28線綠美化維護工作</t>
+          <t>楓港工務段楓港監工站116年度省道預約經常性公路零星修復工程</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
-        <v>9077984</v>
+        <v>9089078</v>
       </c>
       <c r="I43" s="7" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
       </c>
       <c r="J43" s="7" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
@@ -20052,36 +20052,36 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局北區養護工程分局</t>
+          <t>交通部公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>1161A1C23</t>
+          <t>1155026910</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>中壢段快速公路側車道防護網、側溝等附屬設施改善工程</t>
+          <t>高雄工務段岡山監工站轄區116年度台1線、台19甲線、台28線綠美化維護工作</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
-        <v>8440411</v>
+        <v>9077984</v>
       </c>
       <c r="I44" s="12" t="inlineStr">
         <is>
@@ -20090,7 +20090,7 @@
       </c>
       <c r="J44" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K44" s="9" t="inlineStr">
@@ -20105,7 +20105,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -20115,12 +20115,12 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>高雄市田寮區公所</t>
+          <t>交通部公路局北區養護工程分局</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1151034</t>
+          <t>1161A1C23</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -20130,11 +20130,11 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>高雄市田寮區115年8月豪雨災後搶修工程(開口契約)</t>
+          <t>中壢段快速公路側車道防護網、側溝等附屬設施改善工程</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
-        <v>8375002</v>
+        <v>8440411</v>
       </c>
       <c r="I45" s="7" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
       </c>
       <c r="J45" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
@@ -20158,7 +20158,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -20168,12 +20168,12 @@
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>嘉義縣立竹崎高級中學</t>
+          <t>高雄市田寮區公所</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>1151020</t>
+          <t>1151034</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -20183,11 +20183,11 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>嘉義縣立竹崎高中教育部補助運動場整修工程</t>
+          <t>高雄市田寮區115年8月豪雨災後搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
-        <v>8196487</v>
+        <v>8375002</v>
       </c>
       <c r="I46" s="12" t="inlineStr">
         <is>
@@ -20196,7 +20196,7 @@
       </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K46" s="9" t="inlineStr">
@@ -20211,22 +20211,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>明陽中學</t>
+          <t>嘉義縣立竹崎高級中學</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>MYG115007</t>
+          <t>1151020</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -20236,11 +20236,11 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>116年上半年度高雄二區矯正機關收容人副食品聯合採購- 雞鴨肉類</t>
+          <t>嘉義縣立竹崎高中教育部補助運動場整修工程</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
-        <v>7931250</v>
+        <v>8196487</v>
       </c>
       <c r="I47" s="7" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
       </c>
       <c r="J47" s="7" t="inlineStr">
         <is>
-          <t>115/11/06</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
@@ -20264,22 +20264,22 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>明陽中學</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>141-F1151022-1</t>
+          <t>MYG115007</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -20289,11 +20289,11 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>(115年06月豪雨)萬丹鄉萬丹排水中興橋上下游災後復建工程</t>
+          <t>116年上半年度高雄二區矯正機關收容人副食品聯合採購- 雞鴨肉類</t>
         </is>
       </c>
       <c r="H48" s="11" t="n">
-        <v>7838000</v>
+        <v>7931250</v>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
@@ -20302,7 +20302,7 @@
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/06</t>
         </is>
       </c>
       <c r="K48" s="9" t="inlineStr">
@@ -20317,7 +20317,7 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
@@ -20327,26 +20327,26 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>桃園市龜山區文華國民小學</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>c0813-11506</t>
+          <t>141-F1151022-1</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>「114-116年度公立國民中小學老舊廁所整修工程」-「文善樓廁所整修工程」</t>
+          <t>(115年06月豪雨)萬丹鄉萬丹排水中興橋上下游災後復建工程</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
-        <v>7553966</v>
+        <v>7838000</v>
       </c>
       <c r="I49" s="7" t="inlineStr">
         <is>
@@ -20355,7 +20355,7 @@
       </c>
       <c r="J49" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
@@ -20370,7 +20370,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -20380,26 +20380,26 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>臺中市養護工程處</t>
+          <t>桃園市龜山區文華國民小學</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>115A-172</t>
+          <t>c0813-11506</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>臺中市沙鹿區保順一街、自強路等二件道路改善工程</t>
+          <t>「114-116年度公立國民中小學老舊廁所整修工程」-「文善樓廁所整修工程」</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
-        <v>7219200</v>
+        <v>7553966</v>
       </c>
       <c r="I50" s="12" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
       </c>
       <c r="J50" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K50" s="9" t="inlineStr">
@@ -20423,7 +20423,7 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
@@ -20433,26 +20433,26 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>臺中市養護工程處</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>115A130</t>
+          <t>115A-172</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>新竹市115年度市管道路用地維護管理暨道路側溝新設工程(開口契約)</t>
+          <t>臺中市沙鹿區保順一街、自強路等二件道路改善工程</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
-        <v>7200000</v>
+        <v>7219200</v>
       </c>
       <c r="I51" s="7" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
       </c>
       <c r="J51" s="7" t="inlineStr">
         <is>
-          <t>115/11/04</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
@@ -20476,7 +20476,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -20486,26 +20486,26 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>A077-1151022-1</t>
+          <t>115A130</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>(115)泰武鄉北大武山登山口公廁興建及周邊景觀優化工程</t>
+          <t>新竹市115年度市管道路用地維護管理暨道路側溝新設工程(開口契約)</t>
         </is>
       </c>
       <c r="H52" s="11" t="n">
-        <v>7187000</v>
+        <v>7200000</v>
       </c>
       <c r="I52" s="12" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
       </c>
       <c r="J52" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/04</t>
         </is>
       </c>
       <c r="K52" s="9" t="inlineStr">
@@ -20529,7 +20529,7 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
@@ -20539,12 +20539,12 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>彰化縣政府</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>115-171-206-131</t>
+          <t>A077-1151022-1</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -20554,11 +20554,11 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>115年7月巴威颱風秀水鄉安東二排(馬鳴段1391地號旁)災修工程</t>
+          <t>(115)泰武鄉北大武山登山口公廁興建及周邊景觀優化工程</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
-        <v>7148000</v>
+        <v>7187000</v>
       </c>
       <c r="I53" s="7" t="inlineStr">
         <is>
@@ -20567,7 +20567,7 @@
       </c>
       <c r="J53" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
@@ -20582,7 +20582,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -20592,12 +20592,12 @@
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>國防部軍備局生產製造中心</t>
+          <t>彰化縣政府</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>116AO20501170000320</t>
+          <t>115-171-206-131</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -20607,11 +20607,11 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>098號房屋等區域修繕工程</t>
+          <t>115年7月巴威颱風秀水鄉安東二排(馬鳴段1391地號旁)災修工程</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
-        <v>7000000</v>
+        <v>7148000</v>
       </c>
       <c r="I54" s="12" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
       </c>
       <c r="J54" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K54" s="9" t="inlineStr">
@@ -20635,7 +20635,7 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -20645,12 +20645,12 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第九河川分署</t>
+          <t>國防部軍備局生產製造中心</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>116-I-01010-002-154</t>
+          <t>116AO20501170000320</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -20660,11 +20660,11 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>116年度秀姑巒溪水系及花蓮南段海岸緊急搶險(修)工程(開口契約)</t>
+          <t>098號房屋等區域修繕工程</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
-        <v>6820000</v>
+        <v>7000000</v>
       </c>
       <c r="I55" s="7" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
       </c>
       <c r="J55" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
@@ -20688,22 +20688,22 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>財物類</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>明陽中學</t>
+          <t>經濟部水利署第九河川分署</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>MYG115008</t>
+          <t>116-I-01010-002-154</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -20713,11 +20713,11 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>116年上半年度高雄二區矯正機關收容人副食品聯合採購- 魚產類</t>
+          <t>116年度秀姑巒溪水系及花蓮南段海岸緊急搶險(修)工程(開口契約)</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
-        <v>6536100</v>
+        <v>6820000</v>
       </c>
       <c r="I56" s="12" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="J56" s="12" t="inlineStr">
         <is>
-          <t>115/11/06</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K56" s="9" t="inlineStr">
@@ -20741,22 +20741,22 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>新竹縣關西鎮公所</t>
+          <t>明陽中學</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>115WEI-09</t>
+          <t>MYG115008</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -20766,11 +20766,11 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>114-115 年度「城鎮風貌及創生環境營造計畫」-115年新竹縣關西鎮牛欄河西側(親水橋至東安橋)休憩步道改善工程</t>
+          <t>116年上半年度高雄二區矯正機關收容人副食品聯合採購- 魚產類</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
-        <v>6322000</v>
+        <v>6536100</v>
       </c>
       <c r="I57" s="7" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
       </c>
       <c r="J57" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/06</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
@@ -20794,7 +20794,7 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -20804,12 +20804,12 @@
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺南分署</t>
+          <t>新竹縣關西鎮公所</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>115-ADE-49-4-009</t>
+          <t>115WEI-09</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -20819,11 +20819,11 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>東勢埔段1285等地號旁野溪整治工程</t>
+          <t>114-115 年度「城鎮風貌及創生環境營造計畫」-115年新竹縣關西鎮牛欄河西側(親水橋至東安橋)休憩步道改善工程</t>
         </is>
       </c>
       <c r="H58" s="11" t="n">
-        <v>6206447</v>
+        <v>6322000</v>
       </c>
       <c r="I58" s="12" t="inlineStr">
         <is>
@@ -20832,7 +20832,7 @@
       </c>
       <c r="J58" s="12" t="inlineStr">
         <is>
-          <t>115/11/04</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K58" s="9" t="inlineStr">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
@@ -20857,26 +20857,26 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉公所</t>
+          <t>農業部農村發展及水土保持署臺南分署</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>115-01-01</t>
+          <t>115-ADE-49-4-009</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>第 13 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Danas-H-01-07-10-金針山觀光產業道路及農路災害復建合併工程</t>
+          <t>東勢埔段1285等地號旁野溪整治工程</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
-        <v>6169331</v>
+        <v>6206447</v>
       </c>
       <c r="I59" s="7" t="inlineStr">
         <is>
@@ -20885,7 +20885,7 @@
       </c>
       <c r="J59" s="7" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/11/04</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
@@ -20900,7 +20900,7 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
@@ -20910,26 +20910,26 @@
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>雲林縣麥寮鄉橋頭國民小學</t>
+          <t>臺東縣太麻里鄉公所</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>A1151020</t>
+          <t>115-01-01</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 13 次</t>
         </is>
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>115年度整建計畫-雲林縣橋頭國小許厝分校新建五人制人工草皮足球場新建工程</t>
+          <t>Danas-H-01-07-10-金針山觀光產業道路及農路災害復建合併工程</t>
         </is>
       </c>
       <c r="H60" s="11" t="n">
-        <v>6082462</v>
+        <v>6169331</v>
       </c>
       <c r="I60" s="12" t="inlineStr">
         <is>
@@ -20938,7 +20938,7 @@
       </c>
       <c r="J60" s="12" t="inlineStr">
         <is>
-          <t>115/11/04</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K60" s="9" t="inlineStr">
@@ -20953,7 +20953,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -20963,12 +20963,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣富里鄉富里國民小學</t>
+          <t>雲林縣麥寮鄉橋頭國民小學</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>fulps115-06</t>
+          <t>A1151020</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -20978,11 +20978,11 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>富里國小115年度改善偏遠地區國民中小學教師宿舍工程</t>
+          <t>115年度整建計畫-雲林縣橋頭國小許厝分校新建五人制人工草皮足球場新建工程</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
-        <v>5864257</v>
+        <v>6082462</v>
       </c>
       <c r="I61" s="7" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
       </c>
       <c r="J61" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/04</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
@@ -21006,7 +21006,7 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
@@ -21016,12 +21016,12 @@
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>彰化縣政府</t>
+          <t>花蓮縣富里鄉富里國民小學</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>115-171-211-131</t>
+          <t>fulps115-06</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -21031,11 +21031,11 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>115年7月巴威颱風線西鄉田尾排水災修工程</t>
+          <t>富里國小115年度改善偏遠地區國民中小學教師宿舍工程</t>
         </is>
       </c>
       <c r="H62" s="11" t="n">
-        <v>5634000</v>
+        <v>5864257</v>
       </c>
       <c r="I62" s="12" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
@@ -21069,12 +21069,12 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>南投縣仁愛鄉公所</t>
+          <t>彰化縣政府</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>1150510264</t>
+          <t>115-171-211-131</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -21084,11 +21084,11 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>115年4月豪雨A1-006華崗簡易自來水系統災修復建工程</t>
+          <t>115年7月巴威颱風線西鄉田尾排水災修工程</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
-        <v>5574000</v>
+        <v>5634000</v>
       </c>
       <c r="I63" s="7" t="inlineStr">
         <is>
@@ -21097,7 +21097,7 @@
       </c>
       <c r="J63" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
@@ -21122,12 +21122,12 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>南投縣魚池鄉公所</t>
+          <t>南投縣仁愛鄉公所</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>11510201A</t>
+          <t>1150510264</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -21137,11 +21137,11 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>魚池鄉共和村長興巷周邊環境改善工程(115RMA-021-001)</t>
+          <t>115年4月豪雨A1-006華崗簡易自來水系統災修復建工程</t>
         </is>
       </c>
       <c r="H64" s="11" t="n">
-        <v>5390000</v>
+        <v>5574000</v>
       </c>
       <c r="I64" s="12" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
       </c>
       <c r="J64" s="12" t="inlineStr">
         <is>
-          <t>115/11/04</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K64" s="9" t="inlineStr">
@@ -21165,7 +21165,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -21175,12 +21175,12 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>桃園市龜山區幸福國民小學</t>
+          <t>南投縣魚池鄉公所</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>A115-1001</t>
+          <t>11510201A</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -21190,11 +21190,11 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>114年公立國民中小學老舊廁所整修工程</t>
+          <t>魚池鄉共和村長興巷周邊環境改善工程(115RMA-021-001)</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
-        <v>5051193</v>
+        <v>5390000</v>
       </c>
       <c r="I65" s="7" t="inlineStr">
         <is>
@@ -21203,7 +21203,7 @@
       </c>
       <c r="J65" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/04</t>
         </is>
       </c>
       <c r="K65" s="4" t="inlineStr">
@@ -21218,7 +21218,7 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
@@ -21228,26 +21228,26 @@
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮州國民小學</t>
+          <t>桃園市龜山區幸福國民小學</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>cjps11510toilet</t>
+          <t>A115-1001</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮州國民小學 「114-116公立國民中小學老舊廁所整修工程」採購案</t>
+          <t>114年公立國民中小學老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H66" s="11" t="n">
-        <v>4765568</v>
+        <v>5051193</v>
       </c>
       <c r="I66" s="12" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
       </c>
       <c r="J66" s="12" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K66" s="9" t="inlineStr">
@@ -21271,7 +21271,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
@@ -21281,26 +21281,26 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市僑善國民小學</t>
+          <t>屏東縣潮州鎮潮州國民小學</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>CS1151023</t>
+          <t>cjps11510toilet</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>僑善國小115年度校舍油漆粉刷工程</t>
+          <t>屏東縣潮州鎮潮州國民小學 「114-116公立國民中小學老舊廁所整修工程」採購案</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
-        <v>4675587</v>
+        <v>4765568</v>
       </c>
       <c r="I67" s="7" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
       </c>
       <c r="J67" s="7" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K67" s="4" t="inlineStr">
@@ -21324,7 +21324,7 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
@@ -21334,26 +21334,26 @@
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>桃園市立楊明國民中學</t>
+          <t>苗栗縣頭份市僑善國民小學</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>11503A</t>
+          <t>CS1151023</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>育賢樓西北側老舊廁所整修工程採購</t>
+          <t>僑善國小115年度校舍油漆粉刷工程</t>
         </is>
       </c>
       <c r="H68" s="11" t="n">
-        <v>4602973</v>
+        <v>4675587</v>
       </c>
       <c r="I68" s="12" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
       </c>
       <c r="J68" s="12" t="inlineStr">
         <is>
-          <t>115/10/27</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K68" s="9" t="inlineStr">
@@ -21377,7 +21377,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
@@ -21387,26 +21387,26 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府工務局公園處</t>
+          <t>桃園市立楊明國民中學</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>11603CA003</t>
+          <t>11503A</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>高雄市鳥松區澄清湖烤肉區公廁整修工程</t>
+          <t>育賢樓西北側老舊廁所整修工程採購</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
-        <v>4156000</v>
+        <v>4602973</v>
       </c>
       <c r="I69" s="7" t="inlineStr">
         <is>
@@ -21415,7 +21415,7 @@
       </c>
       <c r="J69" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/27</t>
         </is>
       </c>
       <c r="K69" s="4" t="inlineStr">
@@ -21430,7 +21430,7 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
@@ -21440,12 +21440,12 @@
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>高雄市政府工務局公園處</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>115097G</t>
+          <t>11603CA003</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -21455,11 +21455,11 @@
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>三灣鄉大坪村石爺廟旁野溪災害復建工程</t>
+          <t>高雄市鳥松區澄清湖烤肉區公廁整修工程</t>
         </is>
       </c>
       <c r="H70" s="11" t="n">
-        <v>4145000</v>
+        <v>4156000</v>
       </c>
       <c r="I70" s="12" t="inlineStr">
         <is>
@@ -21468,7 +21468,7 @@
       </c>
       <c r="J70" s="12" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K70" s="9" t="inlineStr">
@@ -21483,7 +21483,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -21493,12 +21493,12 @@
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>彰化縣田尾鄉公所</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>115-35</t>
+          <t>115097G</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -21508,11 +21508,11 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>田尾鄉怡心園地坪改善工程</t>
+          <t>三灣鄉大坪村石爺廟旁野溪災害復建工程</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
-        <v>4046000</v>
+        <v>4145000</v>
       </c>
       <c r="I71" s="7" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -21546,12 +21546,12 @@
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>彰化縣田尾鄉公所</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>115FB11511143500610</t>
+          <t>115-35</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -21561,11 +21561,11 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>高雄市「實踐七村」坐落鼓山區鼓山二路37巷66附1號等3棟空置眷舍拆除工程</t>
+          <t>田尾鄉怡心園地坪改善工程</t>
         </is>
       </c>
       <c r="H72" s="11" t="n">
-        <v>4041600</v>
+        <v>4046000</v>
       </c>
       <c r="I72" s="12" t="inlineStr">
         <is>
@@ -21574,7 +21574,7 @@
       </c>
       <c r="J72" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K72" s="9" t="inlineStr">
@@ -21589,7 +21589,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -21599,26 +21599,26 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署南投分署</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>115-ADE-34-3-003</t>
+          <t>115FB11511143500610</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>第 05 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>嘉縣DF044中和支線坑溝整治工程</t>
+          <t>高雄市「實踐七村」坐落鼓山區鼓山二路37巷66附1號等3棟空置眷舍拆除工程</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
-        <v>4035000</v>
+        <v>4041600</v>
       </c>
       <c r="I73" s="7" t="inlineStr">
         <is>
@@ -21627,7 +21627,7 @@
       </c>
       <c r="J73" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K73" s="4" t="inlineStr">
@@ -21652,26 +21652,26 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>國立金門大學</t>
+          <t>農業部農村發展及水土保持署南投分署</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>115NQU107</t>
+          <t>115-ADE-34-3-003</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 05 次</t>
         </is>
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>國立金門大學綜合大樓2、3樓後側廁所整修工程</t>
+          <t>嘉縣DF044中和支線坑溝整治工程</t>
         </is>
       </c>
       <c r="H74" s="11" t="n">
-        <v>3929379</v>
+        <v>4035000</v>
       </c>
       <c r="I74" s="12" t="inlineStr">
         <is>
@@ -21680,7 +21680,7 @@
       </c>
       <c r="J74" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K74" s="9" t="inlineStr">
@@ -21705,12 +21705,12 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>國立清華大學</t>
+          <t>國立金門大學</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>CHYTEST1150901</t>
+          <t>115NQU107</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -21720,11 +21720,11 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>美術館外圍景觀統包工程</t>
+          <t>國立金門大學綜合大樓2、3樓後側廁所整修工程</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
-        <v>3828088</v>
+        <v>3929379</v>
       </c>
       <c r="I75" s="7" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
       </c>
       <c r="J75" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K75" s="4" t="inlineStr">
@@ -21758,12 +21758,12 @@
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>國立清華大學</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>115098G</t>
+          <t>CHYTEST1150901</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -21773,11 +21773,11 @@
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>1115年4月豪雨南庄鄉獅山村4鄰田美105號附近野溪災害復建工程</t>
+          <t>美術館外圍景觀統包工程</t>
         </is>
       </c>
       <c r="H76" s="11" t="n">
-        <v>3792000</v>
+        <v>3828088</v>
       </c>
       <c r="I76" s="12" t="inlineStr">
         <is>
@@ -21811,12 +21811,12 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮中山國民小學</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>js1151022</t>
+          <t>115098G</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -21826,11 +21826,11 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>教學樓補領使照舊有設施設備拆除及改善工程</t>
+          <t>1115年4月豪雨南庄鄉獅山村4鄰田美105號附近野溪災害復建工程</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
-        <v>3687606</v>
+        <v>3792000</v>
       </c>
       <c r="I77" s="7" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
       </c>
       <c r="J77" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K77" s="4" t="inlineStr">
@@ -21854,7 +21854,7 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
@@ -21864,26 +21864,26 @@
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>高雄市立社會教育館</t>
+          <t>苗栗縣苑裡鎮中山國民小學</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>kmsec115-29</t>
+          <t>js1151022</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>高雄市立社教館溜冰場女廁整修工程暨男廁整修工程</t>
+          <t>教學樓補領使照舊有設施設備拆除及改善工程</t>
         </is>
       </c>
       <c r="H78" s="11" t="n">
-        <v>3500000</v>
+        <v>3687606</v>
       </c>
       <c r="I78" s="12" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
       </c>
       <c r="J78" s="12" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K78" s="9" t="inlineStr">
@@ -21907,7 +21907,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
@@ -21917,26 +21917,26 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉公所</t>
+          <t>高雄市立社會教育館</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>115-44</t>
+          <t>kmsec115-29</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>第 05 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>114-115年度太麻里鄉蓄水池興建工程</t>
+          <t>高雄市立社教館溜冰場女廁整修工程暨男廁整修工程</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
-        <v>3112862</v>
+        <v>3500000</v>
       </c>
       <c r="I79" s="7" t="inlineStr">
         <is>
@@ -21975,21 +21975,21 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>115-19</t>
+          <t>115-44</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>第 20 次</t>
+          <t>第 05 次</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Danas-H-01-07-10-三和村9鄰及秀山支線農路災害復建合併工程</t>
+          <t>114-115年度太麻里鄉蓄水池興建工程</t>
         </is>
       </c>
       <c r="H80" s="11" t="n">
-        <v>2994989</v>
+        <v>3112862</v>
       </c>
       <c r="I80" s="12" t="inlineStr">
         <is>
@@ -22013,7 +22013,7 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
@@ -22023,26 +22023,26 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府社會局</t>
+          <t>臺東縣太麻里鄉公所</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>115-19</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 20 次</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>高雄市政府社會局辦理高雄市三民街友服務中心修繕工程</t>
+          <t>Danas-H-01-07-10-三和村9鄰及秀山支線農路災害復建合併工程</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
-        <v>2891826</v>
+        <v>2994989</v>
       </c>
       <c r="I81" s="7" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
       </c>
       <c r="J81" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K81" s="4" t="inlineStr">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -22076,12 +22076,12 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>臺北市立中山國民中學</t>
+          <t>高雄市政府社會局</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>TPZS115017</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -22091,11 +22091,11 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>116學年度新設數理資優班教室整修工程採購案</t>
+          <t>高雄市政府社會局辦理高雄市三民街友服務中心修繕工程</t>
         </is>
       </c>
       <c r="H82" s="11" t="n">
-        <v>2702669</v>
+        <v>2891826</v>
       </c>
       <c r="I82" s="12" t="inlineStr">
         <is>
@@ -22104,7 +22104,7 @@
       </c>
       <c r="J82" s="12" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K82" s="9" t="inlineStr">
@@ -22119,7 +22119,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -22129,26 +22129,26 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>雲林縣私立東南國民中學</t>
+          <t>臺北市立中山國民中學</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>A114001-2</t>
+          <t>TPZS115017</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>老舊廁所整修工程-至真樓</t>
+          <t>116學年度新設數理資優班教室整修工程採購案</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
-        <v>2485107</v>
+        <v>2702669</v>
       </c>
       <c r="I83" s="7" t="inlineStr">
         <is>
@@ -22157,7 +22157,7 @@
       </c>
       <c r="J83" s="7" t="inlineStr">
         <is>
-          <t>115/11/04</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K83" s="4" t="inlineStr">
@@ -22172,7 +22172,7 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
@@ -22182,26 +22182,26 @@
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>臺南市善化區公所</t>
+          <t>雲林縣私立東南國民中學</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>115061</t>
+          <t>A114001-2</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>善化區什乃集會所廁所新建工程</t>
+          <t>老舊廁所整修工程-至真樓</t>
         </is>
       </c>
       <c r="H84" s="11" t="n">
-        <v>2474714</v>
+        <v>2485107</v>
       </c>
       <c r="I84" s="12" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
       </c>
       <c r="J84" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/04</t>
         </is>
       </c>
       <c r="K84" s="9" t="inlineStr">
@@ -22225,7 +22225,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -22235,26 +22235,26 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>彰化縣秀水鄉公所</t>
+          <t>臺南市善化區公所</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>115017</t>
+          <t>115061</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>秀水鄉花秀路(崙雅排水)橋梁修繕工程</t>
+          <t>善化區什乃集會所廁所新建工程</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
-        <v>2467500</v>
+        <v>2474714</v>
       </c>
       <c r="I85" s="7" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
       </c>
       <c r="J85" s="7" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K85" s="4" t="inlineStr">
@@ -22278,7 +22278,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -22288,26 +22288,26 @@
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>高雄市美濃區公所</t>
+          <t>彰化縣秀水鄉公所</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>115-10-21-1</t>
+          <t>115017</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>(115年4月豪雨)美濃區八德排水上游護岸災害復建工程</t>
+          <t>秀水鄉花秀路(崙雅排水)橋梁修繕工程</t>
         </is>
       </c>
       <c r="H86" s="11" t="n">
-        <v>2437708</v>
+        <v>2467500</v>
       </c>
       <c r="I86" s="12" t="inlineStr">
         <is>
@@ -22316,7 +22316,7 @@
       </c>
       <c r="J86" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K86" s="9" t="inlineStr">
@@ -22331,7 +22331,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
@@ -22341,26 +22341,26 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉公所</t>
+          <t>高雄市美濃區公所</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>115-21-01</t>
+          <t>115-10-21-1</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Danas-H-01-07-10-大溪農路及排水溝道路災害復建合併工程</t>
+          <t>(115年4月豪雨)美濃區八德排水上游護岸災害復建工程</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
-        <v>2393543</v>
+        <v>2437708</v>
       </c>
       <c r="I87" s="7" t="inlineStr">
         <is>
@@ -22369,7 +22369,7 @@
       </c>
       <c r="J87" s="7" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K87" s="4" t="inlineStr">
@@ -22394,26 +22394,26 @@
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>南投縣仁愛鄉公所</t>
+          <t>臺東縣太麻里鄉公所</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>1150510265</t>
+          <t>115-21-01</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>115年4月豪雨A1-005力行村溫泉部落簡易自來水災修復建工程</t>
+          <t>Danas-H-01-07-10-大溪農路及排水溝道路災害復建合併工程</t>
         </is>
       </c>
       <c r="H88" s="11" t="n">
-        <v>2349000</v>
+        <v>2393543</v>
       </c>
       <c r="I88" s="12" t="inlineStr">
         <is>
@@ -22422,7 +22422,7 @@
       </c>
       <c r="J88" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K88" s="9" t="inlineStr">
@@ -22437,7 +22437,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -22447,26 +22447,26 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>屏東縣長治鄉公所</t>
+          <t>南投縣仁愛鄉公所</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>1150914</t>
+          <t>1150510265</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>第 03 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>115-長治鄉繁昌村昌隆一街28巷道路拓寬工程</t>
+          <t>115年4月豪雨A1-005力行村溫泉部落簡易自來水災修復建工程</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
-        <v>2278000</v>
+        <v>2349000</v>
       </c>
       <c r="I89" s="7" t="inlineStr">
         <is>
@@ -22475,7 +22475,7 @@
       </c>
       <c r="J89" s="7" t="inlineStr">
         <is>
-          <t>115/10/28</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K89" s="4" t="inlineStr">
@@ -22490,7 +22490,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -22500,26 +22500,26 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>桃園市立南崁幼兒園</t>
+          <t>屏東縣長治鄉公所</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>NK1151001</t>
+          <t>1150914</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 03 次</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>115年度桃園市中山非營利幼兒園永續經營設施設備改善統包工程</t>
+          <t>115-長治鄉繁昌村昌隆一街28巷道路拓寬工程</t>
         </is>
       </c>
       <c r="H90" s="11" t="n">
-        <v>2247000</v>
+        <v>2278000</v>
       </c>
       <c r="I90" s="12" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
       </c>
       <c r="J90" s="12" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/10/28</t>
         </is>
       </c>
       <c r="K90" s="9" t="inlineStr">
@@ -22543,7 +22543,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -22553,26 +22553,26 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>新北市立新店高級中學</t>
+          <t>桃園市立南崁幼兒園</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>1151005</t>
+          <t>NK1151001</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>新北市立新店高中女兒牆改建工程</t>
+          <t>115年度桃園市中山非營利幼兒園永續經營設施設備改善統包工程</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
-        <v>2159838</v>
+        <v>2247000</v>
       </c>
       <c r="I91" s="7" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
       </c>
       <c r="J91" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K91" s="4" t="inlineStr">
@@ -22596,7 +22596,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -22606,26 +22606,26 @@
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>臺北市政府財政局</t>
+          <t>新北市立新店高級中學</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>CA1150602</t>
+          <t>1151005</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
         <is>
-          <t>第 01 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>臺北市文山區木新路3段147、149號1樓建築物損壞修復補強工程（含申請室內裝修許可）</t>
+          <t>新北市立新店高中女兒牆改建工程</t>
         </is>
       </c>
       <c r="H92" s="11" t="n">
-        <v>2095687</v>
+        <v>2159838</v>
       </c>
       <c r="I92" s="12" t="inlineStr">
         <is>
@@ -22649,7 +22649,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -22659,12 +22659,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>屏東縣高樹鄉大路關國民小學</t>
+          <t>臺北市政府財政局</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>Dlg1151019</t>
+          <t>CA1150602</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -22674,11 +22674,11 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>114年度屏東縣大路關國小老舊廁所整修工程</t>
+          <t>臺北市文山區木新路3段147、149號1樓建築物損壞修復補強工程（含申請室內裝修許可）</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
-        <v>2036748</v>
+        <v>2095687</v>
       </c>
       <c r="I93" s="7" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
       </c>
       <c r="J93" s="7" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K93" s="4" t="inlineStr">
@@ -22702,7 +22702,7 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
@@ -22712,12 +22712,12 @@
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>桃園市復興區公所</t>
+          <t>屏東縣高樹鄉大路關國民小學</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>115A191</t>
+          <t>Dlg1151019</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -22727,11 +22727,11 @@
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>115年4月豪雨-義盛里11鄰義興道路叉路口災害復建工程</t>
+          <t>114年度屏東縣大路關國小老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H94" s="11" t="n">
-        <v>2028119</v>
+        <v>2036748</v>
       </c>
       <c r="I94" s="12" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
       </c>
       <c r="J94" s="12" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K94" s="9" t="inlineStr">
@@ -22755,7 +22755,7 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
@@ -22765,12 +22765,12 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>南投縣草屯鎮公所</t>
+          <t>桃園市復興區公所</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>1150131</t>
+          <t>115A191</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -22780,11 +22780,11 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>115年度草屯鎮轄區緊急搶修暨零星小型二期工程(開口契約)</t>
+          <t>115年4月豪雨-義盛里11鄰義興道路叉路口災害復建工程</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
-        <v>1958000</v>
+        <v>2028119</v>
       </c>
       <c r="I95" s="7" t="inlineStr">
         <is>
@@ -22793,7 +22793,7 @@
       </c>
       <c r="J95" s="7" t="inlineStr">
         <is>
-          <t>115/11/09</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K95" s="4" t="inlineStr">
@@ -22808,7 +22808,7 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
@@ -22818,12 +22818,12 @@
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>桃園市大溪區百吉國民小學</t>
+          <t>南投縣草屯鎮公所</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>11510A</t>
+          <t>1150131</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -22833,11 +22833,11 @@
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>114年公立國民中小學老舊廁所整修工程</t>
+          <t>115年度草屯鎮轄區緊急搶修暨零星小型二期工程(開口契約)</t>
         </is>
       </c>
       <c r="H96" s="11" t="n">
-        <v>1926915</v>
+        <v>1958000</v>
       </c>
       <c r="I96" s="12" t="inlineStr">
         <is>
@@ -22846,7 +22846,7 @@
       </c>
       <c r="J96" s="12" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>115/11/09</t>
         </is>
       </c>
       <c r="K96" s="9" t="inlineStr">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
@@ -22871,12 +22871,12 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣獅潭鄉公所</t>
+          <t>桃園市大溪區百吉國民小學</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>1151003</t>
+          <t>11510A</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -22886,11 +22886,11 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>115年度4月豪雨G1-獅潭鄉和興村湖塘野溪護岸崩塌災害復建工程等2件</t>
+          <t>114年公立國民中小學老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
-        <v>1902000</v>
+        <v>1926915</v>
       </c>
       <c r="I97" s="7" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
       </c>
       <c r="J97" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/11/03</t>
         </is>
       </c>
       <c r="K97" s="4" t="inlineStr">
@@ -22924,26 +22924,26 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>臺東縣太麻里鄉公所</t>
+          <t>苗栗縣獅潭鄉公所</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>115-35</t>
+          <t>1151003</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
         <is>
-          <t>第 11 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>香蘭村及金崙村排水溝、邊坡及農路改善工程</t>
+          <t>115年度4月豪雨G1-獅潭鄉和興村湖塘野溪護岸崩塌災害復建工程等2件</t>
         </is>
       </c>
       <c r="H98" s="11" t="n">
-        <v>1900604</v>
+        <v>1902000</v>
       </c>
       <c r="I98" s="12" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
       </c>
       <c r="J98" s="12" t="inlineStr">
         <is>
-          <t>115/10/29</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K98" s="9" t="inlineStr">
@@ -22967,7 +22967,7 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
@@ -22977,26 +22977,26 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>桃園市立楊光國民中小學</t>
+          <t>臺東縣太麻里鄉公所</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>115009</t>
+          <t>115-35</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 11 次</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>二樓多功能會議室設備暨裝修工程</t>
+          <t>香蘭村及金崙村排水溝、邊坡及農路改善工程</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
-        <v>1797218</v>
+        <v>1900604</v>
       </c>
       <c r="I99" s="7" t="inlineStr">
         <is>
@@ -23005,7 +23005,7 @@
       </c>
       <c r="J99" s="7" t="inlineStr">
         <is>
-          <t>115/11/02</t>
+          <t>115/10/29</t>
         </is>
       </c>
       <c r="K99" s="4" t="inlineStr">
@@ -23020,7 +23020,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -23030,26 +23030,26 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>彰化縣花壇鄉公所</t>
+          <t>桃園市立楊光國民中小學</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>C115-082101</t>
+          <t>115009</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
         <is>
-          <t>第 04 次</t>
+          <t>第 02 次</t>
         </is>
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>花壇鄉中村橋改善工程</t>
+          <t>二樓多功能會議室設備暨裝修工程</t>
         </is>
       </c>
       <c r="H100" s="11" t="n">
-        <v>1750000</v>
+        <v>1797218</v>
       </c>
       <c r="I100" s="12" t="inlineStr">
         <is>
@@ -23058,7 +23058,7 @@
       </c>
       <c r="J100" s="12" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/11/02</t>
         </is>
       </c>
       <c r="K100" s="9" t="inlineStr">

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-23 17:27</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-24 09:47</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-23 17:27</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-24 09:47</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-24 09:47</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-24 16:59</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-24 09:47</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-24 16:59</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-24 16:59</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-25 09:24</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-24 16:59</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-25 09:24</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-25 09:24</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-25 17:16</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-25 09:24</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-25 17:16</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-25 17:16</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-26 09:28</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-25 17:16</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-26 09:28</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-26 09:28</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-26 18:21</t>
         </is>
       </c>
     </row>
@@ -17812,7 +17812,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-26 09:28</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-26 18:21</t>
         </is>
       </c>
     </row>

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-29 11:34</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-29 18:59</t>
         </is>
       </c>
     </row>
@@ -620,12 +620,12 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>衛生福利部國民健康署</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>115FC00600731306000</t>
+          <t>A1151009</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>光隆、后里、竹坑、清泉崗營區新建設施工程專案管理含監造委託技術服務</t>
+          <t>116-117年HPV疫苗接種專案管理計畫</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
@@ -663,7 +663,7 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
@@ -673,12 +673,12 @@
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>桃園市政府衛生局</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>1161014A-002</t>
+          <t>115FC00600731306000</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>桃園市立醫院醫療大樓新建工程委託設計及監造技術服務</t>
+          <t>光隆、后里、竹坑、清泉崗營區新建設施工程專案管理含監造委託技術服務</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
@@ -716,7 +716,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -726,12 +726,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>桃園市政府衛生局</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>141-F1151028-1</t>
+          <t>1161014A-002</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>牛埔溪排水治理工程 (牛埔橋上游~千壽橋)(含橋梁改建)委託設計及後續擴充監造技術服務</t>
+          <t>桃園市立醫院醫療大樓新建工程委託設計及監造技術服務</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>衛生福利部國民健康署</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>A1151009</t>
+          <t>1152B20050</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>116-117年HPV疫苗接種專案管理計畫</t>
+          <t>雲林縣112年度土壤液化調查與風險評估計畫委託技術服務</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>雲林縣政府</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>1152B20050</t>
+          <t>141-F1151028-1</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>雲林縣112年度土壤液化調查與風險評估計畫委託技術服務</t>
+          <t>牛埔溪排水治理工程 (牛埔橋上游~千壽橋)(含橋梁改建)委託設計及後續擴充監造技術服務</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>yk1151024</t>
+          <t>yk1150716-1</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>陶工科雙美未計畫空間設計裝修統包工程採購案</t>
+          <t>新北市AI應用與數位設計中心空間設計裝修統包工程採購案</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>yk1150716-1</t>
+          <t>yk1151024</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>新北市AI應用與數位設計中心空間設計裝修統包工程採購案</t>
+          <t>陶工科雙美未計畫空間設計裝修統包工程採購案</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
@@ -5824,7 +5824,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-29 11:34</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-29 18:59</t>
         </is>
       </c>
     </row>
@@ -5891,22 +5891,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>屏東縣里港鄉玉田國民小學</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>SP15547</t>
+          <t>B1151103</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5916,11 +5916,11 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>微生物科用試劑35項(開口契約)</t>
+          <t>「屏東縣政府115年度中小學數位學習行動載具」採購案</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
-        <v>63846288</v>
+        <v>0</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -5929,12 +5929,12 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>115/11/30</t>
+          <t>詳見公告</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>招標文件公開閱覽資料</t>
         </is>
       </c>
     </row>
@@ -5944,36 +5944,36 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>臺中市烏日區九德國民小學</t>
+          <t>高雄市政府社會局</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>115RH007</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
         <is>
-          <t>第 02 次</t>
+          <t>第 01 次</t>
         </is>
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>臺中市烏日區九德國小前棟大樓左側老舊廁所整修工程</t>
+          <t>116年度照顧服務員人力勞務委外</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>3877911</v>
+        <v>0</v>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
@@ -5982,12 +5982,12 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>詳見公告</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>招標文件公開閱覽資料</t>
         </is>
       </c>
     </row>
@@ -5997,22 +5997,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>臺中市政府水利局</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>CH1154015</t>
+          <t>1151028009</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -6022,11 +6022,11 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>菜寮抽水站3號機等維護工程</t>
+          <t>大甲溪水系逕流分擔之-沙連溪排水-東勢國小設置地下貯水設施工程</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>460951</v>
+        <v>0</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>115/11/03</t>
+          <t>詳見公告</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>招標文件公開閱覽資料</t>
         </is>
       </c>
     </row>
@@ -6060,12 +6060,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府社會局</t>
+          <t>高雄市政府社會局兒童福利服務中心</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>115RH007</t>
+          <t>115011</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>116年度照顧服務員人力勞務委外</t>
+          <t>高雄市政府社會局兒童福利服務中心委託辦理鹽埕等7區兒童發展社區服務</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -6113,12 +6113,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>臺中市政府水利局</t>
+          <t>新北市政府農業局</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1151028009</t>
+          <t>115B009</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>大甲溪水系逕流分擔之-沙連溪排水-東勢國小設置地下貯水設施工程</t>
+          <t>新店動物之家新建及改建工程</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府文化局</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>115229</t>
+          <t>115FA01617580200120</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -6181,7 +6181,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>116年度眷村園區暨逍遙園文化館舍服務管理委託勞務採購案</t>
+          <t>停車鋼棚新建及附屬設施整修工程</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -6219,12 +6219,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>新北市政府農業局</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>115B009</t>
+          <t>115FC12118065803920</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>新店動物之家新建及改建工程</t>
+          <t>涼山營區室內攻堅射擊場整修工程</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -6262,7 +6262,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -6272,12 +6272,12 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>屏東縣里港鄉玉田國民小學</t>
+          <t>高雄市政府文化局</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>B1151103</t>
+          <t>115229</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -6287,7 +6287,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>「屏東縣政府115年度中小學數位學習行動載具」採購案</t>
+          <t>116年度眷村園區暨逍遙園文化館舍服務管理委託勞務採購案</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府社會局兒童福利服務中心</t>
+          <t>桃園市八德區公所</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>115011</t>
+          <t>BB1151028</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>高雄市政府社會局兒童福利服務中心委託辦理鹽埕等7區兒童發展社區服務</t>
+          <t>八德生命紀念館增設塔位工程</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
@@ -6421,7 +6421,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>115FA01617580200120</t>
+          <t>11151008</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -6446,7 +6446,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>停車鋼棚新建及附屬設施整修工程</t>
+          <t>衛生福利部台南醫院多房間職務宿舍新建工程</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6484,12 +6484,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>桃園市八德區公所</t>
+          <t>台灣電力股份有限公司輸變電工程處</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>BB1151028</t>
+          <t>6531590203</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -6499,7 +6499,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>八德生命紀念館增設塔位工程</t>
+          <t>乙式-公告再利用事業廢棄物</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
@@ -6517,7 +6517,7 @@
       </c>
       <c r="K14" s="9" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料</t>
+          <t>財物變賣</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -6537,12 +6537,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>經濟部水利署</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>11151008</t>
+          <t>1140204-1</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -6552,7 +6552,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>衛生福利部台南醫院多房間職務宿舍新建工程</t>
+          <t>「App &amp;amp; API Protector及Edge DNS 1 Zone安全管理方案」使用授權</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
@@ -6570,7 +6570,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6590,12 +6590,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>115FC12118065803920</t>
+          <t>1151106</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -6605,7 +6605,7 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>涼山營區室內攻堅射擊場整修工程</t>
+          <t>臺南市政府工務局115年度公務電動汽車1台變賣案</t>
         </is>
       </c>
       <c r="H16" s="11" t="n">
@@ -6623,7 +6623,7 @@
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料</t>
+          <t>財物變賣</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -6643,12 +6643,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>6531590203</t>
+          <t>115EL75421357702010</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -6658,7 +6658,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>乙式-公告再利用事業廢棄物</t>
+          <t>北部地區刺絲網整修工程</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
@@ -6676,7 +6676,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>財物變賣</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>1140204-1</t>
+          <t>115FA018182123000120</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>「App &amp;amp; API Protector及Edge DNS 1 Zone安全管理方案」使用授權</t>
+          <t>庫房暨庫儲附屬設施整修工程等2處</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -6749,12 +6749,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>國立清華大學</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>115EL75421357702010</t>
+          <t>PH11514</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>北部地區刺絲網整修工程</t>
+          <t>116年旺宏館空調主系統預約式單價維護工程</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
@@ -6792,7 +6792,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -6802,12 +6802,12 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>1151106</t>
+          <t>115FA02319869500110</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -6817,7 +6817,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>臺南市政府工務局115年度公務電動汽車1台變賣案</t>
+          <t>犁頭山營區鋼棚新建工程案</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
@@ -6835,7 +6835,7 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>財物變賣</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -6855,12 +6855,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>高雄港區土地開發股份有限公司</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>115FA018182123000120</t>
+          <t>KPLD1151028</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -6870,7 +6870,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>庫房暨庫儲附屬設施整修工程等2處</t>
+          <t>116年棧庫群商場污水處理設備維護保養採購</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6908,12 +6908,12 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>國立清華大學</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>PH11514</t>
+          <t>GQP15031</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -6923,7 +6923,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>116年旺宏館空調主系統預約式單價維護工程</t>
+          <t>保修棚廠管路間暨排水系統改善工程</t>
         </is>
       </c>
       <c r="H22" s="11" t="n">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>115FA02319869500110</t>
+          <t>116FB564</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -6976,7 +6976,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>犁頭山營區鋼棚新建工程案</t>
+          <t>嘉興東營區101兵舍整修工程</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
@@ -7004,7 +7004,7 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
@@ -7014,12 +7014,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>台灣電力股份有限公司台南區營業處</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>GQP15031</t>
+          <t>TPC1081550012</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>保修棚廠管路間暨排水系統改善工程</t>
+          <t>116年度晒圖、影印裝訂等文件供應一批</t>
         </is>
       </c>
       <c r="H24" s="11" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>財團法人國家衛生研究院</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>1115MR1549</t>
+          <t>115FB15079P</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -7082,7 +7082,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>實驗室與辦公室防水工程1式</t>
+          <t>115-116年度「陸軍南部地區單位級設施修繕維護工程」電力修繕開口式契約</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -7120,12 +7120,12 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>115FB15079P</t>
+          <t>IL11508D02</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>115-116年度「陸軍南部地區單位級設施修繕維護工程」電力修繕開口式契約</t>
+          <t>115年資訊機房高架地板及消防預警等設備擴充案</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>財團法人國家衛生研究院</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t>116FB564</t>
+          <t>1115MR1549</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>嘉興東營區101兵舍整修工程</t>
+          <t>實驗室與辦公室防水工程1式</t>
         </is>
       </c>
       <c r="H27" s="6" t="n">
@@ -7216,22 +7216,22 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5129-其他用途建築工程</t>
         </is>
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>高雄港區土地開發股份有限公司</t>
+          <t>交通部高速公路局北區養護工程分局</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>KPLD1151028</t>
+          <t>115B010P074</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -7241,7 +7241,7 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>116年棧庫群商場污水處理設備維護保養採購</t>
+          <t>湖口服務區北上加油站新建工程</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
@@ -7259,7 +7259,7 @@
       </c>
       <c r="K28" s="9" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7269,22 +7269,22 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司台南區營業處</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>TPC1081550012</t>
+          <t>SP15146</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>116年度晒圖、影印裝訂等文件供應一批</t>
+          <t>醫療特材計12項(開口契約) (本次招標2項)</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7322,22 +7322,22 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5169-其他安裝工程</t>
         </is>
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司屏東區營業處</t>
+          <t>金門縣採購招標所</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>20261028</t>
+          <t>N115230210088</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -7347,7 +7347,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>租用複印機1套</t>
+          <t>金酒公司行政大樓電梯設備更新案</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
@@ -7365,7 +7365,7 @@
       </c>
       <c r="K30" s="9" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7375,22 +7375,22 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>IL11508D02</t>
+          <t>115FA01915836400110</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -7400,7 +7400,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>115年資訊機房高架地板及消防預警等設備擴充案</t>
+          <t>紅柴林營區手榴彈實彈投擲場新建工程</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
@@ -7418,7 +7418,7 @@
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7428,22 +7428,22 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>SP15146</t>
+          <t>CN-116-514002-2501-B1Q1</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -7453,7 +7453,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>醫療特材計12項(開口契約) (本次招標2項)</t>
+          <t>116年度各渠道整修(新營分處疏濬及堤岸整理)工作(開口契約)</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
@@ -7481,22 +7481,22 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>工程類5129-其他用途建築工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>交通部高速公路局北區養護工程分局</t>
+          <t>台灣電力股份有限公司屏東區營業處</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>115B010P074</t>
+          <t>20261028</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>湖口服務區北上加油站新建工程</t>
+          <t>租用複印機1套</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
@@ -7524,7 +7524,7 @@
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -7539,17 +7539,17 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>工程類5169-其他安裝工程</t>
+          <t>工程類5153-屋頂及防水工程</t>
         </is>
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>金門縣採購招標所</t>
+          <t>國防大學</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>N115230210088</t>
+          <t>115HC06002476902820</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -7559,7 +7559,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>金酒公司行政大樓電梯設備更新案</t>
+          <t>中正堂屋頂防水工程</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
@@ -7587,22 +7587,22 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>115FA01915836400110</t>
+          <t>SP15547</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>紅柴林營區手榴彈實彈投擲場新建工程</t>
+          <t>微生物科用試劑35項(開口契約)</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
@@ -7640,22 +7640,22 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/中油</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>工程類5153-屋頂及防水工程</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>國防大學</t>
+          <t>台灣中油股份有限公司油品行銷事業部基隆營業處</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>115HC06002476902820</t>
+          <t>DAB1520004</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -7665,7 +7665,7 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>中正堂屋頂防水工程</t>
+          <t>石門供油中心浴廁修繕工作長約</t>
         </is>
       </c>
       <c r="H36" s="11" t="n">
@@ -7693,22 +7693,22 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>中央/中油</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司油品行銷事業部基隆營業處</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>DAB1520004</t>
+          <t>SP15624</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -7718,7 +7718,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>石門供油中心浴廁修繕工作長約</t>
+          <t>腎臟科用過醋酸計1項(開口契約)</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
@@ -7746,22 +7746,22 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>CN-116-514002-2501-B1Q1</t>
+          <t>SP15498</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>116年度各渠道整修(新營分處疏濬及堤岸整理)工作(開口契約)</t>
+          <t>微生物科用耗材20項(開口契約)</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
@@ -7799,22 +7799,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>屏東縣議會</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>SP15498</t>
+          <t>115046</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -7824,7 +7824,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>微生物科用耗材20項(開口契約)</t>
+          <t>4至7樓研究室內天花板及走道壁布汰換整修工程</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
@@ -7867,7 +7867,7 @@
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>SP15624</t>
+          <t>SP15497</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -7877,7 +7877,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>腎臟科用過醋酸計1項(開口契約)</t>
+          <t>放射腫瘤部用耗材計1項(開口契約)</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
@@ -7905,22 +7905,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>屏東縣議會</t>
+          <t>新北市政府採購處</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>115046</t>
+          <t>1151124-3</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>4至7樓研究室內天花板及走道壁布汰換整修工程</t>
+          <t>新北市立圖書館板橋分館拆除暨新建工程（新建工程）</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
@@ -7958,22 +7958,22 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>新北市立烏來國民中小學</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>SP15497</t>
+          <t>11507</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -7983,7 +7983,7 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>放射腫瘤部用耗材計1項(開口契約)</t>
+          <t>幼兒園辦公室與器材教具室修繕工程</t>
         </is>
       </c>
       <c r="H42" s="11" t="n">
@@ -8011,22 +8011,22 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>財物類421-結構金屬產品及其零件</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>國防部軍備局生產製造中心</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>SP15545</t>
+          <t>JE15310P265</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>微生物科用試劑40項(開口契約)</t>
+          <t>組合工具總成等4項</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
@@ -8064,22 +8064,22 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>基隆市政府</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>115A106</t>
+          <t>SP15545</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>活動中心無障礙設施改善工程</t>
+          <t>微生物科用試劑40項(開口契約)</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
@@ -8122,17 +8122,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>財物類421-結構金屬產品及其零件</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>國防部軍備局生產製造中心</t>
+          <t>基隆市政府</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>JE15310P265</t>
+          <t>115A106</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>組合工具總成等4項</t>
+          <t>活動中心無障礙設施改善工程</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
@@ -8175,17 +8175,17 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>新北市政府採購處</t>
+          <t>新北市立烏來國民中小學</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>1151124-3</t>
+          <t>11508</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -8195,7 +8195,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>新北市立圖書館板橋分館拆除暨新建工程（新建工程）</t>
+          <t>114-116年公立國民中小學老舊廁所整修工程計畫-專科樓老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
@@ -8223,22 +8223,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5153-屋頂及防水工程</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>新北市立烏來國民中小學</t>
+          <t>桃園市中壢區華勛國民小學</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>115006</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -8248,7 +8248,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>幼兒園辦公室與器材教具室修繕工程</t>
+          <t>星空樓屋頂防水隔熱整修工程</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
@@ -8382,22 +8382,22 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>工程類5153-屋頂及防水工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>桃園市中壢區華勛國民小學</t>
+          <t>衛生福利部樂生醫院</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>115006</t>
+          <t>lslp-2540-11529</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -8407,7 +8407,7 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>星空樓屋頂防水隔熱整修工程</t>
+          <t>B棟6樓單人病房2間整修工程採購案</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
@@ -8435,22 +8435,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>財物類452-計算機及其零件與配件</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>衛生福利部樂生醫院</t>
+          <t>高雄市立空中大學</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>lslp-2540-11529</t>
+          <t>OUK11512</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -8460,7 +8460,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>B棟6樓單人病房2間整修工程採購案</t>
+          <t>115年度個人電腦租賃採購案</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
@@ -8488,22 +8488,22 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>財物類452-計算機及其零件與配件</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>高雄市立空中大學</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>OUK11512</t>
+          <t>115EQ635077310001200</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -8513,7 +8513,7 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>115年度個人電腦租賃採購案</t>
+          <t>調節營舍整修工程</t>
         </is>
       </c>
       <c r="H52" s="11" t="n">
@@ -8541,22 +8541,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>苗栗縣南庄鄉蓬萊國民小學</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>115EQ635077310001200</t>
+          <t>1151010</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>調節營舍整修工程</t>
+          <t>蓬萊國小115年度跑道暨球場整修工程</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
@@ -8594,22 +8594,22 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>新北市立烏來國民中小學</t>
+          <t>農業部農村發展及水土保持署南投分署</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>11508</t>
+          <t>115PD302</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -8619,7 +8619,7 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>114-116年公立國民中小學老舊廁所整修工程計畫-專科樓老舊廁所整修工程</t>
+          <t>古坑鄉華山土石流教學園區環境改善二期工程</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
@@ -8647,22 +8647,22 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署南投分署</t>
+          <t>桃園市中壢區中原國民小學</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>115PD302</t>
+          <t>CU-11517</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -8672,7 +8672,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>古坑鄉華山土石流教學園區環境改善二期工程</t>
+          <t>中原國小國際教室整修美化工程</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
@@ -8700,22 +8700,22 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣南庄鄉蓬萊國民小學</t>
+          <t>臺南市北區公園國民小學</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>1151010</t>
+          <t>GYES115009</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -8725,7 +8725,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>蓬萊國小115年度跑道暨球場整修工程</t>
+          <t>臺南市公園國小附設幼兒園改善教學環境設備改善工程</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
@@ -8753,7 +8753,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>臺南市北區公園國民小學</t>
+          <t>苗栗縣立建國國民中學</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>GYES115009</t>
+          <t>1151010</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -8778,7 +8778,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>臺南市公園國小附設幼兒園改善教學環境設備改善工程</t>
+          <t>籃球場改善工程採購案</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
@@ -8806,22 +8806,22 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>財物類481-醫療,外科及矯形設備</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>桃園市中壢區中原國民小學</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>CU-11517</t>
+          <t>LP16027</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>中原國小國際教室整修美化工程</t>
+          <t>骨折手術床1組</t>
         </is>
       </c>
       <c r="H58" s="11" t="n">
@@ -8864,17 +8864,17 @@
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣立建國國民中學</t>
+          <t>南投縣草屯鎮炎峰國民小學</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>1151010</t>
+          <t>115-10-001-E</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -8884,7 +8884,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>籃球場改善工程採購案</t>
+          <t>炎峰國小114年老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
@@ -8912,22 +8912,22 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>財物類481-醫療,外科及矯形設備</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>花蓮縣立三民國民中學</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>LP16027</t>
+          <t>smjh115TDrenovation</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -8937,7 +8937,7 @@
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>骨折手術床1組</t>
+          <t>三民國中115年度教師宿舍改善工程</t>
         </is>
       </c>
       <c r="H60" s="11" t="n">
@@ -8965,7 +8965,7 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -8975,12 +8975,12 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>南投縣草屯鎮炎峰國民小學</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>115-10-001-E</t>
+          <t>115EZ686208638016800</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>炎峰國小114年老舊廁所整修工程</t>
+          <t>南埔餐廳牆面及地坪整修工程</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
@@ -9018,22 +9018,22 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>工程類5173-油漆工程</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>臺灣高等法院</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>115THC037</t>
+          <t>TR1150006906</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -9043,7 +9043,7 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>臺灣高等法院刑事庭大廈公共空間油漆整修工程</t>
+          <t>花蓮縣燈會燈籠掛設由包燈改為表燈之轉型計畫(開口契約)</t>
         </is>
       </c>
       <c r="H62" s="11" t="n">
@@ -9071,22 +9071,22 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>工程類5173-油漆工程</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>臺灣高等法院</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>TR1150006906</t>
+          <t>115THC037</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -9096,7 +9096,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>花蓮縣燈會燈籠掛設由包燈改為表燈之轉型計畫(開口契約)</t>
+          <t>臺灣高等法院刑事庭大廈公共空間油漆整修工程</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
@@ -9124,22 +9124,22 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5172-粉刷工程</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>苗栗縣竹南鎮海口國民小學</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>115EZ686208638016800</t>
+          <t>1151001</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>南埔餐廳牆面及地坪整修工程</t>
+          <t>115年度校舍油漆粉刷工程</t>
         </is>
       </c>
       <c r="H64" s="11" t="n">
@@ -9182,17 +9182,17 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>工程類5172-粉刷工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣竹南鎮海口國民小學</t>
+          <t>國防部軍醫局</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>1151001</t>
+          <t>115NB00030692800920</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>115年度校舍油漆粉刷工程</t>
+          <t>經理庫房整修工程</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
@@ -9235,17 +9235,17 @@
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>國防部軍醫局</t>
+          <t>苗栗縣立通霄國民中學</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>115NB00030692800920</t>
+          <t>115017</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>經理庫房整修工程</t>
+          <t>115年度通霄國中操場跑道暨田徑場整建工程案</t>
         </is>
       </c>
       <c r="H66" s="11" t="n">
@@ -9336,22 +9336,22 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5173-油漆工程</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣立三民國民中學</t>
+          <t>苗栗縣頭份市六合國民小學</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>smjh115TDrenovation</t>
+          <t>LH-115019</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>三民國中115年度教師宿舍改善工程</t>
+          <t>六合國小115學年度油漆工程採購</t>
         </is>
       </c>
       <c r="H68" s="11" t="n">
@@ -9447,17 +9447,17 @@
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>工程類5173-油漆工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市六合國民小學</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>LH-115019</t>
+          <t>115-409</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -9467,7 +9467,7 @@
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>六合國小115學年度油漆工程採購</t>
+          <t>116年度南投段轄區省道標線工程(開口契約)</t>
         </is>
       </c>
       <c r="H70" s="11" t="n">
@@ -9510,7 +9510,7 @@
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>115-409</t>
+          <t>1162B0121002</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -9520,7 +9520,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>116年度南投段轄區省道標線工程(開口契約)</t>
+          <t>116年度信義段轄區預約經常性災害搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>1162B0121002</t>
+          <t>115-610</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -9573,7 +9573,7 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>116年度信義段轄區預約經常性災害搶修工程(開口契約)</t>
+          <t>116年度埔里段轄區省道台14線49K+208-67K、台21線17K-47k路容清理工作及災害搶修工作(開口契約)</t>
         </is>
       </c>
       <c r="H72" s="11" t="n">
@@ -9606,17 +9606,17 @@
       </c>
       <c r="C73" s="3" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5173-油漆工程</t>
         </is>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣立通霄國民中學</t>
+          <t>苗栗縣苗栗市啟文國民小學</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>115017</t>
+          <t>115-005</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>115年度通霄國中操場跑道暨田徑場整建工程案</t>
+          <t>115年度苗栗縣啟文國民小學校舍油漆粉刷工程</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
@@ -9659,17 +9659,17 @@
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
+          <t>工程類5173-油漆工程</t>
         </is>
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>苗栗縣苑裡鎮山腳國民小學</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>115-610</t>
+          <t>sj1151002</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -9679,7 +9679,7 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>116年度埔里段轄區省道台14線49K+208-67K、台21線17K-47k路容清理工作及災害搶修工作(開口契約)</t>
+          <t>山腳國小115年校舍油漆粉刷工程</t>
         </is>
       </c>
       <c r="H74" s="11" t="n">
@@ -9712,17 +9712,17 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>工程類5173-油漆工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣苑裡鎮山腳國民小學</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>sj1151002</t>
+          <t>115120a</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -9732,7 +9732,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>山腳國小115年校舍油漆粉刷工程</t>
+          <t>龍鳳排水安和橋及龍鳳橋上游災害復建工程</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
@@ -9760,22 +9760,22 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>工程類5173-油漆工程</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣苗栗市啟文國民小學</t>
+          <t>國立臺中教育大學附設實驗國民小學</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>115-005</t>
+          <t>1151010</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -9785,7 +9785,7 @@
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>115年度苗栗縣啟文國民小學校舍油漆粉刷工程</t>
+          <t>115年度操場跑道更新工程</t>
         </is>
       </c>
       <c r="H76" s="11" t="n">
@@ -9818,17 +9818,17 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>115120a</t>
+          <t>115-620</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -9838,7 +9838,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>龍鳳排水安和橋及龍鳳橋上游災害復建工程</t>
+          <t>116年度埔里段轄區省道瀝青鋪面擇要路段修復工程(開口契約)</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>國立臺中教育大學附設實驗國民小學</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>1151010</t>
+          <t>115119a</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -9891,7 +9891,7 @@
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>115年度操場跑道更新工程</t>
+          <t>農苗通227(0K+807~1K+398)及延伸段農路改善工程</t>
         </is>
       </c>
       <c r="H78" s="11" t="n">
@@ -9919,22 +9919,22 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>臺中市烏日區九德國民小學</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>115119a</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>農苗通227(0K+807~1K+398)及延伸段農路改善工程</t>
+          <t>臺中市烏日區九德國小前棟大樓左側老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
@@ -9972,22 +9972,22 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>屏東縣牡丹鄉公所</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>115-620</t>
+          <t>A11514</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>116年度埔里段轄區省道瀝青鋪面擇要路段修復工程(開口契約)</t>
+          <t>牡丹東源聯絡道路養護工程</t>
         </is>
       </c>
       <c r="H80" s="11" t="n">
@@ -10078,7 +10078,7 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>屏東縣牡丹鄉公所</t>
+          <t>基隆市政府</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>A11514</t>
+          <t>115A102</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -10103,7 +10103,7 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>牡丹東源聯絡道路養護工程</t>
+          <t>中正區武昌街104巷23號後方邊坡復建工程</t>
         </is>
       </c>
       <c r="H82" s="11" t="n">
@@ -10131,7 +10131,7 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>基隆市政府</t>
+          <t>屏東縣恆春鎮公所</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>115A102</t>
+          <t>F-261003</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -10156,7 +10156,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>中正區武昌街104巷23號後方邊坡復建工程</t>
+          <t>恆春鎮鵝鑾里籠埔路、南灣里柴西巷及一心路農路排水改善工程</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
@@ -10237,7 +10237,7 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
@@ -10247,12 +10247,12 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>屏東縣牡丹鄉公所</t>
+          <t>台灣自來水股份有限公司第一區管理處</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>A11515</t>
+          <t>LU-115-0101-0005</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>牡丹高士聯絡道路養護工程</t>
+          <t>馥記山莊高地社區供水管線改善工程(土建)</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
@@ -10290,7 +10290,7 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第一區管理處</t>
+          <t>屏東縣牡丹鄉公所</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>LU-115-0101-0005</t>
+          <t>A11515</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -10315,7 +10315,7 @@
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>馥記山莊高地社區供水管線改善工程(土建)</t>
+          <t>牡丹高士聯絡道路養護工程</t>
         </is>
       </c>
       <c r="H86" s="11" t="n">
@@ -10343,22 +10343,22 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>私立龍華科技大學</t>
+          <t>台灣電力股份有限公司彰化區營業處</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>LHU1151028P01</t>
+          <t>1061570003</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>B115000306工程學院-採購雙面下針針台系統</t>
+          <t>彰化區營業處115年甲工區配電管路工程</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
@@ -10396,22 +10396,22 @@
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公所</t>
+          <t>私立龍華科技大學</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>F-261003</t>
+          <t>LHU1151028P01</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>恆春鎮鵝鑾里籠埔路、南灣里柴西巷及一心路農路排水改善工程</t>
+          <t>B115000306工程學院-採購雙面下針針台系統</t>
         </is>
       </c>
       <c r="H88" s="11" t="n">
@@ -10449,22 +10449,22 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>財物類496-航空器,太空船及其零件</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司彰化區營業處</t>
+          <t>高雄市政府地政局土地開發處</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>1061570003</t>
+          <t>1150930</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>彰化區營業處115年甲工區配電管路工程</t>
+          <t>115年RTK測繪用遙控無人機組</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
@@ -10502,22 +10502,22 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>財物類496-航空器,太空船及其零件</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府地政局土地開發處</t>
+          <t>屏東縣牡丹鄉公所</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>1150930</t>
+          <t>A11516</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -10527,7 +10527,7 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>115年RTK測繪用遙控無人機組</t>
+          <t>石門四林聯絡道路養護工程</t>
         </is>
       </c>
       <c r="H90" s="11" t="n">
@@ -10555,22 +10555,22 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>中央/中油</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類421-結構金屬產品及其零件</t>
         </is>
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>屏東縣牡丹鄉公所</t>
+          <t>台灣中油股份有限公司煉製事業部桃園煉油廠</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>A11516</t>
+          <t>I7315D059</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>石門四林聯絡道路養護工程</t>
+          <t>115~116年一般維修用不鏽鋼片、板及碳鋼板長約</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
@@ -10608,22 +10608,22 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>桃園市平鎮區公所</t>
+          <t>桃園市大溪區公所</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>1151006B</t>
+          <t>115101301</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -10633,7 +10633,7 @@
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>116年平鎮區公園景觀步道體健器材、遊樂設施修繕工程(開口合約)</t>
+          <t>115年6月豪雨造成大溪區10處公共設施損壞之復建工程</t>
         </is>
       </c>
       <c r="H92" s="11" t="n">
@@ -10661,22 +10661,22 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>中央/中油</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>財物類421-結構金屬產品及其零件</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司煉製事業部桃園煉油廠</t>
+          <t>苗栗縣南庄鄉公所</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>I7315D059</t>
+          <t>115-059</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -10686,7 +10686,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>115~116年一般維修用不鏽鋼片、板及碳鋼板長約</t>
+          <t>獅山礦業古道鋪面改善工程</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
@@ -10714,22 +10714,22 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>桃園市中壢區公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>115-10-100</t>
+          <t>CN-115-514002-2501-B1U11</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -10739,7 +10739,7 @@
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>116年度中壢區公園土建設施改善工程(開口契約)</t>
+          <t>115年度各渠道附屬及安全設施修護(烏山頭分處水門修護及油漆)工程</t>
         </is>
       </c>
       <c r="H94" s="11" t="n">
@@ -10772,17 +10772,17 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣南庄鄉公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>115-059</t>
+          <t>KS115M027</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -10792,7 +10792,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>獅山礦業古道鋪面改善工程</t>
+          <t>115及116年度大寮站林園圳圳路設施維護開口契約</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
@@ -10820,22 +10820,22 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>新竹縣五峰鄉公所</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>CN-115-514002-2501-B1U11</t>
+          <t>B11518</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -10845,7 +10845,7 @@
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>115年度各渠道附屬及安全設施修護(烏山頭分處水門修護及油漆)工程</t>
+          <t>清石道路7.5k邊坡改善工程</t>
         </is>
       </c>
       <c r="H96" s="11" t="n">
@@ -10873,22 +10873,22 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>桃園市平鎮區公所</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>KS115M027</t>
+          <t>1151006B</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -10898,7 +10898,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>115及116年度大寮站林園圳圳路設施維護開口契約</t>
+          <t>116年平鎮區公園景觀步道體健器材、遊樂設施修繕工程(開口合約)</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
@@ -10926,7 +10926,7 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
@@ -10936,12 +10936,12 @@
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>桃園市大溪區公所</t>
+          <t>桃園市中壢區公所</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>115101301</t>
+          <t>115-10-100</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -10951,7 +10951,7 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>115年6月豪雨造成大溪區10處公共設施損壞之復建工程</t>
+          <t>116年度中壢區公園土建設施改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H98" s="11" t="n">
@@ -10979,22 +10979,22 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>新竹縣五峰鄉公所</t>
+          <t>臺南市仁德區仁德國民小學</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>B11518</t>
+          <t>11508-01rdes</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>清石道路7.5k邊坡改善工程</t>
+          <t>臺南市115年度學校基地内污水匯流工程(第九組)</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
@@ -11032,22 +11032,22 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>臺南市仁德區仁德國民小學</t>
+          <t>經濟部水利署第一河川分署</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>11508-01rdes</t>
+          <t>115-B-004-02-002-612</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -11057,7 +11057,7 @@
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>臺南市115年度學校基地内污水匯流工程(第九組)</t>
+          <t>115年度宜蘭河及蘭陽溪等8座水門構造物維修改善工程</t>
         </is>
       </c>
       <c r="H100" s="11" t="n">
@@ -11085,22 +11085,22 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>高雄市茂林區公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>115095</t>
+          <t>CN114R05</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -11110,7 +11110,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>Danas-H-06-02-8-茂林伊拉呢橋上下邊坡災復工程</t>
+          <t>烏山頭水庫西口導水路抽淤工程</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
@@ -11138,22 +11138,22 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第一河川分署</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>115-B-004-02-002-612</t>
+          <t>1151008B-1</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>115年度宜蘭河及蘭陽溪等8座水門構造物維修改善工程</t>
+          <t>花蓮縣玉里鎮大禹里花69線樺加沙颱風復建工程</t>
         </is>
       </c>
       <c r="H102" s="11" t="n">
@@ -11191,22 +11191,22 @@
       </c>
       <c r="B103" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5169-其他安裝工程</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>桃園市大溪區公所</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>CN114R05</t>
+          <t>115101501</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>烏山頭水庫西口導水路抽淤工程</t>
+          <t>116年度大溪區交通標誌工程(開口契約)</t>
         </is>
       </c>
       <c r="H103" s="6" t="n">
@@ -11244,22 +11244,22 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>工程類5169-其他安裝工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>桃園市大溪區公所</t>
+          <t>高雄市政府海洋局</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>115101501</t>
+          <t>1156030</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -11269,7 +11269,7 @@
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>116年度大溪區交通標誌工程(開口契約)</t>
+          <t>永安區保寧段39地號排水渠道新設護岸工程</t>
         </is>
       </c>
       <c r="H104" s="11" t="n">
@@ -11297,22 +11297,22 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>1151008B-1</t>
+          <t>CH1151031</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -11322,7 +11322,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮大禹里花69線樺加沙颱風復建工程</t>
+          <t>大義中排18-2鎮安段401地號等改善工程</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
@@ -11350,22 +11350,22 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府海洋局</t>
+          <t>臺南市北門區公所</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>1156030</t>
+          <t>115100701</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
@@ -11375,7 +11375,7 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>永安區保寧段39地號排水渠道新設護岸工程</t>
+          <t>北門區三光里蘆竹溝水溝改善工程(2)</t>
         </is>
       </c>
       <c r="H106" s="11" t="n">
@@ -11403,22 +11403,22 @@
       </c>
       <c r="B107" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>臺南市北門區公所</t>
+          <t>高雄市政府農業局</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>115100701</t>
+          <t>BR11510</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -11428,7 +11428,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>北門區三光里蘆竹溝水溝改善工程(2)</t>
+          <t>高雄果菜批發市場簡易修繕工程</t>
         </is>
       </c>
       <c r="H107" s="6" t="n">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府農業局</t>
+          <t>高雄市茂林區公所</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>BR11510</t>
+          <t>115095</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>高雄果菜批發市場簡易修繕工程</t>
+          <t>Danas-H-06-02-8-茂林伊拉呢橋上下邊坡災復工程</t>
         </is>
       </c>
       <c r="H108" s="11" t="n">
@@ -11668,22 +11668,22 @@
       </c>
       <c r="B112" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>彰化縣溪州鄉公所</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>CH1151031</t>
+          <t>1150824</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -11693,7 +11693,7 @@
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>大義中排18-2鎮安段401地號等改善工程</t>
+          <t>溪州鄉庄北段185-187地號旁擋土設施改善工程</t>
         </is>
       </c>
       <c r="H112" s="11" t="n">
@@ -11721,22 +11721,22 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>彰化縣溪州鄉公所</t>
+          <t>台灣電力股份有限公司台南區營業處</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>1150824</t>
+          <t>1081575502</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>溪州鄉庄北段185-187地號旁擋土設施改善工程</t>
+          <t>115年乙工區配電外線工程</t>
         </is>
       </c>
       <c r="H113" s="6" t="n">
@@ -11774,22 +11774,22 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司台南區營業處</t>
+          <t>宜蘭縣政府</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>1081575502</t>
+          <t>TRCO116002</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
@@ -11799,7 +11799,7 @@
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>115年乙工區配電外線工程</t>
+          <t>116年度宜蘭縣停車設施及道路標誌標線改善維護</t>
         </is>
       </c>
       <c r="H114" s="11" t="n">
@@ -11827,22 +11827,22 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣政府</t>
+          <t>臺南市北門區公所</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>TRCO116002</t>
+          <t>115100702</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -11852,7 +11852,7 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>116年度宜蘭縣停車設施及道路標誌標線改善維護</t>
+          <t>北門區雙春里渡子頭段586護岸改善工程</t>
         </is>
       </c>
       <c r="H115" s="6" t="n">
@@ -11880,7 +11880,7 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
@@ -11890,12 +11890,12 @@
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>臺南市北門區公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>115100702</t>
+          <t>YL115A05</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -11905,7 +11905,7 @@
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>北門區雙春里渡子頭段586護岸改善工程</t>
+          <t>庄口圳幹線改善工程</t>
         </is>
       </c>
       <c r="H116" s="11" t="n">
@@ -11933,7 +11933,7 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
@@ -11943,12 +11943,12 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>新竹市政府</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>YL115A05</t>
+          <t>115A137</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -11958,7 +11958,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>庄口圳幹線改善工程</t>
+          <t>115下半年至116年度新竹市水利工程 (開口契約) □第一案□第二案</t>
         </is>
       </c>
       <c r="H117" s="6" t="n">
@@ -11986,22 +11986,22 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>新竹市政府</t>
+          <t>屏東縣屏東市公所</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>115A137</t>
+          <t>115067</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -12011,7 +12011,7 @@
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>115下半年至116年度新竹市水利工程 (開口契約) □第一案□第二案</t>
+          <t>屏東市湖南里歸禮巷農路改善工程</t>
         </is>
       </c>
       <c r="H118" s="11" t="n">
@@ -12039,22 +12039,22 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>115067</t>
+          <t>YL115AGD11</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -12064,7 +12064,7 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>屏東市湖南里歸禮巷農路改善工程</t>
+          <t>柴裡埤小排5-1等改善工程</t>
         </is>
       </c>
       <c r="H119" s="6" t="n">
@@ -12107,7 +12107,7 @@
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>YL115AGD11</t>
+          <t>YL115J265</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
@@ -12117,7 +12117,7 @@
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>柴裡埤小排5-1等改善工程</t>
+          <t>115年度春牛埔(東)農地重劃區大北門小排1-3等緊急農水路改善工程</t>
         </is>
       </c>
       <c r="H120" s="11" t="n">
@@ -12145,22 +12145,22 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>臺南市北門區公所</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>YL115J265</t>
+          <t>115100501</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -12170,7 +12170,7 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>115年度春牛埔(東)農地重劃區大北門小排1-3等緊急農水路改善工程</t>
+          <t>北門區蚵寮、保吉聯合活動中心二期增建工程</t>
         </is>
       </c>
       <c r="H121" s="6" t="n">
@@ -12198,22 +12198,22 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>南台灣 (跨縣市)</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類449-其他特殊用途之機具及其零件</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>臺南市北門區公所</t>
+          <t>交通部高速公路局南區養護工程分局</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>115100501</t>
+          <t>115D120P026</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
@@ -12223,7 +12223,7 @@
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>北門區蚵寮、保吉聯合活動中心二期增建工程</t>
+          <t>國3關廟服務區空氣調節箱及變頻氣冷式冰水主機汰換採購(115)</t>
         </is>
       </c>
       <c r="H122" s="11" t="n">
@@ -12251,22 +12251,22 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>南台灣 (跨縣市)</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>財物類449-其他特殊用途之機具及其零件</t>
+          <t>工程類5173-油漆工程</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>交通部高速公路局南區養護工程分局</t>
+          <t>苗栗縣頭份市尖山國民小學</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>115D120P026</t>
+          <t>JS115-08</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>國3關廟服務區空氣調節箱及變頻氣冷式冰水主機汰換採購(115)</t>
+          <t>校舍油漆粉刷工程</t>
         </is>
       </c>
       <c r="H123" s="6" t="n">
@@ -12309,17 +12309,17 @@
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>工程類5173-油漆工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市尖山國民小學</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>JS115-08</t>
+          <t>YL115J269</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
@@ -12329,7 +12329,7 @@
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>校舍油漆粉刷工程</t>
+          <t>115年度四美農地重劃區新吉小排3-1緊急農水路改善工程</t>
         </is>
       </c>
       <c r="H124" s="11" t="n">
@@ -12415,17 +12415,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>苗栗縣頭份市斗煥國民小學</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>YL115J269</t>
+          <t>1151002</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>115年度四美農地重劃區新吉小排3-1緊急農水路改善工程</t>
+          <t>斗煥國小暨社區活動中心二樓增建工程</t>
         </is>
       </c>
       <c r="H126" s="11" t="n">
@@ -12468,17 +12468,17 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣頭份市斗煥國民小學</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>1151002</t>
+          <t>CH1154015</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -12488,7 +12488,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>斗煥國小暨社區活動中心二樓增建工程</t>
+          <t>菜寮抽水站3號機等維護工程</t>
         </is>
       </c>
       <c r="H127" s="6" t="n">
@@ -12622,22 +12622,22 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>工程類5161-暖氣,通風及空調工程</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>嘉義市東區嘉北國民小學</t>
+          <t>國立臺東大學附屬體育高級中學</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>115015A</t>
+          <t>115E004</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -12647,7 +12647,7 @@
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>115年度嘉北國小演藝廳整修工程</t>
+          <t>游泳教學設施能效提升暨水質優化改善（二期）</t>
         </is>
       </c>
       <c r="H130" s="11" t="n">
@@ -12675,22 +12675,22 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>嘉義縣溪口鄉公所</t>
+          <t>桃園國際機場股份有限公司</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>115-20</t>
+          <t>P1161003570</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>溪口鄉游厝農地重劃區南北十二路改善工程</t>
+          <t>116至117年度航空地面燈光維護汰換暨設施改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H131" s="6" t="n">
@@ -12728,22 +12728,22 @@
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>工程類5161-暖氣,通風及空調工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>國立臺東大學附屬體育高級中學</t>
+          <t>嘉義縣溪口鄉公所</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>115E004</t>
+          <t>115-20</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -12753,7 +12753,7 @@
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>游泳教學設施能效提升暨水質優化改善（二期）</t>
+          <t>溪口鄉游厝農地重劃區南北十二路改善工程</t>
         </is>
       </c>
       <c r="H132" s="11" t="n">
@@ -12781,22 +12781,22 @@
       </c>
       <c r="B133" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>桃園國際機場股份有限公司</t>
+          <t>嘉義市東區嘉北國民小學</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>P1161003570</t>
+          <t>115015A</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -12806,7 +12806,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>116至117年度航空地面燈光維護汰換暨設施改善工程(開口契約)</t>
+          <t>115年度嘉北國小演藝廳整修工程</t>
         </is>
       </c>
       <c r="H133" s="6" t="n">
@@ -12993,22 +12993,22 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第十區管理處</t>
+          <t>雲林縣東勢鄉公所</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>WA-116-1001-01</t>
+          <t>5139-1151027</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -13018,7 +13018,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>116年台東營運所屆(逾)齡水量計委外換裝作業</t>
+          <t>115年度東勢鄉轄內市區道路改善工程</t>
         </is>
       </c>
       <c r="H137" s="6" t="n">
@@ -13099,22 +13099,22 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>雲林縣東勢鄉公所</t>
+          <t>新北市樹林區樹林國民小學</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>5139-1151027</t>
+          <t>1151001</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -13124,7 +13124,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>115年度東勢鄉轄內市區道路改善工程</t>
+          <t>新北市樹林國小劍道館室內空間修繕工程採購案</t>
         </is>
       </c>
       <c r="H139" s="6" t="n">
@@ -13152,22 +13152,22 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5129-其他用途建築工程</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>新北市樹林區樹林國民小學</t>
+          <t>普濟寺（原名鐵真院）</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>1151001</t>
+          <t>PUJI11500002</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
@@ -13177,7 +13177,7 @@
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
-          <t>新北市樹林國小劍道館室內空間修繕工程採購案</t>
+          <t>直轄市定古蹟「北投普濟寺」修復工程</t>
         </is>
       </c>
       <c r="H140" s="11" t="n">
@@ -13210,17 +13210,17 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>工程類5129-其他用途建築工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>普濟寺（原名鐵真院）</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>PUJI11500002</t>
+          <t>115178c</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -13230,7 +13230,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>直轄市定古蹟「北投普濟寺」修復工程</t>
+          <t>後龍鎮中和里往過港隧道聯絡道路加寬改善工程</t>
         </is>
       </c>
       <c r="H141" s="6" t="n">
@@ -13258,22 +13258,22 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>嘉義縣大埔鄉公所</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>115178c</t>
+          <t>115090203</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -13283,7 +13283,7 @@
       </c>
       <c r="G142" s="10" t="inlineStr">
         <is>
-          <t>後龍鎮中和里往過港隧道聯絡道路加寬改善工程</t>
+          <t>白馬亭復建工程</t>
         </is>
       </c>
       <c r="H142" s="11" t="n">
@@ -13311,22 +13311,22 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>彰化縣彰化市大成國民小學</t>
+          <t>台灣自來水股份有限公司第十區管理處</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>115109</t>
+          <t>WA-116-1001-01</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -13336,7 +13336,7 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>大成國小足球場整修工程採購</t>
+          <t>116年台東營運所屆(逾)齡水量計委外換裝作業</t>
         </is>
       </c>
       <c r="H143" s="6" t="n">
@@ -13364,22 +13364,22 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>嘉義縣大埔鄉公所</t>
+          <t>彰化縣彰化市大成國民小學</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>115090203</t>
+          <t>115109</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
@@ -13389,7 +13389,7 @@
       </c>
       <c r="G144" s="10" t="inlineStr">
         <is>
-          <t>白馬亭復建工程</t>
+          <t>大成國小足球場整修工程採購</t>
         </is>
       </c>
       <c r="H144" s="11" t="n">
@@ -13470,22 +13470,22 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5175-其他鋪地板,牆面及壁紙工程</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>屏東縣泰武鄉公所</t>
+          <t>國立嘉義高級工業職業學校</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>115EE007</t>
+          <t>115028-1</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
@@ -13495,7 +13495,7 @@
       </c>
       <c r="G146" s="10" t="inlineStr">
         <is>
-          <t>(115年6月豪雨)泰武鄉平和2號農路災後復建工程</t>
+          <t>體育館地下室地坪整建工程</t>
         </is>
       </c>
       <c r="H146" s="11" t="n">
@@ -13523,22 +13523,22 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>工程類5175-其他鋪地板,牆面及壁紙工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>國立嘉義高級工業職業學校</t>
+          <t>屏東縣泰武鄉公所</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>115028-1</t>
+          <t>115EE007</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -13548,7 +13548,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>體育館地下室地坪整建工程</t>
+          <t>(115年6月豪雨)泰武鄉平和2號農路災後復建工程</t>
         </is>
       </c>
       <c r="H147" s="6" t="n">
@@ -13629,22 +13629,22 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5112-拆除工程</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>國立嘉義女子高級中學</t>
+          <t>國立岡山高級農工職業學校</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>11510C4</t>
+          <t>115A-04</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -13654,7 +13654,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>污水及排水系統建置改善及車棚整修工程</t>
+          <t>教職員工職務宿舍區建物拆除工程</t>
         </is>
       </c>
       <c r="H149" s="6" t="n">
@@ -13682,22 +13682,22 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>工程類5112-拆除工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>國立岡山高級農工職業學校</t>
+          <t>國立嘉義女子高級中學</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>115A-04</t>
+          <t>11510C4</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="G150" s="10" t="inlineStr">
         <is>
-          <t>教職員工職務宿舍區建物拆除工程</t>
+          <t>污水及排水系統建置改善及車棚整修工程</t>
         </is>
       </c>
       <c r="H150" s="11" t="n">

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-30 10:46</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-30 18:57</t>
         </is>
       </c>
     </row>
@@ -615,17 +615,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>勞務類8672-工程服務</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>115-830</t>
+          <t>115FB11519448300120</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -635,11 +635,11 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>台76線27K+300(隧道口)~32K+600(隧道尾)及台76線部分路段路面改善工程-委託監造服務工作</t>
+          <t>考潭、仁美營區新建設施工程專案管理含監造委託技術服務</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
-        <v>4248787</v>
+        <v>0</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -648,12 +648,12 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>115/12/01</t>
+          <t>詳見公告</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>招標文件公開閱覽資料</t>
         </is>
       </c>
     </row>
@@ -731,7 +731,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>115FB11519448300120</t>
+          <t>117</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -741,7 +741,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>考潭、仁美營區新建設施工程專案管理含監造委託技術服務</t>
+          <t>國防部會議室改建先期規劃</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
@@ -759,7 +759,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -822,7 +822,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/海軍</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>國防部海軍司令部</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>117</t>
+          <t>114-5160005513000220-2</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>國防部會議室改建先期規劃</t>
+          <t>兩棲偵搜大隊舟艇維修間整修工程第二次變更設計</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
@@ -875,7 +875,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>中央/海軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -885,12 +885,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>國防部海軍司令部</t>
+          <t>國防部軍備局生產製造中心</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>114-5160005513000220-2</t>
+          <t>115-839</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>兩棲偵搜大隊舟艇維修間整修工程第二次變更設計</t>
+          <t>發射藥線廠房修繕工程委託設計</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
@@ -933,17 +933,17 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>國防部軍備局生產製造中心</t>
+          <t>國立臺東大學附屬體育高級中學</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>115-839</t>
+          <t>115C012-1</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>發射藥線廠房修繕工程委託設計</t>
+          <t>校舍結構震損復原工程</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>國立臺東大學附屬體育高級中學</t>
+          <t>天主教振聲學校財團法人桃園市振聲高級中等學校</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>115C012-1</t>
+          <t>FXSH115009</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>校舍結構震損復原工程</t>
+          <t>四維樓7樓羽球場暨多功能活動空間規劃工程</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
@@ -1034,22 +1034,22 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>勞務類8676-技術檢定與分析服務</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>天主教振聲學校財團法人桃園市振聲高級中等學校</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>FXSH115009</t>
+          <t>CP15072</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>四維樓7樓羽球場暨多功能活動空間規劃工程</t>
+          <t>兒童醫學部委託代檢勞務21項</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
@@ -1087,22 +1087,22 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>勞務類8676-技術檢定與分析服務</t>
+          <t>勞務類8672-工程服務</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>CP15072</t>
+          <t>115-830</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>兒童醫學部委託代檢勞務21項</t>
+          <t>台76線27K+300(隧道口)~32K+600(隧道尾)及台76線部分路段路面改善工程-委託監造服務工作</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
@@ -5392,7 +5392,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-30 10:46</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-30 18:57</t>
         </is>
       </c>
     </row>
@@ -5459,22 +5459,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>屏東縣恆春鎮公所</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>115ER00317945401620</t>
+          <t>F-261004</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5484,11 +5484,11 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>教學大樓暨砲塔教室訓練設施改善工程</t>
+          <t>115-恆春鎮大光里大光路旁人行步道改善工程</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
-        <v>59420970</v>
+        <v>6195000</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -5497,7 +5497,7 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>115/11/23</t>
+          <t>115/11/09</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>臺北市政府工務局新建工程處</t>
+          <t>花蓮縣新城鄉嘉里國民小學</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>11507003030201501</t>
+          <t>zlips1151030</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>文和橋上部改建工程（含台電管線代辦）</t>
+          <t>花蓮縣嘉里國民小學校區污雜排水管配合公共下水道納管改善工程</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
@@ -5618,7 +5618,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉嘉里國民小學</t>
+          <t>工程招標機關</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>zlips1151030</t>
+          <t>L0515P1079S</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>花蓮縣嘉里國民小學校區污雜排水管配合公共下水道納管改善工程</t>
+          <t>宜蘭工務段轄區鐵路跨河橋梁基礎裸露補強工程(A-1標接續工程)</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府經濟發展局</t>
+          <t>台灣電力股份有限公司桃園區營業處</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>115094</t>
+          <t>1031570108</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>116年高雄會展產業推動服務案</t>
+          <t>桃園區營業處115年丙工區零星配電管路工程</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府工務局</t>
+          <t>高雄市政府經濟發展局</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>1151686</t>
+          <t>115094</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>116年度高雄市寬頻管道委託維修管理服務</t>
+          <t>116年高雄會展產業推動服務案</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司桃園區營業處</t>
+          <t>高雄市政府工務局</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1031570108</t>
+          <t>1151686</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>桃園區營業處115年丙工區零星配電管路工程</t>
+          <t>116年度高雄市寬頻管道委託維修管理服務</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>工程招標機關</t>
+          <t>臺北市政府工務局新建工程處</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>L0515P1079S</t>
+          <t>11507003030201501</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>宜蘭工務段轄區鐵路跨河橋梁基礎裸露補強工程(A-1標接續工程)</t>
+          <t>文和橋上部改建工程（含台電管線代辦）</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1151027-A8</t>
+          <t>115EP634143199002200</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>桃園市觀音草漯多功能場館新建統包工程</t>
+          <t>D005工程</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>TIPC115B06</t>
+          <t>A058-1151029-2</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>116年度高雄港海域污染應變工作勞務作業</t>
+          <t>屏東縣身心障礙者社會生活適應計畫</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="K12" s="9" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料更正</t>
+          <t>招標文件公開閱覽資料</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>115EP634143199002200</t>
+          <t>1151027-A8</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>D005工程</t>
+          <t>桃園市觀音草漯多功能場館新建統包工程</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>工程招標機關</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>JTY00115061</t>
+          <t>11151008</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>高雄市三民區中華段二小段686-2、690、690-3、691等25筆地號土地</t>
+          <t>衛生福利部台南醫院多房間職務宿舍新建工程</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>財物出租</t>
+          <t>招標文件公開閱覽資料更正</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>W65411566007</t>
+          <t>W65411566006</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>基隆市安樂區新城段291-1地號土地</t>
+          <t>基隆市安樂區代天府段951-1地號土地</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>行政院公共工程委員會</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>A058-1151029-2</t>
+          <t>115S0001</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>屏東縣身心障礙者社會生活適應計畫</t>
+          <t>標售本會奉准報廢設備財物一批</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料</t>
+          <t>財物變賣</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>行政院公共工程委員會</t>
+          <t>臺灣港務股份有限公司</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>115S0001</t>
+          <t>TIPC115B06</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>標售本會奉准報廢設備財物一批</t>
+          <t>116年度高雄港海域污染應變工作勞務作業</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>財物變賣</t>
+          <t>招標文件公開閱覽資料更正</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
+          <t>高雄市路竹區蔡文國民小學</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>W65411566006</t>
+          <t>tsw11510</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>基隆市安樂區代天府段951-1地號土地</t>
+          <t>115學年度幼至五年級戶外教育採購</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>財物變賣</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>高雄市路竹區蔡文國民小學</t>
+          <t>工程招標機關</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>tsw11510</t>
+          <t>JTY00115061</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>115學年度幼至五年級戶外教育採購</t>
+          <t>高雄市三民區中華段二小段686-2、690、690-3、691等25筆地號土地</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>財物出租</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司桃園區營業處</t>
+          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>103153-7</t>
+          <t>W65411566007</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>116年甲工區零星配電外線工程</t>
+          <t>基隆市安樂區新城段291-1地號土地</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>財物變賣</t>
         </is>
       </c>
     </row>
@@ -6582,12 +6582,12 @@
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>桃園市大園區農會</t>
+          <t>台灣電力股份有限公司桃園區營業處</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>1151029-1</t>
+          <t>103153-7</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
@@ -6597,7 +6597,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>115年度大園區農會「農業金融業務發展計畫」本會及三和辦事處停車場設備升級工程</t>
+          <t>116年甲工區零星配電外線工程</t>
         </is>
       </c>
       <c r="H24" s="11" t="n">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>桃園市大園區農會</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>CP15054</t>
+          <t>1151029-1</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>臨床檢驗科委託代檢計1項</t>
+          <t>115年度大園區農會「農業金融業務發展計畫」本會及三和辦事處停車場設備升級工程</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>臺北市政府捷運工程局第二區工程處</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>CF750</t>
+          <t>CP15054</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>臺北都會區大眾捷運系統環狀線東環段CF750區段標工程</t>
+          <t>臨床檢驗科委託代檢計1項</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>臺北市政府捷運工程局第二區工程處</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>11151008</t>
+          <t>CF750</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>衛生福利部台南醫院多房間職務宿舍新建工程</t>
+          <t>臺北都會區大眾捷運系統環狀線東環段CF750區段標工程</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
@@ -6880,7 +6880,7 @@
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料更正</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>衛生福利部桃園醫院</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>TY115-1029</t>
+          <t>CN115F02</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>廢水設備維修汰換改善工程</t>
+          <t>臺南市安南區城東段1029、1029-1、1030地號等3筆土地強制執行建物拆除工程採購案</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>衛生福利部桃園醫院</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>CN115F02</t>
+          <t>TY115-1029</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>臺南市安南區城東段1029、1029-1、1030地號等3筆土地強制執行建物拆除工程採購案</t>
+          <t>廢水設備維修汰換改善工程</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
@@ -7266,17 +7266,17 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署</t>
+          <t>台灣電力股份有限公司花東供電區營運處</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>1150201</t>
+          <t>4951570011</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>「主機安全管理與資安漏洞整治平台」使用授權</t>
+          <t>69kV立霧~北埔線#16~#19鐵塔及基礎改建工程</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7314,22 +7314,22 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5129-其他用途建築工程</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>臺北大眾捷運股份有限公司</t>
+          <t>高雄市楠梓區油廠國民小學</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>B15A06926</t>
+          <t>ORPS11511</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>371型電聯車車廂內飾板修復工作</t>
+          <t>北三棟老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料更正</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7367,22 +7367,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>高雄市旗津區中洲國民小學</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>IL11508D02</t>
+          <t>115107</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>115年資訊機房高架地板及消防預警等設備擴充案</t>
+          <t>115年度防空噪音防制設施防音門更新工程</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料更正</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7420,22 +7420,22 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>工程類5129-其他用途建築工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>高雄市楠梓區油廠國民小學</t>
+          <t>臺北大眾捷運股份有限公司</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>ORPS11511</t>
+          <t>B15A06926</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>北三棟老舊廁所整修工程</t>
+          <t>371型電聯車車廂內飾板修復工作</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開徵求廠商提供參考資料更正</t>
         </is>
       </c>
     </row>
@@ -7473,22 +7473,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>高雄市旗津區中洲國民小學</t>
+          <t>經濟部水利署</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>115107</t>
+          <t>1150201</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>115年度防空噪音防制設施防音門更新工程</t>
+          <t>「主機安全管理與資安漏洞整治平台」使用授權</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -7531,17 +7531,17 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司花東供電區營運處</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>4951570011</t>
+          <t>IL11508D02</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>69kV立霧~北埔線#16~#19鐵塔及基礎改建工程</t>
+          <t>115年資訊機房高架地板及消防預警等設備擴充案</t>
         </is>
       </c>
       <c r="H42" s="11" t="n">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開徵求廠商提供參考資料更正</t>
         </is>
       </c>
     </row>
@@ -7632,22 +7632,22 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>臺東縣臺東市公所</t>
+          <t>彰化縣立原斗國民中小學</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>E115092301</t>
+          <t>115-10</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>115年度農地重劃區緊急農水路改善工程-臺東市第二梯次</t>
+          <t>115年度偏遠地區學校及非山非市學校設施設備計畫-國中部教室整修工程</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
@@ -7685,22 +7685,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>彰化縣立原斗國民中小學</t>
+          <t>臺東縣臺東市公所</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>115-10</t>
+          <t>E115092301</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>115年度偏遠地區學校及非山非市學校設施設備計畫-國中部教室整修工程</t>
+          <t>115年度農地重劃區緊急農水路改善工程-臺東市第二梯次</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
@@ -7950,7 +7950,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -7960,12 +7960,12 @@
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>臺中市太平區公所</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>116FF00302317100110</t>
+          <t>115-C17</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>光華南營區核訓場改建工程</t>
+          <t>115年太平區山田路大湖桶農路支線下邊坡復建工程</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
@@ -8003,22 +8003,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司屏東區管理處</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>13S-15-1331-01</t>
+          <t>116FF00302317100110</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>115年度潮州所管線單價工程(一)(開口契約)</t>
+          <t>光華南營區核訓場改建工程</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
@@ -8114,17 +8114,17 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮州國民小學</t>
+          <t>台灣自來水股份有限公司屏東區管理處</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>cjps11510toilet</t>
+          <t>13S-15-1331-01</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮州國民小學 「114-116公立國民中小學老舊廁所整修工程」採購案</t>
+          <t>115年度潮州所管線單價工程(一)(開口契約)</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
@@ -8162,22 +8162,22 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>桃園市楊梅區水美國民小學</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>HC1155103</t>
+          <t>c0402-1151001</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>客雅南圳幹線等6處維修工程</t>
+          <t>新設多功能風雨教室廁所暨通道周邊設施工程</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
@@ -8268,22 +8268,22 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>臺中市太平區公所</t>
+          <t>澎湖縣政府文化局</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>115-C17</t>
+          <t>SV-115049</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>115年太平區山田路大湖桶農路支線下邊坡復建工程</t>
+          <t>澎湖縣圖書館BigMaker計畫-閱覽空間改造工程採購案</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
@@ -8321,22 +8321,22 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>桃園市楊梅區水美國民小學</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>c0402-1151001</t>
+          <t>1151007A-3</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>新設多功能風雨教室廁所暨通道周邊設施工程</t>
+          <t>Danas-H-06-02-11-玉里大禹里13鄰野溪護岸災害復建工程等2案</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
@@ -8374,22 +8374,22 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>屏東縣潮州鎮潮州國民小學</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>1151007A-3</t>
+          <t>cjps11510toilet</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>Danas-H-06-02-11-玉里大禹里13鄰野溪護岸災害復建工程等2案</t>
+          <t>屏東縣潮州鎮潮州國民小學 「114-116公立國民中小學老舊廁所整修工程」採購案</t>
         </is>
       </c>
       <c r="H58" s="11" t="n">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>財物類481-醫療,外科及矯形設備</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>澎湖縣政府文化局</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>SV-115049</t>
+          <t>LP16084</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>澎湖縣圖書館BigMaker計畫-閱覽空間改造工程採購案</t>
+          <t>「水雷射牙科治療儀1組」</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>臺東縣綠島鄉公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>115017</t>
+          <t>HC1155103</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>石頭公廟旁大排水溝工程</t>
+          <t>客雅南圳幹線等6處維修工程</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
@@ -8586,22 +8586,22 @@
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>財物類481-醫療,外科及矯形設備</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D62" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>臺東縣綠島鄉公所</t>
         </is>
       </c>
       <c r="E62" s="8" t="inlineStr">
         <is>
-          <t>LP16084</t>
+          <t>115017</t>
         </is>
       </c>
       <c r="F62" s="8" t="inlineStr">
@@ -8611,7 +8611,7 @@
       </c>
       <c r="G62" s="10" t="inlineStr">
         <is>
-          <t>「水雷射牙科治療儀1組」</t>
+          <t>石頭公廟旁大排水溝工程</t>
         </is>
       </c>
       <c r="H62" s="11" t="n">
@@ -8639,22 +8639,22 @@
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>工程類5153-屋頂及防水工程</t>
+          <t>財物類481-醫療,外科及矯形設備</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>116EK62120704500120</t>
+          <t>LP16018</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>地勤寢室南棟整修工程</t>
+          <t>超音波掃描儀1組</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
@@ -8813,7 +8813,7 @@
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>LP16018</t>
+          <t>LP16189</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>超音波掃描儀1組</t>
+          <t>全景掃描儀(全景數位病理切片掃描儀)1組</t>
         </is>
       </c>
       <c r="H66" s="11" t="n">
@@ -8851,22 +8851,22 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>財物類481-醫療,外科及矯形設備</t>
+          <t>工程類5153-屋頂及防水工程</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>LP16189</t>
+          <t>116EK62120704500120</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>全景掃描儀(全景數位病理切片掃描儀)1組</t>
+          <t>地勤寢室南棟整修工程</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
@@ -9063,22 +9063,22 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺北分署</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>115-SWC-1-4-011</t>
+          <t>115ER00317945401620</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>115年度新竹縣新埔鎮等地區(第2標)水土保持工程開口契約</t>
+          <t>教學大樓暨砲塔教室訓練設施改善工程</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>115-SWC-1-4-012</t>
+          <t>115-SWC-1-4-011</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>115年度新竹縣寶山鄉等地區(第2標)水土保持工程開口契約</t>
+          <t>115年度新竹縣新埔鎮等地區(第2標)水土保持工程開口契約</t>
         </is>
       </c>
       <c r="H72" s="11" t="n">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>農業部農村發展及水土保持署臺北分署</t>
         </is>
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>TT114H009</t>
+          <t>115-SWC-1-4-013</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>小馬圳南溪幹線圳災害復建工程-楊柳颱風</t>
+          <t>115年度新竹市香山區等地區水土保持工程開口契約</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
@@ -9222,7 +9222,7 @@
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -9232,12 +9232,12 @@
       </c>
       <c r="D74" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>農業部農村發展及水土保持署臺北分署</t>
         </is>
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>TT115A15</t>
+          <t>115-SWC-1-4-012</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>卑南圳知本農場支線系統強化工程(第2期)</t>
+          <t>115年度新竹縣寶山鄉等地區(第2標)水土保持工程開口契約</t>
         </is>
       </c>
       <c r="H74" s="11" t="n">
@@ -9275,22 +9275,22 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>嘉義縣阿里山鄉達邦國民小學</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>115-512</t>
+          <t>dbps1151002</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>116年度谷關段轄區省道交通安全設施、標線改善及災害搶修工程(開口契約)</t>
+          <t>115年度改善偏遠地區國民中小學教師宿舍計畫－里佳分校宿舍修繕工程</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
@@ -9328,22 +9328,22 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺北分署</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>115-SWC-1-4-013</t>
+          <t>115-512</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>115年度新竹市香山區等地區水土保持工程開口契約</t>
+          <t>116年度谷關段轄區省道交通安全設施、標線改善及災害搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H76" s="11" t="n">
@@ -9381,22 +9381,22 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>SP15630</t>
+          <t>TT115A15</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>高雄榮總衛材集中採購(院內)計100項(開口契約)</t>
+          <t>卑南圳知本農場支線系統強化工程(第2期)</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
@@ -9434,22 +9434,22 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>嘉義縣阿里山鄉達邦國民小學</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>dbps1151002</t>
+          <t>TT114H009</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>115年度改善偏遠地區國民中小學教師宿舍計畫－里佳分校宿舍修繕工程</t>
+          <t>小馬圳南溪幹線圳災害復建工程-楊柳颱風</t>
         </is>
       </c>
       <c r="H78" s="11" t="n">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>VP15001</t>
+          <t>SP15630</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>高雄榮總116年至117年衛材集中採購(輔標)計64項(開口契約)</t>
+          <t>高雄榮總衛材集中採購(院內)計100項(開口契約)</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
@@ -9545,7 +9545,7 @@
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>財物類481-醫療,外科及矯形設備</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
@@ -9555,7 +9555,7 @@
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>LP16149</t>
+          <t>VP15001</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>器械清洗消毒烘乾機1台</t>
+          <t>高雄榮總116年至117年衛材集中採購(輔標)計64項(開口契約)</t>
         </is>
       </c>
       <c r="H80" s="11" t="n">
@@ -9593,22 +9593,22 @@
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類481-醫療,外科及矯形設備</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>1150929A-1</t>
+          <t>LP16149</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>「Danas-H-01-07-11－玉里源城里花71線支線農路災復工程等2案」暨「115年度上半年基層座談會（里長提案補助）」等二案合併採購</t>
+          <t>器械清洗消毒烘乾機1台</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
@@ -9646,22 +9646,22 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>工程類5174-地板及牆面貼磚工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>桃園市新屋區社子國民小學</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>SZES11505</t>
+          <t>115-318</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>「115年度補助本市市立各級學校什項修繕工程及教學設備經費」—校園鋪面及圍牆欄杆建置工程</t>
+          <t>116年度彰化段轄區省道台17線路容清理工作、綠美化維護及災害搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H82" s="11" t="n">
@@ -9699,22 +9699,22 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>115-318</t>
+          <t>1150929A-1</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>116年度彰化段轄區省道台17線路容清理工作、綠美化維護及災害搶修工程(開口契約)</t>
+          <t>「Danas-H-01-07-11－玉里源城里花71線支線農路災復工程等2案」暨「115年度上半年基層座談會（里長提案補助）」等二案合併採購</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
@@ -9752,22 +9752,22 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5174-地板及牆面貼磚工程</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第九區管理處</t>
+          <t>桃園市新屋區社子國民小學</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>WC-11509010012</t>
+          <t>SZES11505</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>115年花蓮給水廠(花蓮所轄區A)管線設備單價採購工程及115年花蓮給水廠(花蓮服務所轄區)管線設備維修開口契約併案發包</t>
+          <t>「115年度補助本市市立各級學校什項修繕工程及教學設備經費」—校園鋪面及圍牆欄杆建置工程</t>
         </is>
       </c>
       <c r="H84" s="11" t="n">
@@ -9858,22 +9858,22 @@
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>台灣自來水股份有限公司第九區管理處</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>115AA038</t>
+          <t>WC-11509010012</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>瑪雅里環里道路災後復建工程</t>
+          <t>115年花蓮給水廠(花蓮所轄區A)管線設備單價採購工程及115年花蓮給水廠(花蓮服務所轄區)管線設備維修開口契約併案發包</t>
         </is>
       </c>
       <c r="H86" s="11" t="n">
@@ -9916,17 +9916,17 @@
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>KS115E006</t>
+          <t>115AA038</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>橋頭農地重劃區頂鹽田支線小給六之三(0K+230)等改善工程</t>
+          <t>瑪雅里環里道路災後復建工程</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
@@ -9969,17 +9969,17 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>115AA035</t>
+          <t>KS115E006</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>115年度那瑪夏區部落安全環境建設及原民地區農路修繕工程</t>
+          <t>橋頭農地重劃區頂鹽田支線小給六之三(0K+230)等改善工程</t>
         </is>
       </c>
       <c r="H88" s="11" t="n">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
@@ -10027,12 +10027,12 @@
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府都市發展局</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>115B305</t>
+          <t>115AA036</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>新化水圳南圳綠堤縫合計畫工程</t>
+          <t>那瑪夏區達卡努瓦里丘平溪七七孔橋上游災害復建工程</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>臺南市政府都市發展局</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>115B305</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>Danas-H-01-06-9-獅子鄉南世村金卡來農路災害復建工程</t>
+          <t>新化水圳南圳綠堤縫合計畫工程</t>
         </is>
       </c>
       <c r="H90" s="11" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>115AA036</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>那瑪夏區達卡努瓦里丘平溪七七孔橋上游災害復建工程</t>
+          <t>Danas-H-01-06-9-獅子鄉南世村金卡來農路災害復建工程</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
@@ -10335,22 +10335,22 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>115AA049</t>
+          <t>115-218</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>那瑪夏區達卡努瓦橋南端護岸災後復建工程</t>
+          <t>台61線130K~145K平面路口行穿線照明設施改善工程</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
@@ -10393,17 +10393,17 @@
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>勞務類8676-技術檢定與分析服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>CP15088</t>
+          <t>115AA049</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>病理檢驗部委外代檢勞務採購1項</t>
+          <t>那瑪夏區達卡努瓦橋南端護岸災後復建工程</t>
         </is>
       </c>
       <c r="H96" s="11" t="n">
@@ -10441,22 +10441,22 @@
       </c>
       <c r="B97" s="3" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>115EE63017980500410</t>
+          <t>115AA035</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>營區雨遮設施改善工程</t>
+          <t>115年度那瑪夏區部落安全環境建設及原民地區農路修繕工程</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
@@ -10494,22 +10494,22 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>勞務類8676-技術檢定與分析服務</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>115-218</t>
+          <t>CP15088</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>台61線130K~145K平面路口行穿線照明設施改善工程</t>
+          <t>病理檢驗部委外代檢勞務採購1項</t>
         </is>
       </c>
       <c r="H98" s="11" t="n">
@@ -10600,22 +10600,22 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>雲林縣政府</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>1151A30021</t>
+          <t>SP15493</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>雲林縣虎尾鎮B幹線(文化路)雨水下水道改道工程</t>
+          <t>過敏免疫風濕科用試劑計2項(開口契約)</t>
         </is>
       </c>
       <c r="H100" s="11" t="n">
@@ -10653,22 +10653,22 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>SP15493</t>
+          <t>1151A30021</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>過敏免疫風濕科用試劑計2項(開口契約)</t>
+          <t>雲林縣虎尾鎮B幹線(文化路)雨水下水道改道工程</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
@@ -10918,22 +10918,22 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>115-125</t>
+          <t>115EE63017980500410</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>116年度苗栗工務段標線工程(開口契約)</t>
+          <t>營區雨遮設施改善工程</t>
         </is>
       </c>
       <c r="H106" s="11" t="n">
@@ -10976,17 +10976,17 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>M116107</t>
+          <t>115-125</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>116年度高屏溪構造物維修改善工程(開口契約)</t>
+          <t>116年度苗栗工務段標線工程(開口契約)</t>
         </is>
       </c>
       <c r="H107" s="6" t="n">
@@ -11024,22 +11024,22 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>國立花蓮高級商業職業學校</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>KS115M028</t>
+          <t>115C06</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>115及116年度九曲站轄內圳路設施維護開口契約</t>
+          <t>115年風雨球場等工程</t>
         </is>
       </c>
       <c r="H108" s="11" t="n">
@@ -11077,22 +11077,22 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>國立花蓮高級商業職業學校</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>115C06</t>
+          <t>M116107</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>115年風雨球場等工程</t>
+          <t>116年度高屏溪構造物維修改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H109" s="6" t="n">
@@ -11183,22 +11183,22 @@
       </c>
       <c r="B111" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司屏東區管理處</t>
+          <t>交通部高速公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>13S-15-1350-03-1</t>
+          <t>115C010P073</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>115年牡丹廠管線單價工程、115年度牡丹廠管線設備維修工程(併案發包)</t>
+          <t>116年大甲工務段轄區部分業務委外勞務承攬工作</t>
         </is>
       </c>
       <c r="H111" s="6" t="n">
@@ -11246,12 +11246,12 @@
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>交通部高速公路局中區養護工程分局</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>115C010P073</t>
+          <t>KS115M028</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>116年大甲工務段轄區部分業務委外勞務承攬工作</t>
+          <t>115及116年度九曲站轄內圳路設施維護開口契約</t>
         </is>
       </c>
       <c r="H112" s="11" t="n">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -11299,12 +11299,12 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府水利局</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>C1150918</t>
+          <t>M116109</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>左營區和光街(和光街109巷至和光街206巷)災修復建工程</t>
+          <t>116年度七河分署轄區中央管排水構造物維修改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H113" s="6" t="n">
@@ -11342,7 +11342,7 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
@@ -11352,12 +11352,12 @@
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>高雄市政府水利局</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>M116109</t>
+          <t>C1150918</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>116年度七河分署轄區中央管排水構造物維修改善工程(開口契約)</t>
+          <t>左營區和光街(和光街109巷至和光街206巷)災修復建工程</t>
         </is>
       </c>
       <c r="H114" s="11" t="n">
@@ -11395,22 +11395,22 @@
       </c>
       <c r="B115" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>新北市八里區長坑國民小學</t>
+          <t>台灣自來水股份有限公司屏東區管理處</t>
         </is>
       </c>
       <c r="E115" s="3" t="inlineStr">
         <is>
-          <t>CKES11507</t>
+          <t>13S-15-1350-03-1</t>
         </is>
       </c>
       <c r="F115" s="3" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>115年長坑國小職務宿舍修建工程</t>
+          <t>115年牡丹廠管線單價工程、115年度牡丹廠管線設備維修工程(併案發包)</t>
         </is>
       </c>
       <c r="H115" s="6" t="n">
@@ -11448,22 +11448,22 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>新北市八里區長坑國民小學</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>KS115E035</t>
+          <t>CKES11507</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>獅四輪小排四之十五(0K+035)等改善工程</t>
+          <t>115年長坑國小職務宿舍修建工程</t>
         </is>
       </c>
       <c r="H116" s="11" t="n">
@@ -11501,22 +11501,22 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>115213</t>
+          <t>KS115E035</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>永大、武立、興豐公園增設遮陽設施及兒童遊戲場環境設施改善工程</t>
+          <t>獅四輪小排四之十五(0K+035)等改善工程</t>
         </is>
       </c>
       <c r="H117" s="6" t="n">
@@ -11554,22 +11554,22 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>南投縣中寮鄉公所</t>
+          <t>屏東縣屏東市公所</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>115-0118</t>
+          <t>115213</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>114中寮鄉崁頂村後寮段744-6地號蝕溝整治工程</t>
+          <t>永大、武立、興豐公園增設遮陽設施及兒童遊戲場環境設施改善工程</t>
         </is>
       </c>
       <c r="H118" s="11" t="n">
@@ -11607,22 +11607,22 @@
       </c>
       <c r="B119" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>財物類381-傢具</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>臺北市政府工務局新建工程處</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>NCOdecor11501</t>
+          <t>M116110</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>115年度新建工程處辦公傢俱及附屬設備(含電源線路配置)財物採購案</t>
+          <t>116年度七河分署轄區構造物維修改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H119" s="6" t="n">
@@ -11665,17 +11665,17 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>南投縣中寮鄉公所</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>M116110</t>
+          <t>115-0118</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>116年度七河分署轄區構造物維修改善工程(開口契約)</t>
+          <t>114中寮鄉崁頂村後寮段744-6地號蝕溝整治工程</t>
         </is>
       </c>
       <c r="H120" s="11" t="n">
@@ -11713,22 +11713,22 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>財物類381-傢具</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣立苑裡高級中學</t>
+          <t>臺北市政府工務局新建工程處</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>1150023</t>
+          <t>NCOdecor11501</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>115年度運動場地整建工程採購案</t>
+          <t>115年度新建工程處辦公傢俱及附屬設備(含電源線路配置)財物採購案</t>
         </is>
       </c>
       <c r="H121" s="6" t="n">
@@ -11766,22 +11766,22 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>工程類5159-其他專業工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>新北市新莊區公所</t>
+          <t>苗栗縣立苑裡高級中學</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>1151027J2</t>
+          <t>1150023</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>116年度新莊區抽水機代操作、維護保養工作（開口合約）</t>
+          <t>115年度運動場地整建工程採購案</t>
         </is>
       </c>
       <c r="H122" s="11" t="n">
@@ -11819,22 +11819,22 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
+          <t>工程類5159-其他專業工程</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>新北市新莊區公所</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>M116048</t>
+          <t>1151027J2</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>116年度東港溪堤防樹木修剪維護管理工作(開口契約)</t>
+          <t>116年度新莊區抽水機代操作、維護保養工作（開口合約）</t>
         </is>
       </c>
       <c r="H123" s="6" t="n">
@@ -11872,22 +11872,22 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>財物類4393-其他通用機具</t>
+          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>高雄市左營區文府國民小學</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>115M1008</t>
+          <t>M116048</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>115學年度消防系統設備改善案</t>
+          <t>116年度東港溪堤防樹木修剪維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H124" s="11" t="n">
@@ -11925,22 +11925,22 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類4393-其他通用機具</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣南庄鄉公所</t>
+          <t>高雄市左營區文府國民小學</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>115-034</t>
+          <t>115M1008</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>115年4月豪雨南庄鄉南富村18鄰農路災後復建工程</t>
+          <t>115學年度消防系統設備改善案</t>
         </is>
       </c>
       <c r="H125" s="6" t="n">
@@ -11983,17 +11983,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣南庄鄉公所</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>115-038</t>
+          <t>M116044</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>115年4月豪雨南庄鄉獅山村10鄰及17鄰農路災後復建工程</t>
+          <t>116年度高屏溪堤防維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H126" s="11" t="n">
@@ -12036,17 +12036,17 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>苗栗縣南庄鄉公所</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>M116052</t>
+          <t>115-038</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>116年度隘寮溪堤防維護管理工作(開口契約)</t>
+          <t>115年4月豪雨南庄鄉獅山村10鄰及17鄰農路災後復建工程</t>
         </is>
       </c>
       <c r="H127" s="6" t="n">
@@ -12084,22 +12084,22 @@
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>工程類5129-其他用途建築工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉公所</t>
+          <t>苗栗縣南庄鄉公所</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>115014</t>
+          <t>115-034</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉社區多功能綜合館新建工程</t>
+          <t>115年4月豪雨南庄鄉南富村18鄰農路災後復建工程</t>
         </is>
       </c>
       <c r="H128" s="11" t="n">
@@ -12152,7 +12152,7 @@
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>M116044</t>
+          <t>M116052</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>116年度高屏溪堤防維護管理工作(開口契約)</t>
+          <t>116年度隘寮溪堤防維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H129" s="6" t="n">
@@ -12190,22 +12190,22 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
+          <t>工程類5129-其他用途建築工程</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>宜蘭縣三星鄉公所</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>M116045</t>
+          <t>115014</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>116年度東港溪水系及海堤堤防維護管理工作(開口契約)</t>
+          <t>宜蘭縣三星鄉社區多功能綜合館新建工程</t>
         </is>
       </c>
       <c r="H130" s="11" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
+          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>RC-114-0701-0021-3</t>
+          <t>M116045</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>高市梓官區梓官路汰換管線工程</t>
+          <t>116年度東港溪水系及海堤堤防維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H131" s="6" t="n">
@@ -12301,17 +12301,17 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司綜合研究所</t>
+          <t>中央研究院</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>5461500173</t>
+          <t>115-M39</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>跨領域單一軟體之工程模擬全物理場高階多核心平行求解授權1套</t>
+          <t>後棟學人招待所整修工程</t>
         </is>
       </c>
       <c r="H132" s="11" t="n">
@@ -12354,17 +12354,17 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>中央研究院</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>115-M39</t>
+          <t>RC-114-0701-0021-3</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>後棟學人招待所整修工程</t>
+          <t>高市梓官區梓官路汰換管線工程</t>
         </is>
       </c>
       <c r="H133" s="6" t="n">
@@ -12407,17 +12407,17 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
+          <t>台灣電力股份有限公司綜合研究所</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>6541551032</t>
+          <t>5461500173</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>345kV汐止~板橋線#68、#69鐵塔更換工程</t>
+          <t>跨領域單一軟體之工程模擬全物理場高階多核心平行求解授權1套</t>
         </is>
       </c>
       <c r="H134" s="11" t="n">
@@ -12773,22 +12773,22 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>臺中市西區中正國民小學</t>
+          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>CCES115-1028</t>
+          <t>6541551032</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>臺中市西區中正國民小學公益樓A棟廁所整修工程(第二次)</t>
+          <t>345kV汐止~板橋線#68、#69鐵塔更換工程</t>
         </is>
       </c>
       <c r="H141" s="6" t="n">
@@ -12826,22 +12826,22 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>基隆市政府</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>115A107</t>
+          <t>C1151008-P1</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="G142" s="10" t="inlineStr">
         <is>
-          <t>(116)基隆市人行道雨陽棚整建工程(單價標)</t>
+          <t>115年水利村及塭豐漁港泊地及航道清疏工程(開口契約)</t>
         </is>
       </c>
       <c r="H142" s="11" t="n">
@@ -12879,22 +12879,22 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>臺中市南屯區南屯國民小學</t>
+          <t>基隆市政府</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Ntes114-11-a</t>
+          <t>115A107</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>114年度南屯國小南棟前側老舊廁所整修工程採購案</t>
+          <t>(116)基隆市人行道雨陽棚整建工程(單價標)</t>
         </is>
       </c>
       <c r="H143" s="6" t="n">
@@ -12932,22 +12932,22 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>臺中市西區中正國民小學</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>C1151008-P1</t>
+          <t>CCES115-1028</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="G144" s="10" t="inlineStr">
         <is>
-          <t>115年水利村及塭豐漁港泊地及航道清疏工程(開口契約)</t>
+          <t>臺中市西區中正國民小學公益樓A棟廁所整修工程(第二次)</t>
         </is>
       </c>
       <c r="H144" s="11" t="n">
@@ -12985,22 +12985,22 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>工程類5132-橋樑,高架快速道路,隧道及地鐵</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>桃園市中壢區公所</t>
+          <t>臺中市南屯區南屯國民小學</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>115-10-094</t>
+          <t>Ntes114-11-a</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>桃園市中壢區新街溪河岸南園二路57巷18弄新設人行跨橋工程</t>
+          <t>114年度南屯國小南棟前側老舊廁所整修工程採購案</t>
         </is>
       </c>
       <c r="H145" s="6" t="n">
@@ -13091,22 +13091,22 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5132-橋樑,高架快速道路,隧道及地鐵</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第四區管理處</t>
+          <t>桃園市中壢區公所</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>W4-115-0401-528</t>
+          <t>115-10-094</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>大里服務所、烏日、霧峰等營運所管線設備修理工程(115年開口契約)</t>
+          <t>桃園市中壢區新街溪河岸南園二路57巷18弄新設人行跨橋工程</t>
         </is>
       </c>
       <c r="H147" s="6" t="n">
@@ -13144,22 +13144,22 @@
       </c>
       <c r="B148" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公所</t>
+          <t>台灣自來水股份有限公司第四區管理處</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>F-261004</t>
+          <t>W4-115-0401-528</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="G148" s="10" t="inlineStr">
         <is>
-          <t>115-恆春鎮大光里大光路旁人行步道改善工程</t>
+          <t>大里服務所、烏日、霧峰等營運所管線設備修理工程(115年開口契約)</t>
         </is>
       </c>
       <c r="H148" s="11" t="n">
@@ -13308,17 +13308,17 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>臺中市豐原區豐原國民小學</t>
+          <t>台灣自來水股份有限公司第四區管理處</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>W4-115-0401-529</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>豐原國小115年度公立幼兒園充實及改善教學環境設施設備工程」</t>
+          <t>台中給水廠北工區管線設備修理工程(115開口契約)</t>
         </is>
       </c>
       <c r="H151" s="6" t="n">
@@ -13356,22 +13356,22 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>勞務類751-郵政及專差服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司高雄郵局</t>
+          <t>臺中市豐原區豐原國民小學</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>115-050</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="G152" s="10" t="inlineStr">
         <is>
-          <t>高雄郵局掛號、限時及國際郵件處理勞務承攬</t>
+          <t>豐原國小115年度公立幼兒園充實及改善教學環境設施設備工程」</t>
         </is>
       </c>
       <c r="H152" s="11" t="n">
@@ -13409,22 +13409,22 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>勞務類751-郵政及專差服務</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第四區管理處</t>
+          <t>中華郵政股份有限公司高雄郵局</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>W4-115-0401-529</t>
+          <t>115-050</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>台中給水廠北工區管線設備修理工程(115開口契約)</t>
+          <t>高雄郵局掛號、限時及國際郵件處理勞務承攬</t>
         </is>
       </c>
       <c r="H153" s="6" t="n">
@@ -13462,7 +13462,7 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
@@ -13472,12 +13472,12 @@
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>桃園市八德區公所</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>BB1151029</t>
+          <t>1151029A-3</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="G154" s="10" t="inlineStr">
         <is>
-          <t>八德區霖園公園空間再造工程</t>
+          <t>花蓮縣玉里鎮大禹里瑟冷部落災後復建工程</t>
         </is>
       </c>
       <c r="H154" s="11" t="n">
@@ -13515,22 +13515,22 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>彰化縣埔心鄉明聖國民小學</t>
+          <t>高雄市田寮區公所</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>MSPS-11510</t>
+          <t>1151037</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>彰化縣明聖國民小學114年度公立國民中小學老舊廁所整修工程計畫</t>
+          <t>田寮區七星里高38往謝家祠堂路面災害復建工程等2案</t>
         </is>
       </c>
       <c r="H155" s="6" t="n">
@@ -13568,22 +13568,22 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>國立岡山高級農工職業學校</t>
+          <t>桃園市八德區公所</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>115A-05</t>
+          <t>BB1151029</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G156" s="10" t="inlineStr">
         <is>
-          <t>實習處階梯教室修繕第二期工程</t>
+          <t>八德區霖園公園空間再造工程</t>
         </is>
       </c>
       <c r="H156" s="11" t="n">
@@ -13621,22 +13621,22 @@
       </c>
       <c r="B157" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>國立岡山高級農工職業學校</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>1151029A-3</t>
+          <t>115A-05</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮大禹里瑟冷部落災後復建工程</t>
+          <t>實習處階梯教室修繕第二期工程</t>
         </is>
       </c>
       <c r="H157" s="6" t="n">
@@ -13674,22 +13674,22 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>彰化縣埔心鄉明聖國民小學</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>RC-115-0701-0025</t>
+          <t>MSPS-11510</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="G158" s="10" t="inlineStr">
         <is>
-          <t>高市前鎮區49至57號碼頭汰換管線工程</t>
+          <t>彰化縣明聖國民小學114年度公立國民中小學老舊廁所整修工程計畫</t>
         </is>
       </c>
       <c r="H158" s="11" t="n">
@@ -13727,22 +13727,22 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>004-C1151008-1</t>
+          <t>RC-115-0701-0025</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>115年屏東縣東港溪0826天然災害清疏工程</t>
+          <t>高市前鎮區49至57號碼頭汰換管線工程</t>
         </is>
       </c>
       <c r="H159" s="6" t="n">
@@ -13780,7 +13780,7 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
@@ -13790,12 +13790,12 @@
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>高雄市田寮區公所</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>1151037</t>
+          <t>004-C1151008-1</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
-          <t>田寮區七星里高38往謝家祠堂路面災害復建工程等2案</t>
+          <t>115年屏東縣東港溪0826天然災害清疏工程</t>
         </is>
       </c>
       <c r="H160" s="11" t="n">
@@ -13939,22 +13939,22 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第六河川分署</t>
+          <t>花蓮縣光復鄉公所</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>115-B-004-02-002-629</t>
+          <t>1151008-B87</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>115年度臺南市北門海埔地海堤構造物維修改善工程</t>
+          <t>MTA-D-08-01-07-花蓮縣光復鄉災後道路提報計畫-大華村</t>
         </is>
       </c>
       <c r="H163" s="6" t="n">
@@ -13992,22 +13992,22 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣光復鄉公所</t>
+          <t>經濟部水利署第六河川分署</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>1151008-B87</t>
+          <t>115-B-004-02-002-629</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="G164" s="10" t="inlineStr">
         <is>
-          <t>MTA-D-08-01-07-花蓮縣光復鄉災後道路提報計畫-大華村</t>
+          <t>115年度臺南市北門海埔地海堤構造物維修改善工程</t>
         </is>
       </c>
       <c r="H164" s="11" t="n">
@@ -14045,22 +14045,22 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>桃園市復興區光華國民小學</t>
+          <t>彰化縣彰化市南郭國民小學</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>KH-11502</t>
+          <t>11506A</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>115年度改善偏遠地區國民中小學教師宿舍</t>
+          <t>115年度運動操場及周邊設施整建工程</t>
         </is>
       </c>
       <c r="H165" s="6" t="n">
@@ -14098,22 +14098,22 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>彰化縣彰化市南郭國民小學</t>
+          <t>桃園市復興區光華國民小學</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>11506A</t>
+          <t>KH-11502</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="G166" s="10" t="inlineStr">
         <is>
-          <t>115年度運動操場及周邊設施整建工程</t>
+          <t>115年度改善偏遠地區國民中小學教師宿舍</t>
         </is>
       </c>
       <c r="H166" s="11" t="n">
@@ -35139,22 +35139,22 @@
       </c>
       <c r="B563" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C563" s="3" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣立苑裡高級中學</t>
+          <t>臺南市龍崎區公所</t>
         </is>
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>1150024</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="F563" s="3" t="inlineStr">
@@ -35164,7 +35164,7 @@
       </c>
       <c r="G563" s="5" t="inlineStr">
         <is>
-          <t>115年度賈宓圖書館空間改善工程採購案</t>
+          <t>龍崎區大溪清水宮廁所新建工程</t>
         </is>
       </c>
       <c r="H563" s="6" t="n">
@@ -35192,22 +35192,22 @@
       </c>
       <c r="B564" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C564" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D564" s="9" t="inlineStr">
         <is>
-          <t>臺南市龍崎區公所</t>
+          <t>苗栗縣立苑裡高級中學</t>
         </is>
       </c>
       <c r="E564" s="8" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>1150024</t>
         </is>
       </c>
       <c r="F564" s="8" t="inlineStr">
@@ -35217,7 +35217,7 @@
       </c>
       <c r="G564" s="10" t="inlineStr">
         <is>
-          <t>龍崎區大溪清水宮廁所新建工程</t>
+          <t>115年度賈宓圖書館空間改善工程採購案</t>
         </is>
       </c>
       <c r="H564" s="11" t="n">

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-30 18:57</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-31 10:37</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>115FB11519448300120</t>
+          <t>115FA02419445800120</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -635,7 +635,7 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>考潭、仁美營區新建設施工程專案管理含監造委託技術服務</t>
+          <t>雙連坡營區新建工程專案管理及監造委託技術服務</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
@@ -678,7 +678,7 @@
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>115FA02419445800120</t>
+          <t>115FB11519448300120</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -688,7 +688,7 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>雙連坡營區新建工程專案管理及監造委託技術服務</t>
+          <t>考潭、仁美營區新建設施工程專案管理含監造委託技術服務</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
@@ -769,7 +769,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/海軍</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>內政部消防署</t>
+          <t>國防部海軍司令部</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>G116-014</t>
+          <t>114-5160005513000220-2</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>「印太地區災害防救韌性與能力建構整合計畫」116年專案管理勞務委託採購案</t>
+          <t>兩棲偵搜大隊舟艇維修間整修工程第二次變更設計</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>中央/海軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>國防部海軍司令部</t>
+          <t>內政部消防署</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>114-5160005513000220-2</t>
+          <t>G116-014</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>兩棲偵搜大隊舟艇維修間整修工程第二次變更設計</t>
+          <t>「印太地區災害防救韌性與能力建構整合計畫」116年專案管理勞務委託採購案</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
@@ -5392,7 +5392,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-30 18:57</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-31 10:37</t>
         </is>
       </c>
     </row>
@@ -5459,22 +5459,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>勞務</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>屏東縣恆春鎮公所</t>
+          <t>臺灣港務股份有限公司</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>F-261004</t>
+          <t>TIPC115B06</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5484,11 +5484,11 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>115-恆春鎮大光里大光路旁人行步道改善工程</t>
+          <t>116年度高雄港海域污染應變工作勞務作業</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
-        <v>6195000</v>
+        <v>6182864</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>115/11/09</t>
+          <t>115/11/05</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>限制性招標(經公開評選或公開徵求者)</t>
         </is>
       </c>
     </row>
@@ -5512,22 +5512,22 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>勞務類8673-綜合工程服務</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>國立臺灣大學醫學院附設醫院</t>
+          <t>臺灣港務股份有限公司高雄港務分公司</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>FB2609180E</t>
+          <t>115-AE-055</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -5537,11 +5537,11 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>尖端醫療研究大樓新建統包工程</t>
+          <t>116-117年安平港區道路、橋梁、碼頭及其他公共設施巡查工作</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>0</v>
+        <v>4889635</v>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
@@ -5550,12 +5550,12 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>詳見公告</t>
+          <t>115/11/19</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -5565,22 +5565,22 @@
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉嘉里國民小學</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>zlips1151030</t>
+          <t>KS115E035</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>花蓮縣嘉里國民小學校區污雜排水管配合公共下水道納管改善工程</t>
+          <t>獅四輪小排四之十五(0K+035)等改善工程</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0</v>
+        <v>2971000</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -5603,12 +5603,12 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>詳見公告</t>
+          <t>115/11/09</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>工程招標機關</t>
+          <t>花蓮縣新城鄉嘉里國民小學</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>L0515P1079S</t>
+          <t>zlips1151030</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>宜蘭工務段轄區鐵路跨河橋梁基礎裸露補強工程(A-1標接續工程)</t>
+          <t>花蓮縣嘉里國民小學校區污雜排水管配合公共下水道納管改善工程</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府經濟發展局</t>
+          <t>國立臺灣大學醫學院附設醫院</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>115094</t>
+          <t>FB2609180E</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>116年高雄會展產業推動服務案</t>
+          <t>尖端醫療研究大樓新建統包工程</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府工務局</t>
+          <t>工程招標機關</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>1151686</t>
+          <t>L0515P1079S</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>116年度高雄市寬頻管道委託維修管理服務</t>
+          <t>宜蘭工務段轄區鐵路跨河橋梁基礎裸露補強工程(A-1標接續工程)</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -5883,7 +5883,7 @@
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>115EP634143199002200</t>
+          <t>1151027-A8</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>D005工程</t>
+          <t>桃園市觀音草漯多功能場館新建統包工程</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>高雄市政府工務局</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>A058-1151029-2</t>
+          <t>1151686</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>屏東縣身心障礙者社會生活適應計畫</t>
+          <t>116年度高雄市寬頻管道委託維修管理服務</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府社會局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>A058-1151029-2</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>高雄市政府社會局委託辦理「高雄市路得學舍」</t>
+          <t>屏東縣身心障礙者社會生活適應計畫</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>高雄市政府經濟發展局</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>1151027-A8</t>
+          <t>115094</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>桃園市觀音草漯多功能場館新建統包工程</t>
+          <t>116年高雄會展產業推動服務案</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府工務局</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>11151008</t>
+          <t>115EP634143199002200</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>衛生福利部台南醫院多房間職務宿舍新建工程</t>
+          <t>D005工程</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料更正</t>
+          <t>招標文件公開閱覽資料</t>
         </is>
       </c>
     </row>
@@ -6148,7 +6148,7 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="D16" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>臺南市政府工務局</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>1151HH001</t>
+          <t>11151008</t>
         </is>
       </c>
       <c r="F16" s="8" t="inlineStr">
@@ -6173,7 +6173,7 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>高雄市苓雅區武聖段1124地號土地標租（出租面積共337.5平方公尺）。</t>
+          <t>衛生福利部台南醫院多房間職務宿舍新建工程</t>
         </is>
       </c>
       <c r="H16" s="11" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="K16" s="9" t="inlineStr">
         <is>
-          <t>財物出租</t>
+          <t>招標文件公開閱覽資料更正</t>
         </is>
       </c>
     </row>
@@ -6201,7 +6201,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C17" s="3" t="inlineStr">
@@ -6211,12 +6211,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>W65411566006</t>
+          <t>1151HH001</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>基隆市安樂區代天府段951-1地號土地</t>
+          <t>高雄市苓雅區武聖段1124地號土地標租（出租面積共337.5平方公尺）。</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>財物變賣</t>
+          <t>財物出租</t>
         </is>
       </c>
     </row>
@@ -6264,12 +6264,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>行政院公共工程委員會</t>
+          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>115S0001</t>
+          <t>W65411566006</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>標售本會奉准報廢設備財物一批</t>
+          <t>基隆市安樂區代天府段951-1地號土地</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司</t>
+          <t>高雄市政府社會局</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>TIPC115B06</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>116年度高雄港海域污染應變工作勞務作業</t>
+          <t>高雄市政府社會局委託辦理「高雄市路得學舍」</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料更正</t>
+          <t>招標文件公開閱覽資料</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>高雄市路竹區蔡文國民小學</t>
+          <t>行政院公共工程委員會</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>tsw11510</t>
+          <t>115S0001</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>115學年度幼至五年級戶外教育採購</t>
+          <t>標售本會奉准報廢設備財物一批</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>財物變賣</t>
         </is>
       </c>
     </row>
@@ -6423,12 +6423,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>工程招標機關</t>
+          <t>高雄市路竹區蔡文國民小學</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>JTY00115061</t>
+          <t>tsw11510</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>高雄市三民區中華段二小段686-2、690、690-3、691等25筆地號土地</t>
+          <t>115學年度幼至五年級戶外教育採購</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>財物出租</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>臺北大眾捷運股份有限公司</t>
+          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>A16B00107</t>
+          <t>W65411566007</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>文湖線大安站等4站站體下方包板及骨架銹蝕重置工程</t>
+          <t>基隆市安樂區新城段291-1地號土地</t>
         </is>
       </c>
       <c r="H22" s="11" t="n">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>財物變賣</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
+          <t>工程招標機關</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>W65411566007</t>
+          <t>JTY00115061</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>基隆市安樂區新城段291-1地號土地</t>
+          <t>高雄市三民區中華段二小段686-2、690、690-3、691等25筆地號土地</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>財物變賣</t>
+          <t>財物出租</t>
         </is>
       </c>
     </row>
@@ -6625,7 +6625,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>中央/中油</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -6635,12 +6635,12 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司液化天然氣工程處</t>
+          <t>臺北大眾捷運股份有限公司</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>G23154001</t>
+          <t>A16B00107</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -6650,7 +6650,7 @@
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>116年液工處二人座廂式貨車新購2輛</t>
+          <t>文湖線大安站等4站站體下方包板及骨架銹蝕重置工程</t>
         </is>
       </c>
       <c r="H25" s="6" t="n">
@@ -6678,7 +6678,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>中央/中油</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -6688,12 +6688,12 @@
       </c>
       <c r="D26" s="9" t="inlineStr">
         <is>
-          <t>桃園市大園區農會</t>
+          <t>台灣中油股份有限公司液化天然氣工程處</t>
         </is>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
-          <t>1151029-1</t>
+          <t>G23154001</t>
         </is>
       </c>
       <c r="F26" s="8" t="inlineStr">
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>115年度大園區農會「農業金融業務發展計畫」本會及三和辦事處停車場設備升級工程</t>
+          <t>116年液工處二人座廂式貨車新購2輛</t>
         </is>
       </c>
       <c r="H26" s="11" t="n">
@@ -6837,7 +6837,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -6847,12 +6847,12 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>臺北市政府捷運工程局第二區工程處</t>
+          <t>桃園市大園區農會</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t>CF750</t>
+          <t>1151029-1</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
@@ -6862,7 +6862,7 @@
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>臺北都會區大眾捷運系統環狀線東環段CF750區段標工程</t>
+          <t>115年度大園區農會「農業金融業務發展計畫」本會及三和辦事處停車場設備升級工程</t>
         </is>
       </c>
       <c r="H29" s="6" t="n">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>臺北市政府捷運工程局第二區工程處</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>115FB004195847001200</t>
+          <t>CF750</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>四支部高雄廠九曲堂營區甲車鋼棚暨保修辦公室整修工程</t>
+          <t>臺北都會區大眾捷運系統環狀線東環段CF750區段標工程</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>衛生福利部桃園醫院</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>TY115-1029</t>
+          <t>115FB004195847001200</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>廢水設備維修汰換改善工程</t>
+          <t>四支部高雄廠九曲堂營區甲車鋼棚暨保修辦公室整修工程</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
@@ -7155,7 +7155,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -7165,12 +7165,12 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司高雄區營業處</t>
+          <t>衛生福利部桃園醫院</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>TY115-1029</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>數位自動電話錄音機</t>
+          <t>廢水設備維修汰換改善工程</t>
         </is>
       </c>
       <c r="H35" s="6" t="n">
@@ -7261,22 +7261,22 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司花東供電區營運處</t>
+          <t>台灣電力股份有限公司高雄區營業處</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>4951570011</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>69kV立霧~北埔線#16~#19鐵塔及基礎改建工程</t>
+          <t>數位自動電話錄音機</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
@@ -7304,7 +7304,7 @@
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -7314,22 +7314,22 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>工程類5129-其他用途建築工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D38" s="9" t="inlineStr">
         <is>
-          <t>高雄市楠梓區油廠國民小學</t>
+          <t>經濟部水利署</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>ORPS11511</t>
+          <t>1150201</t>
         </is>
       </c>
       <c r="F38" s="8" t="inlineStr">
@@ -7339,7 +7339,7 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>北三棟老舊廁所整修工程</t>
+          <t>「主機安全管理與資安漏洞整治平台」使用授權</t>
         </is>
       </c>
       <c r="H38" s="11" t="n">
@@ -7357,7 +7357,7 @@
       </c>
       <c r="K38" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -7367,22 +7367,22 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>高雄市旗津區中洲國民小學</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>115107</t>
+          <t>IL11508D02</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>115年度防空噪音防制設施防音門更新工程</t>
+          <t>115年資訊機房高架地板及消防預警等設備擴充案</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開徵求廠商提供參考資料更正</t>
         </is>
       </c>
     </row>
@@ -7420,22 +7420,22 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>臺北大眾捷運股份有限公司</t>
+          <t>台灣電力股份有限公司花東供電區營運處</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>B15A06926</t>
+          <t>4951570011</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>371型電聯車車廂內飾板修復工作</t>
+          <t>69kV立霧~北埔線#16~#19鐵塔及基礎改建工程</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料更正</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7473,22 +7473,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5129-其他用途建築工程</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署</t>
+          <t>高雄市楠梓區油廠國民小學</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>1150201</t>
+          <t>ORPS11511</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>「主機安全管理與資安漏洞整治平台」使用授權</t>
+          <t>北三棟老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7526,22 +7526,22 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D42" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>高雄市旗津區中洲國民小學</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>IL11508D02</t>
+          <t>115107</t>
         </is>
       </c>
       <c r="F42" s="8" t="inlineStr">
@@ -7551,7 +7551,7 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>115年資訊機房高架地板及消防預警等設備擴充案</t>
+          <t>115年度防空噪音防制設施防音門更新工程</t>
         </is>
       </c>
       <c r="H42" s="11" t="n">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="K42" s="9" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料更正</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7632,22 +7632,22 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>彰化縣立原斗國民中小學</t>
+          <t>臺東縣臺東市公所</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>115-10</t>
+          <t>E115092301</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>115年度偏遠地區學校及非山非市學校設施設備計畫-國中部教室整修工程</t>
+          <t>115年度農地重劃區緊急農水路改善工程-臺東市第二梯次</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
@@ -7685,22 +7685,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>臺東縣臺東市公所</t>
+          <t>彰化縣立原斗國民中小學</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>E115092301</t>
+          <t>115-10</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>115年度農地重劃區緊急農水路改善工程-臺東市第二梯次</t>
+          <t>115年度偏遠地區學校及非山非市學校設施設備計畫-國中部教室整修工程</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>臺北大眾捷運股份有限公司</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>KS115E025</t>
+          <t>B15A06926</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>援中港第一支線電動制排水門更新工程</t>
+          <t>371型電聯車車廂內飾板修復工作</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開徵求廠商提供參考資料更正</t>
         </is>
       </c>
     </row>
@@ -7844,22 +7844,22 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>新北市萬里區公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>115-199-008</t>
+          <t>KS115E025</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>115年萬里區公園、步道、廣場修繕工程</t>
+          <t>援中港第一支線電動制排水門更新工程</t>
         </is>
       </c>
       <c r="H48" s="11" t="n">
@@ -8003,22 +8003,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>屏東縣潮州鎮潮州國民小學</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>116FF00302317100110</t>
+          <t>cjps11510toilet</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>光華南營區核訓場改建工程</t>
+          <t>屏東縣潮州鎮潮州國民小學 「114-116公立國民中小學老舊廁所整修工程」採購案</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
@@ -8109,22 +8109,22 @@
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司屏東區管理處</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>13S-15-1331-01</t>
+          <t>116FF00302317100110</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>115年度潮州所管線單價工程(一)(開口契約)</t>
+          <t>光華南營區核訓場改建工程</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
@@ -8162,22 +8162,22 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>桃園市楊梅區水美國民小學</t>
+          <t>新北市萬里區公所</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>c0402-1151001</t>
+          <t>115-199-008</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>新設多功能風雨教室廁所暨通道周邊設施工程</t>
+          <t>115年萬里區公園、步道、廣場修繕工程</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
@@ -8215,22 +8215,22 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>台灣自來水股份有限公司屏東區管理處</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>1150917A-1</t>
+          <t>13S-15-1331-01</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮長良里花73線樺加沙颱風復建工程</t>
+          <t>115年度潮州所管線單價工程(一)(開口契約)</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
@@ -8268,22 +8268,22 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>澎湖縣政府文化局</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>SV-115049</t>
+          <t>HC1155103</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>澎湖縣圖書館BigMaker計畫-閱覽空間改造工程採購案</t>
+          <t>客雅南圳幹線等6處維修工程</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
@@ -8336,7 +8336,7 @@
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>1151007A-3</t>
+          <t>1150917A-1</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Danas-H-06-02-11-玉里大禹里13鄰野溪護岸災害復建工程等2案</t>
+          <t>花蓮縣玉里鎮長良里花73線樺加沙颱風復建工程</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
@@ -8374,22 +8374,22 @@
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D58" s="9" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮州國民小學</t>
+          <t>澎湖縣政府文化局</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>cjps11510toilet</t>
+          <t>SV-115049</t>
         </is>
       </c>
       <c r="F58" s="8" t="inlineStr">
@@ -8399,7 +8399,7 @@
       </c>
       <c r="G58" s="10" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮州國民小學 「114-116公立國民中小學老舊廁所整修工程」採購案</t>
+          <t>澎湖縣圖書館BigMaker計畫-閱覽空間改造工程採購案</t>
         </is>
       </c>
       <c r="H58" s="11" t="n">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>財物類481-醫療,外科及矯形設備</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>桃園市楊梅區水美國民小學</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>LP16084</t>
+          <t>c0402-1151001</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>「水雷射牙科治療儀1組」</t>
+          <t>新設多功能風雨教室廁所暨通道周邊設施工程</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
@@ -8480,22 +8480,22 @@
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>勞務類8673-綜合工程服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D60" s="9" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司高雄港務分公司</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>115-AE-055</t>
+          <t>1151007A-3</t>
         </is>
       </c>
       <c r="F60" s="8" t="inlineStr">
@@ -8505,7 +8505,7 @@
       </c>
       <c r="G60" s="10" t="inlineStr">
         <is>
-          <t>116-117年安平港區道路、橋梁、碼頭及其他公共設施巡查工作</t>
+          <t>Danas-H-06-02-11-玉里大禹里13鄰野溪護岸災害復建工程等2案</t>
         </is>
       </c>
       <c r="H60" s="11" t="n">
@@ -8533,22 +8533,22 @@
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>財物類481-醫療,外科及矯形設備</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>HC1155103</t>
+          <t>LP16084</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>客雅南圳幹線等6處維修工程</t>
+          <t>「水雷射牙科治療儀1組」</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
@@ -8692,7 +8692,7 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -8702,12 +8702,12 @@
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>新竹縣政府</t>
+          <t>行政院主計總處</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>C115-0048</t>
+          <t>115102234</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>新竹縣竹北市興隆路左側（自強南路至隘口二路）人行安全改善計畫</t>
+          <t>行政院主計總處「115年主計人員訓練中心停車場及園區相關環境設施整修工程」採購案</t>
         </is>
       </c>
       <c r="H64" s="11" t="n">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
@@ -8755,12 +8755,12 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>行政院主計總處</t>
+          <t>新竹縣政府</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>115102234</t>
+          <t>C115-0048</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>行政院主計總處「115年主計人員訓練中心停車場及園區相關環境設施整修工程」採購案</t>
+          <t>新竹縣竹北市興隆路左側（自強南路至隘口二路）人行安全改善計畫</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
@@ -8798,22 +8798,22 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>財物類481-醫療,外科及矯形設備</t>
+          <t>工程類5153-屋頂及防水工程</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>LP16189</t>
+          <t>116EK62120704500120</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>全景掃描儀(全景數位病理切片掃描儀)1組</t>
+          <t>地勤寢室南棟整修工程</t>
         </is>
       </c>
       <c r="H66" s="11" t="n">
@@ -8851,22 +8851,22 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>工程類5153-屋頂及防水工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>國防部政治作戰局</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>116EK62120704500120</t>
+          <t>115-0350000389900110</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>地勤寢室南棟整修工程</t>
+          <t>安南營區污水下水道接管工程(安南區安中路三段105號污水下水道前端接管工程)</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
@@ -8957,22 +8957,22 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>國防部政治作戰局</t>
+          <t>農業部農村發展及水土保持署南投分署</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>115-0350000389900110</t>
+          <t>115-LL-11-3-007</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>安南營區污水下水道接管工程(安南區安中路三段105號污水下水道前端接管工程)</t>
+          <t>投縣LL006六肩道路改善及坑溝整治工程</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
@@ -9010,22 +9010,22 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類481-醫療,外科及矯形設備</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署南投分署</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>115-LL-11-3-007</t>
+          <t>LP16189</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>投縣LL006六肩道路改善及坑溝整治工程</t>
+          <t>全景掃描儀(全景數位病理切片掃描儀)1組</t>
         </is>
       </c>
       <c r="H70" s="11" t="n">
@@ -9131,7 +9131,7 @@
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>115-SWC-1-4-011</t>
+          <t>115-SWC-1-4-012</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>115年度新竹縣新埔鎮等地區(第2標)水土保持工程開口契約</t>
+          <t>115年度新竹縣寶山鄉等地區(第2標)水土保持工程開口契約</t>
         </is>
       </c>
       <c r="H72" s="11" t="n">
@@ -9237,7 +9237,7 @@
       </c>
       <c r="E74" s="8" t="inlineStr">
         <is>
-          <t>115-SWC-1-4-012</t>
+          <t>115-SWC-1-4-011</t>
         </is>
       </c>
       <c r="F74" s="8" t="inlineStr">
@@ -9247,7 +9247,7 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>115年度新竹縣寶山鄉等地區(第2標)水土保持工程開口契約</t>
+          <t>115年度新竹縣新埔鎮等地區(第2標)水土保持工程開口契約</t>
         </is>
       </c>
       <c r="H74" s="11" t="n">
@@ -9333,17 +9333,17 @@
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>115-512</t>
+          <t>TT114H009</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>116年度谷關段轄區省道交通安全設施、標線改善及災害搶修工程(開口契約)</t>
+          <t>小馬圳南溪幹線圳災害復建工程-楊柳颱風</t>
         </is>
       </c>
       <c r="H76" s="11" t="n">
@@ -9434,22 +9434,22 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>TT114H009</t>
+          <t>SP15630</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>小馬圳南溪幹線圳災害復建工程-楊柳颱風</t>
+          <t>高雄榮總衛材集中採購(院內)計100項(開口契約)</t>
         </is>
       </c>
       <c r="H78" s="11" t="n">
@@ -9487,22 +9487,22 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>SP15630</t>
+          <t>115-512</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>高雄榮總衛材集中採購(院內)計100項(開口契約)</t>
+          <t>116年度谷關段轄區省道交通安全設施、標線改善及災害搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
@@ -9646,22 +9646,22 @@
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D82" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E82" s="8" t="inlineStr">
         <is>
-          <t>115-318</t>
+          <t>1150929A-1</t>
         </is>
       </c>
       <c r="F82" s="8" t="inlineStr">
@@ -9671,7 +9671,7 @@
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>116年度彰化段轄區省道台17線路容清理工作、綠美化維護及災害搶修工程(開口契約)</t>
+          <t>「Danas-H-01-07-11－玉里源城里花71線支線農路災復工程等2案」暨「115年度上半年基層座談會（里長提案補助）」等二案合併採購</t>
         </is>
       </c>
       <c r="H82" s="11" t="n">
@@ -9714,7 +9714,7 @@
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>1150929A-1</t>
+          <t>1151027A-3</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>「Danas-H-01-07-11－玉里源城里花71線支線農路災復工程等2案」暨「115年度上半年基層座談會（里長提案補助）」等二案合併採購</t>
+          <t>Danas-H-01-07-11-玉里哈拉灣產業道路邊坡復建工程等4件</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
@@ -9805,22 +9805,22 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>1151027A-3</t>
+          <t>115-318</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Danas-H-01-07-11-玉里哈拉灣產業道路邊坡復建工程等4件</t>
+          <t>116年度彰化段轄區省道台17線路容清理工作、綠美化維護及災害搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
@@ -10032,7 +10032,7 @@
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>115AA036</t>
+          <t>115AA035</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>那瑪夏區達卡努瓦里丘平溪七七孔橋上游災害復建工程</t>
+          <t>115年度那瑪夏區部落安全環境建設及原民地區農路修繕工程</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
@@ -10070,7 +10070,7 @@
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C90" s="8" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="D90" s="9" t="inlineStr">
         <is>
-          <t>臺南市政府都市發展局</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>115B305</t>
+          <t>115AA036</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>新化水圳南圳綠堤縫合計畫工程</t>
+          <t>那瑪夏區達卡努瓦里丘平溪七七孔橋上游災害復建工程</t>
         </is>
       </c>
       <c r="H90" s="11" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>屏東縣獅子鄉公所</t>
+          <t>臺南市政府都市發展局</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>115B305</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Danas-H-01-06-9-獅子鄉南世村金卡來農路災害復建工程</t>
+          <t>新化水圳南圳綠堤縫合計畫工程</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="B92" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C92" s="8" t="inlineStr">
@@ -10186,12 +10186,12 @@
       </c>
       <c r="D92" s="9" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>屏東縣獅子鄉公所</t>
         </is>
       </c>
       <c r="E92" s="8" t="inlineStr">
         <is>
-          <t>115AA046</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="F92" s="8" t="inlineStr">
@@ -10201,7 +10201,7 @@
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>114年9月樺加沙颱風那瑪夏區托亞奇伊段野溪及瑪雅里托亞奇伊段護岸災後復建工程</t>
+          <t>Danas-H-01-06-9-獅子鄉南世村金卡來農路災害復建工程</t>
         </is>
       </c>
       <c r="H92" s="11" t="n">
@@ -10234,17 +10234,17 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>勞務類8676-技術檢定與分析服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>CP15087</t>
+          <t>115AA046</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>病理檢驗部委外代檢勞務採購2項</t>
+          <t>114年9月樺加沙颱風那瑪夏區托亞奇伊段野溪及瑪雅里托亞奇伊段護岸災後復建工程</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
@@ -10282,22 +10282,22 @@
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C94" s="8" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>勞務類8676-技術檢定與分析服務</t>
         </is>
       </c>
       <c r="D94" s="9" t="inlineStr">
         <is>
-          <t>國立彰化高級商業職業學校</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E94" s="8" t="inlineStr">
         <is>
-          <t>1150901</t>
+          <t>CP15087</t>
         </is>
       </c>
       <c r="F94" s="8" t="inlineStr">
@@ -10307,7 +10307,7 @@
       </c>
       <c r="G94" s="10" t="inlineStr">
         <is>
-          <t>115年活動中心多功能球場整修工程</t>
+          <t>病理檢驗部委外代檢勞務採購2項</t>
         </is>
       </c>
       <c r="H94" s="11" t="n">
@@ -10335,22 +10335,22 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>國立彰化高級商業職業學校</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>115-218</t>
+          <t>1150901</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>台61線130K~145K平面路口行穿線照明設施改善工程</t>
+          <t>115年活動中心多功能球場整修工程</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>勞務類8676-技術檢定與分析服務</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>115AA035</t>
+          <t>CP15088</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>115年度那瑪夏區部落安全環境建設及原民地區農路修繕工程</t>
+          <t>病理檢驗部委外代檢勞務採購1項</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
@@ -10494,22 +10494,22 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>勞務類8676-技術檢定與分析服務</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>CP15088</t>
+          <t>115EE63017980500410</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>病理檢驗部委外代檢勞務採購1項</t>
+          <t>營區雨遮設施改善工程</t>
         </is>
       </c>
       <c r="H98" s="11" t="n">
@@ -10600,22 +10600,22 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>SP15493</t>
+          <t>1151A30021</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>過敏免疫風濕科用試劑計2項(開口契約)</t>
+          <t>雲林縣虎尾鎮B幹線(文化路)雨水下水道改道工程</t>
         </is>
       </c>
       <c r="H100" s="11" t="n">
@@ -10653,22 +10653,22 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>雲林縣政府</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>1151A30021</t>
+          <t>SP15493</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>雲林縣虎尾鎮B幹線(文化路)雨水下水道改道工程</t>
+          <t>過敏免疫風濕科用試劑計2項(開口契約)</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
@@ -10812,22 +10812,22 @@
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>財物類421-結構金屬產品及其零件</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>陸軍軍官學校</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>FP16003P001</t>
+          <t>115-218</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>反裝甲靶場避彈坑設施改善</t>
+          <t>台61線130K~145K平面路口行穿線照明設施改善工程</t>
         </is>
       </c>
       <c r="H104" s="11" t="n">
@@ -10865,22 +10865,22 @@
       </c>
       <c r="B105" s="3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類421-結構金屬產品及其零件</t>
         </is>
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>宜蘭縣宜蘭市公所</t>
+          <t>陸軍軍官學校</t>
         </is>
       </c>
       <c r="E105" s="3" t="inlineStr">
         <is>
-          <t>115-i21</t>
+          <t>FP16003P001</t>
         </is>
       </c>
       <c r="F105" s="3" t="inlineStr">
@@ -10890,7 +10890,7 @@
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>116年度宜蘭市路面路容、橋梁及附屬設施維護預約工程(開口契約)</t>
+          <t>反裝甲靶場避彈坑設施改善</t>
         </is>
       </c>
       <c r="H105" s="6" t="n">
@@ -10918,22 +10918,22 @@
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C106" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D106" s="9" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>宜蘭縣宜蘭市公所</t>
         </is>
       </c>
       <c r="E106" s="8" t="inlineStr">
         <is>
-          <t>115EE63017980500410</t>
+          <t>115-i21</t>
         </is>
       </c>
       <c r="F106" s="8" t="inlineStr">
@@ -10943,7 +10943,7 @@
       </c>
       <c r="G106" s="10" t="inlineStr">
         <is>
-          <t>營區雨遮設施改善工程</t>
+          <t>116年度宜蘭市路面路容、橋梁及附屬設施維護預約工程(開口契約)</t>
         </is>
       </c>
       <c r="H106" s="11" t="n">
@@ -10976,17 +10976,17 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E107" s="3" t="inlineStr">
         <is>
-          <t>115-125</t>
+          <t>KS115M028</t>
         </is>
       </c>
       <c r="F107" s="3" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>116年度苗栗工務段標線工程(開口契約)</t>
+          <t>115及116年度九曲站轄內圳路設施維護開口契約</t>
         </is>
       </c>
       <c r="H107" s="6" t="n">
@@ -11024,22 +11024,22 @@
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C108" s="8" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D108" s="9" t="inlineStr">
         <is>
-          <t>國立花蓮高級商業職業學校</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E108" s="8" t="inlineStr">
         <is>
-          <t>115C06</t>
+          <t>115-125</t>
         </is>
       </c>
       <c r="F108" s="8" t="inlineStr">
@@ -11049,7 +11049,7 @@
       </c>
       <c r="G108" s="10" t="inlineStr">
         <is>
-          <t>115年風雨球場等工程</t>
+          <t>116年度苗栗工務段標線工程(開口契約)</t>
         </is>
       </c>
       <c r="H108" s="11" t="n">
@@ -11077,22 +11077,22 @@
       </c>
       <c r="B109" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>國立花蓮高級商業職業學校</t>
         </is>
       </c>
       <c r="E109" s="3" t="inlineStr">
         <is>
-          <t>M116107</t>
+          <t>115C06</t>
         </is>
       </c>
       <c r="F109" s="3" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>116年度高屏溪構造物維修改善工程(開口契約)</t>
+          <t>115年風雨球場等工程</t>
         </is>
       </c>
       <c r="H109" s="6" t="n">
@@ -11130,22 +11130,22 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司台中區營業處</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>1051570037</t>
+          <t>M116107</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>116年雅潭工區配電線路改善及設備更換工作</t>
+          <t>116年度高屏溪構造物維修改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H110" s="11" t="n">
@@ -11241,17 +11241,17 @@
       </c>
       <c r="C112" s="8" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D112" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E112" s="8" t="inlineStr">
         <is>
-          <t>KS115M028</t>
+          <t>M116109</t>
         </is>
       </c>
       <c r="F112" s="8" t="inlineStr">
@@ -11261,7 +11261,7 @@
       </c>
       <c r="G112" s="10" t="inlineStr">
         <is>
-          <t>115及116年度九曲站轄內圳路設施維護開口契約</t>
+          <t>116年度七河分署轄區中央管排水構造物維修改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H112" s="11" t="n">
@@ -11289,7 +11289,7 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
@@ -11299,12 +11299,12 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>高雄市政府水利局</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>M116109</t>
+          <t>C1150918</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>116年度七河分署轄區中央管排水構造物維修改善工程(開口契約)</t>
+          <t>左營區和光街(和光街109巷至和光街206巷)災修復建工程</t>
         </is>
       </c>
       <c r="H113" s="6" t="n">
@@ -11342,22 +11342,22 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府水利局</t>
+          <t>新北市八里區長坑國民小學</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>C1150918</t>
+          <t>CKES11507</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>左營區和光街(和光街109巷至和光街206巷)災修復建工程</t>
+          <t>115年長坑國小職務宿舍修建工程</t>
         </is>
       </c>
       <c r="H114" s="11" t="n">
@@ -11448,22 +11448,22 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>新北市八里區長坑國民小學</t>
+          <t>屏東縣屏東市公所</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>CKES11507</t>
+          <t>115213</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>115年長坑國小職務宿舍修建工程</t>
+          <t>永大、武立、興豐公園增設遮陽設施及兒童遊戲場環境設施改善工程</t>
         </is>
       </c>
       <c r="H116" s="11" t="n">
@@ -11501,22 +11501,22 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>台灣電力股份有限公司台中區營業處</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>KS115E035</t>
+          <t>1051570037</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>獅四輪小排四之十五(0K+035)等改善工程</t>
+          <t>116年雅潭工區配電線路改善及設備更換工作</t>
         </is>
       </c>
       <c r="H117" s="6" t="n">
@@ -11554,22 +11554,22 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公所</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>115213</t>
+          <t>M116110</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>永大、武立、興豐公園增設遮陽設施及兒童遊戲場環境設施改善工程</t>
+          <t>116年度七河分署轄區構造物維修改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H118" s="11" t="n">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>南投縣中寮鄉公所</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>M116110</t>
+          <t>115-0118</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>116年度七河分署轄區構造物維修改善工程(開口契約)</t>
+          <t>114中寮鄉崁頂村後寮段744-6地號蝕溝整治工程</t>
         </is>
       </c>
       <c r="H119" s="6" t="n">
@@ -11665,17 +11665,17 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>南投縣中寮鄉公所</t>
+          <t>苗栗縣立苑裡高級中學</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>115-0118</t>
+          <t>1150023</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>114中寮鄉崁頂村後寮段744-6地號蝕溝整治工程</t>
+          <t>115年度運動場地整建工程採購案</t>
         </is>
       </c>
       <c r="H120" s="11" t="n">
@@ -11713,22 +11713,22 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>財物類381-傢具</t>
+          <t>工程類5159-其他專業工程</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>臺北市政府工務局新建工程處</t>
+          <t>新北市新莊區公所</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>NCOdecor11501</t>
+          <t>1151027J2</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>115年度新建工程處辦公傢俱及附屬設備(含電源線路配置)財物採購案</t>
+          <t>116年度新莊區抽水機代操作、維護保養工作（開口合約）</t>
         </is>
       </c>
       <c r="H121" s="6" t="n">
@@ -11766,22 +11766,22 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>財物類4393-其他通用機具</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣立苑裡高級中學</t>
+          <t>高雄市左營區文府國民小學</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>1150023</t>
+          <t>115M1008</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>115年度運動場地整建工程採購案</t>
+          <t>115學年度消防系統設備改善案</t>
         </is>
       </c>
       <c r="H122" s="11" t="n">
@@ -11819,22 +11819,22 @@
       </c>
       <c r="B123" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>工程類5159-其他專業工程</t>
+          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
         </is>
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>新北市新莊區公所</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E123" s="3" t="inlineStr">
         <is>
-          <t>1151027J2</t>
+          <t>M116048</t>
         </is>
       </c>
       <c r="F123" s="3" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>116年度新莊區抽水機代操作、維護保養工作（開口合約）</t>
+          <t>116年度東港溪堤防樹木修剪維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H123" s="6" t="n">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
@@ -11887,7 +11887,7 @@
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>M116048</t>
+          <t>M116044</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>116年度東港溪堤防樹木修剪維護管理工作(開口契約)</t>
+          <t>116年度高屏溪堤防維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H124" s="11" t="n">
@@ -11925,22 +11925,22 @@
       </c>
       <c r="B125" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>財物類4393-其他通用機具</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>高雄市左營區文府國民小學</t>
+          <t>苗栗縣南庄鄉公所</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>115M1008</t>
+          <t>115-034</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>115學年度消防系統設備改善案</t>
+          <t>115年4月豪雨南庄鄉南富村18鄰農路災後復建工程</t>
         </is>
       </c>
       <c r="H125" s="6" t="n">
@@ -11983,17 +11983,17 @@
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>苗栗縣南庄鄉公所</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>M116044</t>
+          <t>115-038</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>116年度高屏溪堤防維護管理工作(開口契約)</t>
+          <t>115年4月豪雨南庄鄉獅山村10鄰及17鄰農路災後復建工程</t>
         </is>
       </c>
       <c r="H126" s="11" t="n">
@@ -12031,22 +12031,22 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類381-傢具</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣南庄鄉公所</t>
+          <t>臺北市政府工務局新建工程處</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>115-038</t>
+          <t>NCOdecor11501</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>115年4月豪雨南庄鄉獅山村10鄰及17鄰農路災後復建工程</t>
+          <t>115年度新建工程處辦公傢俱及附屬設備(含電源線路配置)財物採購案</t>
         </is>
       </c>
       <c r="H127" s="6" t="n">
@@ -12089,17 +12089,17 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣南庄鄉公所</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>115-034</t>
+          <t>M116052</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>115年4月豪雨南庄鄉南富村18鄰農路災後復建工程</t>
+          <t>116年度隘寮溪堤防維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H128" s="11" t="n">
@@ -12137,22 +12137,22 @@
       </c>
       <c r="B129" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
+          <t>工程類5129-其他用途建築工程</t>
         </is>
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>宜蘭縣三星鄉公所</t>
         </is>
       </c>
       <c r="E129" s="3" t="inlineStr">
         <is>
-          <t>M116052</t>
+          <t>115014</t>
         </is>
       </c>
       <c r="F129" s="3" t="inlineStr">
@@ -12162,7 +12162,7 @@
       </c>
       <c r="G129" s="5" t="inlineStr">
         <is>
-          <t>116年度隘寮溪堤防維護管理工作(開口契約)</t>
+          <t>宜蘭縣三星鄉社區多功能綜合館新建工程</t>
         </is>
       </c>
       <c r="H129" s="6" t="n">
@@ -12190,22 +12190,22 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
         <is>
-          <t>工程類5129-其他用途建築工程</t>
+          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
         </is>
       </c>
       <c r="D130" s="9" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉公所</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>115014</t>
+          <t>M116045</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>宜蘭縣三星鄉社區多功能綜合館新建工程</t>
+          <t>116年度東港溪水系及海堤堤防維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H130" s="11" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
+          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>台灣電力股份有限公司綜合研究所</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>M116045</t>
+          <t>5461500173</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>116年度東港溪水系及海堤堤防維護管理工作(開口契約)</t>
+          <t>跨領域單一軟體之工程模擬全物理場高階多核心平行求解授權1套</t>
         </is>
       </c>
       <c r="H131" s="6" t="n">
@@ -12301,17 +12301,17 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>中央研究院</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>115-M39</t>
+          <t>RC-114-0701-0021-3</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>後棟學人招待所整修工程</t>
+          <t>高市梓官區梓官路汰換管線工程</t>
         </is>
       </c>
       <c r="H132" s="11" t="n">
@@ -12354,17 +12354,17 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>中央研究院</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>RC-114-0701-0021-3</t>
+          <t>115-M39</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>高市梓官區梓官路汰換管線工程</t>
+          <t>後棟學人招待所整修工程</t>
         </is>
       </c>
       <c r="H133" s="6" t="n">
@@ -12407,17 +12407,17 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司綜合研究所</t>
+          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>5461500173</t>
+          <t>6541551032</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>跨領域單一軟體之工程模擬全物理場高階多核心平行求解授權1套</t>
+          <t>345kV汐止~板橋線#68、#69鐵塔更換工程</t>
         </is>
       </c>
       <c r="H134" s="11" t="n">
@@ -12773,22 +12773,22 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
+          <t>臺中市西區中正國民小學</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>6541551032</t>
+          <t>CCES115-1028</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>345kV汐止~板橋線#68、#69鐵塔更換工程</t>
+          <t>臺中市西區中正國民小學公益樓A棟廁所整修工程(第二次)</t>
         </is>
       </c>
       <c r="H141" s="6" t="n">
@@ -12826,22 +12826,22 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>基隆市政府</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>C1151008-P1</t>
+          <t>115A107</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="G142" s="10" t="inlineStr">
         <is>
-          <t>115年水利村及塭豐漁港泊地及航道清疏工程(開口契約)</t>
+          <t>(116)基隆市人行道雨陽棚整建工程(單價標)</t>
         </is>
       </c>
       <c r="H142" s="11" t="n">
@@ -12879,22 +12879,22 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>基隆市政府</t>
+          <t>臺中市南屯區南屯國民小學</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>115A107</t>
+          <t>Ntes114-11-a</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>(116)基隆市人行道雨陽棚整建工程(單價標)</t>
+          <t>114年度南屯國小南棟前側老舊廁所整修工程採購案</t>
         </is>
       </c>
       <c r="H143" s="6" t="n">
@@ -12932,22 +12932,22 @@
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C144" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D144" s="9" t="inlineStr">
         <is>
-          <t>臺中市西區中正國民小學</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E144" s="8" t="inlineStr">
         <is>
-          <t>CCES115-1028</t>
+          <t>C1151008-P1</t>
         </is>
       </c>
       <c r="F144" s="8" t="inlineStr">
@@ -12957,7 +12957,7 @@
       </c>
       <c r="G144" s="10" t="inlineStr">
         <is>
-          <t>臺中市西區中正國民小學公益樓A棟廁所整修工程(第二次)</t>
+          <t>115年水利村及塭豐漁港泊地及航道清疏工程(開口契約)</t>
         </is>
       </c>
       <c r="H144" s="11" t="n">
@@ -12985,22 +12985,22 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5132-橋樑,高架快速道路,隧道及地鐵</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>臺中市南屯區南屯國民小學</t>
+          <t>桃園市中壢區公所</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>Ntes114-11-a</t>
+          <t>115-10-094</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>114年度南屯國小南棟前側老舊廁所整修工程採購案</t>
+          <t>桃園市中壢區新街溪河岸南園二路57巷18弄新設人行跨橋工程</t>
         </is>
       </c>
       <c r="H145" s="6" t="n">
@@ -13091,22 +13091,22 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>工程類5132-橋樑,高架快速道路,隧道及地鐵</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>桃園市中壢區公所</t>
+          <t>台灣自來水股份有限公司第四區管理處</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>115-10-094</t>
+          <t>W4-115-0401-528</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>桃園市中壢區新街溪河岸南園二路57巷18弄新設人行跨橋工程</t>
+          <t>大里服務所、烏日、霧峰等營運所管線設備修理工程(115年開口契約)</t>
         </is>
       </c>
       <c r="H147" s="6" t="n">
@@ -13149,17 +13149,17 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第四區管理處</t>
+          <t>南投縣國姓鄉北山國民小學</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>W4-115-0401-528</t>
+          <t>psps1150914</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="G148" s="10" t="inlineStr">
         <is>
-          <t>大里服務所、烏日、霧峰等營運所管線設備修理工程(115年開口契約)</t>
+          <t>老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H148" s="11" t="n">
@@ -13197,22 +13197,22 @@
       </c>
       <c r="B149" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>南投縣國姓鄉北山國民小學</t>
+          <t>屏東縣恆春鎮公所</t>
         </is>
       </c>
       <c r="E149" s="3" t="inlineStr">
         <is>
-          <t>psps1150914</t>
+          <t>F-261004</t>
         </is>
       </c>
       <c r="F149" s="3" t="inlineStr">
@@ -13222,7 +13222,7 @@
       </c>
       <c r="G149" s="5" t="inlineStr">
         <is>
-          <t>老舊廁所整修工程</t>
+          <t>115-恆春鎮大光里大光路旁人行步道改善工程</t>
         </is>
       </c>
       <c r="H149" s="6" t="n">
@@ -13250,22 +13250,22 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>勞務類751-郵政及專差服務</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>嘉義縣梅山鄉梅圳國民小學</t>
+          <t>中華郵政股份有限公司高雄郵局</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>mj11502</t>
+          <t>115-050</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="G150" s="10" t="inlineStr">
         <is>
-          <t>梅圳國小114-116老舊廁所整修工程採購案</t>
+          <t>高雄郵局掛號、限時及國際郵件處理勞務承攬</t>
         </is>
       </c>
       <c r="H150" s="11" t="n">
@@ -13308,17 +13308,17 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第四區管理處</t>
+          <t>臺中市豐原區豐原國民小學</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>W4-115-0401-529</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>台中給水廠北工區管線設備修理工程(115開口契約)</t>
+          <t>豐原國小115年度公立幼兒園充實及改善教學環境設施設備工程」</t>
         </is>
       </c>
       <c r="H151" s="6" t="n">
@@ -13356,7 +13356,7 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>臺中市豐原區豐原國民小學</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>1151029A-3</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="G152" s="10" t="inlineStr">
         <is>
-          <t>豐原國小115年度公立幼兒園充實及改善教學環境設施設備工程」</t>
+          <t>花蓮縣玉里鎮大禹里瑟冷部落災後復建工程</t>
         </is>
       </c>
       <c r="H152" s="11" t="n">
@@ -13414,17 +13414,17 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>勞務類751-郵政及專差服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司高雄郵局</t>
+          <t>高雄市田寮區公所</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>115-050</t>
+          <t>1151037</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>高雄郵局掛號、限時及國際郵件處理勞務承攬</t>
+          <t>田寮區七星里高38往謝家祠堂路面災害復建工程等2案</t>
         </is>
       </c>
       <c r="H153" s="6" t="n">
@@ -13462,22 +13462,22 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>國立岡山高級農工職業學校</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>1151029A-3</t>
+          <t>115A-05</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="G154" s="10" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮大禹里瑟冷部落災後復建工程</t>
+          <t>實習處階梯教室修繕第二期工程</t>
         </is>
       </c>
       <c r="H154" s="11" t="n">
@@ -13515,22 +13515,22 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>高雄市田寮區公所</t>
+          <t>嘉義縣梅山鄉梅圳國民小學</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>1151037</t>
+          <t>mj11502</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>田寮區七星里高38往謝家祠堂路面災害復建工程等2案</t>
+          <t>梅圳國小114-116老舊廁所整修工程採購案</t>
         </is>
       </c>
       <c r="H155" s="6" t="n">
@@ -13568,22 +13568,22 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>桃園市八德區公所</t>
+          <t>彰化縣埔心鄉明聖國民小學</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>BB1151029</t>
+          <t>MSPS-11510</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G156" s="10" t="inlineStr">
         <is>
-          <t>八德區霖園公園空間再造工程</t>
+          <t>彰化縣明聖國民小學114年度公立國民中小學老舊廁所整修工程計畫</t>
         </is>
       </c>
       <c r="H156" s="11" t="n">
@@ -13626,17 +13626,17 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>國立岡山高級農工職業學校</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>115A-05</t>
+          <t>RC-115-0701-0025</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>實習處階梯教室修繕第二期工程</t>
+          <t>高市前鎮區49至57號碼頭汰換管線工程</t>
         </is>
       </c>
       <c r="H157" s="6" t="n">
@@ -13674,22 +13674,22 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>彰化縣埔心鄉明聖國民小學</t>
+          <t>台灣自來水股份有限公司第四區管理處</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>MSPS-11510</t>
+          <t>W4-115-0401-529</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="G158" s="10" t="inlineStr">
         <is>
-          <t>彰化縣明聖國民小學114年度公立國民中小學老舊廁所整修工程計畫</t>
+          <t>台中給水廠北工區管線設備修理工程(115開口契約)</t>
         </is>
       </c>
       <c r="H158" s="11" t="n">
@@ -13727,22 +13727,22 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>RC-115-0701-0025</t>
+          <t>004-C1151008-1</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>高市前鎮區49至57號碼頭汰換管線工程</t>
+          <t>115年屏東縣東港溪0826天然災害清疏工程</t>
         </is>
       </c>
       <c r="H159" s="6" t="n">
@@ -13780,22 +13780,22 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類421-結構金屬產品及其零件</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>國防部資通電軍指揮部</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>004-C1151008-1</t>
+          <t>HK15184P084</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
-          <t>115年屏東縣東港溪0826天然災害清疏工程</t>
+          <t>庫儲料架櫃採購案</t>
         </is>
       </c>
       <c r="H160" s="11" t="n">
@@ -13833,22 +13833,22 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>財物類421-結構金屬產品及其零件</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>國防部資通電軍指揮部</t>
+          <t>桃園市八德區公所</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>HK15184P084</t>
+          <t>BB1151029</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>庫儲料架櫃採購案</t>
+          <t>八德區霖園公園空間再造工程</t>
         </is>
       </c>
       <c r="H161" s="6" t="n">
@@ -13939,22 +13939,22 @@
       </c>
       <c r="B163" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣光復鄉公所</t>
+          <t>經濟部水利署第六河川分署</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>1151008-B87</t>
+          <t>115-B-004-02-002-629</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>MTA-D-08-01-07-花蓮縣光復鄉災後道路提報計畫-大華村</t>
+          <t>115年度臺南市北門海埔地海堤構造物維修改善工程</t>
         </is>
       </c>
       <c r="H163" s="6" t="n">
@@ -13992,22 +13992,22 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第六河川分署</t>
+          <t>花蓮縣光復鄉公所</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>115-B-004-02-002-629</t>
+          <t>1151008-B87</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="G164" s="10" t="inlineStr">
         <is>
-          <t>115年度臺南市北門海埔地海堤構造物維修改善工程</t>
+          <t>MTA-D-08-01-07-花蓮縣光復鄉災後道路提報計畫-大華村</t>
         </is>
       </c>
       <c r="H164" s="11" t="n">
@@ -35091,17 +35091,17 @@
       </c>
       <c r="C562" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D562" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>苗栗縣立苑裡高級中學</t>
         </is>
       </c>
       <c r="E562" s="8" t="inlineStr">
         <is>
-          <t>115158c</t>
+          <t>1150024</t>
         </is>
       </c>
       <c r="F562" s="8" t="inlineStr">
@@ -35111,7 +35111,7 @@
       </c>
       <c r="G562" s="10" t="inlineStr">
         <is>
-          <t>頭份市後庄里信義路690巷排水溝加蓋改善工程</t>
+          <t>115年度賈宓圖書館空間改善工程採購案</t>
         </is>
       </c>
       <c r="H562" s="11" t="n">
@@ -35139,7 +35139,7 @@
       </c>
       <c r="B563" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C563" s="3" t="inlineStr">
@@ -35149,12 +35149,12 @@
       </c>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>臺南市龍崎區公所</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>115058</t>
+          <t>115158c</t>
         </is>
       </c>
       <c r="F563" s="3" t="inlineStr">
@@ -35164,7 +35164,7 @@
       </c>
       <c r="G563" s="5" t="inlineStr">
         <is>
-          <t>龍崎區大溪清水宮廁所新建工程</t>
+          <t>頭份市後庄里信義路690巷排水溝加蓋改善工程</t>
         </is>
       </c>
       <c r="H563" s="6" t="n">
@@ -35192,22 +35192,22 @@
       </c>
       <c r="B564" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C564" s="8" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D564" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣立苑裡高級中學</t>
+          <t>臺南市龍崎區公所</t>
         </is>
       </c>
       <c r="E564" s="8" t="inlineStr">
         <is>
-          <t>1150024</t>
+          <t>115058</t>
         </is>
       </c>
       <c r="F564" s="8" t="inlineStr">
@@ -35217,7 +35217,7 @@
       </c>
       <c r="G564" s="10" t="inlineStr">
         <is>
-          <t>115年度賈宓圖書館空間改善工程採購案</t>
+          <t>龍崎區大溪清水宮廁所新建工程</t>
         </is>
       </c>
       <c r="H564" s="11" t="n">

--- a/tenders_today.xlsx
+++ b/tenders_today.xlsx
@@ -543,7 +543,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-31 10:37</t>
+          <t>NOVERA 全國公共工程標案 — 設計監造與技術服務類 ｜ 更新時間：2026-10-31 18:29</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>中央/海軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -779,12 +779,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>國防部海軍司令部</t>
+          <t>內政部消防署</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>114-5160005513000220-2</t>
+          <t>G116-014</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>兩棲偵搜大隊舟艇維修間整修工程第二次變更設計</t>
+          <t>「印太地區災害防救韌性與能力建構整合計畫」116年專案管理勞務委託採購案</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
@@ -822,7 +822,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/海軍</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -832,12 +832,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>內政部消防署</t>
+          <t>國防部海軍司令部</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>G116-014</t>
+          <t>114-5160005513000220-2</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>「印太地區災害防救韌性與能力建構整合計畫」116年專案管理勞務委託採購案</t>
+          <t>兩棲偵搜大隊舟艇維修間整修工程第二次變更設計</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
@@ -5392,7 +5392,7 @@
     <row r="1" ht="42" customHeight="1">
       <c r="A1" s="13" t="inlineStr">
         <is>
-          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-31 10:37</t>
+          <t>NOVERA 全國公共工程標案 — 施工與統包工程類 ｜ 更新時間：2026-10-31 18:29</t>
         </is>
       </c>
     </row>
@@ -5459,22 +5459,22 @@
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>雲林縣</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>勞務</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司</t>
+          <t>雲林縣政府</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>TIPC115B06</t>
+          <t>1151A30021</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -5484,11 +5484,11 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>116年度高雄港海域污染應變工作勞務作業</t>
+          <t>雲林縣虎尾鎮B幹線(文化路)雨水下水道改道工程</t>
         </is>
       </c>
       <c r="H3" s="6" t="n">
-        <v>6182864</v>
+        <v>16750000</v>
       </c>
       <c r="I3" s="7" t="inlineStr">
         <is>
@@ -5497,12 +5497,12 @@
       </c>
       <c r="J3" s="7" t="inlineStr">
         <is>
-          <t>115/11/05</t>
+          <t>115/11/10</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
         <is>
-          <t>限制性招標(經公開評選或公開徵求者)</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -5512,22 +5512,22 @@
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>勞務類8673-綜合工程服務</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D4" s="9" t="inlineStr">
         <is>
-          <t>臺灣港務股份有限公司高雄港務分公司</t>
+          <t>桃園市復興區光華國民小學</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>115-AE-055</t>
+          <t>KH-11502</t>
         </is>
       </c>
       <c r="F4" s="8" t="inlineStr">
@@ -5537,11 +5537,11 @@
       </c>
       <c r="G4" s="10" t="inlineStr">
         <is>
-          <t>116-117年安平港區道路、橋梁、碼頭及其他公共設施巡查工作</t>
+          <t>115年度改善偏遠地區國民中小學教師宿舍</t>
         </is>
       </c>
       <c r="H4" s="11" t="n">
-        <v>4889635</v>
+        <v>2339535</v>
       </c>
       <c r="I4" s="12" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
       </c>
       <c r="J4" s="12" t="inlineStr">
         <is>
-          <t>115/11/19</t>
+          <t>115/11/12</t>
         </is>
       </c>
       <c r="K4" s="9" t="inlineStr">
@@ -5570,17 +5570,17 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>國立臺灣大學醫學院附設醫院</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>KS115E035</t>
+          <t>FB2609180E</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -5590,11 +5590,11 @@
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>獅四輪小排四之十五(0K+035)等改善工程</t>
+          <t>尖端醫療研究大樓新建統包工程</t>
         </is>
       </c>
       <c r="H5" s="6" t="n">
-        <v>2971000</v>
+        <v>0</v>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
@@ -5603,12 +5603,12 @@
       </c>
       <c r="J5" s="7" t="inlineStr">
         <is>
-          <t>115/11/09</t>
+          <t>詳見公告</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>招標文件公開閱覽資料</t>
         </is>
       </c>
     </row>
@@ -5618,7 +5618,7 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C6" s="8" t="inlineStr">
@@ -5628,12 +5628,12 @@
       </c>
       <c r="D6" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣新城鄉嘉里國民小學</t>
+          <t>高雄市政府經濟發展局</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>zlips1151030</t>
+          <t>115094</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>花蓮縣嘉里國民小學校區污雜排水管配合公共下水道納管改善工程</t>
+          <t>116年高雄會展產業推動服務案</t>
         </is>
       </c>
       <c r="H6" s="11" t="n">
@@ -5671,7 +5671,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>宜蘭縣</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -5681,12 +5681,12 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司桃園區營業處</t>
+          <t>工程招標機關</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t>1031570108</t>
+          <t>L0515P1079S</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>桃園區營業處115年丙工區零星配電管路工程</t>
+          <t>宜蘭工務段轄區鐵路跨河橋梁基礎裸露補強工程(A-1標接續工程)</t>
         </is>
       </c>
       <c r="H7" s="6" t="n">
@@ -5724,7 +5724,7 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
@@ -5734,12 +5734,12 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>國立臺灣大學醫學院附設醫院</t>
+          <t>花蓮縣新城鄉嘉里國民小學</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>FB2609180E</t>
+          <t>zlips1151030</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>尖端醫療研究大樓新建統包工程</t>
+          <t>花蓮縣嘉里國民小學校區污雜排水管配合公共下水道納管改善工程</t>
         </is>
       </c>
       <c r="H8" s="11" t="n">
@@ -5777,7 +5777,7 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>宜蘭縣</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>工程招標機關</t>
+          <t>臺北市政府工務局新建工程處</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t>L0515P1079S</t>
+          <t>11507003030201501</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
@@ -5802,7 +5802,7 @@
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>宜蘭工務段轄區鐵路跨河橋梁基礎裸露補強工程(A-1標接續工程)</t>
+          <t>文和橋上部改建工程（含台電管線代辦）</t>
         </is>
       </c>
       <c r="H9" s="6" t="n">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>臺北市政府工務局新建工程處</t>
+          <t>桃園市政府工務局</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
         <is>
-          <t>11507003030201501</t>
+          <t>1151027-A8</t>
         </is>
       </c>
       <c r="F10" s="8" t="inlineStr">
@@ -5855,7 +5855,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>文和橋上部改建工程（含台電管線代辦）</t>
+          <t>桃園市觀音草漯多功能場館新建統包工程</t>
         </is>
       </c>
       <c r="H10" s="11" t="n">
@@ -5893,12 +5893,12 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>桃園市政府工務局</t>
+          <t>台灣電力股份有限公司桃園區營業處</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t>1151027-A8</t>
+          <t>1031570108</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
@@ -5908,7 +5908,7 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>桃園市觀音草漯多功能場館新建統包工程</t>
+          <t>桃園區營業處115年丙工區零星配電管路工程</t>
         </is>
       </c>
       <c r="H11" s="6" t="n">
@@ -5936,7 +5936,7 @@
       </c>
       <c r="B12" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
@@ -5946,12 +5946,12 @@
       </c>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府工務局</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>1151686</t>
+          <t>A058-1151029-2</t>
         </is>
       </c>
       <c r="F12" s="8" t="inlineStr">
@@ -5961,7 +5961,7 @@
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>116年度高雄市寬頻管道委託維修管理服務</t>
+          <t>屏東縣身心障礙者社會生活適應計畫</t>
         </is>
       </c>
       <c r="H12" s="11" t="n">
@@ -5989,7 +5989,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>高雄市政府工務局</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t>A058-1151029-2</t>
+          <t>1151686</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>屏東縣身心障礙者社會生活適應計畫</t>
+          <t>116年度高雄市寬頻管道委託維修管理服務</t>
         </is>
       </c>
       <c r="H13" s="6" t="n">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
@@ -6052,12 +6052,12 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>高雄市政府經濟發展局</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>115094</t>
+          <t>115EP634143199002200</t>
         </is>
       </c>
       <c r="F14" s="8" t="inlineStr">
@@ -6067,7 +6067,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>116年高雄會展產業推動服務案</t>
+          <t>D005工程</t>
         </is>
       </c>
       <c r="H14" s="11" t="n">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C15" s="3" t="inlineStr">
@@ -6105,12 +6105,12 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>臺灣港務股份有限公司</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t>115EP634143199002200</t>
+          <t>TIPC115B06</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
@@ -6120,7 +6120,7 @@
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>D005工程</t>
+          <t>116年度高雄港海域污染應變工作勞務作業</t>
         </is>
       </c>
       <c r="H15" s="6" t="n">
@@ -6138,7 +6138,7 @@
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料</t>
+          <t>招標文件公開閱覽資料更正</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>工程招標機關</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t>1151HH001</t>
+          <t>JTY00115061</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>高雄市苓雅區武聖段1124地號土地標租（出租面積共337.5平方公尺）。</t>
+          <t>高雄市三民區中華段二小段686-2、690、690-3、691等25筆地號土地</t>
         </is>
       </c>
       <c r="H17" s="6" t="n">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
@@ -6264,12 +6264,12 @@
       </c>
       <c r="D18" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>W65411566006</t>
+          <t>1151HH001</t>
         </is>
       </c>
       <c r="F18" s="8" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>基隆市安樂區代天府段951-1地號土地</t>
+          <t>高雄市苓雅區武聖段1124地號土地標租（出租面積共337.5平方公尺）。</t>
         </is>
       </c>
       <c r="H18" s="11" t="n">
@@ -6297,7 +6297,7 @@
       </c>
       <c r="K18" s="9" t="inlineStr">
         <is>
-          <t>財物變賣</t>
+          <t>財物出租</t>
         </is>
       </c>
     </row>
@@ -6307,7 +6307,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
@@ -6317,12 +6317,12 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府社會局</t>
+          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>W65411566006</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>高雄市政府社會局委託辦理「高雄市路得學舍」</t>
+          <t>基隆市安樂區代天府段951-1地號土地</t>
         </is>
       </c>
       <c r="H19" s="6" t="n">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>招標文件公開閱覽資料</t>
+          <t>財物變賣</t>
         </is>
       </c>
     </row>
@@ -6360,7 +6360,7 @@
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
@@ -6370,12 +6370,12 @@
       </c>
       <c r="D20" s="9" t="inlineStr">
         <is>
-          <t>行政院公共工程委員會</t>
+          <t>高雄市政府社會局</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>115S0001</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="F20" s="8" t="inlineStr">
@@ -6385,7 +6385,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>標售本會奉准報廢設備財物一批</t>
+          <t>高雄市政府社會局委託辦理「高雄市路得學舍」</t>
         </is>
       </c>
       <c r="H20" s="11" t="n">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
-          <t>財物變賣</t>
+          <t>招標文件公開閱覽資料</t>
         </is>
       </c>
     </row>
@@ -6413,7 +6413,7 @@
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C21" s="3" t="inlineStr">
@@ -6423,12 +6423,12 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>高雄市路竹區蔡文國民小學</t>
+          <t>行政院公共工程委員會</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t>tsw11510</t>
+          <t>115S0001</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>115學年度幼至五年級戶外教育採購</t>
+          <t>標售本會奉准報廢設備財物一批</t>
         </is>
       </c>
       <c r="H21" s="6" t="n">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料</t>
+          <t>財物變賣</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="D22" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
+          <t>高雄市路竹區蔡文國民小學</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>W65411566007</t>
+          <t>tsw11510</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
@@ -6491,7 +6491,7 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>基隆市安樂區新城段291-1地號土地</t>
+          <t>115學年度幼至五年級戶外教育採購</t>
         </is>
       </c>
       <c r="H22" s="11" t="n">
@@ -6509,7 +6509,7 @@
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>財物變賣</t>
+          <t>公開徵求廠商提供參考資料</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>工程招標機關</t>
+          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t>JTY00115061</t>
+          <t>W65411566007</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>高雄市三民區中華段二小段686-2、690、690-3、691等25筆地號土地</t>
+          <t>基隆市安樂區新城段291-1地號土地</t>
         </is>
       </c>
       <c r="H23" s="6" t="n">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>財物出租</t>
+          <t>財物變賣</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -6794,12 +6794,12 @@
       </c>
       <c r="D28" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>臺北市政府捷運工程局第二區工程處</t>
         </is>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
-          <t>CP15054</t>
+          <t>CF750</t>
         </is>
       </c>
       <c r="F28" s="8" t="inlineStr">
@@ -6809,7 +6809,7 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>臨床檢驗科委託代檢計1項</t>
+          <t>臺北都會區大眾捷運系統環狀線東環段CF750區段標工程</t>
         </is>
       </c>
       <c r="H28" s="11" t="n">
@@ -6890,7 +6890,7 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -6900,12 +6900,12 @@
       </c>
       <c r="D30" s="9" t="inlineStr">
         <is>
-          <t>臺北市政府捷運工程局第二區工程處</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
-          <t>CF750</t>
+          <t>CP15054</t>
         </is>
       </c>
       <c r="F30" s="8" t="inlineStr">
@@ -6915,7 +6915,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>臺北都會區大眾捷運系統環狀線東環段CF750區段標工程</t>
+          <t>臨床檢驗科委託代檢計1項</t>
         </is>
       </c>
       <c r="H30" s="11" t="n">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t>115FB004195848001200</t>
+          <t>115FB004195847001200</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
@@ -6968,7 +6968,7 @@
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>四支部高雄廠九曲堂營區二級廠整建工程</t>
+          <t>四支部高雄廠九曲堂營區甲車鋼棚暨保修辦公室整修工程</t>
         </is>
       </c>
       <c r="H31" s="6" t="n">
@@ -7006,12 +7006,12 @@
       </c>
       <c r="D32" s="9" t="inlineStr">
         <is>
-          <t>法務部矯正署高雄第二監獄</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>KSSP116002</t>
+          <t>115FB004195848001200</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>116年度經濟不利收容人基本生活物資</t>
+          <t>四支部高雄廠九曲堂營區二級廠整建工程</t>
         </is>
       </c>
       <c r="H32" s="11" t="n">
@@ -7049,7 +7049,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -7059,12 +7059,12 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>法務部矯正署高雄第二監獄</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t>CN115F02</t>
+          <t>KSSP116002</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
@@ -7074,7 +7074,7 @@
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>臺南市安南區城東段1029、1029-1、1030地號等3筆土地強制執行建物拆除工程採購案</t>
+          <t>116年度經濟不利收容人基本生活物資</t>
         </is>
       </c>
       <c r="H33" s="6" t="n">
@@ -7102,7 +7102,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -7112,12 +7112,12 @@
       </c>
       <c r="D34" s="9" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>115FB004195847001200</t>
+          <t>CN115F02</t>
         </is>
       </c>
       <c r="F34" s="8" t="inlineStr">
@@ -7127,7 +7127,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>四支部高雄廠九曲堂營區甲車鋼棚暨保修辦公室整修工程</t>
+          <t>臺南市安南區城東段1029、1029-1、1030地號等3筆土地強制執行建物拆除工程採購案</t>
         </is>
       </c>
       <c r="H34" s="11" t="n">
@@ -7208,7 +7208,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>中央/中油</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -7218,12 +7218,12 @@
       </c>
       <c r="D36" s="9" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司探採事業部鑽探工程處</t>
+          <t>台灣電力股份有限公司高雄區營業處</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>B4390001</t>
+          <t>20261030</t>
         </is>
       </c>
       <c r="F36" s="8" t="inlineStr">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="G36" s="10" t="inlineStr">
         <is>
-          <t>宜蘭地區水井鑽鑿與汲水服務</t>
+          <t>數位自動電話錄音機</t>
         </is>
       </c>
       <c r="H36" s="11" t="n">
@@ -7261,7 +7261,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>中央/中油</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司高雄區營業處</t>
+          <t>台灣中油股份有限公司探採事業部鑽探工程處</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>20261030</t>
+          <t>B4390001</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -7286,7 +7286,7 @@
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>數位自動電話錄音機</t>
+          <t>宜蘭地區水井鑽鑿與汲水服務</t>
         </is>
       </c>
       <c r="H37" s="6" t="n">
@@ -7367,7 +7367,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -7377,12 +7377,12 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>臺北大眾捷運股份有限公司</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>IL11508D02</t>
+          <t>B15A06926</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -7392,7 +7392,7 @@
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>115年資訊機房高架地板及消防預警等設備擴充案</t>
+          <t>371型電聯車車廂內飾板修復工作</t>
         </is>
       </c>
       <c r="H39" s="6" t="n">
@@ -7425,17 +7425,17 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>工程類</t>
         </is>
       </c>
       <c r="D40" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司花東供電區營運處</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>4951570011</t>
+          <t>IL11508D02</t>
         </is>
       </c>
       <c r="F40" s="8" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>69kV立霧~北埔線#16~#19鐵塔及基礎改建工程</t>
+          <t>115年資訊機房高架地板及消防預警等設備擴充案</t>
         </is>
       </c>
       <c r="H40" s="11" t="n">
@@ -7463,7 +7463,7 @@
       </c>
       <c r="K40" s="9" t="inlineStr">
         <is>
-          <t>公開招標</t>
+          <t>公開徵求廠商提供參考資料更正</t>
         </is>
       </c>
     </row>
@@ -7473,22 +7473,22 @@
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>工程類5129-其他用途建築工程</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>高雄市楠梓區油廠國民小學</t>
+          <t>台灣電力股份有限公司花東供電區營運處</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t>ORPS11511</t>
+          <t>4951570011</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>北三棟老舊廁所整修工程</t>
+          <t>69kV立霧~北埔線#16~#19鐵塔及基礎改建工程</t>
         </is>
       </c>
       <c r="H41" s="6" t="n">
@@ -7584,17 +7584,17 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5129-其他用途建築工程</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>高雄市小港區小港國民小學</t>
+          <t>高雄市楠梓區油廠國民小學</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t>1150502</t>
+          <t>ORPS11511</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
@@ -7604,7 +7604,7 @@
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>小港國小114年忠孝樓老舊廁所整修工程</t>
+          <t>北三棟老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H43" s="6" t="n">
@@ -7632,22 +7632,22 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D44" s="9" t="inlineStr">
         <is>
-          <t>臺東縣臺東市公所</t>
+          <t>高雄市小港區小港國民小學</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>E115092301</t>
+          <t>1150502</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
@@ -7657,7 +7657,7 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>115年度農地重劃區緊急農水路改善工程-臺東市第二梯次</t>
+          <t>小港國小114年忠孝樓老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H44" s="11" t="n">
@@ -7685,22 +7685,22 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>彰化縣立原斗國民中小學</t>
+          <t>臺東縣臺東市公所</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>115-10</t>
+          <t>E115092301</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -7710,7 +7710,7 @@
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>115年度偏遠地區學校及非山非市學校設施設備計畫-國中部教室整修工程</t>
+          <t>115年度農地重劃區緊急農水路改善工程-臺東市第二梯次</t>
         </is>
       </c>
       <c r="H45" s="6" t="n">
@@ -7738,22 +7738,22 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>工程類</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D46" s="9" t="inlineStr">
         <is>
-          <t>臺北大眾捷運股份有限公司</t>
+          <t>彰化縣立原斗國民中小學</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>B15A06926</t>
+          <t>115-10</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
@@ -7763,7 +7763,7 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>371型電聯車車廂內飾板修復工作</t>
+          <t>115年度偏遠地區學校及非山非市學校設施設備計畫-國中部教室整修工程</t>
         </is>
       </c>
       <c r="H46" s="11" t="n">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="K46" s="9" t="inlineStr">
         <is>
-          <t>公開徵求廠商提供參考資料更正</t>
+          <t>公開招標</t>
         </is>
       </c>
     </row>
@@ -7791,22 +7791,22 @@
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E47" s="3" t="inlineStr">
         <is>
-          <t>DC-115-0701-0014</t>
+          <t>KS115E025</t>
         </is>
       </c>
       <c r="F47" s="3" t="inlineStr">
@@ -7816,7 +7816,7 @@
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>115年鳳山所分區計量管網委外建置工程及漏水調查</t>
+          <t>援中港第一支線電動制排水門更新工程</t>
         </is>
       </c>
       <c r="H47" s="6" t="n">
@@ -7844,22 +7844,22 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
         </is>
       </c>
       <c r="D48" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>KS115E025</t>
+          <t>DC-115-0701-0014</t>
         </is>
       </c>
       <c r="F48" s="8" t="inlineStr">
@@ -7869,7 +7869,7 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>援中港第一支線電動制排水門更新工程</t>
+          <t>115年鳳山所分區計量管網委外建置工程及漏水調查</t>
         </is>
       </c>
       <c r="H48" s="11" t="n">
@@ -7897,22 +7897,22 @@
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第六區管理處</t>
+          <t>新北市萬里區公所</t>
         </is>
       </c>
       <c r="E49" s="3" t="inlineStr">
         <is>
-          <t>RC-115-0601-0048</t>
+          <t>115-199-008</t>
         </is>
       </c>
       <c r="F49" s="3" t="inlineStr">
@@ -7922,7 +7922,7 @@
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>安南區府安路四段等汰換管線工程</t>
+          <t>115年萬里區公園、步道、廣場修繕工程</t>
         </is>
       </c>
       <c r="H49" s="6" t="n">
@@ -7950,22 +7950,22 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D50" s="9" t="inlineStr">
         <is>
-          <t>臺中市太平區公所</t>
+          <t>台灣自來水股份有限公司第六區管理處</t>
         </is>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>115-C17</t>
+          <t>RC-115-0601-0048</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
@@ -7975,7 +7975,7 @@
       </c>
       <c r="G50" s="10" t="inlineStr">
         <is>
-          <t>115年太平區山田路大湖桶農路支線下邊坡復建工程</t>
+          <t>安南區府安路四段等汰換管線工程</t>
         </is>
       </c>
       <c r="H50" s="11" t="n">
@@ -8003,22 +8003,22 @@
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>中央/陸軍</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮州國民小學</t>
+          <t>國防部陸軍司令部</t>
         </is>
       </c>
       <c r="E51" s="3" t="inlineStr">
         <is>
-          <t>cjps11510toilet</t>
+          <t>116FF00302317100110</t>
         </is>
       </c>
       <c r="F51" s="3" t="inlineStr">
@@ -8028,7 +8028,7 @@
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>屏東縣潮州鎮潮州國民小學 「114-116公立國民中小學老舊廁所整修工程」採購案</t>
+          <t>光華南營區核訓場改建工程</t>
         </is>
       </c>
       <c r="H51" s="6" t="n">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>中央/陸軍</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="D52" s="9" t="inlineStr">
         <is>
-          <t>國防部陸軍司令部</t>
+          <t>臺中市太平區公所</t>
         </is>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
-          <t>115FF00301506002710</t>
+          <t>115-C17</t>
         </is>
       </c>
       <c r="F52" s="8" t="inlineStr">
@@ -8081,7 +8081,7 @@
       </c>
       <c r="G52" s="10" t="inlineStr">
         <is>
-          <t>虎井營區靶場整修建案</t>
+          <t>115年太平區山田路大湖桶農路支線下邊坡復建工程</t>
         </is>
       </c>
       <c r="H52" s="11" t="n">
@@ -8124,7 +8124,7 @@
       </c>
       <c r="E53" s="3" t="inlineStr">
         <is>
-          <t>116FF00302317100110</t>
+          <t>115FF00301506002710</t>
         </is>
       </c>
       <c r="F53" s="3" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>光華南營區核訓場改建工程</t>
+          <t>虎井營區靶場整修建案</t>
         </is>
       </c>
       <c r="H53" s="6" t="n">
@@ -8162,22 +8162,22 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D54" s="9" t="inlineStr">
         <is>
-          <t>新北市萬里區公所</t>
+          <t>台灣自來水股份有限公司屏東區管理處</t>
         </is>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
-          <t>115-199-008</t>
+          <t>13S-15-1331-01</t>
         </is>
       </c>
       <c r="F54" s="8" t="inlineStr">
@@ -8187,7 +8187,7 @@
       </c>
       <c r="G54" s="10" t="inlineStr">
         <is>
-          <t>115年萬里區公園、步道、廣場修繕工程</t>
+          <t>115年度潮州所管線單價工程(一)(開口契約)</t>
         </is>
       </c>
       <c r="H54" s="11" t="n">
@@ -8215,22 +8215,22 @@
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司屏東區管理處</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E55" s="3" t="inlineStr">
         <is>
-          <t>13S-15-1331-01</t>
+          <t>HC1155103</t>
         </is>
       </c>
       <c r="F55" s="3" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>115年度潮州所管線單價工程(一)(開口契約)</t>
+          <t>客雅南圳幹線等6處維修工程</t>
         </is>
       </c>
       <c r="H55" s="6" t="n">
@@ -8268,22 +8268,22 @@
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D56" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E56" s="8" t="inlineStr">
         <is>
-          <t>HC1155103</t>
+          <t>1150917A-1</t>
         </is>
       </c>
       <c r="F56" s="8" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="G56" s="10" t="inlineStr">
         <is>
-          <t>客雅南圳幹線等6處維修工程</t>
+          <t>花蓮縣玉里鎮長良里花73線樺加沙颱風復建工程</t>
         </is>
       </c>
       <c r="H56" s="11" t="n">
@@ -8321,22 +8321,22 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>桃園市楊梅區水美國民小學</t>
         </is>
       </c>
       <c r="E57" s="3" t="inlineStr">
         <is>
-          <t>1150917A-1</t>
+          <t>c0402-1151001</t>
         </is>
       </c>
       <c r="F57" s="3" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮長良里花73線樺加沙颱風復建工程</t>
+          <t>新設多功能風雨教室廁所暨通道周邊設施工程</t>
         </is>
       </c>
       <c r="H57" s="6" t="n">
@@ -8427,22 +8427,22 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>桃園市楊梅區水美國民小學</t>
+          <t>屏東縣潮州鎮潮州國民小學</t>
         </is>
       </c>
       <c r="E59" s="3" t="inlineStr">
         <is>
-          <t>c0402-1151001</t>
+          <t>cjps11510toilet</t>
         </is>
       </c>
       <c r="F59" s="3" t="inlineStr">
@@ -8452,7 +8452,7 @@
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>新設多功能風雨教室廁所暨通道周邊設施工程</t>
+          <t>屏東縣潮州鎮潮州國民小學 「114-116公立國民中小學老舊廁所整修工程」採購案</t>
         </is>
       </c>
       <c r="H59" s="6" t="n">
@@ -8538,17 +8538,17 @@
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>財物類481-醫療,外科及矯形設備</t>
+          <t>勞務類8673-綜合工程服務</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>臺灣港務股份有限公司高雄港務分公司</t>
         </is>
       </c>
       <c r="E61" s="3" t="inlineStr">
         <is>
-          <t>LP16084</t>
+          <t>115-AE-055</t>
         </is>
       </c>
       <c r="F61" s="3" t="inlineStr">
@@ -8558,7 +8558,7 @@
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>「水雷射牙科治療儀1組」</t>
+          <t>116-117年安平港區道路、橋梁、碼頭及其他公共設施巡查工作</t>
         </is>
       </c>
       <c r="H61" s="6" t="n">
@@ -8654,7 +8654,7 @@
       </c>
       <c r="E63" s="3" t="inlineStr">
         <is>
-          <t>LP16018</t>
+          <t>LP16084</t>
         </is>
       </c>
       <c r="F63" s="3" t="inlineStr">
@@ -8664,7 +8664,7 @@
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>超音波掃描儀1組</t>
+          <t>「水雷射牙科治療儀1組」</t>
         </is>
       </c>
       <c r="H63" s="6" t="n">
@@ -8692,22 +8692,22 @@
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類481-醫療,外科及矯形設備</t>
         </is>
       </c>
       <c r="D64" s="9" t="inlineStr">
         <is>
-          <t>行政院主計總處</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E64" s="8" t="inlineStr">
         <is>
-          <t>115102234</t>
+          <t>LP16189</t>
         </is>
       </c>
       <c r="F64" s="8" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="G64" s="10" t="inlineStr">
         <is>
-          <t>行政院主計總處「115年主計人員訓練中心停車場及園區相關環境設施整修工程」採購案</t>
+          <t>全景掃描儀(全景數位病理切片掃描儀)1組</t>
         </is>
       </c>
       <c r="H64" s="11" t="n">
@@ -8745,22 +8745,22 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>新竹縣/市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類481-醫療,外科及矯形設備</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>新竹縣政府</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E65" s="3" t="inlineStr">
         <is>
-          <t>C115-0048</t>
+          <t>LP16018</t>
         </is>
       </c>
       <c r="F65" s="3" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>新竹縣竹北市興隆路左側（自強南路至隘口二路）人行安全改善計畫</t>
+          <t>超音波掃描儀1組</t>
         </is>
       </c>
       <c r="H65" s="6" t="n">
@@ -8798,22 +8798,22 @@
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>工程類5153-屋頂及防水工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D66" s="9" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>行政院主計總處</t>
         </is>
       </c>
       <c r="E66" s="8" t="inlineStr">
         <is>
-          <t>116EK62120704500120</t>
+          <t>115102234</t>
         </is>
       </c>
       <c r="F66" s="8" t="inlineStr">
@@ -8823,7 +8823,7 @@
       </c>
       <c r="G66" s="10" t="inlineStr">
         <is>
-          <t>地勤寢室南棟整修工程</t>
+          <t>行政院主計總處「115年主計人員訓練中心停車場及園區相關環境設施整修工程」採購案</t>
         </is>
       </c>
       <c r="H66" s="11" t="n">
@@ -8851,22 +8851,22 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>新竹縣/市</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>國防部政治作戰局</t>
+          <t>新竹縣政府</t>
         </is>
       </c>
       <c r="E67" s="3" t="inlineStr">
         <is>
-          <t>115-0350000389900110</t>
+          <t>C115-0048</t>
         </is>
       </c>
       <c r="F67" s="3" t="inlineStr">
@@ -8876,7 +8876,7 @@
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>安南營區污水下水道接管工程(安南區安中路三段105號污水下水道前端接管工程)</t>
+          <t>新竹縣竹北市興隆路左側（自強南路至隘口二路）人行安全改善計畫</t>
         </is>
       </c>
       <c r="H67" s="6" t="n">
@@ -8904,22 +8904,22 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5153-屋頂及防水工程</t>
         </is>
       </c>
       <c r="D68" s="9" t="inlineStr">
         <is>
-          <t>國立玉里高級中學</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E68" s="8" t="inlineStr">
         <is>
-          <t>115028</t>
+          <t>116EK62120704500120</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -8929,7 +8929,7 @@
       </c>
       <c r="G68" s="10" t="inlineStr">
         <is>
-          <t>職業群科大樓新建工程</t>
+          <t>地勤寢室南棟整修工程</t>
         </is>
       </c>
       <c r="H68" s="11" t="n">
@@ -8962,17 +8962,17 @@
       </c>
       <c r="C69" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署南投分署</t>
+          <t>國立玉里高級中學</t>
         </is>
       </c>
       <c r="E69" s="3" t="inlineStr">
         <is>
-          <t>115-LL-11-3-007</t>
+          <t>115028</t>
         </is>
       </c>
       <c r="F69" s="3" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>投縣LL006六肩道路改善及坑溝整治工程</t>
+          <t>職業群科大樓新建工程</t>
         </is>
       </c>
       <c r="H69" s="6" t="n">
@@ -9010,22 +9010,22 @@
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>財物類481-醫療,外科及矯形設備</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D70" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>國防部政治作戰局</t>
         </is>
       </c>
       <c r="E70" s="8" t="inlineStr">
         <is>
-          <t>LP16189</t>
+          <t>115-0350000389900110</t>
         </is>
       </c>
       <c r="F70" s="8" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>全景掃描儀(全景數位病理切片掃描儀)1組</t>
+          <t>安南營區污水下水道接管工程(安南區安中路三段105號污水下水道前端接管工程)</t>
         </is>
       </c>
       <c r="H70" s="11" t="n">
@@ -9068,17 +9068,17 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>國防部</t>
+          <t>農業部農村發展及水土保持署南投分署</t>
         </is>
       </c>
       <c r="E71" s="3" t="inlineStr">
         <is>
-          <t>115ER00317945401620</t>
+          <t>115-LL-11-3-007</t>
         </is>
       </c>
       <c r="F71" s="3" t="inlineStr">
@@ -9088,7 +9088,7 @@
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>教學大樓暨砲塔教室訓練設施改善工程</t>
+          <t>投縣LL006六肩道路改善及坑溝整治工程</t>
         </is>
       </c>
       <c r="H71" s="6" t="n">
@@ -9116,22 +9116,22 @@
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D72" s="9" t="inlineStr">
         <is>
-          <t>農業部農村發展及水土保持署臺北分署</t>
+          <t>國防部</t>
         </is>
       </c>
       <c r="E72" s="8" t="inlineStr">
         <is>
-          <t>115-SWC-1-4-012</t>
+          <t>115ER00317945401620</t>
         </is>
       </c>
       <c r="F72" s="8" t="inlineStr">
@@ -9141,7 +9141,7 @@
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>115年度新竹縣寶山鄉等地區(第2標)水土保持工程開口契約</t>
+          <t>教學大樓暨砲塔教室訓練設施改善工程</t>
         </is>
       </c>
       <c r="H72" s="11" t="n">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="E73" s="3" t="inlineStr">
         <is>
-          <t>115-SWC-1-4-013</t>
+          <t>115-SWC-1-4-012</t>
         </is>
       </c>
       <c r="F73" s="3" t="inlineStr">
@@ -9194,7 +9194,7 @@
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>115年度新竹市香山區等地區水土保持工程開口契約</t>
+          <t>115年度新竹縣寶山鄉等地區(第2標)水土保持工程開口契約</t>
         </is>
       </c>
       <c r="H73" s="6" t="n">
@@ -9275,22 +9275,22 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>工程類5127-教育用建築工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>嘉義縣阿里山鄉達邦國民小學</t>
+          <t>農業部農村發展及水土保持署臺北分署</t>
         </is>
       </c>
       <c r="E75" s="3" t="inlineStr">
         <is>
-          <t>dbps1151002</t>
+          <t>115-SWC-1-4-013</t>
         </is>
       </c>
       <c r="F75" s="3" t="inlineStr">
@@ -9300,7 +9300,7 @@
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>115年度改善偏遠地區國民中小學教師宿舍計畫－里佳分校宿舍修繕工程</t>
+          <t>115年度新竹市香山區等地區水土保持工程開口契約</t>
         </is>
       </c>
       <c r="H75" s="6" t="n">
@@ -9328,22 +9328,22 @@
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5127-教育用建築工程</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>嘉義縣阿里山鄉達邦國民小學</t>
         </is>
       </c>
       <c r="E76" s="8" t="inlineStr">
         <is>
-          <t>TT114H009</t>
+          <t>dbps1151002</t>
         </is>
       </c>
       <c r="F76" s="8" t="inlineStr">
@@ -9353,7 +9353,7 @@
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>小馬圳南溪幹線圳災害復建工程-楊柳颱風</t>
+          <t>115年度改善偏遠地區國民中小學教師宿舍計畫－里佳分校宿舍修繕工程</t>
         </is>
       </c>
       <c r="H76" s="11" t="n">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="E77" s="3" t="inlineStr">
         <is>
-          <t>TT115A15</t>
+          <t>TT114H009</t>
         </is>
       </c>
       <c r="F77" s="3" t="inlineStr">
@@ -9406,7 +9406,7 @@
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>卑南圳知本農場支線系統強化工程(第2期)</t>
+          <t>小馬圳南溪幹線圳災害復建工程-楊柳颱風</t>
         </is>
       </c>
       <c r="H77" s="6" t="n">
@@ -9434,22 +9434,22 @@
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D78" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E78" s="8" t="inlineStr">
         <is>
-          <t>SP15630</t>
+          <t>TT115A15</t>
         </is>
       </c>
       <c r="F78" s="8" t="inlineStr">
@@ -9459,7 +9459,7 @@
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>高雄榮總衛材集中採購(院內)計100項(開口契約)</t>
+          <t>卑南圳知本農場支線系統強化工程(第2期)</t>
         </is>
       </c>
       <c r="H78" s="11" t="n">
@@ -9487,22 +9487,22 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C79" s="3" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E79" s="3" t="inlineStr">
         <is>
-          <t>115-512</t>
+          <t>SP15630</t>
         </is>
       </c>
       <c r="F79" s="3" t="inlineStr">
@@ -9512,7 +9512,7 @@
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>116年度谷關段轄區省道交通安全設施、標線改善及災害搶修工程(開口契約)</t>
+          <t>高雄榮總衛材集中採購(院內)計100項(開口契約)</t>
         </is>
       </c>
       <c r="H79" s="6" t="n">
@@ -9540,22 +9540,22 @@
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D80" s="9" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E80" s="8" t="inlineStr">
         <is>
-          <t>VP15001</t>
+          <t>115-512</t>
         </is>
       </c>
       <c r="F80" s="8" t="inlineStr">
@@ -9565,7 +9565,7 @@
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>高雄榮總116年至117年衛材集中採購(輔標)計64項(開口契約)</t>
+          <t>116年度谷關段轄區省道交通安全設施、標線改善及災害搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H80" s="11" t="n">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="C81" s="3" t="inlineStr">
         <is>
-          <t>財物類481-醫療,外科及矯形設備</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D81" s="4" t="inlineStr">
@@ -9608,7 +9608,7 @@
       </c>
       <c r="E81" s="3" t="inlineStr">
         <is>
-          <t>LP16149</t>
+          <t>VP15001</t>
         </is>
       </c>
       <c r="F81" s="3" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>器械清洗消毒烘乾機1台</t>
+          <t>高雄榮總116年至117年衛材集中採購(輔標)計64項(開口契約)</t>
         </is>
       </c>
       <c r="H81" s="6" t="n">
@@ -9699,22 +9699,22 @@
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類481-醫療,外科及矯形設備</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E83" s="3" t="inlineStr">
         <is>
-          <t>1151027A-3</t>
+          <t>LP16149</t>
         </is>
       </c>
       <c r="F83" s="3" t="inlineStr">
@@ -9724,7 +9724,7 @@
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Danas-H-01-07-11-玉里哈拉灣產業道路邊坡復建工程等4件</t>
+          <t>器械清洗消毒烘乾機1台</t>
         </is>
       </c>
       <c r="H83" s="6" t="n">
@@ -9752,22 +9752,22 @@
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C84" s="8" t="inlineStr">
         <is>
-          <t>工程類5174-地板及牆面貼磚工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D84" s="9" t="inlineStr">
         <is>
-          <t>桃園市新屋區社子國民小學</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E84" s="8" t="inlineStr">
         <is>
-          <t>SZES11505</t>
+          <t>115-318</t>
         </is>
       </c>
       <c r="F84" s="8" t="inlineStr">
@@ -9777,7 +9777,7 @@
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>「115年度補助本市市立各級學校什項修繕工程及教學設備經費」—校園鋪面及圍牆欄杆建置工程</t>
+          <t>116年度彰化段轄區省道台17線路容清理工作、綠美化維護及災害搶修工程(開口契約)</t>
         </is>
       </c>
       <c r="H84" s="11" t="n">
@@ -9805,22 +9805,22 @@
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C85" s="3" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5174-地板及牆面貼磚工程</t>
         </is>
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>桃園市新屋區社子國民小學</t>
         </is>
       </c>
       <c r="E85" s="3" t="inlineStr">
         <is>
-          <t>115-318</t>
+          <t>SZES11505</t>
         </is>
       </c>
       <c r="F85" s="3" t="inlineStr">
@@ -9830,7 +9830,7 @@
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>116年度彰化段轄區省道台17線路容清理工作、綠美化維護及災害搶修工程(開口契約)</t>
+          <t>「115年度補助本市市立各級學校什項修繕工程及教學設備經費」—校園鋪面及圍牆欄杆建置工程</t>
         </is>
       </c>
       <c r="H85" s="6" t="n">
@@ -9863,17 +9863,17 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D86" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第九區管理處</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>WC-11509010012</t>
+          <t>1151027A-3</t>
         </is>
       </c>
       <c r="F86" s="8" t="inlineStr">
@@ -9883,7 +9883,7 @@
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>115年花蓮給水廠(花蓮所轄區A)管線設備單價採購工程及115年花蓮給水廠(花蓮服務所轄區)管線設備維修開口契約併案發包</t>
+          <t>Danas-H-01-07-11-玉里哈拉灣產業道路邊坡復建工程等4件</t>
         </is>
       </c>
       <c r="H86" s="11" t="n">
@@ -9911,22 +9911,22 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C87" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>台灣自來水股份有限公司第九區管理處</t>
         </is>
       </c>
       <c r="E87" s="3" t="inlineStr">
         <is>
-          <t>115AA038</t>
+          <t>WC-11509010012</t>
         </is>
       </c>
       <c r="F87" s="3" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>瑪雅里環里道路災後復建工程</t>
+          <t>115年花蓮給水廠(花蓮所轄區A)管線設備單價採購工程及115年花蓮給水廠(花蓮服務所轄區)管線設備維修開口契約併案發包</t>
         </is>
       </c>
       <c r="H87" s="6" t="n">
@@ -9969,17 +9969,17 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D88" s="9" t="inlineStr">
         <is>
-          <t>農業部農田水利署</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>KS115E006</t>
+          <t>115AA038</t>
         </is>
       </c>
       <c r="F88" s="8" t="inlineStr">
@@ -9989,7 +9989,7 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>橋頭農地重劃區頂鹽田支線小給六之三(0K+230)等改善工程</t>
+          <t>瑪雅里環里道路災後復建工程</t>
         </is>
       </c>
       <c r="H88" s="11" t="n">
@@ -10022,17 +10022,17 @@
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E89" s="3" t="inlineStr">
         <is>
-          <t>115AA035</t>
+          <t>KS115E006</t>
         </is>
       </c>
       <c r="F89" s="3" t="inlineStr">
@@ -10042,7 +10042,7 @@
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>115年度那瑪夏區部落安全環境建設及原民地區農路修繕工程</t>
+          <t>橋頭農地重劃區頂鹽田支線小給六之三(0K+230)等改善工程</t>
         </is>
       </c>
       <c r="H89" s="6" t="n">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>115AA036</t>
+          <t>115AA035</t>
         </is>
       </c>
       <c r="F90" s="8" t="inlineStr">
@@ -10095,7 +10095,7 @@
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>那瑪夏區達卡努瓦里丘平溪七七孔橋上游災害復建工程</t>
+          <t>115年度那瑪夏區部落安全環境建設及原民地區農路修繕工程</t>
         </is>
       </c>
       <c r="H90" s="11" t="n">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C91" s="3" t="inlineStr">
@@ -10133,12 +10133,12 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>臺南市政府都市發展局</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E91" s="3" t="inlineStr">
         <is>
-          <t>115B305</t>
+          <t>115AA036</t>
         </is>
       </c>
       <c r="F91" s="3" t="inlineStr">
@@ -10148,7 +10148,7 @@
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>新化水圳南圳綠堤縫合計畫工程</t>
+          <t>那瑪夏區達卡努瓦里丘平溪七七孔橋上游災害復建工程</t>
         </is>
       </c>
       <c r="H91" s="6" t="n">
@@ -10229,7 +10229,7 @@
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C93" s="3" t="inlineStr">
@@ -10239,12 +10239,12 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>臺南市政府都市發展局</t>
         </is>
       </c>
       <c r="E93" s="3" t="inlineStr">
         <is>
-          <t>115AA046</t>
+          <t>115B305</t>
         </is>
       </c>
       <c r="F93" s="3" t="inlineStr">
@@ -10254,7 +10254,7 @@
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>114年9月樺加沙颱風那瑪夏區托亞奇伊段野溪及瑪雅里托亞奇伊段護岸災後復建工程</t>
+          <t>新化水圳南圳綠堤縫合計畫工程</t>
         </is>
       </c>
       <c r="H93" s="6" t="n">
@@ -10335,22 +10335,22 @@
       </c>
       <c r="B95" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>國立彰化高級商業職業學校</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E95" s="3" t="inlineStr">
         <is>
-          <t>1150901</t>
+          <t>115AA046</t>
         </is>
       </c>
       <c r="F95" s="3" t="inlineStr">
@@ -10360,7 +10360,7 @@
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>115年活動中心多功能球場整修工程</t>
+          <t>114年9月樺加沙颱風那瑪夏區托亞奇伊段野溪及瑪雅里托亞奇伊段護岸災後復建工程</t>
         </is>
       </c>
       <c r="H95" s="6" t="n">
@@ -10388,22 +10388,22 @@
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C96" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D96" s="9" t="inlineStr">
         <is>
-          <t>高雄市那瑪夏區公所</t>
+          <t>國立彰化高級商業職業學校</t>
         </is>
       </c>
       <c r="E96" s="8" t="inlineStr">
         <is>
-          <t>115AA049</t>
+          <t>1150901</t>
         </is>
       </c>
       <c r="F96" s="8" t="inlineStr">
@@ -10413,7 +10413,7 @@
       </c>
       <c r="G96" s="10" t="inlineStr">
         <is>
-          <t>那瑪夏區達卡努瓦橋南端護岸災後復建工程</t>
+          <t>115年活動中心多功能球場整修工程</t>
         </is>
       </c>
       <c r="H96" s="11" t="n">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>勞務類8676-技術檢定與分析服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>高雄市那瑪夏區公所</t>
         </is>
       </c>
       <c r="E97" s="3" t="inlineStr">
         <is>
-          <t>CP15088</t>
+          <t>115AA049</t>
         </is>
       </c>
       <c r="F97" s="3" t="inlineStr">
@@ -10466,7 +10466,7 @@
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>病理檢驗部委外代檢勞務採購1項</t>
+          <t>那瑪夏區達卡努瓦橋南端護岸災後復建工程</t>
         </is>
       </c>
       <c r="H97" s="6" t="n">
@@ -10494,22 +10494,22 @@
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t>中央/空軍</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C98" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D98" s="9" t="inlineStr">
         <is>
-          <t>國防部空軍司令部</t>
+          <t>交通部公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E98" s="8" t="inlineStr">
         <is>
-          <t>115EE63017980500410</t>
+          <t>115-218</t>
         </is>
       </c>
       <c r="F98" s="8" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="G98" s="10" t="inlineStr">
         <is>
-          <t>營區雨遮設施改善工程</t>
+          <t>台61線130K~145K平面路口行穿線照明設施改善工程</t>
         </is>
       </c>
       <c r="H98" s="11" t="n">
@@ -10547,22 +10547,22 @@
       </c>
       <c r="B99" s="3" t="inlineStr">
         <is>
-          <t>澎湖縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>勞務類8676-技術檢定與分析服務</t>
         </is>
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>澎湖縣政府</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E99" s="3" t="inlineStr">
         <is>
-          <t>CW-11150044</t>
+          <t>CP15088</t>
         </is>
       </c>
       <c r="F99" s="3" t="inlineStr">
@@ -10572,7 +10572,7 @@
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>115年龍門漁港漁具倉庫南側突堤修建工程</t>
+          <t>病理檢驗部委外代檢勞務採購1項</t>
         </is>
       </c>
       <c r="H99" s="6" t="n">
@@ -10600,7 +10600,7 @@
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t>雲林縣</t>
+          <t>澎湖縣</t>
         </is>
       </c>
       <c r="C100" s="8" t="inlineStr">
@@ -10610,12 +10610,12 @@
       </c>
       <c r="D100" s="9" t="inlineStr">
         <is>
-          <t>雲林縣政府</t>
+          <t>澎湖縣政府</t>
         </is>
       </c>
       <c r="E100" s="8" t="inlineStr">
         <is>
-          <t>1151A30021</t>
+          <t>CW-11150044</t>
         </is>
       </c>
       <c r="F100" s="8" t="inlineStr">
@@ -10625,7 +10625,7 @@
       </c>
       <c r="G100" s="10" t="inlineStr">
         <is>
-          <t>雲林縣虎尾鎮B幹線(文化路)雨水下水道改道工程</t>
+          <t>115年龍門漁港漁具倉庫南側突堤修建工程</t>
         </is>
       </c>
       <c r="H100" s="11" t="n">
@@ -10653,22 +10653,22 @@
       </c>
       <c r="B101" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>中央/空軍</t>
         </is>
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>財物類352-醫藥產品</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>高雄榮民總醫院</t>
+          <t>國防部空軍司令部</t>
         </is>
       </c>
       <c r="E101" s="3" t="inlineStr">
         <is>
-          <t>SP15493</t>
+          <t>115EE63017980500410</t>
         </is>
       </c>
       <c r="F101" s="3" t="inlineStr">
@@ -10678,7 +10678,7 @@
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>過敏免疫風濕科用試劑計2項(開口契約)</t>
+          <t>營區雨遮設施改善工程</t>
         </is>
       </c>
       <c r="H101" s="6" t="n">
@@ -10706,22 +10706,22 @@
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C102" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類352-醫藥產品</t>
         </is>
       </c>
       <c r="D102" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣造橋鄉公所</t>
+          <t>高雄榮民總醫院</t>
         </is>
       </c>
       <c r="E102" s="8" t="inlineStr">
         <is>
-          <t>1151028001</t>
+          <t>SP15493</t>
         </is>
       </c>
       <c r="F102" s="8" t="inlineStr">
@@ -10731,7 +10731,7 @@
       </c>
       <c r="G102" s="10" t="inlineStr">
         <is>
-          <t>造橋鄉自然運動公園整體環境營造計畫</t>
+          <t>過敏免疫風濕科用試劑計2項(開口契約)</t>
         </is>
       </c>
       <c r="H102" s="11" t="n">
@@ -10764,17 +10764,17 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處中區施工處</t>
+          <t>苗栗縣造橋鄉公所</t>
         </is>
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>6551551043</t>
+          <t>1151028001</t>
         </is>
       </c>
       <c r="F103" s="3" t="inlineStr">
@@ -10784,7 +10784,7 @@
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>第六工務段中市檢驗站辦公室修繕工程</t>
+          <t>造橋鄉自然運動公園整體環境營造計畫</t>
         </is>
       </c>
       <c r="H103" s="6" t="n">
@@ -10817,17 +10817,17 @@
       </c>
       <c r="C104" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D104" s="9" t="inlineStr">
         <is>
-          <t>交通部公路局中區養護工程分局</t>
+          <t>台灣電力股份有限公司輸變電工程處中區施工處</t>
         </is>
       </c>
       <c r="E104" s="8" t="inlineStr">
         <is>
-          <t>115-218</t>
+          <t>6551551043</t>
         </is>
       </c>
       <c r="F104" s="8" t="inlineStr">
@@ -10837,7 +10837,7 @@
       </c>
       <c r="G104" s="10" t="inlineStr">
         <is>
-          <t>台61線130K~145K平面路口行穿線照明設施改善工程</t>
+          <t>第六工務段中市檢驗站辦公室修繕工程</t>
         </is>
       </c>
       <c r="H104" s="11" t="n">
@@ -11130,22 +11130,22 @@
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C110" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D110" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>台灣電力股份有限公司台中區營業處</t>
         </is>
       </c>
       <c r="E110" s="8" t="inlineStr">
         <is>
-          <t>M116107</t>
+          <t>1051570037</t>
         </is>
       </c>
       <c r="F110" s="8" t="inlineStr">
@@ -11155,7 +11155,7 @@
       </c>
       <c r="G110" s="10" t="inlineStr">
         <is>
-          <t>116年度高屏溪構造物維修改善工程(開口契約)</t>
+          <t>116年雅潭工區配電線路改善及設備更換工作</t>
         </is>
       </c>
       <c r="H110" s="11" t="n">
@@ -11188,17 +11188,17 @@
       </c>
       <c r="C111" s="3" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>交通部高速公路局中區養護工程分局</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E111" s="3" t="inlineStr">
         <is>
-          <t>115C010P073</t>
+          <t>M116107</t>
         </is>
       </c>
       <c r="F111" s="3" t="inlineStr">
@@ -11208,7 +11208,7 @@
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>116年大甲工務段轄區部分業務委外勞務承攬工作</t>
+          <t>116年度高屏溪構造物維修改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H111" s="6" t="n">
@@ -11289,22 +11289,22 @@
       </c>
       <c r="B113" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>高雄市政府水利局</t>
+          <t>交通部高速公路局中區養護工程分局</t>
         </is>
       </c>
       <c r="E113" s="3" t="inlineStr">
         <is>
-          <t>C1150918</t>
+          <t>115C010P073</t>
         </is>
       </c>
       <c r="F113" s="3" t="inlineStr">
@@ -11314,7 +11314,7 @@
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>左營區和光街(和光街109巷至和光街206巷)災修復建工程</t>
+          <t>116年大甲工務段轄區部分業務委外勞務承攬工作</t>
         </is>
       </c>
       <c r="H113" s="6" t="n">
@@ -11342,22 +11342,22 @@
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C114" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D114" s="9" t="inlineStr">
         <is>
-          <t>新北市八里區長坑國民小學</t>
+          <t>高雄市政府水利局</t>
         </is>
       </c>
       <c r="E114" s="8" t="inlineStr">
         <is>
-          <t>CKES11507</t>
+          <t>C1150918</t>
         </is>
       </c>
       <c r="F114" s="8" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="G114" s="10" t="inlineStr">
         <is>
-          <t>115年長坑國小職務宿舍修建工程</t>
+          <t>左營區和光街(和光街109巷至和光街206巷)災修復建工程</t>
         </is>
       </c>
       <c r="H114" s="11" t="n">
@@ -11448,22 +11448,22 @@
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C116" s="8" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D116" s="9" t="inlineStr">
         <is>
-          <t>屏東縣屏東市公所</t>
+          <t>新北市八里區長坑國民小學</t>
         </is>
       </c>
       <c r="E116" s="8" t="inlineStr">
         <is>
-          <t>115213</t>
+          <t>CKES11507</t>
         </is>
       </c>
       <c r="F116" s="8" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="G116" s="10" t="inlineStr">
         <is>
-          <t>永大、武立、興豐公園增設遮陽設施及兒童遊戲場環境設施改善工程</t>
+          <t>115年長坑國小職務宿舍修建工程</t>
         </is>
       </c>
       <c r="H116" s="11" t="n">
@@ -11501,22 +11501,22 @@
       </c>
       <c r="B117" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司台中區營業處</t>
+          <t>農業部農田水利署</t>
         </is>
       </c>
       <c r="E117" s="3" t="inlineStr">
         <is>
-          <t>1051570037</t>
+          <t>KS115E035</t>
         </is>
       </c>
       <c r="F117" s="3" t="inlineStr">
@@ -11526,7 +11526,7 @@
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>116年雅潭工區配電線路改善及設備更換工作</t>
+          <t>獅四輪小排四之十五(0K+035)等改善工程</t>
         </is>
       </c>
       <c r="H117" s="6" t="n">
@@ -11554,22 +11554,22 @@
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C118" s="8" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D118" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>屏東縣屏東市公所</t>
         </is>
       </c>
       <c r="E118" s="8" t="inlineStr">
         <is>
-          <t>M116110</t>
+          <t>115213</t>
         </is>
       </c>
       <c r="F118" s="8" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="G118" s="10" t="inlineStr">
         <is>
-          <t>116年度七河分署轄區構造物維修改善工程(開口契約)</t>
+          <t>永大、武立、興豐公園增設遮陽設施及兒童遊戲場環境設施改善工程</t>
         </is>
       </c>
       <c r="H118" s="11" t="n">
@@ -11612,17 +11612,17 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>南投縣中寮鄉公所</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E119" s="3" t="inlineStr">
         <is>
-          <t>115-0118</t>
+          <t>M116110</t>
         </is>
       </c>
       <c r="F119" s="3" t="inlineStr">
@@ -11632,7 +11632,7 @@
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>114中寮鄉崁頂村後寮段744-6地號蝕溝整治工程</t>
+          <t>116年度七河分署轄區構造物維修改善工程(開口契約)</t>
         </is>
       </c>
       <c r="H119" s="6" t="n">
@@ -11665,17 +11665,17 @@
       </c>
       <c r="C120" s="8" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D120" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣立苑裡高級中學</t>
+          <t>南投縣中寮鄉公所</t>
         </is>
       </c>
       <c r="E120" s="8" t="inlineStr">
         <is>
-          <t>1150023</t>
+          <t>115-0118</t>
         </is>
       </c>
       <c r="F120" s="8" t="inlineStr">
@@ -11685,7 +11685,7 @@
       </c>
       <c r="G120" s="10" t="inlineStr">
         <is>
-          <t>115年度運動場地整建工程採購案</t>
+          <t>114中寮鄉崁頂村後寮段744-6地號蝕溝整治工程</t>
         </is>
       </c>
       <c r="H120" s="11" t="n">
@@ -11713,22 +11713,22 @@
       </c>
       <c r="B121" s="3" t="inlineStr">
         <is>
-          <t>新北市</t>
+          <t>臺北市</t>
         </is>
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>工程類5159-其他專業工程</t>
+          <t>財物類381-傢具</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>新北市新莊區公所</t>
+          <t>臺北市政府工務局新建工程處</t>
         </is>
       </c>
       <c r="E121" s="3" t="inlineStr">
         <is>
-          <t>1151027J2</t>
+          <t>NCOdecor11501</t>
         </is>
       </c>
       <c r="F121" s="3" t="inlineStr">
@@ -11738,7 +11738,7 @@
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>116年度新莊區抽水機代操作、維護保養工作（開口合約）</t>
+          <t>115年度新建工程處辦公傢俱及附屬設備(含電源線路配置)財物採購案</t>
         </is>
       </c>
       <c r="H121" s="6" t="n">
@@ -11766,22 +11766,22 @@
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C122" s="8" t="inlineStr">
         <is>
-          <t>財物類4393-其他通用機具</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D122" s="9" t="inlineStr">
         <is>
-          <t>高雄市左營區文府國民小學</t>
+          <t>苗栗縣立苑裡高級中學</t>
         </is>
       </c>
       <c r="E122" s="8" t="inlineStr">
         <is>
-          <t>115M1008</t>
+          <t>1150023</t>
         </is>
       </c>
       <c r="F122" s="8" t="inlineStr">
@@ -11791,7 +11791,7 @@
       </c>
       <c r="G122" s="10" t="inlineStr">
         <is>
-          <t>115學年度消防系統設備改善案</t>
+          <t>115年度運動場地整建工程採購案</t>
         </is>
       </c>
       <c r="H122" s="11" t="n">
@@ -11872,22 +11872,22 @@
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>新北市</t>
         </is>
       </c>
       <c r="C124" s="8" t="inlineStr">
         <is>
-          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
+          <t>工程類5159-其他專業工程</t>
         </is>
       </c>
       <c r="D124" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>新北市新莊區公所</t>
         </is>
       </c>
       <c r="E124" s="8" t="inlineStr">
         <is>
-          <t>M116044</t>
+          <t>1151027J2</t>
         </is>
       </c>
       <c r="F124" s="8" t="inlineStr">
@@ -11897,7 +11897,7 @@
       </c>
       <c r="G124" s="10" t="inlineStr">
         <is>
-          <t>116年度高屏溪堤防維護管理工作(開口契約)</t>
+          <t>116年度新莊區抽水機代操作、維護保養工作（開口合約）</t>
         </is>
       </c>
       <c r="H124" s="11" t="n">
@@ -11930,17 +11930,17 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
         </is>
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣南庄鄉公所</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E125" s="3" t="inlineStr">
         <is>
-          <t>115-034</t>
+          <t>M116044</t>
         </is>
       </c>
       <c r="F125" s="3" t="inlineStr">
@@ -11950,7 +11950,7 @@
       </c>
       <c r="G125" s="5" t="inlineStr">
         <is>
-          <t>115年4月豪雨南庄鄉南富村18鄰農路災後復建工程</t>
+          <t>116年度高屏溪堤防維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H125" s="6" t="n">
@@ -11978,22 +11978,22 @@
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C126" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類4393-其他通用機具</t>
         </is>
       </c>
       <c r="D126" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣南庄鄉公所</t>
+          <t>高雄市左營區文府國民小學</t>
         </is>
       </c>
       <c r="E126" s="8" t="inlineStr">
         <is>
-          <t>115-038</t>
+          <t>115M1008</t>
         </is>
       </c>
       <c r="F126" s="8" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="G126" s="10" t="inlineStr">
         <is>
-          <t>115年4月豪雨南庄鄉獅山村10鄰及17鄰農路災後復建工程</t>
+          <t>115學年度消防系統設備改善案</t>
         </is>
       </c>
       <c r="H126" s="11" t="n">
@@ -12031,22 +12031,22 @@
       </c>
       <c r="B127" s="3" t="inlineStr">
         <is>
-          <t>臺北市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>財物類381-傢具</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>臺北市政府工務局新建工程處</t>
+          <t>苗栗縣南庄鄉公所</t>
         </is>
       </c>
       <c r="E127" s="3" t="inlineStr">
         <is>
-          <t>NCOdecor11501</t>
+          <t>115-034</t>
         </is>
       </c>
       <c r="F127" s="3" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="G127" s="5" t="inlineStr">
         <is>
-          <t>115年度新建工程處辦公傢俱及附屬設備(含電源線路配置)財物採購案</t>
+          <t>115年4月豪雨南庄鄉南富村18鄰農路災後復建工程</t>
         </is>
       </c>
       <c r="H127" s="6" t="n">
@@ -12089,17 +12089,17 @@
       </c>
       <c r="C128" s="8" t="inlineStr">
         <is>
-          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D128" s="9" t="inlineStr">
         <is>
-          <t>經濟部水利署第七河川分署</t>
+          <t>苗栗縣南庄鄉公所</t>
         </is>
       </c>
       <c r="E128" s="8" t="inlineStr">
         <is>
-          <t>M116052</t>
+          <t>115-038</t>
         </is>
       </c>
       <c r="F128" s="8" t="inlineStr">
@@ -12109,7 +12109,7 @@
       </c>
       <c r="G128" s="10" t="inlineStr">
         <is>
-          <t>116年度隘寮溪堤防維護管理工作(開口契約)</t>
+          <t>115年4月豪雨南庄鄉獅山村10鄰及17鄰農路災後復建工程</t>
         </is>
       </c>
       <c r="H128" s="11" t="n">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="B130" s="8" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C130" s="8" t="inlineStr">
@@ -12205,7 +12205,7 @@
       </c>
       <c r="E130" s="8" t="inlineStr">
         <is>
-          <t>M116045</t>
+          <t>M116052</t>
         </is>
       </c>
       <c r="F130" s="8" t="inlineStr">
@@ -12215,7 +12215,7 @@
       </c>
       <c r="G130" s="10" t="inlineStr">
         <is>
-          <t>116年度東港溪水系及海堤堤防維護管理工作(開口契約)</t>
+          <t>116年度隘寮溪堤防維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H130" s="11" t="n">
@@ -12243,22 +12243,22 @@
       </c>
       <c r="B131" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
+          <t>勞務類94-污水及垃圾處理、公共衛生及其他環保服務</t>
         </is>
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司綜合研究所</t>
+          <t>經濟部水利署第七河川分署</t>
         </is>
       </c>
       <c r="E131" s="3" t="inlineStr">
         <is>
-          <t>5461500173</t>
+          <t>M116045</t>
         </is>
       </c>
       <c r="F131" s="3" t="inlineStr">
@@ -12268,7 +12268,7 @@
       </c>
       <c r="G131" s="5" t="inlineStr">
         <is>
-          <t>跨領域單一軟體之工程模擬全物理場高階多核心平行求解授權1套</t>
+          <t>116年度東港溪水系及海堤堤防維護管理工作(開口契約)</t>
         </is>
       </c>
       <c r="H131" s="6" t="n">
@@ -12301,17 +12301,17 @@
       </c>
       <c r="C132" s="8" t="inlineStr">
         <is>
-          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
+          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
         </is>
       </c>
       <c r="D132" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>台灣電力股份有限公司綜合研究所</t>
         </is>
       </c>
       <c r="E132" s="8" t="inlineStr">
         <is>
-          <t>RC-114-0701-0021-3</t>
+          <t>5461500173</t>
         </is>
       </c>
       <c r="F132" s="8" t="inlineStr">
@@ -12321,7 +12321,7 @@
       </c>
       <c r="G132" s="10" t="inlineStr">
         <is>
-          <t>高市梓官區梓官路汰換管線工程</t>
+          <t>跨領域單一軟體之工程模擬全物理場高階多核心平行求解授權1套</t>
         </is>
       </c>
       <c r="H132" s="11" t="n">
@@ -12354,17 +12354,17 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>中央研究院</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E133" s="3" t="inlineStr">
         <is>
-          <t>115-M39</t>
+          <t>RC-114-0701-0021-3</t>
         </is>
       </c>
       <c r="F133" s="3" t="inlineStr">
@@ -12374,7 +12374,7 @@
       </c>
       <c r="G133" s="5" t="inlineStr">
         <is>
-          <t>後棟學人招待所整修工程</t>
+          <t>高市梓官區梓官路汰換管線工程</t>
         </is>
       </c>
       <c r="H133" s="6" t="n">
@@ -12407,17 +12407,17 @@
       </c>
       <c r="C134" s="8" t="inlineStr">
         <is>
-          <t>工程類5164-電力工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D134" s="9" t="inlineStr">
         <is>
-          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
+          <t>中央研究院</t>
         </is>
       </c>
       <c r="E134" s="8" t="inlineStr">
         <is>
-          <t>6541551032</t>
+          <t>115-M39</t>
         </is>
       </c>
       <c r="F134" s="8" t="inlineStr">
@@ -12427,7 +12427,7 @@
       </c>
       <c r="G134" s="10" t="inlineStr">
         <is>
-          <t>345kV汐止~板橋線#68、#69鐵塔更換工程</t>
+          <t>後棟學人招待所整修工程</t>
         </is>
       </c>
       <c r="H134" s="11" t="n">
@@ -12455,22 +12455,22 @@
       </c>
       <c r="B135" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
+          <t>工程類5164-電力工程</t>
         </is>
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>高雄醫學大學</t>
+          <t>台灣電力股份有限公司輸變電工程處北區施工處</t>
         </is>
       </c>
       <c r="E135" s="3" t="inlineStr">
         <is>
-          <t>115H018</t>
+          <t>6541551032</t>
         </is>
       </c>
       <c r="F135" s="3" t="inlineStr">
@@ -12480,7 +12480,7 @@
       </c>
       <c r="G135" s="5" t="inlineStr">
         <is>
-          <t>IVC實驗動物飼養系統</t>
+          <t>345kV汐止~板橋線#68、#69鐵塔更換工程</t>
         </is>
       </c>
       <c r="H135" s="6" t="n">
@@ -12508,22 +12508,22 @@
       </c>
       <c r="B136" s="8" t="inlineStr">
         <is>
-          <t>中央/中油</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C136" s="8" t="inlineStr">
         <is>
-          <t>勞務類522-土木工程施工服務</t>
+          <t>財物類482-做為測量、檢查、航行及其他目的用之儀器和裝置，除光學儀器;工業程序控制設備;上述各項之零件及附件</t>
         </is>
       </c>
       <c r="D136" s="9" t="inlineStr">
         <is>
-          <t>台灣中油股份有限公司</t>
+          <t>高雄醫學大學</t>
         </is>
       </c>
       <c r="E136" s="8" t="inlineStr">
         <is>
-          <t>DAB1521001</t>
+          <t>115H018</t>
         </is>
       </c>
       <c r="F136" s="8" t="inlineStr">
@@ -12533,7 +12533,7 @@
       </c>
       <c r="G136" s="10" t="inlineStr">
         <is>
-          <t>115年南區零售中心轄屬加油站等單位土木零星修護工作(1年開口契約)</t>
+          <t>IVC實驗動物飼養系統</t>
         </is>
       </c>
       <c r="H136" s="11" t="n">
@@ -12561,22 +12561,22 @@
       </c>
       <c r="B137" s="3" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>中央/中油</t>
         </is>
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>勞務類522-土木工程施工服務</t>
         </is>
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>花蓮縣政府</t>
+          <t>台灣中油股份有限公司</t>
         </is>
       </c>
       <c r="E137" s="3" t="inlineStr">
         <is>
-          <t>AG115102902</t>
+          <t>DAB1521001</t>
         </is>
       </c>
       <c r="F137" s="3" t="inlineStr">
@@ -12586,7 +12586,7 @@
       </c>
       <c r="G137" s="5" t="inlineStr">
         <is>
-          <t>114農路橋梁維修工程</t>
+          <t>115年南區零售中心轄屬加油站等單位土木零星修護工作(1年開口契約)</t>
         </is>
       </c>
       <c r="H137" s="6" t="n">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C138" s="8" t="inlineStr">
@@ -12624,12 +12624,12 @@
       </c>
       <c r="D138" s="9" t="inlineStr">
         <is>
-          <t>國立成功大學附屬臺南工業高級中等學校</t>
+          <t>花蓮縣政府</t>
         </is>
       </c>
       <c r="E138" s="8" t="inlineStr">
         <is>
-          <t>115A-09</t>
+          <t>AG115102902</t>
         </is>
       </c>
       <c r="F138" s="8" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="G138" s="10" t="inlineStr">
         <is>
-          <t>國立成功大學附屬臺南工業高級中等學校通學步道改善工程</t>
+          <t>114農路橋梁維修工程</t>
         </is>
       </c>
       <c r="H138" s="11" t="n">
@@ -12667,22 +12667,22 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>彰化縣員林市公所</t>
+          <t>國立成功大學附屬臺南工業高級中等學校</t>
         </is>
       </c>
       <c r="E139" s="3" t="inlineStr">
         <is>
-          <t>01115024</t>
+          <t>115A-09</t>
         </is>
       </c>
       <c r="F139" s="3" t="inlineStr">
@@ -12692,7 +12692,7 @@
       </c>
       <c r="G139" s="5" t="inlineStr">
         <is>
-          <t>教育部國民及學前教育署補助本市幼兒園115年度充實及改善教學環境設施設備-員林市立幼兒園遊戲場鋪面改善工程</t>
+          <t>國立成功大學附屬臺南工業高級中等學校通學步道改善工程</t>
         </is>
       </c>
       <c r="H139" s="6" t="n">
@@ -12720,22 +12720,22 @@
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C140" s="8" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D140" s="9" t="inlineStr">
         <is>
-          <t>臺南市立安平國民中學</t>
+          <t>彰化縣員林市公所</t>
         </is>
       </c>
       <c r="E140" s="8" t="inlineStr">
         <is>
-          <t>115014</t>
+          <t>01115024</t>
         </is>
       </c>
       <c r="F140" s="8" t="inlineStr">
@@ -12745,7 +12745,7 @@
       </c>
       <c r="G140" s="10" t="inlineStr">
         <is>
-          <t>115年安平國中校園污水匯流工程</t>
+          <t>教育部國民及學前教育署補助本市幼兒園115年度充實及改善教學環境設施設備-員林市立幼兒園遊戲場鋪面改善工程</t>
         </is>
       </c>
       <c r="H140" s="11" t="n">
@@ -12773,22 +12773,22 @@
       </c>
       <c r="B141" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>臺中市西區中正國民小學</t>
+          <t>臺南市立安平國民中學</t>
         </is>
       </c>
       <c r="E141" s="3" t="inlineStr">
         <is>
-          <t>CCES115-1028</t>
+          <t>115014</t>
         </is>
       </c>
       <c r="F141" s="3" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="G141" s="5" t="inlineStr">
         <is>
-          <t>臺中市西區中正國民小學公益樓A棟廁所整修工程(第二次)</t>
+          <t>115年安平國中校園污水匯流工程</t>
         </is>
       </c>
       <c r="H141" s="6" t="n">
@@ -12826,22 +12826,22 @@
       </c>
       <c r="B142" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C142" s="8" t="inlineStr">
         <is>
-          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D142" s="9" t="inlineStr">
         <is>
-          <t>基隆市政府</t>
+          <t>臺中市西區中正國民小學</t>
         </is>
       </c>
       <c r="E142" s="8" t="inlineStr">
         <is>
-          <t>115A107</t>
+          <t>CCES115-1028</t>
         </is>
       </c>
       <c r="F142" s="8" t="inlineStr">
@@ -12851,7 +12851,7 @@
       </c>
       <c r="G142" s="10" t="inlineStr">
         <is>
-          <t>(116)基隆市人行道雨陽棚整建工程(單價標)</t>
+          <t>臺中市西區中正國民小學公益樓A棟廁所整修工程(第二次)</t>
         </is>
       </c>
       <c r="H142" s="11" t="n">
@@ -12879,22 +12879,22 @@
       </c>
       <c r="B143" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5131-快速道路(不含高架快速道路),街道,馬路,鐵路及機場跑道</t>
         </is>
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>臺中市南屯區南屯國民小學</t>
+          <t>基隆市政府</t>
         </is>
       </c>
       <c r="E143" s="3" t="inlineStr">
         <is>
-          <t>Ntes114-11-a</t>
+          <t>115A107</t>
         </is>
       </c>
       <c r="F143" s="3" t="inlineStr">
@@ -12904,7 +12904,7 @@
       </c>
       <c r="G143" s="5" t="inlineStr">
         <is>
-          <t>114年度南屯國小南棟前側老舊廁所整修工程採購案</t>
+          <t>(116)基隆市人行道雨陽棚整建工程(單價標)</t>
         </is>
       </c>
       <c r="H143" s="6" t="n">
@@ -12985,22 +12985,22 @@
       </c>
       <c r="B145" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>工程類5132-橋樑,高架快速道路,隧道及地鐵</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>桃園市中壢區公所</t>
+          <t>臺中市南屯區南屯國民小學</t>
         </is>
       </c>
       <c r="E145" s="3" t="inlineStr">
         <is>
-          <t>115-10-094</t>
+          <t>Ntes114-11-a</t>
         </is>
       </c>
       <c r="F145" s="3" t="inlineStr">
@@ -13010,7 +13010,7 @@
       </c>
       <c r="G145" s="5" t="inlineStr">
         <is>
-          <t>桃園市中壢區新街溪河岸南園二路57巷18弄新設人行跨橋工程</t>
+          <t>114年度南屯國小南棟前側老舊廁所整修工程採購案</t>
         </is>
       </c>
       <c r="H145" s="6" t="n">
@@ -13038,22 +13038,22 @@
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C146" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5132-橋樑,高架快速道路,隧道及地鐵</t>
         </is>
       </c>
       <c r="D146" s="9" t="inlineStr">
         <is>
-          <t>臺南市龍崎區公所</t>
+          <t>桃園市中壢區公所</t>
         </is>
       </c>
       <c r="E146" s="8" t="inlineStr">
         <is>
-          <t>115056</t>
+          <t>115-10-094</t>
         </is>
       </c>
       <c r="F146" s="8" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="G146" s="10" t="inlineStr">
         <is>
-          <t>115年0625豪雨龍崎區石嘈里171區道2k+600(石嘈高幹80)災後復建工程</t>
+          <t>桃園市中壢區新街溪河岸南園二路57巷18弄新設人行跨橋工程</t>
         </is>
       </c>
       <c r="H146" s="11" t="n">
@@ -13091,22 +13091,22 @@
       </c>
       <c r="B147" s="3" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第四區管理處</t>
+          <t>臺南市龍崎區公所</t>
         </is>
       </c>
       <c r="E147" s="3" t="inlineStr">
         <is>
-          <t>W4-115-0401-528</t>
+          <t>115056</t>
         </is>
       </c>
       <c r="F147" s="3" t="inlineStr">
@@ -13116,7 +13116,7 @@
       </c>
       <c r="G147" s="5" t="inlineStr">
         <is>
-          <t>大里服務所、烏日、霧峰等營運所管線設備修理工程(115年開口契約)</t>
+          <t>115年0625豪雨龍崎區石嘈里171區道2k+600(石嘈高幹80)災後復建工程</t>
         </is>
       </c>
       <c r="H147" s="6" t="n">
@@ -13149,17 +13149,17 @@
       </c>
       <c r="C148" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D148" s="9" t="inlineStr">
         <is>
-          <t>南投縣國姓鄉北山國民小學</t>
+          <t>台灣自來水股份有限公司第四區管理處</t>
         </is>
       </c>
       <c r="E148" s="8" t="inlineStr">
         <is>
-          <t>psps1150914</t>
+          <t>W4-115-0401-528</t>
         </is>
       </c>
       <c r="F148" s="8" t="inlineStr">
@@ -13169,7 +13169,7 @@
       </c>
       <c r="G148" s="10" t="inlineStr">
         <is>
-          <t>老舊廁所整修工程</t>
+          <t>大里服務所、烏日、霧峰等營運所管線設備修理工程(115年開口契約)</t>
         </is>
       </c>
       <c r="H148" s="11" t="n">
@@ -13250,22 +13250,22 @@
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>嘉義縣/市</t>
         </is>
       </c>
       <c r="C150" s="8" t="inlineStr">
         <is>
-          <t>勞務類751-郵政及專差服務</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D150" s="9" t="inlineStr">
         <is>
-          <t>中華郵政股份有限公司高雄郵局</t>
+          <t>嘉義縣梅山鄉梅圳國民小學</t>
         </is>
       </c>
       <c r="E150" s="8" t="inlineStr">
         <is>
-          <t>115-050</t>
+          <t>mj11502</t>
         </is>
       </c>
       <c r="F150" s="8" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="G150" s="10" t="inlineStr">
         <is>
-          <t>高雄郵局掛號、限時及國際郵件處理勞務承攬</t>
+          <t>梅圳國小114-116老舊廁所整修工程採購案</t>
         </is>
       </c>
       <c r="H150" s="11" t="n">
@@ -13303,22 +13303,22 @@
       </c>
       <c r="B151" s="3" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>臺中市豐原區豐原國民小學</t>
+          <t>南投縣國姓鄉北山國民小學</t>
         </is>
       </c>
       <c r="E151" s="3" t="inlineStr">
         <is>
-          <t>11513</t>
+          <t>psps1150914</t>
         </is>
       </c>
       <c r="F151" s="3" t="inlineStr">
@@ -13328,7 +13328,7 @@
       </c>
       <c r="G151" s="5" t="inlineStr">
         <is>
-          <t>豐原國小115年度公立幼兒園充實及改善教學環境設施設備工程」</t>
+          <t>老舊廁所整修工程</t>
         </is>
       </c>
       <c r="H151" s="6" t="n">
@@ -13356,22 +13356,22 @@
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C152" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>勞務類751-郵政及專差服務</t>
         </is>
       </c>
       <c r="D152" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮公所</t>
+          <t>中華郵政股份有限公司高雄郵局</t>
         </is>
       </c>
       <c r="E152" s="8" t="inlineStr">
         <is>
-          <t>1151029A-3</t>
+          <t>115-050</t>
         </is>
       </c>
       <c r="F152" s="8" t="inlineStr">
@@ -13381,7 +13381,7 @@
       </c>
       <c r="G152" s="10" t="inlineStr">
         <is>
-          <t>花蓮縣玉里鎮大禹里瑟冷部落災後復建工程</t>
+          <t>高雄郵局掛號、限時及國際郵件處理勞務承攬</t>
         </is>
       </c>
       <c r="H152" s="11" t="n">
@@ -13409,22 +13409,22 @@
       </c>
       <c r="B153" s="3" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5162-水管及排水設施鋪設工程</t>
         </is>
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>高雄市田寮區公所</t>
+          <t>台灣自來水股份有限公司第四區管理處</t>
         </is>
       </c>
       <c r="E153" s="3" t="inlineStr">
         <is>
-          <t>1151037</t>
+          <t>W4-115-0401-529</t>
         </is>
       </c>
       <c r="F153" s="3" t="inlineStr">
@@ -13434,7 +13434,7 @@
       </c>
       <c r="G153" s="5" t="inlineStr">
         <is>
-          <t>田寮區七星里高38往謝家祠堂路面災害復建工程等2案</t>
+          <t>台中給水廠北工區管線設備修理工程(115開口契約)</t>
         </is>
       </c>
       <c r="H153" s="6" t="n">
@@ -13462,22 +13462,22 @@
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t>高雄市</t>
+          <t>臺中市</t>
         </is>
       </c>
       <c r="C154" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D154" s="9" t="inlineStr">
         <is>
-          <t>國立岡山高級農工職業學校</t>
+          <t>臺中市豐原區豐原國民小學</t>
         </is>
       </c>
       <c r="E154" s="8" t="inlineStr">
         <is>
-          <t>115A-05</t>
+          <t>11513</t>
         </is>
       </c>
       <c r="F154" s="8" t="inlineStr">
@@ -13487,7 +13487,7 @@
       </c>
       <c r="G154" s="10" t="inlineStr">
         <is>
-          <t>實習處階梯教室修繕第二期工程</t>
+          <t>豐原國小115年度公立幼兒園充實及改善教學環境設施設備工程」</t>
         </is>
       </c>
       <c r="H154" s="11" t="n">
@@ -13515,22 +13515,22 @@
       </c>
       <c r="B155" s="3" t="inlineStr">
         <is>
-          <t>嘉義縣/市</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>嘉義縣梅山鄉梅圳國民小學</t>
+          <t>花蓮縣玉里鎮公所</t>
         </is>
       </c>
       <c r="E155" s="3" t="inlineStr">
         <is>
-          <t>mj11502</t>
+          <t>1151029A-3</t>
         </is>
       </c>
       <c r="F155" s="3" t="inlineStr">
@@ -13540,7 +13540,7 @@
       </c>
       <c r="G155" s="5" t="inlineStr">
         <is>
-          <t>梅圳國小114-116老舊廁所整修工程採購案</t>
+          <t>花蓮縣玉里鎮大禹里瑟冷部落災後復建工程</t>
         </is>
       </c>
       <c r="H155" s="6" t="n">
@@ -13568,22 +13568,22 @@
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>桃園市</t>
         </is>
       </c>
       <c r="C156" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D156" s="9" t="inlineStr">
         <is>
-          <t>彰化縣埔心鄉明聖國民小學</t>
+          <t>桃園市八德區公所</t>
         </is>
       </c>
       <c r="E156" s="8" t="inlineStr">
         <is>
-          <t>MSPS-11510</t>
+          <t>BB1151029</t>
         </is>
       </c>
       <c r="F156" s="8" t="inlineStr">
@@ -13593,7 +13593,7 @@
       </c>
       <c r="G156" s="10" t="inlineStr">
         <is>
-          <t>彰化縣明聖國民小學114年度公立國民中小學老舊廁所整修工程計畫</t>
+          <t>八德區霖園公園空間再造工程</t>
         </is>
       </c>
       <c r="H156" s="11" t="n">
@@ -13626,17 +13626,17 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第七區管理處</t>
+          <t>高雄市田寮區公所</t>
         </is>
       </c>
       <c r="E157" s="3" t="inlineStr">
         <is>
-          <t>RC-115-0701-0025</t>
+          <t>1151037</t>
         </is>
       </c>
       <c r="F157" s="3" t="inlineStr">
@@ -13646,7 +13646,7 @@
       </c>
       <c r="G157" s="5" t="inlineStr">
         <is>
-          <t>高市前鎮區49至57號碼頭汰換管線工程</t>
+          <t>田寮區七星里高38往謝家祠堂路面災害復建工程等2案</t>
         </is>
       </c>
       <c r="H157" s="6" t="n">
@@ -13674,22 +13674,22 @@
       </c>
       <c r="B158" s="8" t="inlineStr">
         <is>
-          <t>臺中市</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C158" s="8" t="inlineStr">
         <is>
-          <t>工程類5162-水管及排水設施鋪設工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D158" s="9" t="inlineStr">
         <is>
-          <t>台灣自來水股份有限公司第四區管理處</t>
+          <t>國立岡山高級農工職業學校</t>
         </is>
       </c>
       <c r="E158" s="8" t="inlineStr">
         <is>
-          <t>W4-115-0401-529</t>
+          <t>115A-05</t>
         </is>
       </c>
       <c r="F158" s="8" t="inlineStr">
@@ -13699,7 +13699,7 @@
       </c>
       <c r="G158" s="10" t="inlineStr">
         <is>
-          <t>台中給水廠北工區管線設備修理工程(115開口契約)</t>
+          <t>實習處階梯教室修繕第二期工程</t>
         </is>
       </c>
       <c r="H158" s="11" t="n">
@@ -13727,22 +13727,22 @@
       </c>
       <c r="B159" s="3" t="inlineStr">
         <is>
-          <t>屏東縣</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5179-其他裝修工程</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>屏東縣政府</t>
+          <t>彰化縣埔心鄉明聖國民小學</t>
         </is>
       </c>
       <c r="E159" s="3" t="inlineStr">
         <is>
-          <t>004-C1151008-1</t>
+          <t>MSPS-11510</t>
         </is>
       </c>
       <c r="F159" s="3" t="inlineStr">
@@ -13752,7 +13752,7 @@
       </c>
       <c r="G159" s="5" t="inlineStr">
         <is>
-          <t>115年屏東縣東港溪0826天然災害清疏工程</t>
+          <t>彰化縣明聖國民小學114年度公立國民中小學老舊廁所整修工程計畫</t>
         </is>
       </c>
       <c r="H159" s="6" t="n">
@@ -13780,22 +13780,22 @@
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t>全國 / 其他</t>
+          <t>高雄市</t>
         </is>
       </c>
       <c r="C160" s="8" t="inlineStr">
         <is>
-          <t>財物類421-結構金屬產品及其零件</t>
+          <t>工程類5135-地區性管線及電纜;輔助性工程</t>
         </is>
       </c>
       <c r="D160" s="9" t="inlineStr">
         <is>
-          <t>國防部資通電軍指揮部</t>
+          <t>台灣自來水股份有限公司第七區管理處</t>
         </is>
       </c>
       <c r="E160" s="8" t="inlineStr">
         <is>
-          <t>HK15184P084</t>
+          <t>RC-115-0701-0025</t>
         </is>
       </c>
       <c r="F160" s="8" t="inlineStr">
@@ -13805,7 +13805,7 @@
       </c>
       <c r="G160" s="10" t="inlineStr">
         <is>
-          <t>庫儲料架櫃採購案</t>
+          <t>高市前鎮區49至57號碼頭汰換管線工程</t>
         </is>
       </c>
       <c r="H160" s="11" t="n">
@@ -13833,7 +13833,7 @@
       </c>
       <c r="B161" s="3" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>屏東縣</t>
         </is>
       </c>
       <c r="C161" s="3" t="inlineStr">
@@ -13843,12 +13843,12 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>桃園市八德區公所</t>
+          <t>屏東縣政府</t>
         </is>
       </c>
       <c r="E161" s="3" t="inlineStr">
         <is>
-          <t>BB1151029</t>
+          <t>004-C1151008-1</t>
         </is>
       </c>
       <c r="F161" s="3" t="inlineStr">
@@ -13858,7 +13858,7 @@
       </c>
       <c r="G161" s="5" t="inlineStr">
         <is>
-          <t>八德區霖園公園空間再造工程</t>
+          <t>115年屏東縣東港溪0826天然災害清疏工程</t>
         </is>
       </c>
       <c r="H161" s="6" t="n">
@@ -13886,22 +13886,22 @@
       </c>
       <c r="B162" s="8" t="inlineStr">
         <is>
-          <t>臺南市</t>
+          <t>全國 / 其他</t>
         </is>
       </c>
       <c r="C162" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>財物類421-結構金屬產品及其零件</t>
         </is>
       </c>
       <c r="D162" s="9" t="inlineStr">
         <is>
-          <t>臺南市龍崎區公所</t>
+          <t>國防部資通電軍指揮部</t>
         </is>
       </c>
       <c r="E162" s="8" t="inlineStr">
         <is>
-          <t>115057</t>
+          <t>HK15184P084</t>
         </is>
       </c>
       <c r="F162" s="8" t="inlineStr">
@@ -13911,7 +13911,7 @@
       </c>
       <c r="G162" s="10" t="inlineStr">
         <is>
-          <t>115年0625豪雨龍崎區楠坑里163-1區道0k+120(樹子高枝3)災後復建工程</t>
+          <t>庫儲料架櫃採購案</t>
         </is>
       </c>
       <c r="H162" s="11" t="n">
@@ -13944,17 +13944,17 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>經濟部水利署第六河川分署</t>
+          <t>臺南市龍崎區公所</t>
         </is>
       </c>
       <c r="E163" s="3" t="inlineStr">
         <is>
-          <t>115-B-004-02-002-629</t>
+          <t>115057</t>
         </is>
       </c>
       <c r="F163" s="3" t="inlineStr">
@@ -13964,7 +13964,7 @@
       </c>
       <c r="G163" s="5" t="inlineStr">
         <is>
-          <t>115年度臺南市北門海埔地海堤構造物維修改善工程</t>
+          <t>115年0625豪雨龍崎區楠坑里163-1區道0k+120(樹子高枝3)災後復建工程</t>
         </is>
       </c>
       <c r="H163" s="6" t="n">
@@ -13992,22 +13992,22 @@
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t>花蓮縣</t>
+          <t>臺南市</t>
         </is>
       </c>
       <c r="C164" s="8" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5133-水道、海港、水壩及其他水利工程</t>
         </is>
       </c>
       <c r="D164" s="9" t="inlineStr">
         <is>
-          <t>花蓮縣光復鄉公所</t>
+          <t>經濟部水利署第六河川分署</t>
         </is>
       </c>
       <c r="E164" s="8" t="inlineStr">
         <is>
-          <t>1151008-B87</t>
+          <t>115-B-004-02-002-629</t>
         </is>
       </c>
       <c r="F164" s="8" t="inlineStr">
@@ -14017,7 +14017,7 @@
       </c>
       <c r="G164" s="10" t="inlineStr">
         <is>
-          <t>MTA-D-08-01-07-花蓮縣光復鄉災後道路提報計畫-大華村</t>
+          <t>115年度臺南市北門海埔地海堤構造物維修改善工程</t>
         </is>
       </c>
       <c r="H164" s="11" t="n">
@@ -14045,22 +14045,22 @@
       </c>
       <c r="B165" s="3" t="inlineStr">
         <is>
-          <t>彰化縣</t>
+          <t>花蓮縣</t>
         </is>
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>工程類5137-運動及娛樂工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>彰化縣彰化市南郭國民小學</t>
+          <t>花蓮縣光復鄉公所</t>
         </is>
       </c>
       <c r="E165" s="3" t="inlineStr">
         <is>
-          <t>11506A</t>
+          <t>1151008-B87</t>
         </is>
       </c>
       <c r="F165" s="3" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="G165" s="5" t="inlineStr">
         <is>
-          <t>115年度運動操場及周邊設施整建工程</t>
+          <t>MTA-D-08-01-07-花蓮縣光復鄉災後道路提報計畫-大華村</t>
         </is>
       </c>
       <c r="H165" s="6" t="n">
@@ -14098,22 +14098,22 @@
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t>桃園市</t>
+          <t>彰化縣</t>
         </is>
       </c>
       <c r="C166" s="8" t="inlineStr">
         <is>
-          <t>工程類5179-其他裝修工程</t>
+          <t>工程類5137-運動及娛樂工程</t>
         </is>
       </c>
       <c r="D166" s="9" t="inlineStr">
         <is>
-          <t>桃園市復興區光華國民小學</t>
+          <t>彰化縣彰化市南郭國民小學</t>
         </is>
       </c>
       <c r="E166" s="8" t="inlineStr">
         <is>
-          <t>KH-11502</t>
+          <t>11506A</t>
         </is>
       </c>
       <c r="F166" s="8" t="inlineStr">
@@ -14123,7 +14123,7 @@
       </c>
       <c r="G166" s="10" t="inlineStr">
         <is>
-          <t>115年度改善偏遠地區國民中小學教師宿舍</t>
+          <t>115年度運動操場及周邊設施整建工程</t>
         </is>
       </c>
       <c r="H166" s="11" t="n">
@@ -35091,17 +35091,17 @@
       </c>
       <c r="C562" s="8" t="inlineStr">
         <is>
-          <t>工程類5177-室內裝潢工程</t>
+          <t>工程類5139-其他土木工程</t>
         </is>
       </c>
       <c r="D562" s="9" t="inlineStr">
         <is>
-          <t>苗栗縣立苑裡高級中學</t>
+          <t>苗栗縣政府</t>
         </is>
       </c>
       <c r="E562" s="8" t="inlineStr">
         <is>
-          <t>1150024</t>
+          <t>115158c</t>
         </is>
       </c>
       <c r="F562" s="8" t="inlineStr">
@@ -35111,7 +35111,7 @@
       </c>
       <c r="G562" s="10" t="inlineStr">
         <is>
-          <t>115年度賈宓圖書館空間改善工程採購案</t>
+          <t>頭份市後庄里信義路690巷排水溝加蓋改善工程</t>
         </is>
       </c>
       <c r="H562" s="11" t="n">
@@ -35144,17 +35144,17 @@
       </c>
       <c r="C563" s="3" t="inlineStr">
         <is>
-          <t>工程類5139-其他土木工程</t>
+          <t>工程類5177-室內裝潢工程</t>
         </is>
       </c>
       <c r="D563" s="4" t="inlineStr">
         <is>
-          <t>苗栗縣政府</t>
+          <t>苗栗縣立苑裡高級中學</t>
         </is>
       </c>
       <c r="E563" s="3" t="inlineStr">
         <is>
-          <t>115158c</t>
+          <t>1150024</t>
         </is>
       </c>
       <c r="F563" s="3" t="inlineStr">
@@ -35164,7 +35164,7 @@
       </c>
       <c r="G563" s="5" t="inlineStr">
         <is>
-          <t>頭份市後庄里信義路690巷排水溝加蓋改善工程</t>
+          <t>115年度賈宓圖書館空間改善工程採購案</t>
         </is>
       </c>
       <c r="H563" s="6" t="n">
